--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3510</v>
+        <v>3566</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-2.13</v>
@@ -813,23 +813,23 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>26.17</v>
+        <v>28.1</v>
       </c>
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>11.63</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>-4.85</v>
+        <v>0.39</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF2" s="2" t="inlineStr"/>
       <c r="AG2" s="2" t="n">
@@ -843,40 +843,40 @@
         </is>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>3271.6</v>
+        <v>3282.8</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>3146.2</v>
+        <v>3151.8</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>3113.325</v>
+        <v>3116.125</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>3220.217</v>
+        <v>3222.083</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>3364.87</v>
+        <v>3365.99</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>3676.476</v>
+        <v>3677.036</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>2696.635</v>
+        <v>2696.915</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>2.5169</v>
+        <v>2.6139</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>-0.5225</v>
+        <v>-0.4762</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>-2.2712</v>
+        <v>-2.2547</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0.3456</v>
+        <v>0.3535</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>0.984</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="3">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16245</v>
+        <v>16700</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8.9</v>
+        <v>12</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>38.24</v>
@@ -931,23 +931,23 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="n">
-        <v>89.16</v>
+        <v>90.08</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>22.79</v>
+        <v>26.05</v>
       </c>
       <c r="AA3" s="2" t="n"/>
       <c r="AB3" s="2" t="n">
-        <v>5.89</v>
+        <v>10.18</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.23</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>32.8</v>
+        <v>33.5</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
@@ -959,40 +959,40 @@
         </is>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>15096.31</v>
+        <v>15187.31</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>14637.224</v>
+        <v>14682.724</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>14927.862</v>
+        <v>14950.612</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>15294.741</v>
+        <v>15309.908</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>15217.145</v>
+        <v>15226.245</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>16269.472</v>
+        <v>16274.022</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>13116.153</v>
+        <v>13118.428</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.7063</v>
+        <v>0.8702</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>-0.847</v>
+        <v>-0.769</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>-0.0013</v>
+        <v>0.0298</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0.0472</v>
+        <v>0.0618</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.9008</v>
       </c>
     </row>
     <row r="4">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11835</v>
+        <v>12110</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11.54</v>
+        <v>11.58</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43.7</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>106.01</v>
+        <v>109.71</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -1051,23 +1051,23 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="n">
-        <v>160.86</v>
+        <v>162.06</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>70.8</v>
+        <v>74.19</v>
       </c>
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="n">
-        <v>-2.22</v>
+        <v>-2.93</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>3.17</v>
+        <v>6.27</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AF4" s="2" t="inlineStr"/>
       <c r="AG4" s="2" t="inlineStr"/>
@@ -1079,40 +1079,40 @@
         </is>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>11404</v>
+        <v>11459</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>10831.593</v>
+        <v>10859.093</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>10492.086</v>
+        <v>10505.836</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>10300.773</v>
+        <v>10309.939</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>9794.697</v>
+        <v>9800.197</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>9988.618</v>
+        <v>9991.368</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>7090.009</v>
+        <v>7088.811</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>3.664</v>
+        <v>3.8053</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>1.5801</v>
+        <v>1.6503</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>1.3654</v>
+        <v>1.3953</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>1.1393</v>
+        <v>1.1539</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>1.6086</v>
+        <v>1.6206</v>
       </c>
     </row>
     <row r="5">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5988</v>
+        <v>5997</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-1.27</v>
@@ -1158,26 +1158,24 @@
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="n">
-        <v>25.93</v>
+        <v>25.97</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-14</v>
+        <v>-13.72</v>
       </c>
       <c r="AA5" s="2" t="n"/>
       <c r="AB5" s="2" t="n">
-        <v>-2.15</v>
+        <v>-0.57</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>-2.1</v>
+        <v>-1.19</v>
       </c>
       <c r="AD5" s="2" t="n">
         <v>-0.4</v>
@@ -1197,40 +1195,40 @@
         </is>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>5900.6</v>
+        <v>5902.4</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>5862.049</v>
+        <v>5862.949</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>5805.951</v>
+        <v>5806.401</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>5874.052</v>
+        <v>5874.352</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>6027.132</v>
+        <v>6027.312</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>6621.203</v>
+        <v>6621.293</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>6198.412</v>
+        <v>6198.457</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.8471</v>
+        <v>0.8552</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>-0.1545</v>
+        <v>-0.1505</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>-1.2444</v>
+        <v>-1.2429</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>-0.5435</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>0.2593</v>
+        <v>0.2597</v>
       </c>
     </row>
     <row r="6">
@@ -1245,7 +1243,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8907</v>
+        <v>8880</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -1256,7 +1254,7 @@
         <v>0.88</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4.9</v>
+        <v>-5.1</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-2.11</v>
@@ -1283,20 +1281,20 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="n">
-        <v>41.28</v>
+        <v>41.19</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-4.58</v>
+        <v>-4.81</v>
       </c>
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="2" t="n">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.36</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AE6" s="2" t="n">
         <v>80</v>
@@ -1313,40 +1311,40 @@
         </is>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>8605.6</v>
+        <v>8600.200000000001</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>8378</v>
+        <v>8375.299999999999</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>8280.299999999999</v>
+        <v>8278.950000000001</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>8418.6</v>
+        <v>8417.700000000001</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>8795.299999999999</v>
+        <v>8794.76</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>9722.124</v>
+        <v>9721.853999999999</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>8683.386</v>
+        <v>8683.251</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>1.5066</v>
+        <v>1.4893</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>-0.0731</v>
+        <v>-0.0815</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>-1.1092</v>
+        <v>-1.1123</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>-0.1825</v>
+        <v>-0.1839</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0.4128</v>
+        <v>0.4119</v>
       </c>
     </row>
     <row r="7">
@@ -1361,7 +1359,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5641</v>
+        <v>5622</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -1372,7 +1370,7 @@
         <v>1.23</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>94.59</v>
@@ -1411,20 +1409,20 @@
       </c>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="n">
-        <v>35.16</v>
+        <v>35.07</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-6.02</v>
+        <v>-6.17</v>
       </c>
       <c r="AA7" s="2" t="n"/>
       <c r="AB7" s="2" t="n">
-        <v>-6.53</v>
+        <v>-6.85</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>-2.54</v>
+        <v>-4.22</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AE7" s="2" t="n">
         <v>15</v>
@@ -1445,40 +1443,40 @@
         </is>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>5743.8</v>
+        <v>5740</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>5782.46</v>
+        <v>5780.56</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>5718.94</v>
+        <v>5717.99</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>5714.245</v>
+        <v>5713.612</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>5616.416</v>
+        <v>5616.036</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>5337.845</v>
+        <v>5337.655</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>5261.155</v>
+        <v>5261.06</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>0.6258</v>
+        <v>0.6085</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>0.0638</v>
+        <v>0.0552</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>0.4522</v>
+        <v>0.4487</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>0.2792</v>
+        <v>0.2773</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0.3516</v>
+        <v>0.3507</v>
       </c>
     </row>
     <row r="8">
@@ -1493,7 +1491,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2277.5</v>
+        <v>2247.5</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -1501,10 +1499,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>80.33</v>
@@ -1535,23 +1533,23 @@
       </c>
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="n">
-        <v>22.25</v>
+        <v>21.9</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-10.25</v>
+        <v>-11.29</v>
       </c>
       <c r="AA8" s="2" t="n"/>
       <c r="AB8" s="2" t="n">
-        <v>-5.71</v>
+        <v>-7.14</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-4.82</v>
+        <v>-7.73</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>82.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AF8" s="2" t="inlineStr"/>
       <c r="AG8" s="2" t="inlineStr"/>
@@ -1565,40 +1563,40 @@
         </is>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>2303.3</v>
+        <v>2297.3</v>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>2313.565</v>
+        <v>2310.565</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>2290.067</v>
+        <v>2288.567</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>2310.873</v>
+        <v>2309.873</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>2272.076</v>
+        <v>2271.476</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>2212.471</v>
+        <v>2212.171</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>2247.216</v>
+        <v>2247.066</v>
       </c>
       <c r="AR8" s="2" t="n">
-        <v>0.9072</v>
+        <v>0.8386</v>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>-0.2802</v>
+        <v>-0.3141</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>0.4573</v>
+        <v>0.4435</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>0.0853</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="AV8" s="2" t="n">
-        <v>0.2225</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="9">
@@ -1613,7 +1611,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2730.5</v>
+        <v>2708</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1621,10 +1619,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>98.16</v>
@@ -1653,23 +1651,23 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="n">
-        <v>-37.96</v>
+        <v>-38.17</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-24.72</v>
+        <v>-25.04</v>
       </c>
       <c r="AA9" s="2" t="n"/>
       <c r="AB9" s="2" t="n">
-        <v>-5.19</v>
+        <v>-6.05</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.79</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>85.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
@@ -1683,40 +1681,40 @@
         </is>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>2767.1</v>
+        <v>2762.6</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>2811.321</v>
+        <v>2809.071</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>2775.596</v>
+        <v>2774.471</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>2784.71</v>
+        <v>2783.96</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>2745.93</v>
+        <v>2745.48</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>2659.751</v>
+        <v>2659.526</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>2803.981</v>
+        <v>2803.869</v>
       </c>
       <c r="AR9" s="2" t="n">
-        <v>0.3859</v>
+        <v>0.344</v>
       </c>
       <c r="AS9" s="2" t="n">
-        <v>-0.3034</v>
+        <v>-0.3244</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>0.1863</v>
+        <v>0.1777</v>
       </c>
       <c r="AU9" s="2" t="n">
-        <v>0.1991</v>
+        <v>0.1947</v>
       </c>
       <c r="AV9" s="2" t="n">
-        <v>-0.3796</v>
+        <v>-0.3817</v>
       </c>
     </row>
     <row r="10">
@@ -1731,7 +1729,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11375</v>
+        <v>11245</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1742,7 +1740,7 @@
         <v>2.32</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>6.32</v>
@@ -1773,23 +1771,23 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="n">
-        <v>31.54</v>
+        <v>31.22</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>-5.35</v>
+        <v>-6.27</v>
       </c>
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n">
-        <v>-1.19</v>
+        <v>-1.97</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-10.2</v>
+        <v>-12.47</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>44.5</v>
+        <v>43.8</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="inlineStr"/>
@@ -1805,40 +1803,40 @@
         </is>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>11381</v>
+        <v>11355</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>11236.5</v>
+        <v>11223.5</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>11476</v>
+        <v>11469.5</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>11729.5</v>
+        <v>11725.167</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>11723</v>
+        <v>11720.4</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>11325.092</v>
+        <v>11323.792</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>10642.221</v>
+        <v>10641.571</v>
       </c>
       <c r="AR10" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.1801</v>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>-0.9585</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="AT10" s="2" t="n">
-        <v>0.1745</v>
+        <v>0.1629</v>
       </c>
       <c r="AU10" s="2" t="n">
-        <v>0.0614</v>
+        <v>0.0554</v>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>0.3154</v>
+        <v>0.3122</v>
       </c>
     </row>
     <row r="11">
@@ -1853,7 +1851,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3335</v>
+        <v>3324</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1861,10 +1859,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1.55</v>
@@ -1881,7 +1879,7 @@
         <v>-9</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
@@ -1893,23 +1891,23 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="n">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>-15.24</v>
+        <v>-15.23</v>
       </c>
       <c r="AA11" s="2" t="n"/>
       <c r="AB11" s="2" t="n">
-        <v>-2.86</v>
+        <v>-3.95</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0.33</v>
+        <v>-1.65</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="n">
@@ -1923,40 +1921,40 @@
         </is>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>3342.5</v>
+        <v>3340.3</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>3330.791</v>
+        <v>3329.691</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>3275.446</v>
+        <v>3274.896</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>3266.985</v>
+        <v>3266.618</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>3374.781</v>
+        <v>3374.561</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>3370.297</v>
+        <v>3370.187</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>3229.755</v>
+        <v>3229.7</v>
       </c>
       <c r="AR11" s="2" t="n">
-        <v>1.1929</v>
+        <v>1.1753</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>0.1089</v>
+        <v>0.1001</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>-0.3603</v>
+        <v>-0.3637</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>0.345</v>
+        <v>0.3433</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="12">
@@ -1971,7 +1969,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4292</v>
+        <v>4426</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -1979,10 +1977,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8.01</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.1</v>
+        <v>11.5</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>71.52</v>
@@ -2019,23 +2017,23 @@
       </c>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="n">
-        <v>120.08</v>
+        <v>121.17</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>35.99</v>
+        <v>39.92</v>
       </c>
       <c r="AA12" s="2" t="n"/>
       <c r="AB12" s="2" t="n">
-        <v>8.18</v>
+        <v>13.52</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>-4.53</v>
+        <v>5.34</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>37.3</v>
+        <v>37.9</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AF12" s="2" t="inlineStr"/>
       <c r="AG12" s="2" t="inlineStr"/>
@@ -2047,40 +2045,40 @@
         </is>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>3943.8</v>
+        <v>3970.6</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>3877.247</v>
+        <v>3890.647</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>3853.691</v>
+        <v>3860.391</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>3860.431</v>
+        <v>3864.897</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>3757.717</v>
+        <v>3760.397</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>4207.063</v>
+        <v>4208.403</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>3290.49</v>
+        <v>3291.16</v>
       </c>
       <c r="AR12" s="2" t="n">
-        <v>0.1052</v>
+        <v>0.2852</v>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>0.001</v>
+        <v>0.0914</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>0.6045</v>
+        <v>0.642</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>-0.2437</v>
+        <v>-0.2272</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>1.2008</v>
+        <v>1.2117</v>
       </c>
     </row>
     <row r="13">
@@ -2095,7 +2093,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2446.5</v>
+        <v>2485.5</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2103,10 +2101,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>16.11</v>
@@ -2123,7 +2121,9 @@
       <c r="Q13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
@@ -2133,23 +2133,23 @@
         <v>1</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>39.67</v>
+        <v>40.12</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA13" s="2" t="n"/>
       <c r="AB13" s="2" t="n">
-        <v>6.23</v>
+        <v>8.69</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>5.02</v>
+        <v>7.11</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AF13" s="2" t="inlineStr"/>
       <c r="AG13" s="2" t="n">
@@ -2163,40 +2163,40 @@
         </is>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>2297.6</v>
+        <v>2305.4</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>2198.753</v>
+        <v>2202.653</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>2142.539</v>
+        <v>2144.489</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>2156.499</v>
+        <v>2157.799</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>2198.103</v>
+        <v>2198.883</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>2526.154</v>
+        <v>2526.544</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>2310.015</v>
+        <v>2310.21</v>
       </c>
       <c r="AR13" s="2" t="n">
-        <v>2.9929</v>
+        <v>3.0905</v>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>0.6228</v>
+        <v>0.6707</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>-0.2497</v>
+        <v>-0.2313</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>-0.3334</v>
+        <v>-0.3254</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>0.3967</v>
+        <v>0.4012</v>
       </c>
     </row>
     <row r="14">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>60590</v>
+        <v>60180</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-2.8</v>
+        <v>-2.81</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.3</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6.86</v>
@@ -2249,20 +2249,20 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="n">
-        <v>29.33</v>
+        <v>29.16</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>-16.9</v>
+        <v>-17.31</v>
       </c>
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="n">
-        <v>6.98</v>
+        <v>6.26</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AE14" s="2" t="n">
         <v>76</v>
@@ -2279,40 +2279,40 @@
         </is>
       </c>
       <c r="AK14" s="2" t="n">
-        <v>57877.8</v>
+        <v>57795.8</v>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>55011.685</v>
+        <v>54970.685</v>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>54255.992</v>
+        <v>54235.492</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>56041.669</v>
+        <v>56028.002</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>58259.921</v>
+        <v>58251.721</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>65579.624</v>
+        <v>65575.524</v>
       </c>
       <c r="AQ14" s="2" t="n">
-        <v>64831.124</v>
+        <v>64829.074</v>
       </c>
       <c r="AR14" s="2" t="n">
-        <v>2.8131</v>
+        <v>2.7722</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>-0.1974</v>
+        <v>-0.217</v>
       </c>
       <c r="AT14" s="2" t="n">
-        <v>-1.0657</v>
+        <v>-1.0728</v>
       </c>
       <c r="AU14" s="2" t="n">
-        <v>-0.6555</v>
+        <v>-0.6587</v>
       </c>
       <c r="AV14" s="2" t="n">
-        <v>0.2933</v>
+        <v>0.2916</v>
       </c>
     </row>
     <row r="15">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4739</v>
+        <v>4758</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>-1.63</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-10</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-8.890000000000001</v>
@@ -2365,20 +2365,20 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="n">
-        <v>20.34</v>
+        <v>20.44</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>-16.36</v>
+        <v>-15.92</v>
       </c>
       <c r="AA15" s="2" t="n"/>
       <c r="AB15" s="2" t="n">
-        <v>0.44</v>
+        <v>3.21</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>-1.42</v>
+        <v>0.9</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="2" t="n">
         <v>82</v>
@@ -2395,40 +2395,40 @@
         </is>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>4666</v>
+        <v>4669.8</v>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>4515.3</v>
+        <v>4517.2</v>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>4439.4</v>
+        <v>4440.35</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>4578.1</v>
+        <v>4578.733</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>4978.28</v>
+        <v>4978.66</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>5388.67</v>
+        <v>5388.86</v>
       </c>
       <c r="AQ15" s="2" t="n">
-        <v>5064.624</v>
+        <v>5064.719</v>
       </c>
       <c r="AR15" s="2" t="n">
-        <v>2.2541</v>
+        <v>2.277</v>
       </c>
       <c r="AS15" s="2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2158</v>
       </c>
       <c r="AT15" s="2" t="n">
-        <v>-1.2046</v>
+        <v>-1.2007</v>
       </c>
       <c r="AU15" s="2" t="n">
-        <v>-0.386</v>
+        <v>-0.3842</v>
       </c>
       <c r="AV15" s="2" t="n">
-        <v>0.2034</v>
+        <v>0.2044</v>
       </c>
     </row>
     <row r="16">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>14500</v>
+        <v>14505</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>2.14</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>32.35</v>
@@ -2491,17 +2491,17 @@
         <v>1</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>35.74</v>
+        <v>35.75</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="AA16" s="2" t="n"/>
       <c r="AB16" s="2" t="n">
-        <v>4.45</v>
+        <v>4.09</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>2.68</v>
+        <v>3.96</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>50.7</v>
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="AK16" s="2" t="n">
-        <v>14052.6</v>
+        <v>14053.6</v>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>13550.463</v>
+        <v>13550.963</v>
       </c>
       <c r="AM16" s="2" t="n">
-        <v>13167.184</v>
+        <v>13167.434</v>
       </c>
       <c r="AN16" s="2" t="n">
-        <v>13363.045</v>
+        <v>13363.212</v>
       </c>
       <c r="AO16" s="2" t="n">
-        <v>13506.637</v>
+        <v>13506.737</v>
       </c>
       <c r="AP16" s="2" t="n">
-        <v>13871.011</v>
+        <v>13871.061</v>
       </c>
       <c r="AQ16" s="2" t="n">
-        <v>12709.406</v>
+        <v>12709.431</v>
       </c>
       <c r="AR16" s="2" t="n">
-        <v>2.8414</v>
+        <v>2.8434</v>
       </c>
       <c r="AS16" s="2" t="n">
-        <v>0.2532</v>
+        <v>0.2541</v>
       </c>
       <c r="AT16" s="2" t="n">
-        <v>0.5779</v>
+        <v>0.5783</v>
       </c>
       <c r="AU16" s="2" t="n">
-        <v>0.1143</v>
+        <v>0.1145</v>
       </c>
       <c r="AV16" s="2" t="n">
-        <v>0.3574</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="17">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2135</v>
+        <v>2050</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>91.51000000000001</v>
@@ -2619,23 +2619,23 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="n">
-        <v>12.54</v>
+        <v>11.64</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>-26.11</v>
+        <v>-28.74</v>
       </c>
       <c r="AA17" s="2" t="n"/>
       <c r="AB17" s="2" t="n">
-        <v>-27.18</v>
+        <v>-29.29</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>-13.78</v>
+        <v>-16.46</v>
       </c>
       <c r="AD17" s="2" t="n">
-        <v>32.2</v>
+        <v>31</v>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF17" s="2" t="inlineStr"/>
       <c r="AG17" s="2" t="inlineStr"/>
@@ -2651,40 +2651,40 @@
         </is>
       </c>
       <c r="AK17" s="2" t="n">
-        <v>2236</v>
+        <v>2219</v>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>2506.8</v>
+        <v>2498.3</v>
       </c>
       <c r="AM17" s="2" t="n">
-        <v>2573.95</v>
+        <v>2569.7</v>
       </c>
       <c r="AN17" s="2" t="n">
-        <v>2583.833</v>
+        <v>2581</v>
       </c>
       <c r="AO17" s="2" t="n">
-        <v>2612.96</v>
+        <v>2611.26</v>
       </c>
       <c r="AP17" s="2" t="n">
-        <v>2650.29</v>
+        <v>2649.44</v>
       </c>
       <c r="AQ17" s="2" t="n">
-        <v>2441.54</v>
+        <v>2441.115</v>
       </c>
       <c r="AR17" s="2" t="n">
-        <v>-4.0829</v>
+        <v>-4.2454</v>
       </c>
       <c r="AS17" s="2" t="n">
-        <v>-1.7483</v>
+        <v>-1.8313</v>
       </c>
       <c r="AT17" s="2" t="n">
-        <v>-0.6927</v>
+        <v>-0.7261</v>
       </c>
       <c r="AU17" s="2" t="n">
-        <v>-0.2319</v>
+        <v>-0.2485</v>
       </c>
       <c r="AV17" s="2" t="n">
-        <v>0.1254</v>
+        <v>0.1164</v>
       </c>
     </row>
     <row r="18">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3152</v>
+        <v>3158</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>3.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>20.49</v>
@@ -2741,20 +2741,20 @@
         </is>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>28.25</v>
+        <v>28.31</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" s="2" t="n"/>
       <c r="AB18" s="2" t="n">
-        <v>2.68</v>
+        <v>3.49</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AE18" s="2" t="n">
         <v>84</v>
@@ -2771,40 +2771,40 @@
         </is>
       </c>
       <c r="AK18" s="2" t="n">
-        <v>3037.4</v>
+        <v>3038.6</v>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>2954.466</v>
+        <v>2955.066</v>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>2892.638</v>
+        <v>2892.938</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>2939.072</v>
+        <v>2939.272</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>2977.252</v>
+        <v>2977.372</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>3245.261</v>
+        <v>3245.321</v>
       </c>
       <c r="AQ18" s="2" t="n">
-        <v>2728.502</v>
+        <v>2728.532</v>
       </c>
       <c r="AR18" s="2" t="n">
-        <v>2.1271</v>
+        <v>2.1381</v>
       </c>
       <c r="AS18" s="2" t="n">
-        <v>-0.0771</v>
+        <v>-0.0717</v>
       </c>
       <c r="AT18" s="2" t="n">
-        <v>-0.1541</v>
+        <v>-0.152</v>
       </c>
       <c r="AU18" s="2" t="n">
-        <v>0.1801</v>
+        <v>0.1811</v>
       </c>
       <c r="AV18" s="2" t="n">
-        <v>0.2825</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="19">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>39050</v>
+        <v>39300</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>52.85</v>
@@ -2865,20 +2865,20 @@
         <v>1</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>74.19</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>30.99</v>
+        <v>31.72</v>
       </c>
       <c r="AA19" s="2" t="n"/>
       <c r="AB19" s="2" t="n">
-        <v>13.89</v>
+        <v>13.07</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>11.01</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AE19" s="2" t="n">
         <v>89</v>
@@ -2893,40 +2893,40 @@
         </is>
       </c>
       <c r="AK19" s="2" t="n">
-        <v>35712</v>
+        <v>35762</v>
       </c>
       <c r="AL19" s="2" t="n">
-        <v>33861</v>
+        <v>33886</v>
       </c>
       <c r="AM19" s="2" t="n">
-        <v>33226</v>
+        <v>33238.5</v>
       </c>
       <c r="AN19" s="2" t="n">
-        <v>33746.667</v>
+        <v>33755</v>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>32948.3</v>
+        <v>32953.3</v>
       </c>
       <c r="AP19" s="2" t="n">
-        <v>30778.8</v>
+        <v>30781.3</v>
       </c>
       <c r="AQ19" s="2" t="n">
-        <v>27387.858</v>
+        <v>27389.108</v>
       </c>
       <c r="AR19" s="2" t="n">
-        <v>3.0637</v>
+        <v>3.1044</v>
       </c>
       <c r="AS19" s="2" t="n">
-        <v>0.4666</v>
+        <v>0.4864</v>
       </c>
       <c r="AT19" s="2" t="n">
-        <v>1.0074</v>
+        <v>1.0155</v>
       </c>
       <c r="AU19" s="2" t="n">
-        <v>0.5659</v>
+        <v>0.5702</v>
       </c>
       <c r="AV19" s="2" t="n">
-        <v>0.7419</v>
+        <v>0.7443</v>
       </c>
     </row>
     <row r="20">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>80630</v>
+        <v>79820</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -2952,10 +2952,10 @@
         <v>3.98</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>31.72</v>
+        <v>42.39</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
         <v>-9</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr"/>
@@ -2983,23 +2983,23 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="n">
-        <v>52.1</v>
+        <v>51.79</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA20" s="2" t="n"/>
       <c r="AB20" s="2" t="n">
-        <v>-0.09</v>
+        <v>-2.74</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>-6.18</v>
+        <v>-5.42</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="2" t="inlineStr"/>
@@ -3011,40 +3011,40 @@
         </is>
       </c>
       <c r="AK20" s="2" t="n">
-        <v>80058</v>
+        <v>79896</v>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>78546.5</v>
+        <v>78465.5</v>
       </c>
       <c r="AM20" s="2" t="n">
-        <v>77622.299</v>
+        <v>77581.799</v>
       </c>
       <c r="AN20" s="2" t="n">
-        <v>78847.656</v>
+        <v>78820.656</v>
       </c>
       <c r="AO20" s="2" t="n">
-        <v>79389.535</v>
+        <v>79373.33500000001</v>
       </c>
       <c r="AP20" s="2" t="n">
-        <v>78113.962</v>
+        <v>78105.86199999999</v>
       </c>
       <c r="AQ20" s="2" t="n">
-        <v>68835.439</v>
+        <v>68831.389</v>
       </c>
       <c r="AR20" s="2" t="n">
-        <v>1.4472</v>
+        <v>1.3921</v>
       </c>
       <c r="AS20" s="2" t="n">
-        <v>-0.3581</v>
+        <v>-0.385</v>
       </c>
       <c r="AT20" s="2" t="n">
-        <v>0.3695</v>
+        <v>0.3588</v>
       </c>
       <c r="AU20" s="2" t="n">
-        <v>0.1108</v>
+        <v>0.1054</v>
       </c>
       <c r="AV20" s="2" t="n">
-        <v>0.521</v>
+        <v>0.5179</v>
       </c>
     </row>
     <row r="21">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46570</v>
+        <v>46770</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2.66</v>
@@ -3105,20 +3105,20 @@
         <v>1</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>47.67</v>
+        <v>47.81</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>13.28</v>
+        <v>13.7</v>
       </c>
       <c r="AA21" s="2" t="n"/>
       <c r="AB21" s="2" t="n">
-        <v>11.26</v>
+        <v>10.29</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>26.47</v>
+        <v>28.28</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AE21" s="2" t="n">
         <v>89</v>
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="AK21" s="2" t="n">
-        <v>42882</v>
+        <v>42922</v>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>40590</v>
+        <v>40610</v>
       </c>
       <c r="AM21" s="2" t="n">
-        <v>37593</v>
+        <v>37603</v>
       </c>
       <c r="AN21" s="2" t="n">
-        <v>36582.333</v>
+        <v>36589</v>
       </c>
       <c r="AO21" s="2" t="n">
-        <v>38098.6</v>
+        <v>38102.6</v>
       </c>
       <c r="AP21" s="2" t="n">
-        <v>41250.609</v>
+        <v>41252.609</v>
       </c>
       <c r="AQ21" s="2" t="n">
-        <v>38004.869</v>
+        <v>38005.869</v>
       </c>
       <c r="AR21" s="2" t="n">
-        <v>5.3975</v>
+        <v>5.4258</v>
       </c>
       <c r="AS21" s="2" t="n">
-        <v>3.2182</v>
+        <v>3.2329</v>
       </c>
       <c r="AT21" s="2" t="n">
-        <v>-0.3635</v>
+        <v>-0.3581</v>
       </c>
       <c r="AU21" s="2" t="n">
-        <v>-0.0424</v>
+        <v>-0.0399</v>
       </c>
       <c r="AV21" s="2" t="n">
-        <v>0.4767</v>
+        <v>0.4781</v>
       </c>
     </row>
     <row r="22">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9809</v>
+        <v>9839</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>8.24</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-1.09</v>
@@ -3216,26 +3216,22 @@
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>22.44</v>
+        <v>22.65</v>
       </c>
       <c r="AA22" s="2" t="n"/>
       <c r="AB22" s="2" t="n">
-        <v>4.99</v>
+        <v>4.07</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>-1.45</v>
+        <v>-2.43</v>
       </c>
       <c r="AD22" s="2" t="n">
         <v>-7.3</v>
@@ -3255,40 +3251,40 @@
         </is>
       </c>
       <c r="AK22" s="2" t="n">
-        <v>9479.6</v>
+        <v>9485.6</v>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>9300.517</v>
+        <v>9303.517</v>
       </c>
       <c r="AM22" s="2" t="n">
-        <v>9202.915999999999</v>
+        <v>9204.415999999999</v>
       </c>
       <c r="AN22" s="2" t="n">
-        <v>9209.951999999999</v>
+        <v>9210.951999999999</v>
       </c>
       <c r="AO22" s="2" t="n">
-        <v>9738.620000000001</v>
+        <v>9739.219999999999</v>
       </c>
       <c r="AP22" s="2" t="n">
-        <v>12077.291</v>
+        <v>12077.591</v>
       </c>
       <c r="AQ22" s="2" t="n">
-        <v>8154.126</v>
+        <v>8154.276</v>
       </c>
       <c r="AR22" s="2" t="n">
-        <v>1.2177</v>
+        <v>1.2349</v>
       </c>
       <c r="AS22" s="2" t="n">
-        <v>0.5577</v>
+        <v>0.5662</v>
       </c>
       <c r="AT22" s="2" t="n">
-        <v>-1.2736</v>
+        <v>-1.2705</v>
       </c>
       <c r="AU22" s="2" t="n">
-        <v>0.6603</v>
+        <v>0.6616</v>
       </c>
       <c r="AV22" s="2" t="n">
-        <v>0.975</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="23">
@@ -3303,7 +3299,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8458</v>
+        <v>8403</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -3311,13 +3307,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>103.73</v>
+        <v>101.38</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -3331,7 +3327,7 @@
         <v>-9</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
@@ -3343,23 +3339,23 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="n">
-        <v>109.06</v>
+        <v>108.81</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>39.36</v>
+        <v>38.23</v>
       </c>
       <c r="AA23" s="2" t="n"/>
       <c r="AB23" s="2" t="n">
-        <v>3.21</v>
+        <v>0.82</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>10.68</v>
+        <v>7.94</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF23" s="2" t="inlineStr"/>
       <c r="AG23" s="2" t="n">
@@ -3373,40 +3369,40 @@
         </is>
       </c>
       <c r="AK23" s="2" t="n">
-        <v>8176</v>
+        <v>8165</v>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>7938.289</v>
+        <v>7932.789</v>
       </c>
       <c r="AM23" s="2" t="n">
-        <v>7564.653</v>
+        <v>7561.903</v>
       </c>
       <c r="AN23" s="2" t="n">
-        <v>7439.112</v>
+        <v>7437.279</v>
       </c>
       <c r="AO23" s="2" t="n">
-        <v>7499.334</v>
+        <v>7498.234</v>
       </c>
       <c r="AP23" s="2" t="n">
-        <v>8321.825999999999</v>
+        <v>8321.276</v>
       </c>
       <c r="AQ23" s="2" t="n">
-        <v>5996.193</v>
+        <v>5995.918</v>
       </c>
       <c r="AR23" s="2" t="n">
-        <v>3.102</v>
+        <v>3.0638</v>
       </c>
       <c r="AS23" s="2" t="n">
-        <v>1.6551</v>
+        <v>1.6356</v>
       </c>
       <c r="AT23" s="2" t="n">
-        <v>-0.3072</v>
+        <v>-0.3148</v>
       </c>
       <c r="AU23" s="2" t="n">
-        <v>0.9133</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="AV23" s="2" t="n">
-        <v>1.0906</v>
+        <v>1.0881</v>
       </c>
     </row>
     <row r="24">
@@ -3421,7 +3417,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -3465,17 +3461,17 @@
         <v>1</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>-8.98</v>
+        <v>-8.99</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>-15.17</v>
+        <v>-14.95</v>
       </c>
       <c r="AA24" s="2" t="n"/>
       <c r="AB24" s="2" t="n">
-        <v>-2.99</v>
+        <v>-2.65</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>0.19</v>
+        <v>-1.47</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>78.59999999999999</v>
@@ -3493,40 +3489,40 @@
         </is>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>3485.4</v>
+        <v>3485.2</v>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>3445.186</v>
+        <v>3445.086</v>
       </c>
       <c r="AM24" s="2" t="n">
-        <v>3355.971</v>
+        <v>3355.921</v>
       </c>
       <c r="AN24" s="2" t="n">
-        <v>3372.635</v>
+        <v>3372.601</v>
       </c>
       <c r="AO24" s="2" t="n">
-        <v>3386.481</v>
+        <v>3386.461</v>
       </c>
       <c r="AP24" s="2" t="n">
-        <v>3238.205</v>
+        <v>3238.195</v>
       </c>
       <c r="AQ24" s="2" t="n">
-        <v>3319.008</v>
+        <v>3319.003</v>
       </c>
       <c r="AR24" s="2" t="n">
-        <v>2.4275</v>
+        <v>2.426</v>
       </c>
       <c r="AS24" s="2" t="n">
-        <v>0.1639</v>
+        <v>0.1631</v>
       </c>
       <c r="AT24" s="2" t="n">
-        <v>0.3627</v>
+        <v>0.3624</v>
       </c>
       <c r="AU24" s="2" t="n">
-        <v>0.3749</v>
+        <v>0.3747</v>
       </c>
       <c r="AV24" s="2" t="n">
-        <v>-0.0898</v>
+        <v>-0.08989999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3541,7 +3537,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3843</v>
+        <v>3849</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -3552,7 +3548,7 @@
         <v>-2.92</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>10.02</v>
@@ -3567,7 +3563,7 @@
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr"/>
@@ -3579,23 +3575,23 @@
       </c>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="n">
-        <v>-2.04</v>
+        <v>-2</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>-23.84</v>
+        <v>-23.51</v>
       </c>
       <c r="AA25" s="2" t="n"/>
       <c r="AB25" s="2" t="n">
-        <v>-4.36</v>
+        <v>-2.46</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.08</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AF25" s="2" t="inlineStr"/>
       <c r="AG25" s="2" t="inlineStr"/>
@@ -3607,40 +3603,40 @@
         </is>
       </c>
       <c r="AK25" s="2" t="n">
-        <v>3837.8</v>
+        <v>3839</v>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>3844.836</v>
+        <v>3845.436</v>
       </c>
       <c r="AM25" s="2" t="n">
-        <v>3791.311</v>
+        <v>3791.611</v>
       </c>
       <c r="AN25" s="2" t="n">
-        <v>3844.745</v>
+        <v>3844.945</v>
       </c>
       <c r="AO25" s="2" t="n">
-        <v>3897.396</v>
+        <v>3897.516</v>
       </c>
       <c r="AP25" s="2" t="n">
-        <v>3860.306</v>
+        <v>3860.366</v>
       </c>
       <c r="AQ25" s="2" t="n">
-        <v>4195.74</v>
+        <v>4195.77</v>
       </c>
       <c r="AR25" s="2" t="n">
-        <v>0.7594</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="AS25" s="2" t="n">
-        <v>-0.2831</v>
+        <v>-0.279</v>
       </c>
       <c r="AT25" s="2" t="n">
-        <v>0.1125</v>
+        <v>0.1142</v>
       </c>
       <c r="AU25" s="2" t="n">
-        <v>-0.502</v>
+        <v>-0.5012</v>
       </c>
       <c r="AV25" s="2" t="n">
-        <v>-0.0204</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="26">
@@ -3655,7 +3651,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>15495</v>
+        <v>15505</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -3666,7 +3662,7 @@
         <v>3.52</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3.1</v>
@@ -3697,17 +3693,17 @@
         <v>1</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>93.06999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>26.51</v>
+        <v>26.52</v>
       </c>
       <c r="AA26" s="2" t="n"/>
       <c r="AB26" s="2" t="n">
-        <v>12.44</v>
+        <v>10.39</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>8.51</v>
+        <v>9.58</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>22.3</v>
@@ -3727,40 +3723,40 @@
         </is>
       </c>
       <c r="AK26" s="2" t="n">
-        <v>14811</v>
+        <v>14813</v>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>13861.134</v>
+        <v>13862.134</v>
       </c>
       <c r="AM26" s="2" t="n">
-        <v>13326.708</v>
+        <v>13327.208</v>
       </c>
       <c r="AN26" s="2" t="n">
-        <v>13306.219</v>
+        <v>13306.552</v>
       </c>
       <c r="AO26" s="2" t="n">
-        <v>13597.201</v>
+        <v>13597.401</v>
       </c>
       <c r="AP26" s="2" t="n">
-        <v>13993.394</v>
+        <v>13993.494</v>
       </c>
       <c r="AQ26" s="2" t="n">
-        <v>11647.467</v>
+        <v>11647.517</v>
       </c>
       <c r="AR26" s="2" t="n">
-        <v>4.8225</v>
+        <v>4.8266</v>
       </c>
       <c r="AS26" s="2" t="n">
-        <v>1.3625</v>
+        <v>1.3645</v>
       </c>
       <c r="AT26" s="2" t="n">
-        <v>-1.1725</v>
+        <v>-1.1717</v>
       </c>
       <c r="AU26" s="2" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7751</v>
       </c>
       <c r="AV26" s="2" t="n">
-        <v>0.9307</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3775,7 +3771,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>23970</v>
+        <v>23990</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -3813,20 +3809,20 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>-21.01</v>
+        <v>-20.76</v>
       </c>
       <c r="AA27" s="2" t="n"/>
       <c r="AB27" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="AC27" s="2" t="n">
-        <v>-3.3</v>
+        <v>-4.19</v>
       </c>
       <c r="AD27" s="2" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="AE27" s="2" t="n">
         <v>75</v>
@@ -3843,40 +3839,40 @@
         </is>
       </c>
       <c r="AK27" s="2" t="n">
-        <v>23751</v>
+        <v>23755</v>
       </c>
       <c r="AL27" s="2" t="n">
-        <v>23303</v>
+        <v>23305</v>
       </c>
       <c r="AM27" s="2" t="n">
-        <v>23365.75</v>
+        <v>23366.75</v>
       </c>
       <c r="AN27" s="2" t="n">
-        <v>23869.333</v>
+        <v>23870</v>
       </c>
       <c r="AO27" s="2" t="n">
-        <v>24460.4</v>
+        <v>24460.8</v>
       </c>
       <c r="AP27" s="2" t="n">
-        <v>25393</v>
+        <v>25393.2</v>
       </c>
       <c r="AQ27" s="2" t="n">
-        <v>26005.612</v>
+        <v>26005.712</v>
       </c>
       <c r="AR27" s="2" t="n">
-        <v>1.1309</v>
+        <v>1.1354</v>
       </c>
       <c r="AS27" s="2" t="n">
-        <v>-0.5036</v>
+        <v>-0.5014</v>
       </c>
       <c r="AT27" s="2" t="n">
-        <v>-0.3333</v>
+        <v>-0.3325</v>
       </c>
       <c r="AU27" s="2" t="n">
-        <v>-0.4559</v>
+        <v>-0.4555</v>
       </c>
       <c r="AV27" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="28">
@@ -3891,7 +3887,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2365</v>
+        <v>2337.5</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -3899,10 +3895,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46.45</v>
@@ -3915,8 +3911,10 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
-        <v>-13</v>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>+13/-13</t>
+        </is>
       </c>
       <c r="Q28" s="2" t="n">
         <v>0</v>
@@ -3930,28 +3928,28 @@
         </is>
       </c>
       <c r="V28" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>-13.1</v>
+        <v>-13.6</v>
       </c>
       <c r="AA28" s="2" t="n"/>
       <c r="AB28" s="2" t="n">
-        <v>-6.08</v>
+        <v>-5.78</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>-7.32</v>
+        <v>-5.66</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="AF28" s="2" t="inlineStr"/>
       <c r="AG28" s="2" t="inlineStr"/>
@@ -3963,40 +3961,40 @@
         </is>
       </c>
       <c r="AK28" s="2" t="n">
-        <v>2375.4</v>
+        <v>2369.9</v>
       </c>
       <c r="AL28" s="2" t="n">
-        <v>2364.14</v>
+        <v>2361.39</v>
       </c>
       <c r="AM28" s="2" t="n">
-        <v>2404.305</v>
+        <v>2402.93</v>
       </c>
       <c r="AN28" s="2" t="n">
-        <v>2432.382</v>
+        <v>2431.465</v>
       </c>
       <c r="AO28" s="2" t="n">
-        <v>2405.176</v>
+        <v>2404.626</v>
       </c>
       <c r="AP28" s="2" t="n">
-        <v>2385.653</v>
+        <v>2385.378</v>
       </c>
       <c r="AQ28" s="2" t="n">
-        <v>2364.826</v>
+        <v>2358.868</v>
       </c>
       <c r="AR28" s="2" t="n">
-        <v>-0.1442</v>
+        <v>-0.2045</v>
       </c>
       <c r="AS28" s="2" t="n">
-        <v>-0.5597</v>
+        <v>-0.5891</v>
       </c>
       <c r="AT28" s="2" t="n">
-        <v>-0.0348</v>
+        <v>-0.0467</v>
       </c>
       <c r="AU28" s="2" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0964</v>
       </c>
       <c r="AV28" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="29">
@@ -4011,7 +4009,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2199.5</v>
+        <v>2184</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -4019,10 +4017,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>101.93</v>
@@ -4044,32 +4042,28 @@
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
       <c r="Y29" s="2" t="n">
-        <v>25.22</v>
+        <v>25.02</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>-5.32</v>
+        <v>-5.8</v>
       </c>
       <c r="AA29" s="2" t="n"/>
       <c r="AB29" s="2" t="n">
-        <v>-3.98</v>
+        <v>-2.84</v>
       </c>
       <c r="AC29" s="2" t="n">
-        <v>2.67</v>
+        <v>0.23</v>
       </c>
       <c r="AD29" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AF29" s="2" t="inlineStr"/>
       <c r="AG29" s="2" t="inlineStr"/>
@@ -4087,40 +4081,40 @@
         </is>
       </c>
       <c r="AK29" s="2" t="n">
-        <v>2194.3</v>
+        <v>2191.2</v>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>2228.903</v>
+        <v>2227.353</v>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>2235.858</v>
+        <v>2235.083</v>
       </c>
       <c r="AN29" s="2" t="n">
-        <v>2180.766</v>
+        <v>2180.249</v>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>2106.325</v>
+        <v>2106.015</v>
       </c>
       <c r="AP29" s="2" t="n">
-        <v>1994.477</v>
+        <v>1994.322</v>
       </c>
       <c r="AQ29" s="2" t="n">
-        <v>1993.762</v>
+        <v>1993.685</v>
       </c>
       <c r="AR29" s="2" t="n">
-        <v>-1.0335</v>
+        <v>-1.0689</v>
       </c>
       <c r="AS29" s="2" t="n">
-        <v>0.541</v>
+        <v>0.5228</v>
       </c>
       <c r="AT29" s="2" t="n">
-        <v>0.7647</v>
+        <v>0.7569</v>
       </c>
       <c r="AU29" s="2" t="n">
-        <v>0.306</v>
+        <v>0.302</v>
       </c>
       <c r="AV29" s="2" t="n">
-        <v>0.2522</v>
+        <v>0.2502</v>
       </c>
     </row>
     <row r="30">
@@ -4135,7 +4129,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4770</v>
+        <v>4741</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -4146,10 +4140,10 @@
         <v>-1.13</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-8.4</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.06</v>
+        <v>9.41</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
@@ -4177,23 +4171,23 @@
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="n">
-        <v>19.23</v>
+        <v>19.08</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>-17.08</v>
+        <v>-17.45</v>
       </c>
       <c r="AA30" s="2" t="n"/>
       <c r="AB30" s="2" t="n">
-        <v>-4.57</v>
+        <v>-4.5</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>-4.46</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="AE30" s="2" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AF30" s="2" t="inlineStr"/>
       <c r="AG30" s="2" t="inlineStr"/>
@@ -4205,40 +4199,40 @@
         </is>
       </c>
       <c r="AK30" s="2" t="n">
-        <v>4785.3</v>
+        <v>4779.5</v>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>4841.007</v>
+        <v>4838.107</v>
       </c>
       <c r="AM30" s="2" t="n">
-        <v>4932.594</v>
+        <v>4931.144</v>
       </c>
       <c r="AN30" s="2" t="n">
-        <v>4910.852</v>
+        <v>4909.885</v>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>4965.156</v>
+        <v>4964.576</v>
       </c>
       <c r="AP30" s="2" t="n">
-        <v>4982.97</v>
+        <v>4982.68</v>
       </c>
       <c r="AQ30" s="2" t="n">
-        <v>5116.038</v>
+        <v>5115.893</v>
       </c>
       <c r="AR30" s="2" t="n">
-        <v>-1.0827</v>
+        <v>-1.1132</v>
       </c>
       <c r="AS30" s="2" t="n">
-        <v>-0.2904</v>
+        <v>-0.3056</v>
       </c>
       <c r="AT30" s="2" t="n">
-        <v>-0.1547</v>
+        <v>-0.1608</v>
       </c>
       <c r="AU30" s="2" t="n">
-        <v>-0.471</v>
+        <v>-0.474</v>
       </c>
       <c r="AV30" s="2" t="n">
-        <v>0.1923</v>
+        <v>0.1908</v>
       </c>
     </row>
     <row r="31">
@@ -4253,18 +4247,18 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
         <v>1.02</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>4.24</v>
@@ -4279,7 +4273,7 @@
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr"/>
@@ -4287,27 +4281,31 @@
       <c r="U31" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="n">
-        <v>31.79</v>
+        <v>31.61</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>-7.49</v>
+        <v>-7.99</v>
       </c>
       <c r="AA31" s="2" t="n"/>
       <c r="AB31" s="2" t="n">
-        <v>-4.71</v>
+        <v>-4.51</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>-3.13</v>
+        <v>-4.69</v>
       </c>
       <c r="AD31" s="2" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AF31" s="2" t="inlineStr"/>
       <c r="AG31" s="2" t="inlineStr"/>
@@ -4319,40 +4317,40 @@
         </is>
       </c>
       <c r="AK31" s="2" t="n">
-        <v>1159.9</v>
+        <v>1158.3</v>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>1158.78</v>
+        <v>1157.98</v>
       </c>
       <c r="AM31" s="2" t="n">
-        <v>1142.594</v>
+        <v>1142.194</v>
       </c>
       <c r="AN31" s="2" t="n">
-        <v>1152.742</v>
+        <v>1152.476</v>
       </c>
       <c r="AO31" s="2" t="n">
-        <v>1167.21</v>
+        <v>1167.05</v>
       </c>
       <c r="AP31" s="2" t="n">
-        <v>1154.988</v>
+        <v>1154.908</v>
       </c>
       <c r="AQ31" s="2" t="n">
-        <v>1115.557</v>
+        <v>1115.517</v>
       </c>
       <c r="AR31" s="2" t="n">
-        <v>0.8242</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="AS31" s="2" t="n">
-        <v>0.0525</v>
+        <v>0.0343</v>
       </c>
       <c r="AT31" s="2" t="n">
-        <v>0.0559</v>
+        <v>0.0487</v>
       </c>
       <c r="AU31" s="2" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0121</v>
       </c>
       <c r="AV31" s="2" t="n">
-        <v>0.3179</v>
+        <v>0.3161</v>
       </c>
     </row>
     <row r="32">
@@ -4367,7 +4365,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>7267</v>
+        <v>7181</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -4375,10 +4373,10 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>101.67</v>
@@ -4401,29 +4399,29 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="n">
-        <v>48.41</v>
+        <v>48.06</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" s="2" t="n"/>
       <c r="AB32" s="2" t="n">
-        <v>-5.58</v>
+        <v>-6.52</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>-7.68</v>
+        <v>-12.25</v>
       </c>
       <c r="AD32" s="2" t="n">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AF32" s="2" t="inlineStr"/>
       <c r="AG32" s="2" t="inlineStr"/>
@@ -4437,40 +4435,40 @@
         </is>
       </c>
       <c r="AK32" s="2" t="n">
-        <v>7235.6</v>
+        <v>7218.4</v>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>7305.995</v>
+        <v>7297.395</v>
       </c>
       <c r="AM32" s="2" t="n">
-        <v>7386.262</v>
+        <v>7381.962</v>
       </c>
       <c r="AN32" s="2" t="n">
-        <v>7373.617</v>
+        <v>7370.75</v>
       </c>
       <c r="AO32" s="2" t="n">
-        <v>7168.571</v>
+        <v>7166.851</v>
       </c>
       <c r="AP32" s="2" t="n">
-        <v>6780.097</v>
+        <v>6779.237</v>
       </c>
       <c r="AQ32" s="2" t="n">
-        <v>6372.132</v>
+        <v>6371.702</v>
       </c>
       <c r="AR32" s="2" t="n">
-        <v>-0.5944</v>
+        <v>-0.6549</v>
       </c>
       <c r="AS32" s="2" t="n">
-        <v>-0.4786</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="AT32" s="2" t="n">
-        <v>0.8565</v>
+        <v>0.8438</v>
       </c>
       <c r="AU32" s="2" t="n">
-        <v>0.2716</v>
+        <v>0.265</v>
       </c>
       <c r="AV32" s="2" t="n">
-        <v>0.4841</v>
+        <v>0.4806</v>
       </c>
     </row>
     <row r="33">
@@ -4485,7 +4483,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4892</v>
+        <v>4879</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
@@ -4496,7 +4494,7 @@
         <v>-0.35</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-6.7</v>
+        <v>-7</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>78.73999999999999</v>
@@ -4523,23 +4521,23 @@
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="n">
-        <v>21.6</v>
+        <v>21.54</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>-15.53</v>
+        <v>-15.61</v>
       </c>
       <c r="AA33" s="2" t="n"/>
       <c r="AB33" s="2" t="n">
-        <v>-4.99</v>
+        <v>-4.62</v>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>-3.51</v>
+        <v>-7.02</v>
       </c>
       <c r="AD33" s="2" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="AE33" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF33" s="2" t="inlineStr"/>
       <c r="AG33" s="2" t="inlineStr"/>
@@ -4551,40 +4549,40 @@
         </is>
       </c>
       <c r="AK33" s="2" t="n">
-        <v>4903.6</v>
+        <v>4901</v>
       </c>
       <c r="AL33" s="2" t="n">
-        <v>4982.322</v>
+        <v>4981.022</v>
       </c>
       <c r="AM33" s="2" t="n">
-        <v>5011.773</v>
+        <v>5011.123</v>
       </c>
       <c r="AN33" s="2" t="n">
-        <v>4963.643</v>
+        <v>4963.209</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>4902.262</v>
+        <v>4902.002</v>
       </c>
       <c r="AP33" s="2" t="n">
-        <v>4927.469</v>
+        <v>4927.339</v>
       </c>
       <c r="AQ33" s="2" t="n">
-        <v>5134.674</v>
+        <v>5134.609</v>
       </c>
       <c r="AR33" s="2" t="n">
-        <v>-0.6879</v>
+        <v>-0.7013</v>
       </c>
       <c r="AS33" s="2" t="n">
-        <v>-0.0727</v>
+        <v>-0.0795</v>
       </c>
       <c r="AT33" s="2" t="n">
-        <v>0.2866</v>
+        <v>0.2838</v>
       </c>
       <c r="AU33" s="2" t="n">
-        <v>-0.3878</v>
+        <v>-0.3891</v>
       </c>
       <c r="AV33" s="2" t="n">
-        <v>0.216</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="34">
@@ -4599,7 +4597,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>12175</v>
+        <v>12110</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
@@ -4607,13 +4605,13 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3.5</v>
+        <v>3.93</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -4641,23 +4639,23 @@
         <v>1</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>76.76000000000001</v>
+        <v>80.66</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>18.68</v>
+        <v>20.01</v>
       </c>
       <c r="AA34" s="2" t="n"/>
       <c r="AB34" s="2" t="n">
-        <v>11.42</v>
+        <v>7.18</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>4.68</v>
+        <v>6.56</v>
       </c>
       <c r="AD34" s="2" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="AE34" s="2" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AF34" s="2" t="inlineStr"/>
       <c r="AG34" s="2" t="n">
@@ -4671,40 +4669,40 @@
         </is>
       </c>
       <c r="AK34" s="2" t="n">
-        <v>11791</v>
+        <v>11778</v>
       </c>
       <c r="AL34" s="2" t="n">
-        <v>11038.193</v>
+        <v>11031.693</v>
       </c>
       <c r="AM34" s="2" t="n">
-        <v>10629.915</v>
+        <v>10626.665</v>
       </c>
       <c r="AN34" s="2" t="n">
-        <v>10645.534</v>
+        <v>10643.367</v>
       </c>
       <c r="AO34" s="2" t="n">
-        <v>10898.966</v>
+        <v>10897.666</v>
       </c>
       <c r="AP34" s="2" t="n">
-        <v>11587.294</v>
+        <v>11586.644</v>
       </c>
       <c r="AQ34" s="2" t="n">
-        <v>9650.967000000001</v>
+        <v>9547.254000000001</v>
       </c>
       <c r="AR34" s="2" t="n">
-        <v>4.5129</v>
+        <v>4.4796</v>
       </c>
       <c r="AS34" s="2" t="n">
-        <v>1.2597</v>
+        <v>1.2434</v>
       </c>
       <c r="AT34" s="2" t="n">
-        <v>-0.8608</v>
+        <v>-0.8669</v>
       </c>
       <c r="AU34" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AV34" s="2" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="35">
@@ -4719,7 +4717,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1752</v>
+        <v>1737</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -4730,7 +4728,7 @@
         <v>1.99</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>96.56</v>
@@ -4759,23 +4757,23 @@
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="n">
-        <v>47.03</v>
+        <v>46.78</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="AA35" s="2" t="n"/>
       <c r="AB35" s="2" t="n">
-        <v>-4.59</v>
+        <v>-5.68</v>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>-5.77</v>
+        <v>-10.04</v>
       </c>
       <c r="AD35" s="2" t="n">
-        <v>82.8</v>
+        <v>82.3</v>
       </c>
       <c r="AE35" s="2" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AF35" s="2" t="inlineStr"/>
       <c r="AG35" s="2" t="inlineStr"/>
@@ -4789,40 +4787,40 @@
         </is>
       </c>
       <c r="AK35" s="2" t="n">
-        <v>1755.2</v>
+        <v>1752.2</v>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>1766.841</v>
+        <v>1765.341</v>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>1783.958</v>
+        <v>1783.208</v>
       </c>
       <c r="AN35" s="2" t="n">
-        <v>1767.993</v>
+        <v>1767.493</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>1727.246</v>
+        <v>1726.946</v>
       </c>
       <c r="AP35" s="2" t="n">
-        <v>1688.06</v>
+        <v>1687.91</v>
       </c>
       <c r="AQ35" s="2" t="n">
-        <v>1573.151</v>
+        <v>1573.076</v>
       </c>
       <c r="AR35" s="2" t="n">
-        <v>-0.5164</v>
+        <v>-0.5601</v>
       </c>
       <c r="AS35" s="2" t="n">
-        <v>-0.0766</v>
+        <v>-0.0984</v>
       </c>
       <c r="AT35" s="2" t="n">
-        <v>0.6448</v>
+        <v>0.6357</v>
       </c>
       <c r="AU35" s="2" t="n">
-        <v>0.1865</v>
+        <v>0.1818</v>
       </c>
       <c r="AV35" s="2" t="n">
-        <v>0.4703</v>
+        <v>0.4678</v>
       </c>
     </row>
     <row r="36">
@@ -4837,7 +4835,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>4695</v>
+        <v>4683</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
@@ -4848,7 +4846,7 @@
         <v>1.19</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>91.69</v>
@@ -4875,20 +4873,20 @@
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="n">
-        <v>30.51</v>
+        <v>30.44</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>-10.78</v>
+        <v>-10.86</v>
       </c>
       <c r="AA36" s="2" t="n"/>
       <c r="AB36" s="2" t="n">
-        <v>-5.02</v>
+        <v>-4.84</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>-3.8</v>
+        <v>-6.95</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AE36" s="2" t="n">
         <v>38</v>
@@ -4903,40 +4901,40 @@
         </is>
       </c>
       <c r="AK36" s="2" t="n">
-        <v>4715.8</v>
+        <v>4713.4</v>
       </c>
       <c r="AL36" s="2" t="n">
-        <v>4780.321</v>
+        <v>4779.121</v>
       </c>
       <c r="AM36" s="2" t="n">
-        <v>4841.652</v>
+        <v>4841.052</v>
       </c>
       <c r="AN36" s="2" t="n">
-        <v>4797.209</v>
+        <v>4796.809</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>4772.749</v>
+        <v>4772.509</v>
       </c>
       <c r="AP36" s="2" t="n">
-        <v>4773.358</v>
+        <v>4773.238</v>
       </c>
       <c r="AQ36" s="2" t="n">
-        <v>4662.452</v>
+        <v>4662.392</v>
       </c>
       <c r="AR36" s="2" t="n">
-        <v>-1.098</v>
+        <v>-1.1108</v>
       </c>
       <c r="AS36" s="2" t="n">
-        <v>-0.0607</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="AT36" s="2" t="n">
-        <v>0.3004</v>
+        <v>0.2977</v>
       </c>
       <c r="AU36" s="2" t="n">
-        <v>-0.2017</v>
+        <v>-0.203</v>
       </c>
       <c r="AV36" s="2" t="n">
-        <v>0.3051</v>
+        <v>0.3044</v>
       </c>
     </row>
     <row r="37">
@@ -4951,7 +4949,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>7200</v>
+        <v>7164</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
@@ -4959,10 +4957,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>98.81999999999999</v>
@@ -4984,32 +4982,28 @@
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="n">
-        <v>56.82</v>
+        <v>56.65</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>10.55</v>
+        <v>10.21</v>
       </c>
       <c r="AA37" s="2" t="n"/>
       <c r="AB37" s="2" t="n">
-        <v>-3.73</v>
+        <v>-4.37</v>
       </c>
       <c r="AC37" s="2" t="n">
-        <v>1.52</v>
+        <v>0.17</v>
       </c>
       <c r="AD37" s="2" t="n">
-        <v>101.4</v>
+        <v>101.2</v>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="2" t="inlineStr"/>
@@ -5023,40 +5017,40 @@
         </is>
       </c>
       <c r="AK37" s="2" t="n">
-        <v>7162.4</v>
+        <v>7155.2</v>
       </c>
       <c r="AL37" s="2" t="n">
-        <v>7225.321</v>
+        <v>7221.721</v>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>7177.358</v>
+        <v>7175.558</v>
       </c>
       <c r="AN37" s="2" t="n">
-        <v>7083.603</v>
+        <v>7082.403</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>6647.118</v>
+        <v>6646.398</v>
       </c>
       <c r="AP37" s="2" t="n">
-        <v>5977.02</v>
+        <v>5976.66</v>
       </c>
       <c r="AQ37" s="2" t="n">
-        <v>5617.804</v>
+        <v>5617.624</v>
       </c>
       <c r="AR37" s="2" t="n">
-        <v>0.1265</v>
+        <v>0.1005</v>
       </c>
       <c r="AS37" s="2" t="n">
-        <v>0.4555</v>
+        <v>0.4423</v>
       </c>
       <c r="AT37" s="2" t="n">
-        <v>1.3783</v>
+        <v>1.3725</v>
       </c>
       <c r="AU37" s="2" t="n">
-        <v>0.713</v>
+        <v>0.7098</v>
       </c>
       <c r="AV37" s="2" t="n">
-        <v>0.5682</v>
+        <v>0.5665</v>
       </c>
     </row>
     <row r="38">
@@ -5071,7 +5065,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>7107</v>
+        <v>7097</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -5082,7 +5076,7 @@
         <v>5.04</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>82.55</v>
@@ -5113,23 +5107,23 @@
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="n">
-        <v>63.4</v>
+        <v>63.35</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="AA38" s="2" t="n"/>
       <c r="AB38" s="2" t="n">
-        <v>-3.38</v>
+        <v>-1.96</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>-0.51</v>
+        <v>-1.34</v>
       </c>
       <c r="AD38" s="2" t="n">
         <v>97.8</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="2" t="inlineStr"/>
@@ -5143,40 +5137,40 @@
         </is>
       </c>
       <c r="AK38" s="2" t="n">
-        <v>7034.2</v>
+        <v>7032.2</v>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>7070.193</v>
+        <v>7069.193</v>
       </c>
       <c r="AM38" s="2" t="n">
-        <v>7019.173</v>
+        <v>7018.673</v>
       </c>
       <c r="AN38" s="2" t="n">
-        <v>7010.12</v>
+        <v>7009.786</v>
       </c>
       <c r="AO38" s="2" t="n">
-        <v>6600.015</v>
+        <v>6599.815</v>
       </c>
       <c r="AP38" s="2" t="n">
-        <v>6022.698</v>
+        <v>6022.598</v>
       </c>
       <c r="AQ38" s="2" t="n">
-        <v>5698.566</v>
+        <v>5698.516</v>
       </c>
       <c r="AR38" s="2" t="n">
-        <v>0.3452</v>
+        <v>0.3378</v>
       </c>
       <c r="AS38" s="2" t="n">
-        <v>0.1634</v>
+        <v>0.1597</v>
       </c>
       <c r="AT38" s="2" t="n">
-        <v>1.289</v>
+        <v>1.2874</v>
       </c>
       <c r="AU38" s="2" t="n">
-        <v>0.5342</v>
+        <v>0.5333</v>
       </c>
       <c r="AV38" s="2" t="n">
-        <v>0.634</v>
+        <v>0.6335</v>
       </c>
     </row>
     <row r="39">
@@ -5191,7 +5185,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3287</v>
+        <v>3273</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5196,7 @@
         <v>5.94</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>89.25</v>
@@ -5229,23 +5223,23 @@
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="n">
-        <v>66.61</v>
+        <v>66.47</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>12.68</v>
+        <v>12.37</v>
       </c>
       <c r="AA39" s="2" t="n"/>
       <c r="AB39" s="2" t="n">
-        <v>-7.27</v>
+        <v>-7.6</v>
       </c>
       <c r="AC39" s="2" t="n">
-        <v>-3.46</v>
+        <v>-5.77</v>
       </c>
       <c r="AD39" s="2" t="n">
-        <v>89.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF39" s="2" t="inlineStr"/>
       <c r="AG39" s="2" t="inlineStr"/>
@@ -5259,40 +5253,40 @@
         </is>
       </c>
       <c r="AK39" s="2" t="n">
-        <v>3301.4</v>
+        <v>3298.6</v>
       </c>
       <c r="AL39" s="2" t="n">
-        <v>3356.717</v>
+        <v>3355.317</v>
       </c>
       <c r="AM39" s="2" t="n">
-        <v>3338.793</v>
+        <v>3338.093</v>
       </c>
       <c r="AN39" s="2" t="n">
-        <v>3316.674</v>
+        <v>3316.207</v>
       </c>
       <c r="AO39" s="2" t="n">
-        <v>3116.333</v>
+        <v>3116.053</v>
       </c>
       <c r="AP39" s="2" t="n">
-        <v>2814.254</v>
+        <v>2814.114</v>
       </c>
       <c r="AQ39" s="2" t="n">
-        <v>2576.115</v>
+        <v>2576.045</v>
       </c>
       <c r="AR39" s="2" t="n">
-        <v>-0.0852</v>
+        <v>-0.1069</v>
       </c>
       <c r="AS39" s="2" t="n">
-        <v>0.0873</v>
+        <v>0.0764</v>
       </c>
       <c r="AT39" s="2" t="n">
-        <v>1.1958</v>
+        <v>1.191</v>
       </c>
       <c r="AU39" s="2" t="n">
-        <v>0.7687</v>
+        <v>0.766</v>
       </c>
       <c r="AV39" s="2" t="n">
-        <v>0.6661</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="40">
@@ -5307,7 +5301,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>71460</v>
+        <v>71470</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
@@ -5351,17 +5345,17 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="n">
-        <v>25.99</v>
+        <v>26</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.41</v>
       </c>
       <c r="AA40" s="2" t="n"/>
       <c r="AB40" s="2" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>-3.97</v>
+        <v>-2.42</v>
       </c>
       <c r="AD40" s="2" t="n">
         <v>0.1</v>
@@ -5381,40 +5375,40 @@
         </is>
       </c>
       <c r="AK40" s="2" t="n">
-        <v>70326</v>
+        <v>70328</v>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>69058</v>
+        <v>69059</v>
       </c>
       <c r="AM40" s="2" t="n">
-        <v>68475</v>
+        <v>68475.5</v>
       </c>
       <c r="AN40" s="2" t="n">
-        <v>69864.398</v>
+        <v>69864.731</v>
       </c>
       <c r="AO40" s="2" t="n">
-        <v>73050.36</v>
+        <v>73050.56</v>
       </c>
       <c r="AP40" s="2" t="n">
-        <v>76153.624</v>
+        <v>76153.724</v>
       </c>
       <c r="AQ40" s="2" t="n">
-        <v>69894.004</v>
+        <v>69894.054</v>
       </c>
       <c r="AR40" s="2" t="n">
-        <v>1.3996</v>
+        <v>1.4004</v>
       </c>
       <c r="AS40" s="2" t="n">
-        <v>-0.2403</v>
+        <v>-0.2399</v>
       </c>
       <c r="AT40" s="2" t="n">
-        <v>-0.6207</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="AU40" s="2" t="n">
-        <v>-0.1167</v>
+        <v>-0.1166</v>
       </c>
       <c r="AV40" s="2" t="n">
-        <v>0.2599</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="41">
@@ -8041,7 +8035,7 @@
         <v>16.1</v>
       </c>
       <c r="AE62" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF62" s="2" t="inlineStr"/>
       <c r="AG62" s="2" t="inlineStr"/>
@@ -15875,7 +15869,7 @@
       <c r="O126" s="2" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr"/>
       <c r="Q126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
       <c r="S126" s="2" t="inlineStr"/>
@@ -20571,7 +20565,7 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>148.07</v>
+        <v>151.06</v>
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" s="2" t="n"/>
@@ -20596,7 +20590,11 @@
       <c r="R165" s="2" t="inlineStr"/>
       <c r="S165" s="2" t="inlineStr"/>
       <c r="T165" s="2" t="inlineStr"/>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="V165" s="2" t="inlineStr"/>
       <c r="W165" s="2" t="inlineStr"/>
       <c r="X165" s="2" t="inlineStr"/>
@@ -20613,30 +20611,30 @@
       <c r="AI165" s="2" t="inlineStr"/>
       <c r="AJ165" s="2" t="inlineStr"/>
       <c r="AK165" s="2" t="n">
-        <v>148.464</v>
+        <v>149.062</v>
       </c>
       <c r="AL165" s="2" t="n">
-        <v>149.799</v>
+        <v>150.098</v>
       </c>
       <c r="AM165" s="2" t="n">
-        <v>149.671</v>
+        <v>149.82</v>
       </c>
       <c r="AN165" s="2" t="n">
-        <v>146.199</v>
+        <v>146.299</v>
       </c>
       <c r="AO165" s="2" t="n">
-        <v>138.143</v>
+        <v>138.203</v>
       </c>
       <c r="AP165" s="2" t="n"/>
       <c r="AQ165" s="2" t="n"/>
       <c r="AR165" s="2" t="n">
-        <v>-0.215</v>
+        <v>-0.1117</v>
       </c>
       <c r="AS165" s="2" t="n">
-        <v>0.5853</v>
+        <v>0.6379</v>
       </c>
       <c r="AT165" s="2" t="n">
-        <v>0.9863</v>
+        <v>1.0092</v>
       </c>
       <c r="AU165" s="2" t="n"/>
       <c r="AV165" s="2" t="n"/>
@@ -21720,7 +21718,7 @@
         <v>-16.55</v>
       </c>
       <c r="AD174" s="2" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AE174" s="2" t="n">
         <v>31</v>
@@ -22107,7 +22105,7 @@
         <v>72</v>
       </c>
       <c r="AE177" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF177" s="2" t="inlineStr"/>
       <c r="AG177" s="2" t="inlineStr"/>
@@ -22661,7 +22659,7 @@
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>6008</v>
+        <v>5984</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
@@ -22672,10 +22670,10 @@
         <v>-3.87</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>-22.4</v>
+        <v>-22.7</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>11.56</v>
+        <v>10.56</v>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr"/>
@@ -22697,23 +22695,23 @@
       <c r="W182" s="2" t="inlineStr"/>
       <c r="X182" s="2" t="inlineStr"/>
       <c r="Y182" s="2" t="n">
-        <v>-30.48</v>
+        <v>-30.56</v>
       </c>
       <c r="Z182" s="2" t="n">
-        <v>-35.91</v>
+        <v>-35.98</v>
       </c>
       <c r="AA182" s="2" t="n"/>
       <c r="AB182" s="2" t="n">
-        <v>-9.5</v>
+        <v>-8.35</v>
       </c>
       <c r="AC182" s="2" t="n">
-        <v>-10.06</v>
+        <v>-10.55</v>
       </c>
       <c r="AD182" s="2" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="AE182" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF182" s="2" t="inlineStr"/>
       <c r="AG182" s="2" t="n">
@@ -22727,40 +22725,40 @@
         </is>
       </c>
       <c r="AK182" s="2" t="n">
-        <v>6173.2</v>
+        <v>6168.4</v>
       </c>
       <c r="AL182" s="2" t="n">
-        <v>6400.8</v>
+        <v>6398.4</v>
       </c>
       <c r="AM182" s="2" t="n">
-        <v>6491.95</v>
+        <v>6490.75</v>
       </c>
       <c r="AN182" s="2" t="n">
-        <v>6655.033</v>
+        <v>6654.233</v>
       </c>
       <c r="AO182" s="2" t="n">
-        <v>6793.84</v>
+        <v>6793.36</v>
       </c>
       <c r="AP182" s="2" t="n">
-        <v>7168.705</v>
+        <v>7168.465</v>
       </c>
       <c r="AQ182" s="2" t="n">
-        <v>7914.437</v>
+        <v>7914.317</v>
       </c>
       <c r="AR182" s="2" t="n">
-        <v>-1.085</v>
+        <v>-1.1041</v>
       </c>
       <c r="AS182" s="2" t="n">
-        <v>-1.5586</v>
+        <v>-1.568</v>
       </c>
       <c r="AT182" s="2" t="n">
-        <v>-0.7987</v>
+        <v>-0.8023</v>
       </c>
       <c r="AU182" s="2" t="n">
-        <v>-0.6499</v>
+        <v>-0.6516</v>
       </c>
       <c r="AV182" s="2" t="n">
-        <v>-0.3048</v>
+        <v>-0.3056</v>
       </c>
     </row>
     <row r="183">
@@ -22775,7 +22773,7 @@
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>1358.5</v>
+        <v>1360</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
@@ -22786,7 +22784,7 @@
         <v>0.77</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>83.7</v>
@@ -22811,23 +22809,23 @@
       <c r="W183" s="2" t="inlineStr"/>
       <c r="X183" s="2" t="inlineStr"/>
       <c r="Y183" s="2" t="n">
-        <v>36.21</v>
+        <v>36.24</v>
       </c>
       <c r="Z183" s="2" t="n">
-        <v>-6.08</v>
+        <v>-5.84</v>
       </c>
       <c r="AA183" s="2" t="n"/>
       <c r="AB183" s="2" t="n">
-        <v>-7.75</v>
+        <v>-7.17</v>
       </c>
       <c r="AC183" s="2" t="n">
-        <v>-1.15</v>
+        <v>-4.58</v>
       </c>
       <c r="AD183" s="2" t="n">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AE183" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF183" s="2" t="inlineStr"/>
       <c r="AG183" s="2" t="inlineStr"/>
@@ -22841,40 +22839,40 @@
         </is>
       </c>
       <c r="AK183" s="2" t="n">
-        <v>1375.3</v>
+        <v>1375.6</v>
       </c>
       <c r="AL183" s="2" t="n">
-        <v>1401.354</v>
+        <v>1401.504</v>
       </c>
       <c r="AM183" s="2" t="n">
-        <v>1394.273</v>
+        <v>1394.348</v>
       </c>
       <c r="AN183" s="2" t="n">
-        <v>1367.211</v>
+        <v>1367.261</v>
       </c>
       <c r="AO183" s="2" t="n">
-        <v>1335.769</v>
+        <v>1335.799</v>
       </c>
       <c r="AP183" s="2" t="n">
-        <v>1294.082</v>
+        <v>1294.097</v>
       </c>
       <c r="AQ183" s="2" t="n">
-        <v>1286.442</v>
+        <v>1286.449</v>
       </c>
       <c r="AR183" s="2" t="n">
-        <v>-0.9173</v>
+        <v>-0.9119</v>
       </c>
       <c r="AS183" s="2" t="n">
-        <v>0.4898</v>
+        <v>0.4926</v>
       </c>
       <c r="AT183" s="2" t="n">
-        <v>0.4969</v>
+        <v>0.4981</v>
       </c>
       <c r="AU183" s="2" t="n">
-        <v>0.1642</v>
+        <v>0.1648</v>
       </c>
       <c r="AV183" s="2" t="n">
-        <v>0.3621</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="184">
@@ -22889,7 +22887,7 @@
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>5294</v>
+        <v>5310</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
@@ -22900,7 +22898,7 @@
         <v>-0.1</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>-6.9</v>
+        <v>-6.6</v>
       </c>
       <c r="G184" s="2" t="n">
         <v>1.22</v>
@@ -22925,23 +22923,23 @@
       <c r="W184" s="2" t="inlineStr"/>
       <c r="X184" s="2" t="inlineStr"/>
       <c r="Y184" s="2" t="n">
-        <v>22.7</v>
+        <v>22.78</v>
       </c>
       <c r="Z184" s="2" t="n">
-        <v>-13.8</v>
+        <v>-13.4</v>
       </c>
       <c r="AA184" s="2" t="n"/>
       <c r="AB184" s="2" t="n">
-        <v>-2.95</v>
+        <v>-0.84</v>
       </c>
       <c r="AC184" s="2" t="n">
-        <v>-6.86</v>
+        <v>-5.54</v>
       </c>
       <c r="AD184" s="2" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="AE184" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AF184" s="2" t="inlineStr"/>
       <c r="AG184" s="2" t="n">
@@ -22955,40 +22953,40 @@
         </is>
       </c>
       <c r="AK184" s="2" t="n">
-        <v>5225</v>
+        <v>5228.2</v>
       </c>
       <c r="AL184" s="2" t="n">
-        <v>5193.859</v>
+        <v>5195.459</v>
       </c>
       <c r="AM184" s="2" t="n">
-        <v>5171.875</v>
+        <v>5172.675</v>
       </c>
       <c r="AN184" s="2" t="n">
-        <v>5304.371</v>
+        <v>5304.905</v>
       </c>
       <c r="AO184" s="2" t="n">
-        <v>5465.43</v>
+        <v>5465.75</v>
       </c>
       <c r="AP184" s="2" t="n">
-        <v>5718.523</v>
+        <v>5718.683</v>
       </c>
       <c r="AQ184" s="2" t="n">
-        <v>5492.156</v>
+        <v>5492.236</v>
       </c>
       <c r="AR184" s="2" t="n">
-        <v>0.772</v>
+        <v>0.7883</v>
       </c>
       <c r="AS184" s="2" t="n">
-        <v>-0.8166</v>
+        <v>-0.8087</v>
       </c>
       <c r="AT184" s="2" t="n">
-        <v>-0.3314</v>
+        <v>-0.3284</v>
       </c>
       <c r="AU184" s="2" t="n">
-        <v>-0.4492</v>
+        <v>-0.4478</v>
       </c>
       <c r="AV184" s="2" t="n">
-        <v>0.227</v>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="185">
@@ -23003,7 +23001,7 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>4750</v>
+        <v>4751</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
@@ -23042,14 +23040,14 @@
         <v>10.31</v>
       </c>
       <c r="Z185" s="2" t="n">
-        <v>-19.83</v>
+        <v>-19.71</v>
       </c>
       <c r="AA185" s="2" t="n"/>
       <c r="AB185" s="2" t="n">
-        <v>0.63</v>
+        <v>2.23</v>
       </c>
       <c r="AC185" s="2" t="n">
-        <v>-3.19</v>
+        <v>-1.79</v>
       </c>
       <c r="AD185" s="2" t="n">
         <v>-3.5</v>
@@ -23069,37 +23067,37 @@
         </is>
       </c>
       <c r="AK185" s="2" t="n">
-        <v>4628.6</v>
+        <v>4628.8</v>
       </c>
       <c r="AL185" s="2" t="n">
-        <v>4517.2</v>
+        <v>4517.3</v>
       </c>
       <c r="AM185" s="2" t="n">
-        <v>4483.25</v>
+        <v>4483.3</v>
       </c>
       <c r="AN185" s="2" t="n">
-        <v>4612.644</v>
+        <v>4612.678</v>
       </c>
       <c r="AO185" s="2" t="n">
-        <v>4815.993</v>
+        <v>4816.013</v>
       </c>
       <c r="AP185" s="2" t="n">
-        <v>5765.46</v>
+        <v>5765.47</v>
       </c>
       <c r="AQ185" s="2" t="n">
-        <v>5326.775</v>
+        <v>5326.78</v>
       </c>
       <c r="AR185" s="2" t="n">
-        <v>1.5555</v>
+        <v>1.5567</v>
       </c>
       <c r="AS185" s="2" t="n">
-        <v>-0.521</v>
+        <v>-0.5205</v>
       </c>
       <c r="AT185" s="2" t="n">
-        <v>-0.8835</v>
+        <v>-0.8833</v>
       </c>
       <c r="AU185" s="2" t="n">
-        <v>-0.4831</v>
+        <v>-0.483</v>
       </c>
       <c r="AV185" s="2" t="n">
         <v>0.1031</v>
@@ -23519,7 +23517,7 @@
         <v>19.3</v>
       </c>
       <c r="AE189" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AF189" s="2" t="inlineStr"/>
       <c r="AG189" s="2" t="inlineStr"/>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -928,7 +928,9 @@
         <v>0</v>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="n">
@@ -2014,7 +2016,9 @@
         <v>0</v>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="n">
         <v>1</v>
@@ -2135,7 +2139,9 @@
         <v>1</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
@@ -2253,7 +2259,9 @@
       </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="inlineStr"/>
@@ -2853,7 +2861,9 @@
       </c>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="inlineStr"/>
@@ -2979,7 +2989,9 @@
       </c>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
@@ -9701,7 +9713,9 @@
       </c>
       <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr"/>
-      <c r="T76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U76" s="2" t="n">
         <v>1</v>
       </c>
@@ -14765,7 +14779,9 @@
       </c>
       <c r="R117" s="2" t="inlineStr"/>
       <c r="S117" s="2" t="inlineStr"/>
-      <c r="T117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr"/>
       <c r="W117" s="2" t="inlineStr"/>
@@ -16725,7 +16741,9 @@
       </c>
       <c r="R133" s="2" t="inlineStr"/>
       <c r="S133" s="2" t="inlineStr"/>
-      <c r="T133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U133" s="2" t="n">
         <v>-1</v>
       </c>
@@ -20209,7 +20227,7 @@
         <v>35</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>108.31</v>
+        <v>108.29</v>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr"/>
@@ -21799,7 +21817,7 @@
         <v>48</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>114.08</v>
+        <v>114.03</v>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr">
@@ -24673,7 +24691,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-03 | 197 只</t>
+          <t>截至: 2026-10-04 | 197 只</t>
         </is>
       </c>
     </row>
@@ -24867,14 +24885,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5% 且距250日收盘高点回落≥5%(创新高处的平台突破归新高, 不算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
+          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置: {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。强度路径: 放量+RS超额+阳线。无位置门(2026-10-02取消: 原A门200日pos&lt;=0.80/B门均线纠缠+距250日高点回落≥5%/门E Stage 1B-2B 全部移除, 高位/新高处的放量突破同样算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
+          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量; 海外大盘股池放宽至1.5x) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
         </is>
       </c>
     </row>
@@ -24995,42 +25013,42 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stage (Weinstein Stage Analysis, MA150=30周线为锚):</t>
+          <t xml:space="preserve">  ★ 海外SOS放量门放宽: 大盘股量能结构性平缓, 2×20日均量几乎不可触发(250日统计37%空榜日) → 海外池(US+JP)降为1.5×, HK/A/ETF维持2× (2026-10-03)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1=筑底(均线走平,价在其下方/附近徘徊) 1B=筑底末期(价已回均线上方但均线未上弯)</t>
+          <t xml:space="preserve">  Stage (Weinstein Stage Analysis, MA150=30周线为锚):</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2A=Stage1→2过渡(近20日收盘创60日新高但均线尚未上弯) 2B=趋势运行中(MA150上行)</t>
+          <t xml:space="preserve">    1=筑底(均线走平,价在其下方/附近徘徊) 1B=筑底末期(价已回均线上方但均线未上弯)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3=顶部(此前3月均线上行后走平, 价在其上方震荡) 4=下行(价在下行均线下方)</t>
+          <t xml:space="preserve">    2A=Stage1→2过渡(近20日收盘创60日新高但均线尚未上弯) 2B=趋势运行中(MA150上行)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MA150斜率20d%: MA150近20日(约1个月)变化%; 距MA150%: 收盘距MA150百分比(&gt;0=上方)</t>
+          <t xml:space="preserve">    3=顶部(此前3月均线上行后走平, 价在其上方震荡) 4=下行(价在下行均线下方)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ★ 美股SOS位置门扩展: A∨B∨(Stage 1B/2A/2B) — 信号K线当日处于筑底末期/Stage1→2过渡/Stage2上行趋势的突破也放行 (门E)</t>
+          <t xml:space="preserve">  MA150斜率20d%: MA150近20日(约1个月)变化%; 距MA150%: 收盘距MA150百分比(&gt;0=上方)</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -1353,7 +1353,7 @@
         <v>9628.039000000001</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>8766.894</v>
+        <v>8766.893</v>
       </c>
       <c r="AR6" s="2" t="n">
         <v>3.5955</v>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="AK45" s="2" t="n">
-        <v>238.599</v>
+        <v>238.6</v>
       </c>
       <c r="AL45" s="2" t="n">
-        <v>237.608</v>
+        <v>237.609</v>
       </c>
       <c r="AM45" s="2" t="n">
         <v>242.72</v>
@@ -6052,10 +6052,10 @@
         <v>256.978</v>
       </c>
       <c r="AR45" s="2" t="n">
-        <v>-0.215</v>
+        <v>-0.2149</v>
       </c>
       <c r="AS45" s="2" t="n">
-        <v>-0.9124</v>
+        <v>-0.9123</v>
       </c>
       <c r="AT45" s="2" t="n">
         <v>-0.1222</v>
@@ -9537,7 +9537,7 @@
         <v>-7.3</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
@@ -12375,7 +12375,7 @@
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr"/>
       <c r="Q97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R97" s="2" t="inlineStr"/>
       <c r="S97" s="2" t="inlineStr"/>
@@ -12839,7 +12839,7 @@
         <v>-9.6</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>4.6</v>
       </c>
       <c r="AE112" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF112" s="2" t="inlineStr"/>
       <c r="AG112" s="2" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
         <v>-27.3</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>-5.2</v>
+        <v>-5.22</v>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
@@ -14914,7 +14914,7 @@
         <v>764.194</v>
       </c>
       <c r="AR117" s="2" t="n">
-        <v>4.1806</v>
+        <v>4.1805</v>
       </c>
       <c r="AS117" s="2" t="n">
         <v>2.1441</v>
@@ -20827,7 +20827,7 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>41.855</v>
+        <v>41.86</v>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
@@ -20872,16 +20872,16 @@
         <v>51.32</v>
       </c>
       <c r="Z166" s="2" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="AA166" s="2" t="n">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="AB166" s="2" t="n">
-        <v>-5.02</v>
+        <v>-5.01</v>
       </c>
       <c r="AC166" s="2" t="n">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="AD166" s="2" t="n">
         <v>99.2</v>
@@ -20905,10 +20905,10 @@
         </is>
       </c>
       <c r="AK166" s="2" t="n">
-        <v>43.243</v>
+        <v>43.244</v>
       </c>
       <c r="AL166" s="2" t="n">
-        <v>42.569</v>
+        <v>42.57</v>
       </c>
       <c r="AM166" s="2" t="n">
         <v>41.166</v>
@@ -20926,16 +20926,16 @@
         <v>32.319</v>
       </c>
       <c r="AR166" s="2" t="n">
-        <v>0.9029</v>
+        <v>0.9035</v>
       </c>
       <c r="AS166" s="2" t="n">
-        <v>1.2917</v>
+        <v>1.292</v>
       </c>
       <c r="AT166" s="2" t="n">
-        <v>2.1197</v>
+        <v>2.1198</v>
       </c>
       <c r="AU166" s="2" t="n">
-        <v>0.8479</v>
+        <v>0.848</v>
       </c>
       <c r="AV166" s="2" t="n">
         <v>0.5132</v>
@@ -24837,7 +24837,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-10 | 197 只</t>
+          <t>截至: 2026-10-11 | 197 只</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -1353,7 +1353,7 @@
         <v>9628.039000000001</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>8766.893</v>
+        <v>8766.894</v>
       </c>
       <c r="AR6" s="2" t="n">
         <v>3.5955</v>
@@ -4259,7 +4259,7 @@
         <v>2377.445</v>
       </c>
       <c r="AQ30" s="2" t="n">
-        <v>2366.394</v>
+        <v>2366.395</v>
       </c>
       <c r="AR30" s="2" t="n">
         <v>0.709</v>
@@ -5801,7 +5801,7 @@
         <v>42.44</v>
       </c>
       <c r="AM43" s="2" t="n">
-        <v>43.721</v>
+        <v>43.722</v>
       </c>
       <c r="AN43" s="2" t="n">
         <v>45.89</v>
@@ -7547,7 +7547,7 @@
         <v>60.022</v>
       </c>
       <c r="AO57" s="2" t="n">
-        <v>62.848</v>
+        <v>62.847</v>
       </c>
       <c r="AP57" s="2" t="n">
         <v>72.49299999999999</v>
@@ -9605,7 +9605,7 @@
         <v>114.757</v>
       </c>
       <c r="AM74" s="2" t="n">
-        <v>120.274</v>
+        <v>120.273</v>
       </c>
       <c r="AN74" s="2" t="n">
         <v>124.931</v>
@@ -10347,7 +10347,7 @@
         <v>190.052</v>
       </c>
       <c r="AO80" s="2" t="n">
-        <v>209.856</v>
+        <v>209.857</v>
       </c>
       <c r="AP80" s="2" t="n">
         <v>221.47</v>
@@ -10592,7 +10592,7 @@
         <v>54.985</v>
       </c>
       <c r="AP82" s="2" t="n">
-        <v>53.594</v>
+        <v>53.593</v>
       </c>
       <c r="AQ82" s="2" t="n">
         <v>53.226</v>
@@ -12307,7 +12307,7 @@
         <v>147.876</v>
       </c>
       <c r="AM96" s="2" t="n">
-        <v>148.728</v>
+        <v>148.727</v>
       </c>
       <c r="AN96" s="2" t="n">
         <v>148.029</v>
@@ -12423,7 +12423,7 @@
         <v>14.901</v>
       </c>
       <c r="AM97" s="2" t="n">
-        <v>14.968</v>
+        <v>14.967</v>
       </c>
       <c r="AN97" s="2" t="n">
         <v>15.408</v>
@@ -14019,7 +14019,7 @@
         <v>260.303</v>
       </c>
       <c r="AM110" s="2" t="n">
-        <v>264.688</v>
+        <v>264.689</v>
       </c>
       <c r="AN110" s="2" t="n">
         <v>266.528</v>
@@ -14645,7 +14645,7 @@
         <v>119.758</v>
       </c>
       <c r="AM115" s="2" t="n">
-        <v>123.521</v>
+        <v>123.52</v>
       </c>
       <c r="AN115" s="2" t="n">
         <v>126.704</v>
@@ -16251,7 +16251,7 @@
         <v>144.364</v>
       </c>
       <c r="AM128" s="2" t="n">
-        <v>145.781</v>
+        <v>145.78</v>
       </c>
       <c r="AN128" s="2" t="n">
         <v>146.394</v>
@@ -17871,7 +17871,7 @@
         <v>37.98</v>
       </c>
       <c r="AM141" s="2" t="n">
-        <v>39.435</v>
+        <v>39.436</v>
       </c>
       <c r="AN141" s="2" t="n">
         <v>41.415</v>
@@ -20581,7 +20581,7 @@
         <v>29.411</v>
       </c>
       <c r="AM163" s="2" t="n">
-        <v>28.488</v>
+        <v>28.489</v>
       </c>
       <c r="AN163" s="2" t="n">
         <v>25.618</v>
@@ -20712,7 +20712,7 @@
         <v>144.815</v>
       </c>
       <c r="AP164" s="2" t="n">
-        <v>130.28</v>
+        <v>130.281</v>
       </c>
       <c r="AQ164" s="2" t="n">
         <v>129.524</v>
@@ -23857,7 +23857,7 @@
         <v>252.582</v>
       </c>
       <c r="AM190" s="2" t="n">
-        <v>252.02</v>
+        <v>252.019</v>
       </c>
       <c r="AN190" s="2" t="n">
         <v>253.731</v>
@@ -24779,7 +24779,7 @@
         <v>187.529</v>
       </c>
       <c r="AM198" s="2" t="n">
-        <v>189.703</v>
+        <v>189.702</v>
       </c>
       <c r="AN198" s="2" t="n">
         <v>191.377</v>
@@ -24837,7 +24837,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-11 | 197 只</t>
+          <t>截至: 2026-10-12 | 197 只</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -845,17 +845,13 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>9d</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="n">
         <v>-1</v>
@@ -1266,11 +1262,11 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" s="2" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
@@ -1546,7 +1542,7 @@
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
@@ -2219,7 +2215,7 @@
         </is>
       </c>
       <c r="W12" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
@@ -2356,11 +2352,11 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
@@ -2507,11 +2503,7 @@
       <c r="W14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
+      <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="n">
         <v>-1</v>
@@ -3611,7 +3603,7 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>49</v>
+        <v>323</v>
       </c>
       <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
@@ -4429,7 +4421,7 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
@@ -4971,7 +4963,7 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
@@ -5644,7 +5636,7 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>56</v>
+        <v>342</v>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr"/>
@@ -6327,11 +6319,11 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
@@ -7445,7 +7437,7 @@
         </is>
       </c>
       <c r="W50" s="2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr"/>
@@ -8134,11 +8126,11 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W55" s="2" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr"/>
@@ -8273,7 +8265,7 @@
         </is>
       </c>
       <c r="W56" s="2" t="n">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="inlineStr"/>
@@ -8692,11 +8684,11 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W59" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X59" s="2" t="inlineStr"/>
       <c r="Y59" s="2" t="inlineStr"/>
@@ -8978,7 +8970,7 @@
         </is>
       </c>
       <c r="W61" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="X61" s="2" t="inlineStr"/>
       <c r="Y61" s="2" t="inlineStr"/>
@@ -9929,7 +9921,7 @@
         </is>
       </c>
       <c r="W68" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="X68" s="2" t="inlineStr"/>
       <c r="Y68" s="2" t="inlineStr"/>
@@ -10056,17 +10048,13 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X69" s="2" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="X69" s="2" t="inlineStr"/>
       <c r="Y69" s="2" t="inlineStr"/>
       <c r="Z69" s="2" t="inlineStr"/>
       <c r="AA69" s="2" t="n">
@@ -10203,11 +10191,7 @@
       <c r="W70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="X70" s="2" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
+      <c r="X70" s="2" t="inlineStr"/>
       <c r="Y70" s="2" t="inlineStr"/>
       <c r="Z70" s="2" t="inlineStr"/>
       <c r="AA70" s="2" t="n">
@@ -10892,11 +10876,7 @@
       <c r="W75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="X75" s="2" t="inlineStr">
-        <is>
-          <t>8d</t>
-        </is>
-      </c>
+      <c r="X75" s="2" t="inlineStr"/>
       <c r="Y75" s="2" t="inlineStr"/>
       <c r="Z75" s="2" t="n">
         <v>-1</v>
@@ -11029,7 +11009,7 @@
         </is>
       </c>
       <c r="W76" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="X76" s="2" t="inlineStr"/>
       <c r="Y76" s="2" t="inlineStr"/>
@@ -12288,7 +12268,7 @@
         </is>
       </c>
       <c r="W85" s="2" t="n">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="X85" s="2" t="inlineStr"/>
       <c r="Y85" s="2" t="inlineStr"/>
@@ -12562,7 +12542,7 @@
         </is>
       </c>
       <c r="W87" s="2" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="X87" s="2" t="inlineStr"/>
       <c r="Y87" s="2" t="inlineStr"/>
@@ -12693,7 +12673,7 @@
         </is>
       </c>
       <c r="W88" s="2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="X88" s="2" t="inlineStr"/>
       <c r="Y88" s="2" t="inlineStr"/>
@@ -12969,7 +12949,7 @@
         </is>
       </c>
       <c r="W90" s="2" t="n">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="X90" s="2" t="inlineStr"/>
       <c r="Y90" s="2" t="inlineStr"/>
@@ -13787,13 +13767,9 @@
         </is>
       </c>
       <c r="W96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="X96" s="2" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="inlineStr"/>
       <c r="Z96" s="2" t="n">
         <v>-1</v>
@@ -14496,7 +14472,7 @@
         </is>
       </c>
       <c r="W101" s="2" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="X101" s="2" t="inlineStr"/>
       <c r="Y101" s="2" t="inlineStr"/>
@@ -15322,11 +15298,11 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W107" s="2" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="X107" s="2" t="inlineStr"/>
       <c r="Y107" s="2" t="inlineStr"/>
@@ -15866,11 +15842,11 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W111" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="X111" s="2" t="inlineStr"/>
       <c r="Y111" s="2" t="inlineStr"/>
@@ -16168,7 +16144,7 @@
         </is>
       </c>
       <c r="W113" s="2" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="X113" s="2" t="inlineStr"/>
       <c r="Y113" s="2" t="inlineStr"/>
@@ -16593,7 +16569,7 @@
         </is>
       </c>
       <c r="W116" s="2" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="X116" s="2" t="inlineStr"/>
       <c r="Y116" s="2" t="inlineStr"/>
@@ -17701,11 +17677,11 @@
       </c>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W124" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X124" s="2" t="inlineStr"/>
       <c r="Y124" s="2" t="inlineStr"/>
@@ -18815,7 +18791,7 @@
         </is>
       </c>
       <c r="W132" s="2" t="n">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="X132" s="2" t="inlineStr"/>
       <c r="Y132" s="2" t="inlineStr"/>
@@ -19526,7 +19502,7 @@
         </is>
       </c>
       <c r="W137" s="2" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="X137" s="2" t="inlineStr"/>
       <c r="Y137" s="2" t="inlineStr"/>
@@ -19955,7 +19931,7 @@
         </is>
       </c>
       <c r="W140" s="2" t="n">
-        <v>52</v>
+        <v>326</v>
       </c>
       <c r="X140" s="2" t="inlineStr"/>
       <c r="Y140" s="2" t="inlineStr"/>
@@ -20243,7 +20219,7 @@
         </is>
       </c>
       <c r="W142" s="2" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="X142" s="2" t="inlineStr"/>
       <c r="Y142" s="2" t="inlineStr"/>
@@ -21339,7 +21315,7 @@
         </is>
       </c>
       <c r="W150" s="2" t="n">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="X150" s="2" t="inlineStr"/>
       <c r="Y150" s="2" t="inlineStr"/>
@@ -21754,7 +21730,7 @@
         </is>
       </c>
       <c r="W153" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="X153" s="2" t="inlineStr"/>
       <c r="Y153" s="2" t="inlineStr"/>
@@ -22443,7 +22419,7 @@
         </is>
       </c>
       <c r="W158" s="2" t="n">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="X158" s="2" t="inlineStr"/>
       <c r="Y158" s="2" t="inlineStr"/>
@@ -23132,7 +23108,7 @@
         </is>
       </c>
       <c r="W163" s="2" t="n">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="X163" s="2" t="inlineStr"/>
       <c r="Y163" s="2" t="inlineStr"/>
@@ -24355,11 +24331,11 @@
       </c>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W172" s="2" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="X172" s="2" t="inlineStr"/>
       <c r="Y172" s="2" t="inlineStr"/>
@@ -24506,7 +24482,7 @@
         </is>
       </c>
       <c r="W173" s="2" t="n">
-        <v>52</v>
+        <v>349</v>
       </c>
       <c r="X173" s="2" t="inlineStr"/>
       <c r="Y173" s="2" t="inlineStr"/>
@@ -25890,11 +25866,11 @@
       </c>
       <c r="V183" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W183" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="X183" s="2" t="inlineStr"/>
       <c r="Y183" s="2" t="inlineStr"/>
@@ -26307,13 +26283,9 @@
         </is>
       </c>
       <c r="W186" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X186" s="2" t="inlineStr">
-        <is>
-          <t>10d</t>
-        </is>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="X186" s="2" t="inlineStr"/>
       <c r="Y186" s="2" t="inlineStr"/>
       <c r="Z186" s="2" t="inlineStr"/>
       <c r="AA186" s="2" t="inlineStr"/>
@@ -26440,11 +26412,7 @@
       <c r="W187" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="X187" s="2" t="inlineStr">
-        <is>
-          <t>9d</t>
-        </is>
-      </c>
+      <c r="X187" s="2" t="inlineStr"/>
       <c r="Y187" s="2" t="inlineStr"/>
       <c r="Z187" s="2" t="inlineStr"/>
       <c r="AA187" s="2" t="inlineStr"/>
@@ -26569,7 +26537,7 @@
         </is>
       </c>
       <c r="W188" s="2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="X188" s="2" t="inlineStr"/>
       <c r="Y188" s="2" t="inlineStr"/>
@@ -26956,11 +26924,11 @@
       </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W191" s="2" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="X191" s="2" t="inlineStr"/>
       <c r="Y191" s="2" t="inlineStr"/>
@@ -27349,13 +27317,9 @@
         </is>
       </c>
       <c r="W194" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="X194" s="2" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="X194" s="2" t="inlineStr"/>
       <c r="Y194" s="2" t="inlineStr"/>
       <c r="Z194" s="2" t="inlineStr"/>
       <c r="AA194" s="2" t="inlineStr"/>
@@ -27484,13 +27448,9 @@
         </is>
       </c>
       <c r="W195" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="X195" s="2" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="X195" s="2" t="inlineStr"/>
       <c r="Y195" s="2" t="inlineStr"/>
       <c r="Z195" s="2" t="inlineStr"/>
       <c r="AA195" s="2" t="inlineStr"/>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2712</v>
+        <v>2661</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>5.07</v>
@@ -857,20 +857,20 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2B→1·3d ← 1→2B·11d ← 2B→1·13d</t>
+          <t>3→2A·7d ← 1B→3·10d ← 3→1B·13d</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -884,20 +884,20 @@
       </c>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="n">
-        <v>87.43000000000001</v>
+        <v>86.94</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>1.44</v>
+        <v>0.36</v>
       </c>
       <c r="AH2" s="2" t="n"/>
       <c r="AI2" s="2" t="n">
-        <v>-27.07</v>
+        <v>-28.15</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>-14.59</v>
+        <v>-15.67</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AL2" s="2" t="n">
         <v>11</v>
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>3164</v>
+        <v>3153.8</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>3393.5</v>
+        <v>3388.4</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>3209.075</v>
+        <v>3206.525</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>3197.883</v>
+        <v>3196.183</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>3348.75</v>
+        <v>3347.73</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>3683.026</v>
+        <v>3682.516</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>2777.552</v>
+        <v>2777.297</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.3269</v>
+        <v>0.2483</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.2303</v>
+        <v>0.1888</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>-0.1579</v>
+        <v>-0.1737</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.0525</v>
+        <v>0.0453</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.8743</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="3">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15250</v>
+        <v>15210</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>38.24</v>
@@ -995,14 +995,14 @@
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>0110111100</t>
+          <t>0110111110</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="W3" s="2" t="n">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>1→2B·11d</t>
+          <t>2A→2C·1d ← 2B→2A·20d</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -1041,23 +1041,23 @@
       </c>
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="n">
-        <v>101.3</v>
+        <v>101.22</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>18.64</v>
+        <v>19.31</v>
       </c>
       <c r="AH3" s="2" t="n"/>
       <c r="AI3" s="2" t="n">
-        <v>-13.41</v>
+        <v>-12.75</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>-0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
@@ -1069,40 +1069,40 @@
         </is>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>16600</v>
+        <v>16592</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>17019</v>
+        <v>17015</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>15578.612</v>
+        <v>15576.612</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>15615.741</v>
+        <v>15614.408</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>15769.445</v>
+        <v>15768.645</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>16277.272</v>
+        <v>16276.872</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>13558.275</v>
+        <v>13558.075</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>3.3681</v>
+        <v>3.3551</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.7406</v>
+        <v>0.7338</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>1.2003</v>
+        <v>1.1976</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>-0.0571</v>
+        <v>-0.0584</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>1.013</v>
+        <v>1.0122</v>
       </c>
     </row>
     <row r="4">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8977</v>
+        <v>9238</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>107.99</v>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0010011000</t>
+          <t>0010111000</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="W4" s="2" t="n">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
@@ -1190,23 +1190,23 @@
       </c>
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="n">
-        <v>137.18</v>
+        <v>138.12</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>31.26</v>
+        <v>36.16</v>
       </c>
       <c r="AH4" s="2" t="n"/>
       <c r="AI4" s="2" t="n">
-        <v>-38.43</v>
+        <v>-33.53</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>-27.59</v>
+        <v>-22.68</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
@@ -1222,40 +1222,40 @@
         </is>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>10683.4</v>
+        <v>10735.6</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>11444.7</v>
+        <v>11470.8</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>10901.736</v>
+        <v>10914.786</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>10697.705</v>
+        <v>10706.405</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>10310.932</v>
+        <v>10316.152</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>10253.252</v>
+        <v>10255.862</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>7418.881</v>
+        <v>7420.186</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>-1.1626</v>
+        <v>-1.0466</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.2763</v>
+        <v>0.3389</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>1.606</v>
+        <v>1.6332</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.7127</v>
+        <v>0.7261</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>1.3718</v>
+        <v>1.3812</v>
       </c>
     </row>
     <row r="5">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5985</v>
+        <v>5971</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2.73</v>
@@ -1308,24 +1308,28 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>1→3B·4d</t>
+          <t>3→4·3d ← 1B→3·7d ← 1A→1B·8d</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1337,23 +1341,23 @@
       </c>
       <c r="AE5" s="2" t="inlineStr"/>
       <c r="AF5" s="2" t="n">
-        <v>28.12</v>
+        <v>28.06</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.35</v>
       </c>
       <c r="AH5" s="2" t="n"/>
       <c r="AI5" s="2" t="n">
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>3.67</v>
+        <v>4.21</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="n">
@@ -1367,40 +1371,40 @@
         </is>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>6087.6</v>
+        <v>6084.8</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>6126.8</v>
+        <v>6125.4</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>5963.856</v>
+        <v>5963.156</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>5910.726</v>
+        <v>5910.259</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>5987.409</v>
+        <v>5987.129</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>6535.908</v>
+        <v>6535.768</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>6254.974</v>
+        <v>6254.904</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>1.0376</v>
+        <v>1.0254</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.7958</v>
+        <v>0.7896</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.0654</v>
+        <v>0.0629</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>-0.3878</v>
+        <v>-0.3889</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.2812</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="6">
@@ -1415,7 +1419,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8209</v>
+        <v>8142</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2.58</v>
@@ -1440,39 +1444,35 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
+          <t>0000000010</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>0000000000</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0000000000</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
       <c r="W6" s="2" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>3A→3B·6d ← 3B→3A·7d ← 1→3B·9d</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="n">
-        <v>47.05</v>
+        <v>46.85</v>
       </c>
       <c r="AG6" s="2" t="n">
         <v>-7.8</v>
@@ -1501,10 +1501,10 @@
         <v>-0.66</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="n">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>8975.6</v>
+        <v>8962.200000000001</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>9058.9</v>
+        <v>9052.200000000001</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>8622.450000000001</v>
+        <v>8619.1</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8516.532999999999</v>
+        <v>8514.299999999999</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>8717.120000000001</v>
+        <v>8715.780000000001</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>9586.606</v>
+        <v>9585.936</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>8812.423000000001</v>
+        <v>8812.088</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>1.8075</v>
+        <v>1.7677</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>1.092</v>
+        <v>1.0714</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>-0.1029</v>
+        <v>-0.1109</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>-0.4139</v>
+        <v>-0.4176</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.4705</v>
+        <v>0.4685</v>
       </c>
     </row>
     <row r="7">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6148</v>
+        <v>6141</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>75.40000000000001</v>
@@ -1601,37 +1601,37 @@
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>1111111101</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1111111101</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>2B→2A·6d</t>
+          <t>2B→2C·10d ← 2C→2B·12d ← 2B→2C·17d</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -1643,20 +1643,20 @@
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="inlineStr"/>
       <c r="AF7" s="2" t="n">
-        <v>39.48</v>
+        <v>39.44</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>8.42</v>
+        <v>9.19</v>
       </c>
       <c r="AH7" s="2" t="n"/>
       <c r="AI7" s="2" t="n">
-        <v>14.3</v>
+        <v>15.07</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>9.67</v>
+        <v>10.44</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AL7" s="2" t="n">
         <v>89</v>
@@ -1673,40 +1673,40 @@
         </is>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>5931.8</v>
+        <v>5930.4</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>5815.7</v>
+        <v>5815</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>5799.718</v>
+        <v>5799.368</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>5752.47</v>
+        <v>5752.237</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>5660.953</v>
+        <v>5660.813</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>5394.747</v>
+        <v>5394.677</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>5322.341</v>
+        <v>5322.306</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.5986</v>
+        <v>0.5923</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>0.7613</v>
+        <v>0.7582</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.2635</v>
+        <v>0.2622</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.3708</v>
+        <v>0.3701</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.3948</v>
+        <v>0.3944</v>
       </c>
     </row>
     <row r="8">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2346.5</v>
+        <v>2343</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>80.33</v>
@@ -1742,37 +1742,37 @@
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>0111101101</t>
+          <t>0111101100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0111101101</t>
+          <t>0111101100</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>3B→3A·1d ← 3A→3B·2d ← 3B→3A·3d</t>
+          <t>2A→2C·8d ← 3→2A·19d</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
@@ -1788,20 +1788,20 @@
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="n">
-        <v>15.27</v>
+        <v>15.22</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>-2.27</v>
+        <v>-1.62</v>
       </c>
       <c r="AH8" s="2" t="n"/>
       <c r="AI8" s="2" t="n">
-        <v>10.72</v>
+        <v>11.38</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>5.02</v>
+        <v>5.68</v>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="AL8" s="2" t="n">
         <v>78</v>
@@ -1818,40 +1818,40 @@
         </is>
       </c>
       <c r="AR8" s="2" t="n">
-        <v>2281</v>
+        <v>2280.3</v>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>2269.45</v>
+        <v>2269.1</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>2288.568</v>
+        <v>2288.393</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>2287.084</v>
+        <v>2286.967</v>
       </c>
       <c r="AV8" s="2" t="n">
-        <v>2285.72</v>
+        <v>2285.65</v>
       </c>
       <c r="AW8" s="2" t="n">
-        <v>2210.362</v>
+        <v>2210.327</v>
       </c>
       <c r="AX8" s="2" t="n">
-        <v>2258.153</v>
+        <v>2258.135</v>
       </c>
       <c r="AY8" s="2" t="n">
-        <v>-0.4557</v>
+        <v>-0.4637</v>
       </c>
       <c r="AZ8" s="2" t="n">
-        <v>0.3532</v>
+        <v>0.3492</v>
       </c>
       <c r="BA8" s="2" t="n">
-        <v>0.1839</v>
+        <v>0.1823</v>
       </c>
       <c r="BB8" s="2" t="n">
-        <v>-0.0004</v>
+        <v>-0.0013</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>0.1527</v>
+        <v>0.1522</v>
       </c>
     </row>
     <row r="9">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6271</v>
+        <v>6254</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2.93</v>
@@ -1908,11 +1908,11 @@
         </is>
       </c>
       <c r="W9" s="2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr"/>
@@ -1929,20 +1929,20 @@
       </c>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="n">
-        <v>-33.46</v>
+        <v>-33.51</v>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>-28.42</v>
+        <v>-28.03</v>
       </c>
       <c r="AH9" s="2" t="n"/>
       <c r="AI9" s="2" t="n">
-        <v>7.51</v>
+        <v>7.91</v>
       </c>
       <c r="AJ9" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AL9" s="2" t="n">
         <v>73</v>
@@ -1967,40 +1967,40 @@
         </is>
       </c>
       <c r="AR9" s="2" t="n">
-        <v>6121.4</v>
+        <v>6118</v>
       </c>
       <c r="AS9" s="2" t="n">
-        <v>6112.4</v>
+        <v>6110.7</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>6293.15</v>
+        <v>6292.3</v>
       </c>
       <c r="AU9" s="2" t="n">
-        <v>6420.9</v>
+        <v>6420.333</v>
       </c>
       <c r="AV9" s="2" t="n">
-        <v>6626.3</v>
+        <v>6625.96</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>7030.675</v>
+        <v>7030.505</v>
       </c>
       <c r="AX9" s="2" t="n">
-        <v>7835.374</v>
+        <v>7835.289</v>
       </c>
       <c r="AY9" s="2" t="n">
-        <v>-1.1172</v>
+        <v>-1.1313</v>
       </c>
       <c r="AZ9" s="2" t="n">
-        <v>-0.7352</v>
+        <v>-0.7421</v>
       </c>
       <c r="BA9" s="2" t="n">
-        <v>-0.742</v>
+        <v>-0.7446</v>
       </c>
       <c r="BB9" s="2" t="n">
-        <v>-0.6424</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="BC9" s="2" t="n">
-        <v>-0.3346</v>
+        <v>-0.3351</v>
       </c>
     </row>
     <row r="10">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2656.5</v>
+        <v>2644.5</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>98.16</v>
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
@@ -2050,25 +2050,25 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0000001100</t>
+          <t>0000001000</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>2A→4B·5d ← 1→2A·15d</t>
+          <t>1B→1A·6d ← 1A→1B·7d ← 1B→1A·10d</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr"/>
@@ -2080,23 +2080,23 @@
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="n">
-        <v>-30.96</v>
+        <v>-31.07</v>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>-20.9</v>
+        <v>-20.61</v>
       </c>
       <c r="AH10" s="2" t="n"/>
       <c r="AI10" s="2" t="n">
-        <v>5.45</v>
+        <v>5.74</v>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>57.7</v>
+        <v>57.4</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
@@ -2114,40 +2114,40 @@
         </is>
       </c>
       <c r="AR10" s="2" t="n">
-        <v>2634</v>
+        <v>2631.6</v>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>2679</v>
+        <v>2677.8</v>
       </c>
       <c r="AT10" s="2" t="n">
-        <v>2750.691</v>
+        <v>2750.091</v>
       </c>
       <c r="AU10" s="2" t="n">
-        <v>2747.625</v>
+        <v>2747.225</v>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>2727.932</v>
+        <v>2727.692</v>
       </c>
       <c r="AW10" s="2" t="n">
-        <v>2665.369</v>
+        <v>2665.249</v>
       </c>
       <c r="AX10" s="2" t="n">
-        <v>2777.904</v>
+        <v>2777.844</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-1.6917</v>
+        <v>-1.7143</v>
       </c>
       <c r="AZ10" s="2" t="n">
-        <v>-0.2505</v>
+        <v>-0.2618</v>
       </c>
       <c r="BA10" s="2" t="n">
-        <v>-0.3275</v>
+        <v>-0.3321</v>
       </c>
       <c r="BB10" s="2" t="n">
-        <v>0.0746</v>
+        <v>0.0723</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>-0.3096</v>
+        <v>-0.3107</v>
       </c>
     </row>
     <row r="11">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12050</v>
+        <v>12025</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6.32</v>
@@ -2204,16 +2204,16 @@
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>1→2B·12d ← 2B→1·13d ← 1→2B·14d</t>
+          <t>2C→2A·13d</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
@@ -2225,23 +2225,23 @@
       <c r="AD11" s="2" t="inlineStr"/>
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="n">
-        <v>31.54</v>
+        <v>31.48</v>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>5.92</v>
+        <v>6.57</v>
       </c>
       <c r="AH11" s="2" t="n"/>
       <c r="AI11" s="2" t="n">
-        <v>12.44</v>
+        <v>13.09</v>
       </c>
       <c r="AJ11" s="2" t="n">
-        <v>5.4</v>
+        <v>6.05</v>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
@@ -2253,40 +2253,40 @@
         </is>
       </c>
       <c r="AR11" s="2" t="n">
-        <v>11716</v>
+        <v>11711</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>11572</v>
+        <v>11569.5</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>11396.75</v>
+        <v>11395.5</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>11568</v>
+        <v>11567.167</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>11787.8</v>
+        <v>11787.3</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>11367.355</v>
+        <v>11367.105</v>
       </c>
       <c r="AX11" s="2" t="n">
-        <v>10742.993</v>
+        <v>10742.868</v>
       </c>
       <c r="AY11" s="2" t="n">
-        <v>1.0615</v>
+        <v>1.05</v>
       </c>
       <c r="AZ11" s="2" t="n">
-        <v>0.1315</v>
+        <v>0.1258</v>
       </c>
       <c r="BA11" s="2" t="n">
-        <v>0.1686</v>
+        <v>0.1664</v>
       </c>
       <c r="BB11" s="2" t="n">
-        <v>0.126</v>
+        <v>0.1248</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>0.3154</v>
+        <v>0.3148</v>
       </c>
     </row>
     <row r="12">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3414</v>
+        <v>3400</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>10.59</v>
@@ -2316,7 +2316,7 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -2339,20 +2339,20 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W12" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>3A→2B·9d ← 3B→3A·18d ← 3A→3B·19d</t>
+          <t>1B→3·14d</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr"/>
@@ -2360,27 +2360,31 @@
       <c r="AB12" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr"/>
       <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>-6.8</v>
+        <v>-6.42</v>
       </c>
       <c r="AH12" s="2" t="n"/>
       <c r="AI12" s="2" t="n">
-        <v>7.3</v>
+        <v>7.68</v>
       </c>
       <c r="AJ12" s="2" t="n">
-        <v>8.43</v>
+        <v>8.81</v>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="n">
@@ -2394,40 +2398,40 @@
         </is>
       </c>
       <c r="AR12" s="2" t="n">
-        <v>3421</v>
+        <v>3418.2</v>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>3406.9</v>
+        <v>3405.5</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>3353.318</v>
+        <v>3352.618</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>3320.713</v>
+        <v>3320.246</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>3330.225</v>
+        <v>3329.945</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>3392.2</v>
+        <v>3392.06</v>
       </c>
       <c r="AX12" s="2" t="n">
-        <v>3234.33</v>
+        <v>3234.26</v>
       </c>
       <c r="AY12" s="2" t="n">
-        <v>0.5845</v>
+        <v>0.5629</v>
       </c>
       <c r="AZ12" s="2" t="n">
-        <v>0.9416</v>
+        <v>0.9306</v>
       </c>
       <c r="BA12" s="2" t="n">
-        <v>-0.4927</v>
+        <v>-0.497</v>
       </c>
       <c r="BB12" s="2" t="n">
-        <v>0.2284</v>
+        <v>0.2263</v>
       </c>
       <c r="BC12" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="13">
@@ -2442,7 +2446,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1358.5</v>
+        <v>1370.5</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>77.91</v>
@@ -2463,39 +2467,35 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
+          <t>0111111100</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0111101100</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0111101100</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>2B→2A·11d</t>
-        </is>
-      </c>
+          <t>2C(减速·顶背离)</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr">
@@ -2507,23 +2507,23 @@
       <c r="AD13" s="2" t="inlineStr"/>
       <c r="AE13" s="2" t="inlineStr"/>
       <c r="AF13" s="2" t="n">
-        <v>30.77</v>
+        <v>31.01</v>
       </c>
       <c r="AG13" s="2" t="n">
-        <v>-0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AH13" s="2" t="n"/>
       <c r="AI13" s="2" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AJ13" s="2" t="n">
-        <v>-6.55</v>
+        <v>-4.86</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>78.7</v>
+        <v>79.2</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
@@ -2537,40 +2537,40 @@
         </is>
       </c>
       <c r="AR13" s="2" t="n">
-        <v>1376.8</v>
+        <v>1379.2</v>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>1370.9</v>
+        <v>1372.1</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>1391.236</v>
+        <v>1391.836</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>1386.133</v>
+        <v>1386.533</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>1348.1</v>
+        <v>1348.34</v>
       </c>
       <c r="AW13" s="2" t="n">
-        <v>1297.788</v>
+        <v>1297.908</v>
       </c>
       <c r="AX13" s="2" t="n">
-        <v>1298.874</v>
+        <v>1298.934</v>
       </c>
       <c r="AY13" s="2" t="n">
-        <v>-0.4157</v>
+        <v>-0.3706</v>
       </c>
       <c r="AZ13" s="2" t="n">
-        <v>-0.3076</v>
+        <v>-0.2853</v>
       </c>
       <c r="BA13" s="2" t="n">
-        <v>0.3167</v>
+        <v>0.326</v>
       </c>
       <c r="BB13" s="2" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>0.3077</v>
+        <v>0.3101</v>
       </c>
     </row>
     <row r="14">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3470</v>
+        <v>3417</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>91.12</v>
@@ -2631,20 +2631,20 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>2B→1·3d ← 1→2B·10d ← 2B→1·15d</t>
+          <t>2C→2B·7d ← 2A→2C·8d ← 2B→2A·20d</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -2658,23 +2658,23 @@
       </c>
       <c r="AE14" s="2" t="inlineStr"/>
       <c r="AF14" s="2" t="n">
-        <v>115.33</v>
+        <v>114.92</v>
       </c>
       <c r="AG14" s="2" t="n">
-        <v>12.52</v>
+        <v>11.72</v>
       </c>
       <c r="AH14" s="2" t="n"/>
       <c r="AI14" s="2" t="n">
-        <v>-23.14</v>
+        <v>-23.94</v>
       </c>
       <c r="AJ14" s="2" t="n">
-        <v>-27.13</v>
+        <v>-27.94</v>
       </c>
       <c r="AK14" s="2" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
@@ -2690,40 +2690,40 @@
         </is>
       </c>
       <c r="AR14" s="2" t="n">
-        <v>3913.2</v>
+        <v>3902.6</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>4142</v>
+        <v>4136.7</v>
       </c>
       <c r="AT14" s="2" t="n">
-        <v>3966.474</v>
+        <v>3963.824</v>
       </c>
       <c r="AU14" s="2" t="n">
-        <v>3931.464</v>
+        <v>3929.698</v>
       </c>
       <c r="AV14" s="2" t="n">
-        <v>3905.91</v>
+        <v>3904.85</v>
       </c>
       <c r="AW14" s="2" t="n">
-        <v>4118.792</v>
+        <v>4118.262</v>
       </c>
       <c r="AX14" s="2" t="n">
-        <v>3417.052</v>
+        <v>3416.787</v>
       </c>
       <c r="AY14" s="2" t="n">
-        <v>0.8176</v>
+        <v>0.75</v>
       </c>
       <c r="AZ14" s="2" t="n">
-        <v>-0.0111</v>
+        <v>-0.0458</v>
       </c>
       <c r="BA14" s="2" t="n">
-        <v>1.195</v>
+        <v>1.1806</v>
       </c>
       <c r="BB14" s="2" t="n">
-        <v>-0.8838</v>
+        <v>-0.8904</v>
       </c>
       <c r="BC14" s="2" t="n">
-        <v>1.1533</v>
+        <v>1.1492</v>
       </c>
     </row>
     <row r="15">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2115.5</v>
+        <v>2115</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>17.52</v>
@@ -2778,20 +2778,20 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W15" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>2B→3B·6d ← 1→2B·7d</t>
+          <t>1B→1A·1d ← 4→1B·2d ← 1B→4·10d</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -2808,20 +2808,20 @@
         <v>37.63</v>
       </c>
       <c r="AG15" s="2" t="n">
-        <v>-9.640000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="AH15" s="2" t="n"/>
       <c r="AI15" s="2" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.75</v>
       </c>
       <c r="AJ15" s="2" t="n">
-        <v>-0.95</v>
+        <v>-0.23</v>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="n">
@@ -2835,37 +2835,37 @@
         </is>
       </c>
       <c r="AR15" s="2" t="n">
-        <v>2296.9</v>
+        <v>2296.8</v>
       </c>
       <c r="AS15" s="2" t="n">
-        <v>2378.9</v>
+        <v>2378.85</v>
       </c>
       <c r="AT15" s="2" t="n">
-        <v>2246.448</v>
+        <v>2246.423</v>
       </c>
       <c r="AU15" s="2" t="n">
-        <v>2207.201</v>
+        <v>2207.184</v>
       </c>
       <c r="AV15" s="2" t="n">
-        <v>2210.917</v>
+        <v>2210.907</v>
       </c>
       <c r="AW15" s="2" t="n">
-        <v>2489.201</v>
+        <v>2489.196</v>
       </c>
       <c r="AX15" s="2" t="n">
-        <v>2338.865</v>
+        <v>2338.863</v>
       </c>
       <c r="AY15" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9756</v>
       </c>
       <c r="AZ15" s="2" t="n">
-        <v>1.0937</v>
+        <v>1.0931</v>
       </c>
       <c r="BA15" s="2" t="n">
-        <v>0.1832</v>
+        <v>0.183</v>
       </c>
       <c r="BB15" s="2" t="n">
-        <v>-0.4868</v>
+        <v>-0.4869</v>
       </c>
       <c r="BC15" s="2" t="n">
         <v>0.3763</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>53490</v>
+        <v>53310</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>6.86</v>
@@ -2927,16 +2927,16 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·19d</t>
+          <t>1A→4·15d</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr"/>
@@ -2950,23 +2950,23 @@
       </c>
       <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="n">
-        <v>21.64</v>
+        <v>21.57</v>
       </c>
       <c r="AG16" s="2" t="n">
-        <v>-22.16</v>
+        <v>-21.79</v>
       </c>
       <c r="AH16" s="2" t="n"/>
       <c r="AI16" s="2" t="n">
-        <v>-4.65</v>
+        <v>-4.27</v>
       </c>
       <c r="AJ16" s="2" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="2" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="n">
@@ -2984,40 +2984,40 @@
         </is>
       </c>
       <c r="AR16" s="2" t="n">
-        <v>58554</v>
+        <v>58518</v>
       </c>
       <c r="AS16" s="2" t="n">
-        <v>60411</v>
+        <v>60393</v>
       </c>
       <c r="AT16" s="2" t="n">
-        <v>56785.181</v>
+        <v>56776.181</v>
       </c>
       <c r="AU16" s="2" t="n">
-        <v>56084.975</v>
+        <v>56078.975</v>
       </c>
       <c r="AV16" s="2" t="n">
-        <v>58222.704</v>
+        <v>58219.104</v>
       </c>
       <c r="AW16" s="2" t="n">
-        <v>65023.81</v>
+        <v>65022.01</v>
       </c>
       <c r="AX16" s="2" t="n">
-        <v>65343.624</v>
+        <v>65342.724</v>
       </c>
       <c r="AY16" s="2" t="n">
-        <v>1.5247</v>
+        <v>1.5088</v>
       </c>
       <c r="AZ16" s="2" t="n">
-        <v>1.0953</v>
+        <v>1.0869</v>
       </c>
       <c r="BA16" s="2" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="BB16" s="2" t="n">
+        <v>-0.2209</v>
+      </c>
+      <c r="BC16" s="2" t="n">
         <v>0.2157</v>
-      </c>
-      <c r="BB16" s="2" t="n">
-        <v>-0.2195</v>
-      </c>
-      <c r="BC16" s="2" t="n">
-        <v>0.2164</v>
       </c>
     </row>
     <row r="17">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4203</v>
+        <v>4162</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>-2.75</v>
@@ -3072,20 +3072,20 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·14d</t>
+          <t>1B→1A·20d</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -3099,23 +3099,23 @@
       </c>
       <c r="AE17" s="2" t="inlineStr"/>
       <c r="AF17" s="2" t="n">
-        <v>19.58</v>
+        <v>19.37</v>
       </c>
       <c r="AG17" s="2" t="n">
-        <v>-21.7</v>
+        <v>-21.83</v>
       </c>
       <c r="AH17" s="2" t="n"/>
       <c r="AI17" s="2" t="n">
-        <v>-5.11</v>
+        <v>-5.23</v>
       </c>
       <c r="AJ17" s="2" t="n">
-        <v>-1.81</v>
+        <v>-1.93</v>
       </c>
       <c r="AK17" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="n">
@@ -3133,40 +3133,40 @@
         </is>
       </c>
       <c r="AR17" s="2" t="n">
-        <v>4590.4</v>
+        <v>4582.2</v>
       </c>
       <c r="AS17" s="2" t="n">
-        <v>4697.4</v>
+        <v>4693.3</v>
       </c>
       <c r="AT17" s="2" t="n">
-        <v>4556.7</v>
+        <v>4554.65</v>
       </c>
       <c r="AU17" s="2" t="n">
-        <v>4517.233</v>
+        <v>4515.867</v>
       </c>
       <c r="AV17" s="2" t="n">
-        <v>4863.26</v>
+        <v>4862.44</v>
       </c>
       <c r="AW17" s="2" t="n">
-        <v>5323.964</v>
+        <v>5323.554</v>
       </c>
       <c r="AX17" s="2" t="n">
-        <v>5098.929</v>
+        <v>5098.724</v>
       </c>
       <c r="AY17" s="2" t="n">
-        <v>0.1866</v>
+        <v>0.1411</v>
       </c>
       <c r="AZ17" s="2" t="n">
-        <v>0.5804</v>
+        <v>0.5568</v>
       </c>
       <c r="BA17" s="2" t="n">
-        <v>-0.7056</v>
+        <v>-0.7143</v>
       </c>
       <c r="BB17" s="2" t="n">
-        <v>-0.3498</v>
+        <v>-0.3538</v>
       </c>
       <c r="BC17" s="2" t="n">
-        <v>0.1958</v>
+        <v>0.1937</v>
       </c>
     </row>
     <row r="18">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4939</v>
+        <v>4912</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>1.22</v>
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>1→3B·18d</t>
+          <t>3→1A·1d ← 1B→3·15d</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -3244,23 +3244,23 @@
       <c r="AD18" s="2" t="inlineStr"/>
       <c r="AE18" s="2" t="inlineStr"/>
       <c r="AF18" s="2" t="n">
-        <v>10.59</v>
+        <v>10.47</v>
       </c>
       <c r="AG18" s="2" t="n">
-        <v>-14.9</v>
+        <v>-14.67</v>
       </c>
       <c r="AH18" s="2" t="n"/>
       <c r="AI18" s="2" t="n">
-        <v>0.86</v>
+        <v>1.09</v>
       </c>
       <c r="AJ18" s="2" t="n">
-        <v>-1.82</v>
+        <v>-1.59</v>
       </c>
       <c r="AK18" s="2" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="n">
@@ -3274,40 +3274,40 @@
         </is>
       </c>
       <c r="AR18" s="2" t="n">
-        <v>5098.8</v>
+        <v>5093.4</v>
       </c>
       <c r="AS18" s="2" t="n">
-        <v>5204.9</v>
+        <v>5202.2</v>
       </c>
       <c r="AT18" s="2" t="n">
-        <v>5177.238</v>
+        <v>5175.888</v>
       </c>
       <c r="AU18" s="2" t="n">
-        <v>5197.42</v>
+        <v>5196.52</v>
       </c>
       <c r="AV18" s="2" t="n">
-        <v>5417.485</v>
+        <v>5416.945</v>
       </c>
       <c r="AW18" s="2" t="n">
-        <v>5633.275</v>
+        <v>5633.005</v>
       </c>
       <c r="AX18" s="2" t="n">
-        <v>5515.481</v>
+        <v>5515.346</v>
       </c>
       <c r="AY18" s="2" t="n">
-        <v>-0.4727</v>
+        <v>-0.4994</v>
       </c>
       <c r="AZ18" s="2" t="n">
-        <v>-0.0496</v>
+        <v>-0.0631</v>
       </c>
       <c r="BA18" s="2" t="n">
-        <v>-0.2822</v>
+        <v>-0.2873</v>
       </c>
       <c r="BB18" s="2" t="n">
-        <v>-0.4844</v>
+        <v>-0.4869</v>
       </c>
       <c r="BC18" s="2" t="n">
-        <v>0.1059</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="19">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>14075</v>
+        <v>14055</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>32.35</v>
@@ -3366,16 +3366,16 @@
         </is>
       </c>
       <c r="W19" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>1→2B·15d</t>
+          <t>3→2A·8d ← 2A→3·16d</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -3391,20 +3391,20 @@
       </c>
       <c r="AE19" s="2" t="inlineStr"/>
       <c r="AF19" s="2" t="n">
-        <v>35.03</v>
+        <v>34.98</v>
       </c>
       <c r="AG19" s="2" t="n">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="AH19" s="2" t="n"/>
       <c r="AI19" s="2" t="n">
-        <v>0.03</v>
+        <v>0.72</v>
       </c>
       <c r="AJ19" s="2" t="n">
-        <v>10.03</v>
+        <v>10.73</v>
       </c>
       <c r="AK19" s="2" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="AL19" s="2" t="n">
         <v>25</v>
@@ -3419,40 +3419,40 @@
         </is>
       </c>
       <c r="AR19" s="2" t="n">
-        <v>14676</v>
+        <v>14672</v>
       </c>
       <c r="AS19" s="2" t="n">
-        <v>14836</v>
+        <v>14834</v>
       </c>
       <c r="AT19" s="2" t="n">
-        <v>13987.673</v>
+        <v>13986.673</v>
       </c>
       <c r="AU19" s="2" t="n">
-        <v>13665.627</v>
+        <v>13664.961</v>
       </c>
       <c r="AV19" s="2" t="n">
-        <v>13873.726</v>
+        <v>13873.326</v>
       </c>
       <c r="AW19" s="2" t="n">
-        <v>13879.384</v>
+        <v>13879.184</v>
       </c>
       <c r="AX19" s="2" t="n">
-        <v>12859.629</v>
+        <v>12859.529</v>
       </c>
       <c r="AY19" s="2" t="n">
-        <v>1.9576</v>
+        <v>1.9504</v>
       </c>
       <c r="AZ19" s="2" t="n">
-        <v>1.7515</v>
+        <v>1.7476</v>
       </c>
       <c r="BA19" s="2" t="n">
-        <v>0.8226</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="BB19" s="2" t="n">
-        <v>-0.0021</v>
+        <v>-0.0029</v>
       </c>
       <c r="BC19" s="2" t="n">
-        <v>0.3503</v>
+        <v>0.3498</v>
       </c>
     </row>
     <row r="20">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4341</v>
+        <v>4291</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>3.34</v>
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·17d</t>
+          <t>1A→4·13d</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
@@ -3536,23 +3536,23 @@
       </c>
       <c r="AE20" s="2" t="inlineStr"/>
       <c r="AF20" s="2" t="n">
-        <v>-3.37</v>
+        <v>-3.62</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>-22.73</v>
+        <v>-22.99</v>
       </c>
       <c r="AH20" s="2" t="n"/>
       <c r="AI20" s="2" t="n">
-        <v>-4.33</v>
+        <v>-4.59</v>
       </c>
       <c r="AJ20" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AK20" s="2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="n">
@@ -3566,40 +3566,40 @@
         </is>
       </c>
       <c r="AR20" s="2" t="n">
-        <v>4693</v>
+        <v>4683</v>
       </c>
       <c r="AS20" s="2" t="n">
-        <v>4786.3</v>
+        <v>4781.3</v>
       </c>
       <c r="AT20" s="2" t="n">
-        <v>4605.05</v>
+        <v>4602.55</v>
       </c>
       <c r="AU20" s="2" t="n">
-        <v>4582.633</v>
+        <v>4580.967</v>
       </c>
       <c r="AV20" s="2" t="n">
-        <v>4789.166</v>
+        <v>4788.166</v>
       </c>
       <c r="AW20" s="2" t="n">
-        <v>5616.622</v>
+        <v>5616.122</v>
       </c>
       <c r="AX20" s="2" t="n">
-        <v>5325.459</v>
+        <v>5325.209</v>
       </c>
       <c r="AY20" s="2" t="n">
-        <v>0.9559</v>
+        <v>0.9006</v>
       </c>
       <c r="AZ20" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.6069</v>
       </c>
       <c r="BA20" s="2" t="n">
-        <v>-0.1427</v>
+        <v>-0.1535</v>
       </c>
       <c r="BB20" s="2" t="n">
-        <v>-0.8542</v>
+        <v>-0.8587</v>
       </c>
       <c r="BC20" s="2" t="n">
-        <v>-0.0337</v>
+        <v>-0.0362</v>
       </c>
     </row>
     <row r="21">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1847</v>
+        <v>1816</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>91.51000000000001</v>
@@ -3668,20 +3668,20 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>1→3B·5d ← 2B→1·13d</t>
+          <t>1B→1A·5d ← 2A→1B·10d ← 2C→2A·12d</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr"/>
@@ -3693,23 +3693,23 @@
       <c r="AD21" s="2" t="inlineStr"/>
       <c r="AE21" s="2" t="inlineStr"/>
       <c r="AF21" s="2" t="n">
-        <v>-2.78</v>
+        <v>-3.11</v>
       </c>
       <c r="AG21" s="2" t="n">
-        <v>-30.84</v>
+        <v>-31.44</v>
       </c>
       <c r="AH21" s="2" t="n"/>
       <c r="AI21" s="2" t="n">
-        <v>-4.92</v>
+        <v>-5.52</v>
       </c>
       <c r="AJ21" s="2" t="n">
-        <v>-28.18</v>
+        <v>-28.78</v>
       </c>
       <c r="AK21" s="2" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
@@ -3725,40 +3725,40 @@
         </is>
       </c>
       <c r="AR21" s="2" t="n">
-        <v>1962.8</v>
+        <v>1956.6</v>
       </c>
       <c r="AS21" s="2" t="n">
-        <v>2054.1</v>
+        <v>2051</v>
       </c>
       <c r="AT21" s="2" t="n">
-        <v>2333.55</v>
+        <v>2332</v>
       </c>
       <c r="AU21" s="2" t="n">
-        <v>2431.233</v>
+        <v>2430.2</v>
       </c>
       <c r="AV21" s="2" t="n">
-        <v>2534.68</v>
+        <v>2534.06</v>
       </c>
       <c r="AW21" s="2" t="n">
-        <v>2602.91</v>
+        <v>2602.6</v>
       </c>
       <c r="AX21" s="2" t="n">
-        <v>2441.42</v>
+        <v>2441.265</v>
       </c>
       <c r="AY21" s="2" t="n">
-        <v>-6.2242</v>
+        <v>-6.2933</v>
       </c>
       <c r="AZ21" s="2" t="n">
-        <v>-3.8569</v>
+        <v>-3.8889</v>
       </c>
       <c r="BA21" s="2" t="n">
-        <v>-1.1645</v>
+        <v>-1.1769</v>
       </c>
       <c r="BB21" s="2" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6408</v>
       </c>
       <c r="BC21" s="2" t="n">
-        <v>-0.0278</v>
+        <v>-0.0311</v>
       </c>
     </row>
     <row r="22">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2937.5</v>
+        <v>2917</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>80.2</v>
@@ -3817,16 +3817,16 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 1→2B·15d</t>
+          <t>3→2A·6d ← 1B→3·10d ← 2A→1B·20d</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -3840,20 +3840,20 @@
       </c>
       <c r="AE22" s="2" t="inlineStr"/>
       <c r="AF22" s="2" t="n">
-        <v>43.39</v>
+        <v>43.2</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.48</v>
       </c>
       <c r="AH22" s="2" t="n"/>
       <c r="AI22" s="2" t="n">
-        <v>-11.32</v>
+        <v>-11.2</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>3.57</v>
+        <v>3.69</v>
       </c>
       <c r="AK22" s="2" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="AL22" s="2" t="n">
         <v>13</v>
@@ -3870,40 +3870,40 @@
         </is>
       </c>
       <c r="AR22" s="2" t="n">
-        <v>3168.7</v>
+        <v>3164.6</v>
       </c>
       <c r="AS22" s="2" t="n">
-        <v>3284.65</v>
+        <v>3282.6</v>
       </c>
       <c r="AT22" s="2" t="n">
-        <v>3082.546</v>
+        <v>3081.521</v>
       </c>
       <c r="AU22" s="2" t="n">
-        <v>3015.42</v>
+        <v>3014.736</v>
       </c>
       <c r="AV22" s="2" t="n">
-        <v>3034.085</v>
+        <v>3033.675</v>
       </c>
       <c r="AW22" s="2" t="n">
-        <v>3273.971</v>
+        <v>3273.766</v>
       </c>
       <c r="AX22" s="2" t="n">
-        <v>2768.956</v>
+        <v>2768.853</v>
       </c>
       <c r="AY22" s="2" t="n">
-        <v>1.8292</v>
+        <v>1.7956</v>
       </c>
       <c r="AZ22" s="2" t="n">
-        <v>1.486</v>
+        <v>1.4682</v>
       </c>
       <c r="BA22" s="2" t="n">
-        <v>0.4926</v>
+        <v>0.4856</v>
       </c>
       <c r="BB22" s="2" t="n">
-        <v>0.1551</v>
+        <v>0.1519</v>
       </c>
       <c r="BC22" s="2" t="n">
-        <v>0.4339</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="23">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>35390</v>
+        <v>34220</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>98.61</v>
@@ -3941,19 +3941,19 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>0110111110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0110111001</t>
+          <t>0110111000</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="W23" s="2" t="n">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·1d ← 2B→2C·10d</t>
+          <t>2C→2B·1d ← 2B→2C·20d</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr"/>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="AE23" s="2" t="inlineStr"/>
       <c r="AF23" s="2" t="n">
-        <v>92.22</v>
+        <v>91.12</v>
       </c>
       <c r="AG23" s="2" t="n">
-        <v>22.73</v>
+        <v>19.66</v>
       </c>
       <c r="AH23" s="2" t="n"/>
       <c r="AI23" s="2" t="n">
-        <v>-11.49</v>
+        <v>-14.56</v>
       </c>
       <c r="AJ23" s="2" t="n">
-        <v>6.27</v>
+        <v>3.21</v>
       </c>
       <c r="AK23" s="2" t="n">
-        <v>86.5</v>
+        <v>85.5</v>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AM23" s="2" t="inlineStr">
         <is>
@@ -4016,47 +4016,51 @@
       <c r="AO23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AP23" s="2" t="inlineStr"/>
+      <c r="AP23" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ23" s="2" t="inlineStr">
         <is>
           <t>柱≥0</t>
         </is>
       </c>
       <c r="AR23" s="2" t="n">
-        <v>39742</v>
+        <v>39508</v>
       </c>
       <c r="AS23" s="2" t="n">
-        <v>39839</v>
+        <v>39722</v>
       </c>
       <c r="AT23" s="2" t="n">
-        <v>36079</v>
+        <v>36020.5</v>
       </c>
       <c r="AU23" s="2" t="n">
-        <v>35110.667</v>
+        <v>35071.667</v>
       </c>
       <c r="AV23" s="2" t="n">
-        <v>34863.2</v>
+        <v>34839.8</v>
       </c>
       <c r="AW23" s="2" t="n">
-        <v>31817.95</v>
+        <v>31806.25</v>
       </c>
       <c r="AX23" s="2" t="n">
-        <v>28191.079</v>
+        <v>28185.229</v>
       </c>
       <c r="AY23" s="2" t="n">
-        <v>4.1965</v>
+        <v>4.0315</v>
       </c>
       <c r="AZ23" s="2" t="n">
-        <v>2.4091</v>
+        <v>2.3209</v>
       </c>
       <c r="BA23" s="2" t="n">
-        <v>1.9415</v>
+        <v>1.9053</v>
       </c>
       <c r="BB23" s="2" t="n">
-        <v>1.1129</v>
+        <v>1.0934</v>
       </c>
       <c r="BC23" s="2" t="n">
-        <v>0.9222</v>
+        <v>0.9112</v>
       </c>
     </row>
     <row r="24">
@@ -4071,7 +4075,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>77800</v>
+        <v>78310</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>31.72</v>
@@ -4115,14 +4119,18 @@
         </is>
       </c>
       <c r="W24" s="2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+          <t>2C(减速·顶背离)</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·3d ← 2C→2A·18d</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="inlineStr"/>
@@ -4134,23 +4142,23 @@
       </c>
       <c r="AE24" s="2" t="inlineStr"/>
       <c r="AF24" s="2" t="n">
-        <v>45.83</v>
+        <v>46.03</v>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>5.14</v>
+        <v>6.7</v>
       </c>
       <c r="AH24" s="2" t="n"/>
       <c r="AI24" s="2" t="n">
-        <v>3.07</v>
+        <v>4.62</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>1.92</v>
+        <v>3.48</v>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
@@ -4162,40 +4170,40 @@
         </is>
       </c>
       <c r="AR24" s="2" t="n">
-        <v>79688</v>
+        <v>79790</v>
       </c>
       <c r="AS24" s="2" t="n">
-        <v>80464</v>
+        <v>80515</v>
       </c>
       <c r="AT24" s="2" t="n">
-        <v>78967.28200000001</v>
+        <v>78992.78200000001</v>
       </c>
       <c r="AU24" s="2" t="n">
-        <v>78686.49099999999</v>
+        <v>78703.49099999999</v>
       </c>
       <c r="AV24" s="2" t="n">
-        <v>80491.87699999999</v>
+        <v>80502.077</v>
       </c>
       <c r="AW24" s="2" t="n">
-        <v>78362.234</v>
+        <v>78367.334</v>
       </c>
       <c r="AX24" s="2" t="n">
-        <v>69857.92</v>
+        <v>69860.47</v>
       </c>
       <c r="AY24" s="2" t="n">
-        <v>0.2018</v>
+        <v>0.2349</v>
       </c>
       <c r="AZ24" s="2" t="n">
-        <v>0.5121</v>
+        <v>0.5291</v>
       </c>
       <c r="BA24" s="2" t="n">
-        <v>0.342</v>
+        <v>0.3486</v>
       </c>
       <c r="BB24" s="2" t="n">
-        <v>0.137</v>
+        <v>0.1403</v>
       </c>
       <c r="BC24" s="2" t="n">
-        <v>0.4583</v>
+        <v>0.4603</v>
       </c>
     </row>
     <row r="25">
@@ -4210,7 +4218,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>39860</v>
+        <v>39430</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>111</v>
@@ -4235,19 +4243,19 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>0111000100</t>
+          <t>0111000110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0111000100</t>
+          <t>0111000110</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -4256,16 +4264,16 @@
         </is>
       </c>
       <c r="W25" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 3A→2B·10d ← 3B→3A·15d</t>
+          <t>3→2A·7d ← 1B→3·16d</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -4281,23 +4289,23 @@
       </c>
       <c r="AE25" s="2" t="inlineStr"/>
       <c r="AF25" s="2" t="n">
-        <v>50.63</v>
+        <v>50.34</v>
       </c>
       <c r="AG25" s="2" t="n">
-        <v>0.93</v>
+        <v>0.66</v>
       </c>
       <c r="AH25" s="2" t="n"/>
       <c r="AI25" s="2" t="n">
-        <v>-9.42</v>
+        <v>-9.68</v>
       </c>
       <c r="AJ25" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AK25" s="2" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
@@ -4309,40 +4317,40 @@
         </is>
       </c>
       <c r="AR25" s="2" t="n">
-        <v>45298</v>
+        <v>45212</v>
       </c>
       <c r="AS25" s="2" t="n">
-        <v>45777</v>
+        <v>45734</v>
       </c>
       <c r="AT25" s="2" t="n">
-        <v>42073</v>
+        <v>42051.5</v>
       </c>
       <c r="AU25" s="2" t="n">
-        <v>39469</v>
+        <v>39454.667</v>
       </c>
       <c r="AV25" s="2" t="n">
-        <v>38950.2</v>
+        <v>38941.6</v>
       </c>
       <c r="AW25" s="2" t="n">
-        <v>41728.476</v>
+        <v>41724.176</v>
       </c>
       <c r="AX25" s="2" t="n">
-        <v>38589.673</v>
+        <v>38587.523</v>
       </c>
       <c r="AY25" s="2" t="n">
-        <v>2.8354</v>
+        <v>2.7839</v>
       </c>
       <c r="AZ25" s="2" t="n">
-        <v>3.2725</v>
+        <v>3.2443</v>
       </c>
       <c r="BA25" s="2" t="n">
-        <v>0.9342</v>
+        <v>0.9225</v>
       </c>
       <c r="BB25" s="2" t="n">
-        <v>0.4825</v>
+        <v>0.4771</v>
       </c>
       <c r="BC25" s="2" t="n">
-        <v>0.5063</v>
+        <v>0.5034</v>
       </c>
     </row>
     <row r="26">
@@ -4357,7 +4365,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10020</v>
+        <v>9867</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>8.98</v>
@@ -4378,14 +4386,14 @@
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S26" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>0111110000</t>
+          <t>0111010000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -4399,21 +4407,21 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>1→2B·10d</t>
+          <t>1B→2A·3d</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
@@ -4426,23 +4434,23 @@
       <c r="AD26" s="2" t="inlineStr"/>
       <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="n">
-        <v>113.16</v>
+        <v>112.67</v>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>28.61</v>
+        <v>27.69</v>
       </c>
       <c r="AH26" s="2" t="n"/>
       <c r="AI26" s="2" t="n">
-        <v>-9.67</v>
+        <v>-10.58</v>
       </c>
       <c r="AJ26" s="2" t="n">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="AK26" s="2" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="n">
@@ -4456,40 +4464,40 @@
         </is>
       </c>
       <c r="AR26" s="2" t="n">
-        <v>10734</v>
+        <v>10703.4</v>
       </c>
       <c r="AS26" s="2" t="n">
-        <v>10695</v>
+        <v>10679.7</v>
       </c>
       <c r="AT26" s="2" t="n">
-        <v>9893.427</v>
+        <v>9885.777</v>
       </c>
       <c r="AU26" s="2" t="n">
-        <v>9649.164000000001</v>
+        <v>9644.064</v>
       </c>
       <c r="AV26" s="2" t="n">
-        <v>9740.129999999999</v>
+        <v>9737.07</v>
       </c>
       <c r="AW26" s="2" t="n">
-        <v>12387.577</v>
+        <v>12386.047</v>
       </c>
       <c r="AX26" s="2" t="n">
-        <v>8443.915999999999</v>
+        <v>8443.151</v>
       </c>
       <c r="AY26" s="2" t="n">
-        <v>4.304</v>
+        <v>4.2235</v>
       </c>
       <c r="AZ26" s="2" t="n">
-        <v>2.0333</v>
+        <v>1.9915</v>
       </c>
       <c r="BA26" s="2" t="n">
-        <v>0.3179</v>
+        <v>0.3015</v>
       </c>
       <c r="BB26" s="2" t="n">
-        <v>0.7389</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="BC26" s="2" t="n">
-        <v>1.1316</v>
+        <v>1.1267</v>
       </c>
     </row>
     <row r="27">
@@ -4504,7 +4512,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6805</v>
+        <v>6736</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>104.12</v>
@@ -4546,16 +4554,16 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2C(顶背离)</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d</t>
+          <t>2A→2C·7d</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
@@ -4567,23 +4575,23 @@
       <c r="AD27" s="2" t="inlineStr"/>
       <c r="AE27" s="2" t="inlineStr"/>
       <c r="AF27" s="2" t="n">
-        <v>93.19</v>
+        <v>92.89</v>
       </c>
       <c r="AG27" s="2" t="n">
-        <v>15.6</v>
+        <v>15.37</v>
       </c>
       <c r="AH27" s="2" t="n"/>
       <c r="AI27" s="2" t="n">
-        <v>-22.65</v>
+        <v>-22.87</v>
       </c>
       <c r="AJ27" s="2" t="n">
-        <v>-17.55</v>
+        <v>-17.78</v>
       </c>
       <c r="AK27" s="2" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AL27" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="n">
@@ -4601,40 +4609,40 @@
         </is>
       </c>
       <c r="AR27" s="2" t="n">
-        <v>7625</v>
+        <v>7611.2</v>
       </c>
       <c r="AS27" s="2" t="n">
-        <v>8136.2</v>
+        <v>8129.3</v>
       </c>
       <c r="AT27" s="2" t="n">
-        <v>7913.81</v>
+        <v>7910.36</v>
       </c>
       <c r="AU27" s="2" t="n">
-        <v>7670.058</v>
+        <v>7667.758</v>
       </c>
       <c r="AV27" s="2" t="n">
-        <v>7571.114</v>
+        <v>7569.734</v>
       </c>
       <c r="AW27" s="2" t="n">
-        <v>8476.564</v>
+        <v>8475.874</v>
       </c>
       <c r="AX27" s="2" t="n">
-        <v>6186.233</v>
+        <v>6185.888</v>
       </c>
       <c r="AY27" s="2" t="n">
-        <v>-0.9781</v>
+        <v>-1.0214</v>
       </c>
       <c r="AZ27" s="2" t="n">
-        <v>0.5435</v>
+        <v>0.5206</v>
       </c>
       <c r="BA27" s="2" t="n">
-        <v>0.286</v>
+        <v>0.2764</v>
       </c>
       <c r="BB27" s="2" t="n">
-        <v>0.4489</v>
+        <v>0.4447</v>
       </c>
       <c r="BC27" s="2" t="n">
-        <v>0.9319</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -4649,7 +4657,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3575</v>
+        <v>3593</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>95.42</v>
@@ -4703,16 +4711,16 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>4B→2A·18d</t>
+          <t>2A→2B·1d ← 3→2A·12d ← 1B→3·14d</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr"/>
@@ -4728,23 +4736,23 @@
       <c r="AD28" s="2" t="inlineStr"/>
       <c r="AE28" s="2" t="inlineStr"/>
       <c r="AF28" s="2" t="n">
-        <v>-5.03</v>
+        <v>-4.89</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>-7.01</v>
+        <v>-5.77</v>
       </c>
       <c r="AH28" s="2" t="n"/>
       <c r="AI28" s="2" t="n">
-        <v>8.09</v>
+        <v>9.33</v>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>11.82</v>
+        <v>13.05</v>
       </c>
       <c r="AK28" s="2" t="n">
-        <v>91.8</v>
+        <v>92.3</v>
       </c>
       <c r="AL28" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AM28" s="2" t="inlineStr">
         <is>
@@ -4762,40 +4770,40 @@
         </is>
       </c>
       <c r="AR28" s="2" t="n">
-        <v>3598.8</v>
+        <v>3602.4</v>
       </c>
       <c r="AS28" s="2" t="n">
-        <v>3573</v>
+        <v>3574.8</v>
       </c>
       <c r="AT28" s="2" t="n">
-        <v>3478.969</v>
+        <v>3479.869</v>
       </c>
       <c r="AU28" s="2" t="n">
-        <v>3429.038</v>
+        <v>3429.638</v>
       </c>
       <c r="AV28" s="2" t="n">
-        <v>3423.85</v>
+        <v>3424.21</v>
       </c>
       <c r="AW28" s="2" t="n">
-        <v>3285.424</v>
+        <v>3285.604</v>
       </c>
       <c r="AX28" s="2" t="n">
-        <v>3313.036</v>
+        <v>3313.126</v>
       </c>
       <c r="AY28" s="2" t="n">
-        <v>0.852</v>
+        <v>0.8786</v>
       </c>
       <c r="AZ28" s="2" t="n">
-        <v>1.5457</v>
+        <v>1.5595</v>
       </c>
       <c r="BA28" s="2" t="n">
-        <v>0.2878</v>
+        <v>0.2933</v>
       </c>
       <c r="BB28" s="2" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5115</v>
       </c>
       <c r="BC28" s="2" t="n">
-        <v>-0.0503</v>
+        <v>-0.0489</v>
       </c>
     </row>
     <row r="29">
@@ -4810,7 +4818,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13760</v>
+        <v>13585</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>107.6</v>
@@ -4835,14 +4843,14 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S29" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>0111111100</t>
+          <t>0110111100</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -4856,7 +4864,7 @@
         </is>
       </c>
       <c r="W29" s="2" t="n">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
@@ -4865,7 +4873,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>1→2B·16d ← 2B→1·17d ← 1→2B·18d</t>
+          <t>2C→2B·3d ← 2B→2C·4d ← 2A→2B·6d</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr"/>
@@ -4881,23 +4889,23 @@
       </c>
       <c r="AE29" s="2" t="inlineStr"/>
       <c r="AF29" s="2" t="n">
-        <v>97.56</v>
+        <v>97.17</v>
       </c>
       <c r="AG29" s="2" t="n">
-        <v>16.7</v>
+        <v>16.17</v>
       </c>
       <c r="AH29" s="2" t="n"/>
       <c r="AI29" s="2" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.98</v>
       </c>
       <c r="AJ29" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="AK29" s="2" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="n">
@@ -4915,40 +4923,40 @@
         </is>
       </c>
       <c r="AR29" s="2" t="n">
-        <v>15377</v>
+        <v>15342</v>
       </c>
       <c r="AS29" s="2" t="n">
-        <v>15587</v>
+        <v>15569.5</v>
       </c>
       <c r="AT29" s="2" t="n">
-        <v>14376.857</v>
+        <v>14368.107</v>
       </c>
       <c r="AU29" s="2" t="n">
-        <v>13942.759</v>
+        <v>13936.926</v>
       </c>
       <c r="AV29" s="2" t="n">
-        <v>13707.995</v>
+        <v>13704.495</v>
       </c>
       <c r="AW29" s="2" t="n">
-        <v>14349.642</v>
+        <v>14347.892</v>
       </c>
       <c r="AX29" s="2" t="n">
-        <v>12006.798</v>
+        <v>12005.923</v>
       </c>
       <c r="AY29" s="2" t="n">
-        <v>2.4419</v>
+        <v>2.3808</v>
       </c>
       <c r="AZ29" s="2" t="n">
-        <v>2.2774</v>
+        <v>2.2444</v>
       </c>
       <c r="BA29" s="2" t="n">
-        <v>0.5795</v>
+        <v>0.5661</v>
       </c>
       <c r="BB29" s="2" t="n">
-        <v>0.796</v>
+        <v>0.7895</v>
       </c>
       <c r="BC29" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="30">
@@ -4963,7 +4971,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>24990</v>
+        <v>24895</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>3.87</v>
@@ -5007,16 +5015,16 @@
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>4A→4B·2d ← 1A→4A·15d ← 3B→1A·16d</t>
+          <t>1A→4·20d</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr"/>
@@ -5030,23 +5038,23 @@
         <v>1</v>
       </c>
       <c r="AF30" s="2" t="n">
-        <v>7.37</v>
+        <v>7.27</v>
       </c>
       <c r="AG30" s="2" t="n">
-        <v>-12.47</v>
+        <v>-12.08</v>
       </c>
       <c r="AH30" s="2" t="n"/>
       <c r="AI30" s="2" t="n">
-        <v>6.24</v>
+        <v>6.62</v>
       </c>
       <c r="AJ30" s="2" t="n">
-        <v>8.4</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AK30" s="2" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="n">
@@ -5060,40 +5068,40 @@
         </is>
       </c>
       <c r="AR30" s="2" t="n">
-        <v>25157</v>
+        <v>25138</v>
       </c>
       <c r="AS30" s="2" t="n">
-        <v>24929</v>
+        <v>24919.5</v>
       </c>
       <c r="AT30" s="2" t="n">
-        <v>23936</v>
+        <v>23931.25</v>
       </c>
       <c r="AU30" s="2" t="n">
-        <v>23924.5</v>
+        <v>23921.333</v>
       </c>
       <c r="AV30" s="2" t="n">
-        <v>24560.8</v>
+        <v>24558.9</v>
       </c>
       <c r="AW30" s="2" t="n">
-        <v>25212.35</v>
+        <v>25211.4</v>
       </c>
       <c r="AX30" s="2" t="n">
-        <v>26063.3</v>
+        <v>26062.825</v>
       </c>
       <c r="AY30" s="2" t="n">
-        <v>1.8949</v>
+        <v>1.8744</v>
       </c>
       <c r="AZ30" s="2" t="n">
-        <v>1.0279</v>
+        <v>1.0174</v>
       </c>
       <c r="BA30" s="2" t="n">
-        <v>0.2216</v>
+        <v>0.2175</v>
       </c>
       <c r="BB30" s="2" t="n">
-        <v>-0.2261</v>
+        <v>-0.228</v>
       </c>
       <c r="BC30" s="2" t="n">
-        <v>0.0737</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="31">
@@ -5108,7 +5116,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2232.5</v>
+        <v>2230.5</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>41.71</v>
@@ -5152,16 +5160,16 @@
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>3B→1·2d ← 3A→3B·5d ← 3B→3A·10d</t>
+          <t>3→1B·1d ← 2A→3·9d ← 2C→2A·13d</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -5173,23 +5181,23 @@
       <c r="AD31" s="2" t="inlineStr"/>
       <c r="AE31" s="2" t="inlineStr"/>
       <c r="AF31" s="2" t="n">
-        <v>-4.25</v>
+        <v>-4.27</v>
       </c>
       <c r="AG31" s="2" t="n">
-        <v>-12.88</v>
+        <v>-12.25</v>
       </c>
       <c r="AH31" s="2" t="n"/>
       <c r="AI31" s="2" t="n">
-        <v>-1.24</v>
+        <v>-0.6</v>
       </c>
       <c r="AJ31" s="2" t="n">
-        <v>-3.84</v>
+        <v>-3.2</v>
       </c>
       <c r="AK31" s="2" t="n">
         <v>43.3</v>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
@@ -5201,40 +5209,40 @@
         </is>
       </c>
       <c r="AR31" s="2" t="n">
-        <v>2332.1</v>
+        <v>2331.7</v>
       </c>
       <c r="AS31" s="2" t="n">
-        <v>2382.2</v>
+        <v>2382</v>
       </c>
       <c r="AT31" s="2" t="n">
-        <v>2363.81</v>
+        <v>2363.71</v>
       </c>
       <c r="AU31" s="2" t="n">
-        <v>2402.767</v>
+        <v>2402.7</v>
       </c>
       <c r="AV31" s="2" t="n">
-        <v>2420.239</v>
+        <v>2420.199</v>
       </c>
       <c r="AW31" s="2" t="n">
-        <v>2381.204</v>
+        <v>2381.184</v>
       </c>
       <c r="AX31" s="2" t="n">
-        <v>2364.928</v>
+        <v>2364.918</v>
       </c>
       <c r="AY31" s="2" t="n">
-        <v>-0.6352</v>
+        <v>-0.6395</v>
       </c>
       <c r="AZ31" s="2" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.8232</v>
       </c>
       <c r="BA31" s="2" t="n">
-        <v>0.2221</v>
+        <v>0.2212</v>
       </c>
       <c r="BB31" s="2" t="n">
-        <v>0.0517</v>
+        <v>0.0513</v>
       </c>
       <c r="BC31" s="2" t="n">
-        <v>-0.0425</v>
+        <v>-0.0427</v>
       </c>
     </row>
     <row r="32">
@@ -5249,7 +5257,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2225.5</v>
+        <v>2215.5</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>92</v>
@@ -5291,16 +5299,16 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>2B→2A·4d ← 2A→2B·20d</t>
+          <t>2B→2C·3d ← 2A→2B·14d</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr"/>
@@ -5312,23 +5320,23 @@
       </c>
       <c r="AE32" s="2" t="inlineStr"/>
       <c r="AF32" s="2" t="n">
-        <v>20.17</v>
+        <v>20.04</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" s="2" t="n"/>
       <c r="AI32" s="2" t="n">
-        <v>10.4</v>
+        <v>10.77</v>
       </c>
       <c r="AJ32" s="2" t="n">
-        <v>-2.45</v>
+        <v>-2.08</v>
       </c>
       <c r="AK32" s="2" t="n">
-        <v>77.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
@@ -5342,40 +5350,40 @@
         </is>
       </c>
       <c r="AR32" s="2" t="n">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="AS32" s="2" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="AT32" s="2" t="n">
-        <v>2219.623</v>
+        <v>2219.123</v>
       </c>
       <c r="AU32" s="2" t="n">
-        <v>2213.986</v>
+        <v>2213.653</v>
       </c>
       <c r="AV32" s="2" t="n">
-        <v>2141.456</v>
+        <v>2141.256</v>
       </c>
       <c r="AW32" s="2" t="n">
-        <v>2009.656</v>
+        <v>2009.556</v>
       </c>
       <c r="AX32" s="2" t="n">
-        <v>2006.582</v>
+        <v>2006.532</v>
       </c>
       <c r="AY32" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.0066</v>
       </c>
       <c r="AZ32" s="2" t="n">
-        <v>-0.3891</v>
+        <v>-0.4007</v>
       </c>
       <c r="BA32" s="2" t="n">
-        <v>0.5209</v>
+        <v>0.516</v>
       </c>
       <c r="BB32" s="2" t="n">
-        <v>0.2751</v>
+        <v>0.2725</v>
       </c>
       <c r="BC32" s="2" t="n">
-        <v>0.2017</v>
+        <v>0.2004</v>
       </c>
     </row>
     <row r="33">
@@ -5390,7 +5398,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4811</v>
+        <v>4805</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>4.42</v>
@@ -5428,28 +5436,24 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·10d</t>
+          <t>3→1A·4d</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr"/>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>10d</t>
-        </is>
-      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="n">
         <v>1</v>
       </c>
@@ -5459,23 +5463,23 @@
       <c r="AD33" s="2" t="inlineStr"/>
       <c r="AE33" s="2" t="inlineStr"/>
       <c r="AF33" s="2" t="n">
-        <v>10.4</v>
+        <v>10.37</v>
       </c>
       <c r="AG33" s="2" t="n">
-        <v>-11.43</v>
+        <v>-10.82</v>
       </c>
       <c r="AH33" s="2" t="n"/>
       <c r="AI33" s="2" t="n">
-        <v>7.07</v>
+        <v>7.68</v>
       </c>
       <c r="AJ33" s="2" t="n">
-        <v>-4.08</v>
+        <v>-3.46</v>
       </c>
       <c r="AK33" s="2" t="n">
         <v>34.6</v>
       </c>
       <c r="AL33" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
@@ -5487,40 +5491,40 @@
         </is>
       </c>
       <c r="AR33" s="2" t="n">
-        <v>4788.8</v>
+        <v>4787.6</v>
       </c>
       <c r="AS33" s="2" t="n">
-        <v>4791.1</v>
+        <v>4790.5</v>
       </c>
       <c r="AT33" s="2" t="n">
-        <v>4832.137</v>
+        <v>4831.837</v>
       </c>
       <c r="AU33" s="2" t="n">
-        <v>4896.382</v>
+        <v>4896.182</v>
       </c>
       <c r="AV33" s="2" t="n">
-        <v>4894.776</v>
+        <v>4894.656</v>
       </c>
       <c r="AW33" s="2" t="n">
-        <v>4921.436</v>
+        <v>4921.376</v>
       </c>
       <c r="AX33" s="2" t="n">
-        <v>5134.831</v>
+        <v>5134.801</v>
       </c>
       <c r="AY33" s="2" t="n">
-        <v>-0.063</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="AZ33" s="2" t="n">
-        <v>-0.6339</v>
+        <v>-0.6371</v>
       </c>
       <c r="BA33" s="2" t="n">
-        <v>-0.4704</v>
+        <v>-0.4717</v>
       </c>
       <c r="BB33" s="2" t="n">
-        <v>-0.4232</v>
+        <v>-0.4239</v>
       </c>
       <c r="BC33" s="2" t="n">
-        <v>0.104</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="34">
@@ -5535,7 +5539,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1191.5</v>
+        <v>1192.5</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>15.64</v>
@@ -5558,37 +5562,37 @@
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S34" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="S34" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>0111101100</t>
+          <t>0111111100</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0011101001</t>
+          <t>0011111001</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>8</v>
+        <v>254</v>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>1→3A·8d ← 2B→1·9d ← 1→2B·11d</t>
+          <t>3→2A·8d ← 2A→3·9d ← 3→2A·11d</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr"/>
@@ -5600,17 +5604,17 @@
       <c r="AD34" s="2" t="inlineStr"/>
       <c r="AE34" s="2" t="inlineStr"/>
       <c r="AF34" s="2" t="n">
-        <v>33.88</v>
+        <v>33.9</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>0.46</v>
+        <v>1.37</v>
       </c>
       <c r="AH34" s="2" t="n"/>
       <c r="AI34" s="2" t="n">
-        <v>7.41</v>
+        <v>8.32</v>
       </c>
       <c r="AJ34" s="2" t="n">
-        <v>5.26</v>
+        <v>6.17</v>
       </c>
       <c r="AK34" s="2" t="n">
         <v>48.3</v>
@@ -5628,40 +5632,40 @@
         </is>
       </c>
       <c r="AR34" s="2" t="n">
-        <v>1211</v>
+        <v>1211.2</v>
       </c>
       <c r="AS34" s="2" t="n">
-        <v>1194.5</v>
+        <v>1194.6</v>
       </c>
       <c r="AT34" s="2" t="n">
-        <v>1172.539</v>
+        <v>1172.589</v>
       </c>
       <c r="AU34" s="2" t="n">
-        <v>1160.343</v>
+        <v>1160.377</v>
       </c>
       <c r="AV34" s="2" t="n">
-        <v>1174.45</v>
+        <v>1174.47</v>
       </c>
       <c r="AW34" s="2" t="n">
-        <v>1161.718</v>
+        <v>1161.728</v>
       </c>
       <c r="AX34" s="2" t="n">
-        <v>1127.306</v>
+        <v>1127.311</v>
       </c>
       <c r="AY34" s="2" t="n">
-        <v>1.0667</v>
+        <v>1.0712</v>
       </c>
       <c r="AZ34" s="2" t="n">
-        <v>1.0109</v>
+        <v>1.0131</v>
       </c>
       <c r="BA34" s="2" t="n">
-        <v>0.2956</v>
+        <v>0.2965</v>
       </c>
       <c r="BB34" s="2" t="n">
-        <v>0.1994</v>
+        <v>0.1998</v>
       </c>
       <c r="BC34" s="2" t="n">
-        <v>0.3388</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="35">
@@ -5676,7 +5680,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>7300</v>
+        <v>7299</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>92.15000000000001</v>
@@ -5699,14 +5703,14 @@
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>0110111101</t>
+          <t>0110111100</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -5720,14 +5724,18 @@
         </is>
       </c>
       <c r="W35" s="2" t="n">
-        <v>58</v>
+        <v>254</v>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·17d</t>
+        </is>
+      </c>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="n">
@@ -5742,20 +5750,20 @@
         <v>43.91</v>
       </c>
       <c r="AG35" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AH35" s="2" t="n"/>
       <c r="AI35" s="2" t="n">
-        <v>6.12</v>
+        <v>6.99</v>
       </c>
       <c r="AJ35" s="2" t="n">
-        <v>-6.18</v>
+        <v>-5.3</v>
       </c>
       <c r="AK35" s="2" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
@@ -5769,37 +5777,37 @@
         </is>
       </c>
       <c r="AR35" s="2" t="n">
-        <v>7262.2</v>
+        <v>7262</v>
       </c>
       <c r="AS35" s="2" t="n">
-        <v>7309.5</v>
+        <v>7309.4</v>
       </c>
       <c r="AT35" s="2" t="n">
-        <v>7317.324</v>
+        <v>7317.274</v>
       </c>
       <c r="AU35" s="2" t="n">
-        <v>7378.594</v>
+        <v>7378.561</v>
       </c>
       <c r="AV35" s="2" t="n">
-        <v>7304.79</v>
+        <v>7304.77</v>
       </c>
       <c r="AW35" s="2" t="n">
-        <v>6799.062</v>
+        <v>6799.052</v>
       </c>
       <c r="AX35" s="2" t="n">
-        <v>6463.145</v>
+        <v>6463.14</v>
       </c>
       <c r="AY35" s="2" t="n">
-        <v>-0.0233</v>
+        <v>-0.024</v>
       </c>
       <c r="AZ35" s="2" t="n">
-        <v>-0.3652</v>
+        <v>-0.3655</v>
       </c>
       <c r="BA35" s="2" t="n">
-        <v>0.5663</v>
+        <v>0.5662</v>
       </c>
       <c r="BB35" s="2" t="n">
-        <v>0.0743</v>
+        <v>0.0742</v>
       </c>
       <c r="BC35" s="2" t="n">
         <v>0.4391</v>
@@ -5817,7 +5825,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>4930</v>
+        <v>4909</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>78.73999999999999</v>
@@ -5832,7 +5840,7 @@
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -5841,7 +5849,7 @@
         <v>3</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
@@ -5850,7 +5858,7 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0101000100</t>
+          <t>0100000100</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -5859,16 +5867,16 @@
         </is>
       </c>
       <c r="W36" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>1→4A·2d ← 3B→1·5d</t>
+          <t>3→1B·12d</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -5880,23 +5888,23 @@
       <c r="AD36" s="2" t="inlineStr"/>
       <c r="AE36" s="2" t="inlineStr"/>
       <c r="AF36" s="2" t="n">
-        <v>11.61</v>
+        <v>11.5</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>-9.85</v>
+        <v>-9.49</v>
       </c>
       <c r="AH36" s="2" t="n"/>
       <c r="AI36" s="2" t="n">
-        <v>7.17</v>
+        <v>7.52</v>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>-1.84</v>
+        <v>-1.48</v>
       </c>
       <c r="AK36" s="2" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="AL36" s="2" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
@@ -5908,40 +5916,40 @@
         </is>
       </c>
       <c r="AR36" s="2" t="n">
-        <v>4869.4</v>
+        <v>4865.2</v>
       </c>
       <c r="AS36" s="2" t="n">
-        <v>4895.9</v>
+        <v>4893.8</v>
       </c>
       <c r="AT36" s="2" t="n">
-        <v>4953.228</v>
+        <v>4952.178</v>
       </c>
       <c r="AU36" s="2" t="n">
-        <v>4981.705</v>
+        <v>4981.005</v>
       </c>
       <c r="AV36" s="2" t="n">
-        <v>4908.781</v>
+        <v>4908.361</v>
       </c>
       <c r="AW36" s="2" t="n">
-        <v>4851.114</v>
+        <v>4850.904</v>
       </c>
       <c r="AX36" s="2" t="n">
-        <v>5157.664</v>
+        <v>5157.559</v>
       </c>
       <c r="AY36" s="2" t="n">
-        <v>-0.3441</v>
+        <v>-0.3663</v>
       </c>
       <c r="AZ36" s="2" t="n">
-        <v>-0.4158</v>
+        <v>-0.4267</v>
       </c>
       <c r="BA36" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0002</v>
       </c>
       <c r="BB36" s="2" t="n">
-        <v>-0.5343</v>
+        <v>-0.5366</v>
       </c>
       <c r="BC36" s="2" t="n">
-        <v>0.1161</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="37">
@@ -5956,7 +5964,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>10520</v>
+        <v>10385</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>96.47</v>
@@ -5979,14 +5987,14 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>0110011000</t>
+          <t>0110001000</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -6000,16 +6008,16 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 1→2B·15d</t>
+          <t>3→2A·10d ← 2A→3·19d</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -6023,20 +6031,20 @@
       </c>
       <c r="AE37" s="2" t="inlineStr"/>
       <c r="AF37" s="2" t="n">
-        <v>73.25</v>
+        <v>72.89</v>
       </c>
       <c r="AG37" s="2" t="n">
-        <v>6.56</v>
+        <v>6.07</v>
       </c>
       <c r="AH37" s="2" t="n"/>
       <c r="AI37" s="2" t="n">
-        <v>-11.66</v>
+        <v>-12.16</v>
       </c>
       <c r="AJ37" s="2" t="n">
-        <v>0.67</v>
+        <v>0.18</v>
       </c>
       <c r="AK37" s="2" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="AL37" s="2" t="n">
         <v>12</v>
@@ -6057,40 +6065,40 @@
         </is>
       </c>
       <c r="AR37" s="2" t="n">
-        <v>11590</v>
+        <v>11563</v>
       </c>
       <c r="AS37" s="2" t="n">
-        <v>12070</v>
+        <v>12056.5</v>
       </c>
       <c r="AT37" s="2" t="n">
-        <v>11297.517</v>
+        <v>11290.767</v>
       </c>
       <c r="AU37" s="2" t="n">
-        <v>11002.254</v>
+        <v>10997.754</v>
       </c>
       <c r="AV37" s="2" t="n">
-        <v>10955.207</v>
+        <v>10952.507</v>
       </c>
       <c r="AW37" s="2" t="n">
-        <v>11774.809</v>
+        <v>11773.459</v>
       </c>
       <c r="AX37" s="2" t="n">
-        <v>9882.629000000001</v>
+        <v>9881.954</v>
       </c>
       <c r="AY37" s="2" t="n">
-        <v>1.0617</v>
+        <v>1.0023</v>
       </c>
       <c r="AZ37" s="2" t="n">
-        <v>1.4705</v>
+        <v>1.4386</v>
       </c>
       <c r="BA37" s="2" t="n">
-        <v>0.3017</v>
+        <v>0.2888</v>
       </c>
       <c r="BB37" s="2" t="n">
-        <v>0.4819</v>
+        <v>0.4759</v>
       </c>
       <c r="BC37" s="2" t="n">
-        <v>0.7325</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="38">
@@ -6105,7 +6113,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1721</v>
+        <v>1708.5</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>86.81</v>
@@ -6149,38 +6157,46 @@
         </is>
       </c>
       <c r="W38" s="2" t="n">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·13d</t>
+        </is>
+      </c>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr"/>
       <c r="AE38" s="2" t="inlineStr"/>
       <c r="AF38" s="2" t="n">
-        <v>35.43</v>
+        <v>35.23</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="AH38" s="2" t="n"/>
       <c r="AI38" s="2" t="n">
-        <v>7.66</v>
+        <v>7.76</v>
       </c>
       <c r="AJ38" s="2" t="n">
-        <v>-7.31</v>
+        <v>-7.21</v>
       </c>
       <c r="AK38" s="2" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
@@ -6194,40 +6210,40 @@
         </is>
       </c>
       <c r="AR38" s="2" t="n">
-        <v>1724.2</v>
+        <v>1721.7</v>
       </c>
       <c r="AS38" s="2" t="n">
-        <v>1730</v>
+        <v>1728.75</v>
       </c>
       <c r="AT38" s="2" t="n">
-        <v>1750.268</v>
+        <v>1749.643</v>
       </c>
       <c r="AU38" s="2" t="n">
-        <v>1769.198</v>
+        <v>1768.781</v>
       </c>
       <c r="AV38" s="2" t="n">
-        <v>1749.951</v>
+        <v>1749.701</v>
       </c>
       <c r="AW38" s="2" t="n">
-        <v>1680.501</v>
+        <v>1680.376</v>
       </c>
       <c r="AX38" s="2" t="n">
-        <v>1591.473</v>
+        <v>1591.41</v>
       </c>
       <c r="AY38" s="2" t="n">
-        <v>-0.5299</v>
+        <v>-0.5671</v>
       </c>
       <c r="AZ38" s="2" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.6932</v>
       </c>
       <c r="BA38" s="2" t="n">
-        <v>0.4269</v>
+        <v>0.4194</v>
       </c>
       <c r="BB38" s="2" t="n">
-        <v>-0.1267</v>
+        <v>-0.1306</v>
       </c>
       <c r="BC38" s="2" t="n">
-        <v>0.3543</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="39">
@@ -6242,7 +6258,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>4695</v>
+        <v>4674</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>12.95</v>
@@ -6261,7 +6277,7 @@
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -6284,20 +6300,20 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>1→3B·7d ← 2B→1·16d ← 1→2B·17d</t>
+          <t>3→2A·10d</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -6307,23 +6323,23 @@
       <c r="AD39" s="2" t="inlineStr"/>
       <c r="AE39" s="2" t="inlineStr"/>
       <c r="AF39" s="2" t="n">
-        <v>28.55</v>
+        <v>28.43</v>
       </c>
       <c r="AG39" s="2" t="n">
-        <v>-5.52</v>
+        <v>-5.17</v>
       </c>
       <c r="AH39" s="2" t="n"/>
       <c r="AI39" s="2" t="n">
-        <v>7.45</v>
+        <v>7.8</v>
       </c>
       <c r="AJ39" s="2" t="n">
-        <v>-5.82</v>
+        <v>-5.47</v>
       </c>
       <c r="AK39" s="2" t="n">
-        <v>67.5</v>
+        <v>67.2</v>
       </c>
       <c r="AL39" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
@@ -6335,40 +6351,40 @@
         </is>
       </c>
       <c r="AR39" s="2" t="n">
-        <v>4668.8</v>
+        <v>4664.6</v>
       </c>
       <c r="AS39" s="2" t="n">
-        <v>4685.8</v>
+        <v>4683.7</v>
       </c>
       <c r="AT39" s="2" t="n">
-        <v>4750.89</v>
+        <v>4749.84</v>
       </c>
       <c r="AU39" s="2" t="n">
-        <v>4796.948</v>
+        <v>4796.248</v>
       </c>
       <c r="AV39" s="2" t="n">
-        <v>4759.405</v>
+        <v>4758.985</v>
       </c>
       <c r="AW39" s="2" t="n">
-        <v>4705.513</v>
+        <v>4705.303</v>
       </c>
       <c r="AX39" s="2" t="n">
-        <v>4703.02</v>
+        <v>4702.915</v>
       </c>
       <c r="AY39" s="2" t="n">
-        <v>-0.4004</v>
+        <v>-0.4235</v>
       </c>
       <c r="AZ39" s="2" t="n">
-        <v>-0.6922</v>
+        <v>-0.7036</v>
       </c>
       <c r="BA39" s="2" t="n">
-        <v>-0.1052</v>
+        <v>-0.1098</v>
       </c>
       <c r="BB39" s="2" t="n">
-        <v>-0.4903</v>
+        <v>-0.4926</v>
       </c>
       <c r="BC39" s="2" t="n">
-        <v>0.2855</v>
+        <v>0.2843</v>
       </c>
     </row>
     <row r="40">
@@ -6383,7 +6399,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>7372</v>
+        <v>7262</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>98.81999999999999</v>
@@ -6409,7 +6425,7 @@
         <v>8</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
@@ -6418,7 +6434,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1111111101</t>
+          <t>0111111101</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -6427,14 +6443,18 @@
         </is>
       </c>
       <c r="W40" s="2" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·10d ← 2C→2B·15d ← 2B→2C·17d</t>
+        </is>
+      </c>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="inlineStr"/>
       <c r="AB40" s="2" t="inlineStr">
@@ -6443,33 +6463,37 @@
         </is>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="inlineStr"/>
       <c r="AF40" s="2" t="n">
-        <v>61.45</v>
+        <v>60.94</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>19.72</v>
+        <v>18.91</v>
       </c>
       <c r="AH40" s="2" t="n"/>
       <c r="AI40" s="2" t="n">
-        <v>13.01</v>
+        <v>12.2</v>
       </c>
       <c r="AJ40" s="2" t="n">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="AK40" s="2" t="n">
-        <v>100.3</v>
+        <v>99.7</v>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="AM40" s="2" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="AM40" s="2" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AN40" s="2" t="inlineStr"/>
       <c r="AO40" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr">
@@ -6478,40 +6502,40 @@
         </is>
       </c>
       <c r="AR40" s="2" t="n">
-        <v>7408.8</v>
+        <v>7386.8</v>
       </c>
       <c r="AS40" s="2" t="n">
-        <v>7262.7</v>
+        <v>7251.7</v>
       </c>
       <c r="AT40" s="2" t="n">
-        <v>7243.639</v>
+        <v>7238.139</v>
       </c>
       <c r="AU40" s="2" t="n">
-        <v>7191.165</v>
+        <v>7187.498</v>
       </c>
       <c r="AV40" s="2" t="n">
-        <v>6875.242</v>
+        <v>6873.042</v>
       </c>
       <c r="AW40" s="2" t="n">
-        <v>6128.497</v>
+        <v>6127.397</v>
       </c>
       <c r="AX40" s="2" t="n">
-        <v>5720.977</v>
+        <v>5720.427</v>
       </c>
       <c r="AY40" s="2" t="n">
-        <v>0.8671</v>
+        <v>0.7871</v>
       </c>
       <c r="AZ40" s="2" t="n">
-        <v>0.4601</v>
+        <v>0.4203</v>
       </c>
       <c r="BA40" s="2" t="n">
-        <v>1.1215</v>
+        <v>1.1045</v>
       </c>
       <c r="BB40" s="2" t="n">
-        <v>0.8423</v>
+        <v>0.8328</v>
       </c>
       <c r="BC40" s="2" t="n">
-        <v>0.6145</v>
+        <v>0.6094000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -6526,7 +6550,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>7429</v>
+        <v>7330</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>82.55</v>
@@ -6545,27 +6569,25 @@
       <c r="N41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O41" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>0111111111</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1111111101</t>
+          <t>1111111111</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -6574,14 +6596,18 @@
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·14d</t>
+        </is>
+      </c>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="inlineStr"/>
       <c r="AB41" s="2" t="inlineStr">
@@ -6595,23 +6621,23 @@
       <c r="AD41" s="2" t="inlineStr"/>
       <c r="AE41" s="2" t="inlineStr"/>
       <c r="AF41" s="2" t="n">
-        <v>68.56999999999999</v>
+        <v>68.12</v>
       </c>
       <c r="AG41" s="2" t="n">
-        <v>21.86</v>
+        <v>21.23</v>
       </c>
       <c r="AH41" s="2" t="n"/>
       <c r="AI41" s="2" t="n">
-        <v>14.32</v>
+        <v>13.69</v>
       </c>
       <c r="AJ41" s="2" t="n">
-        <v>5.9</v>
+        <v>5.28</v>
       </c>
       <c r="AK41" s="2" t="n">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="AL41" s="2" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
@@ -6625,40 +6651,40 @@
         </is>
       </c>
       <c r="AR41" s="2" t="n">
-        <v>7412.6</v>
+        <v>7392.8</v>
       </c>
       <c r="AS41" s="2" t="n">
-        <v>7250.6</v>
+        <v>7240.7</v>
       </c>
       <c r="AT41" s="2" t="n">
-        <v>7149.173</v>
+        <v>7144.223</v>
       </c>
       <c r="AU41" s="2" t="n">
-        <v>7086.17</v>
+        <v>7082.87</v>
       </c>
       <c r="AV41" s="2" t="n">
-        <v>6845.026</v>
+        <v>6843.046</v>
       </c>
       <c r="AW41" s="2" t="n">
-        <v>6145.174</v>
+        <v>6144.184</v>
       </c>
       <c r="AX41" s="2" t="n">
-        <v>5816.225</v>
+        <v>5815.73</v>
       </c>
       <c r="AY41" s="2" t="n">
-        <v>1.5066</v>
+        <v>1.4335</v>
       </c>
       <c r="AZ41" s="2" t="n">
-        <v>0.8187</v>
+        <v>0.7821</v>
       </c>
       <c r="BA41" s="2" t="n">
-        <v>1.2403</v>
+        <v>1.2249</v>
       </c>
       <c r="BB41" s="2" t="n">
-        <v>0.7067</v>
+        <v>0.6982</v>
       </c>
       <c r="BC41" s="2" t="n">
-        <v>0.6857</v>
+        <v>0.6812</v>
       </c>
     </row>
     <row r="42">
@@ -6673,7 +6699,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3403</v>
+        <v>3375</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>89.25</v>
@@ -6694,9 +6720,7 @@
       <c r="N42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="n">
@@ -6721,16 +6745,16 @@
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·16d ← 2B→2C·17d</t>
+          <t>2B→2C·11d ← 2C→2B·15d ← 2B→2C·18d</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -6746,7 +6770,7 @@
       <c r="AD42" s="2" t="inlineStr"/>
       <c r="AE42" s="2" t="inlineStr"/>
       <c r="AF42" s="2" t="n">
-        <v>68.12</v>
+        <v>67.84</v>
       </c>
       <c r="AG42" s="2" t="n">
         <v>22.89</v>
@@ -6759,10 +6783,10 @@
         <v>0.29</v>
       </c>
       <c r="AK42" s="2" t="n">
-        <v>88.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AL42" s="2" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="AM42" s="2" t="inlineStr"/>
       <c r="AN42" s="2" t="inlineStr"/>
@@ -6776,40 +6800,40 @@
         </is>
       </c>
       <c r="AR42" s="2" t="n">
-        <v>3406.6</v>
+        <v>3401</v>
       </c>
       <c r="AS42" s="2" t="n">
-        <v>3330.3</v>
+        <v>3327.5</v>
       </c>
       <c r="AT42" s="2" t="n">
-        <v>3350.659</v>
+        <v>3349.259</v>
       </c>
       <c r="AU42" s="2" t="n">
-        <v>3337.421</v>
+        <v>3336.488</v>
       </c>
       <c r="AV42" s="2" t="n">
-        <v>3209.455</v>
+        <v>3208.895</v>
       </c>
       <c r="AW42" s="2" t="n">
-        <v>2882.585</v>
+        <v>2882.305</v>
       </c>
       <c r="AX42" s="2" t="n">
-        <v>2628.565</v>
+        <v>2628.425</v>
       </c>
       <c r="AY42" s="2" t="n">
-        <v>0.5376</v>
+        <v>0.4934</v>
       </c>
       <c r="AZ42" s="2" t="n">
-        <v>0.3386</v>
+        <v>0.3168</v>
       </c>
       <c r="BA42" s="2" t="n">
-        <v>1.0226</v>
+        <v>1.0133</v>
       </c>
       <c r="BB42" s="2" t="n">
-        <v>0.8236</v>
+        <v>0.8184</v>
       </c>
       <c r="BC42" s="2" t="n">
-        <v>0.6812</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="43">
@@ -6824,7 +6848,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>76550</v>
+        <v>76240</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>4.13</v>
@@ -6868,18 +6892,14 @@
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>3B→3A·3d ← 2B→3B·4d ← 1→2B·8d</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="inlineStr"/>
       <c r="AB43" s="2" t="n">
@@ -6891,23 +6911,23 @@
         <v>1</v>
       </c>
       <c r="AF43" s="2" t="n">
-        <v>34.79</v>
+        <v>34.67</v>
       </c>
       <c r="AG43" s="2" t="n">
-        <v>3.41</v>
+        <v>3.84</v>
       </c>
       <c r="AH43" s="2" t="n"/>
       <c r="AI43" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="AJ43" s="2" t="n">
-        <v>12.28</v>
+        <v>12.71</v>
       </c>
       <c r="AK43" s="2" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="AL43" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AM43" s="2" t="inlineStr"/>
       <c r="AN43" s="2" t="n">
@@ -6921,40 +6941,40 @@
         </is>
       </c>
       <c r="AR43" s="2" t="n">
-        <v>74552</v>
+        <v>74490</v>
       </c>
       <c r="AS43" s="2" t="n">
-        <v>74234</v>
+        <v>74203</v>
       </c>
       <c r="AT43" s="2" t="n">
-        <v>71104.5</v>
+        <v>71089</v>
       </c>
       <c r="AU43" s="2" t="n">
-        <v>70378</v>
+        <v>70367.667</v>
       </c>
       <c r="AV43" s="2" t="n">
-        <v>72405.194</v>
+        <v>72398.99400000001</v>
       </c>
       <c r="AW43" s="2" t="n">
-        <v>76187.064</v>
+        <v>76183.96400000001</v>
       </c>
       <c r="AX43" s="2" t="n">
-        <v>70473.86599999999</v>
+        <v>70472.31600000001</v>
       </c>
       <c r="AY43" s="2" t="n">
-        <v>2.0988</v>
+        <v>2.0762</v>
       </c>
       <c r="AZ43" s="2" t="n">
-        <v>1.3013</v>
+        <v>1.2897</v>
       </c>
       <c r="BA43" s="2" t="n">
-        <v>-0.2398</v>
+        <v>-0.2442</v>
       </c>
       <c r="BB43" s="2" t="n">
-        <v>0.095</v>
+        <v>0.0929</v>
       </c>
       <c r="BC43" s="2" t="n">
-        <v>0.3479</v>
+        <v>0.3467</v>
       </c>
     </row>
     <row r="44">
@@ -7017,11 +7037,11 @@
         </is>
       </c>
       <c r="W44" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr"/>
@@ -7162,16 +7182,16 @@
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>2A→4B·17d ← 1→2A·20d</t>
+          <t>1A→4·13d</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr"/>
@@ -7303,11 +7323,11 @@
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>330</v>
+        <v>272</v>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速·顶背离)</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr"/>
@@ -7442,23 +7462,27 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>1→4B·1d ← 4B→1·5d ← 1→4B·6d</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr"/>
+          <t>1B→2A·3d ← 3→1B·13d</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
       <c r="AA47" s="2" t="inlineStr"/>
       <c r="AB47" s="2" t="n">
         <v>-1</v>
@@ -7595,11 +7619,11 @@
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr"/>
@@ -7736,19 +7760,23 @@
         </is>
       </c>
       <c r="W49" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>2B→1·2d ← 1→2B·18d</t>
-        </is>
-      </c>
-      <c r="Z49" s="2" t="inlineStr"/>
+          <t>3→2A·10d ← 1B→3·12d</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>10d</t>
+        </is>
+      </c>
       <c r="AA49" s="2" t="inlineStr"/>
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="n">
@@ -7893,16 +7921,16 @@
         </is>
       </c>
       <c r="W50" s="2" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(顶背离)</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·1d ← 2B→2C·20d</t>
+          <t>2A→2C·20d</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr"/>
@@ -8040,14 +8068,18 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y51" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·6d ← 2C→2A·8d</t>
+        </is>
+      </c>
       <c r="Z51" s="2" t="inlineStr"/>
       <c r="AA51" s="2" t="inlineStr"/>
       <c r="AB51" s="2" t="inlineStr"/>
@@ -8175,18 +8207,22 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W52" s="2" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y52" s="2" t="inlineStr"/>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>3→2A·1d ← 2A→3·11d ← 2C→2A·16d</t>
+        </is>
+      </c>
       <c r="Z52" s="2" t="inlineStr"/>
       <c r="AA52" s="2" t="inlineStr"/>
       <c r="AB52" s="2" t="n">
@@ -8332,14 +8368,18 @@
         </is>
       </c>
       <c r="W53" s="2" t="n">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·5d</t>
+        </is>
+      </c>
       <c r="Z53" s="2" t="inlineStr"/>
       <c r="AA53" s="2" t="inlineStr"/>
       <c r="AB53" s="2" t="n">
@@ -8479,16 +8519,16 @@
         </is>
       </c>
       <c r="W54" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>3B→3A·1d ← 1→3B·14d</t>
+          <t>2A→3·16d ← 2C→2A·18d</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr"/>
@@ -8620,7 +8660,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" s="2" t="n">
@@ -8628,12 +8668,12 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>1B→4B·15d</t>
+          <t>1B→1A·10d ← 3→1B·15d</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -8775,14 +8815,18 @@
         </is>
       </c>
       <c r="W56" s="2" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·5d ← 2A→2C·9d</t>
+        </is>
+      </c>
       <c r="Z56" s="2" t="inlineStr"/>
       <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr"/>
@@ -8918,11 +8962,11 @@
         </is>
       </c>
       <c r="W57" s="2" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr"/>
@@ -9063,16 +9107,16 @@
         </is>
       </c>
       <c r="W58" s="2" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>3B→1·2d ← 1→3B·4d ← 3B→1·7d</t>
+          <t>1B→1A·5d ← 1A→1B·7d ← 1B→1A·15d</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr"/>
@@ -9208,20 +9252,20 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W59" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>1A→4B·8d ← 4B→1A·20d</t>
+          <t>1B→1A·15d ← 2A→1B·20d</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr"/>
@@ -9361,18 +9405,22 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W60" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="Y60" s="2" t="inlineStr"/>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>1B→1A·18d</t>
+        </is>
+      </c>
       <c r="Z60" s="2" t="inlineStr"/>
       <c r="AA60" s="2" t="inlineStr"/>
       <c r="AB60" s="2" t="inlineStr">
@@ -9506,11 +9554,11 @@
         </is>
       </c>
       <c r="W61" s="2" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr"/>
@@ -9649,16 +9697,16 @@
         </is>
       </c>
       <c r="W62" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>4A→4B·15d</t>
+          <t>1A→4·13d</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
@@ -9796,16 +9844,16 @@
         </is>
       </c>
       <c r="W63" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>2B→1·12d</t>
+          <t>2A→1B·8d ← 2C→2A·16d</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr"/>
@@ -9949,14 +9997,18 @@
         </is>
       </c>
       <c r="W64" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·5d ← 2B→2C·9d ← 2C→2B·11d</t>
+        </is>
+      </c>
       <c r="Z64" s="2" t="inlineStr"/>
       <c r="AA64" s="2" t="inlineStr"/>
       <c r="AB64" s="2" t="inlineStr"/>
@@ -10088,18 +10140,14 @@
         </is>
       </c>
       <c r="W65" s="2" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
-        <is>
-          <t>3B→4A·2d ← 2A→3B·19d ← 3B→2A·20d</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
       <c r="Z65" s="2" t="inlineStr"/>
       <c r="AA65" s="2" t="inlineStr"/>
       <c r="AB65" s="2" t="n">
@@ -10237,14 +10285,18 @@
         </is>
       </c>
       <c r="W66" s="2" t="n">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y66" s="2" t="inlineStr"/>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>2C→2A·11d ← 2B→2C·18d</t>
+        </is>
+      </c>
       <c r="Z66" s="2" t="inlineStr"/>
       <c r="AA66" s="2" t="inlineStr"/>
       <c r="AB66" s="2" t="n">
@@ -10376,20 +10428,20 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W67" s="2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·7d ← 2A→2C·16d ← 1→2A·20d</t>
+          <t>1B→2A·1d</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr"/>
@@ -10517,20 +10569,20 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W68" s="2" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>3B→3A·1d ← 3A→3B·4d ← 3B→3A·7d</t>
+          <t>2C→2A·9d</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
@@ -10662,16 +10714,16 @@
         </is>
       </c>
       <c r="W69" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>1→4B·2d ← 4B→1·4d ← 1→4B·5d</t>
+          <t>1B→1A·1d</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr"/>
@@ -10799,20 +10851,20 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W70" s="2" t="n">
-        <v>7</v>
+        <v>272</v>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>2B→1·2d ← 1→2B·4d ← 2B→1·7d</t>
+          <t>2A→3·2d ← 2C→2A·10d</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr"/>
@@ -10948,20 +11000,20 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W71" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>2B→1·6d ← 1→2B·9d</t>
+          <t>3→1B·1d</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr"/>
@@ -11093,11 +11145,11 @@
         </is>
       </c>
       <c r="W72" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr"/>
@@ -11232,20 +11284,20 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W73" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>4B→1·7d</t>
+          <t>1A→4·18d</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr"/>
@@ -11375,20 +11427,20 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W74" s="2" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>2B→1·15d</t>
+          <t>2A→3·2d ← 2C→2A·7d ← 2B→2C·11d</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
@@ -11526,22 +11578,18 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W75" s="2" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y75" s="2" t="inlineStr">
-        <is>
-          <t>4B→1·5d ← 2A→4B·18d ← 4B→2A·19d</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
       <c r="Z75" s="2" t="inlineStr"/>
       <c r="AA75" s="2" t="inlineStr"/>
       <c r="AB75" s="2" t="inlineStr"/>
@@ -11667,20 +11715,20 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W76" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>2B→1·5d ← 1→2B·10d ← 2B→1·17d</t>
+          <t>2A→3·2d ← 3→2A·8d</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr"/>
@@ -11812,20 +11860,20 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W77" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>2A→4B·1d ← 2B→2A·3d ← 4B→2B·4d</t>
+          <t>1B→1A·1d ← 1A→1B·4d ← 1B→1A·6d</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr"/>
@@ -11969,18 +12017,14 @@
         </is>
       </c>
       <c r="W78" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="Y78" s="2" t="inlineStr">
-        <is>
-          <t>1→2A·1d ← 4A→1·2d ← 1A→4A·10d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
       <c r="Z78" s="2" t="inlineStr"/>
       <c r="AA78" s="2" t="inlineStr"/>
       <c r="AB78" s="2" t="inlineStr"/>
@@ -12114,16 +12158,16 @@
         </is>
       </c>
       <c r="W79" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>1→3B·2d ← 2B→1·14d ← 1→2B·19d</t>
+          <t>1B→1A·1d ← 1A→1B·2d ← 1B→1A·3d</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr"/>
@@ -12253,20 +12297,20 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W80" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 1→2B·18d</t>
+          <t>3→2A·2d ← 1B→3·14d</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
@@ -12406,16 +12450,16 @@
         </is>
       </c>
       <c r="W81" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·20d</t>
+          <t>2A→2C·5d ← 3→2A·16d</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr"/>
@@ -12553,11 +12597,11 @@
         </is>
       </c>
       <c r="W82" s="2" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr"/>
@@ -12698,11 +12742,11 @@
         </is>
       </c>
       <c r="W83" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr"/>
@@ -12849,11 +12893,11 @@
         </is>
       </c>
       <c r="W84" s="2" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr"/>
@@ -12994,16 +13038,16 @@
         </is>
       </c>
       <c r="W85" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>1C→2A·17d ← 1→1C·18d</t>
+          <t>2C→2B·4d ← 2A→2C·9d ← 3→2A·20d</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr"/>
@@ -13145,16 +13189,16 @@
         </is>
       </c>
       <c r="W86" s="2" t="n">
-        <v>358</v>
+        <v>272</v>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>2B→2C·10d ← 2C→2B·17d</t>
+          <t>2B→2C·15d ← 2C→2B·17d</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr"/>
@@ -13286,16 +13330,16 @@
         </is>
       </c>
       <c r="W87" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>1→3B·11d ← 2B→1·16d ← 1→2B·18d</t>
+          <t>2A→3·20d</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr"/>
@@ -13439,7 +13483,7 @@
         </is>
       </c>
       <c r="W88" s="2" t="n">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
@@ -13448,7 +13492,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>1→2B·19d</t>
+          <t>2C→2B·9d ← 2A→2C·11d</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr"/>
@@ -13582,20 +13626,20 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W89" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>2B→1·6d ← 1→2B·7d ← 2B→1·14d</t>
+          <t>2A→3·11d</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr"/>
@@ -13735,14 +13779,18 @@
         </is>
       </c>
       <c r="W90" s="2" t="n">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·8d ← 2A→2C·13d</t>
+        </is>
+      </c>
       <c r="Z90" s="2" t="inlineStr"/>
       <c r="AA90" s="2" t="inlineStr"/>
       <c r="AB90" s="2" t="inlineStr"/>
@@ -13870,14 +13918,18 @@
         </is>
       </c>
       <c r="W91" s="2" t="n">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y91" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·16d</t>
+        </is>
+      </c>
       <c r="Z91" s="2" t="inlineStr"/>
       <c r="AA91" s="2" t="inlineStr"/>
       <c r="AB91" s="2" t="n">
@@ -14007,20 +14059,20 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W92" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>1B→1·1d ← 3A→1B·2d ← 3B→3A·9d</t>
+          <t>2A→2C·11d</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr"/>
@@ -14158,11 +14210,11 @@
         </is>
       </c>
       <c r="W93" s="2" t="n">
-        <v>310</v>
+        <v>272</v>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸·顶背离)</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr"/>
@@ -14297,11 +14349,11 @@
         </is>
       </c>
       <c r="W94" s="2" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr"/>
@@ -14444,20 +14496,20 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W95" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>3A→3B·19d</t>
+          <t>1B→1A·5d ← 3→1B·17d ← 2A→3·18d</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr"/>
@@ -14589,20 +14641,20 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W96" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>3A→3B·13d ← 3B→3A·14d ← 1→3B·19d</t>
+          <t>1B→1A·1d</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr"/>
@@ -14736,23 +14788,19 @@
         </is>
       </c>
       <c r="W97" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 1→2B·10d</t>
-        </is>
-      </c>
-      <c r="Z97" s="2" t="inlineStr">
-        <is>
-          <t>10d</t>
-        </is>
-      </c>
+          <t>3→2A·3d</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr"/>
       <c r="AA97" s="2" t="inlineStr"/>
       <c r="AB97" s="2" t="inlineStr"/>
       <c r="AC97" s="2" t="inlineStr">
@@ -14885,16 +14933,16 @@
         </is>
       </c>
       <c r="W98" s="2" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>2B→2A·19d</t>
+          <t>2B→2C·11d ← 2A→2B·18d</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr"/>
@@ -15036,12 +15084,12 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>1→2B·9d ← 2B→1·10d ← 1→2B·14d</t>
+          <t>2C→2A·6d ← 2B→2C·15d</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr"/>
@@ -15173,18 +15221,14 @@
         </is>
       </c>
       <c r="W100" s="2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y100" s="2" t="inlineStr">
-        <is>
-          <t>2B→1·6d ← 1→2B·7d</t>
-        </is>
-      </c>
+          <t>1B(纠缠)</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
       <c r="Z100" s="2" t="inlineStr"/>
       <c r="AA100" s="2" t="inlineStr"/>
       <c r="AB100" s="2" t="inlineStr"/>
@@ -15316,16 +15360,16 @@
         </is>
       </c>
       <c r="W101" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>3B→2B·8d ← 3A→3B·13d ← 3B→3A·14d</t>
+          <t>3→2A·4d</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr"/>
@@ -15457,7 +15501,7 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W102" s="2" t="n">
@@ -15465,12 +15509,12 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>1→3B·13d</t>
+          <t>3→1B·13d ← 2A→3·15d</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr"/>
@@ -15610,20 +15654,20 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W103" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>4A→4B·3d ← 3B→4A·15d</t>
+          <t>3→1A·11d</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr"/>
@@ -15769,18 +15813,14 @@
         </is>
       </c>
       <c r="W104" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y104" s="2" t="inlineStr">
-        <is>
-          <t>2C→2B·13d ← 2B→2C·19d</t>
-        </is>
-      </c>
+          <t>2C(减速·顶背离)</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
       <c r="Z104" s="2" t="inlineStr"/>
       <c r="AA104" s="2" t="inlineStr"/>
       <c r="AB104" s="2" t="n">
@@ -15922,11 +15962,11 @@
         </is>
       </c>
       <c r="W105" s="2" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr"/>
@@ -16065,20 +16105,20 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W106" s="2" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B(纠缠·底背离)</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>4A→1·1d ← 3B→4A·17d</t>
+          <t>1A→1B·9d</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr"/>
@@ -16222,12 +16262,12 @@
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d</t>
+          <t>2C→2A·13d ← 2B→2C·16d</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr"/>
@@ -16363,22 +16403,18 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W108" s="2" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="Y108" s="2" t="inlineStr">
-        <is>
-          <t>1C→1B·1d ← 1B→1C·4d ← 4B→1B·8d</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
       <c r="Z108" s="2" t="inlineStr"/>
       <c r="AA108" s="2" t="inlineStr"/>
       <c r="AB108" s="2" t="inlineStr">
@@ -16526,18 +16562,14 @@
         </is>
       </c>
       <c r="W109" s="2" t="n">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="Y109" s="2" t="inlineStr">
-        <is>
-          <t>2B→2C·15d ← 2C→2B·16d</t>
-        </is>
-      </c>
+          <t>2C(延伸·顶背离)</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
       <c r="Z109" s="2" t="inlineStr"/>
       <c r="AA109" s="2" t="inlineStr"/>
       <c r="AB109" s="2" t="n">
@@ -16675,11 +16707,11 @@
         </is>
       </c>
       <c r="W110" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr"/>
@@ -16808,22 +16840,18 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W111" s="2" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y111" s="2" t="inlineStr">
-        <is>
-          <t>4B→1·4d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
       <c r="Z111" s="2" t="inlineStr"/>
       <c r="AA111" s="2" t="inlineStr"/>
       <c r="AB111" s="2" t="inlineStr">
@@ -16965,11 +16993,11 @@
         </is>
       </c>
       <c r="W112" s="2" t="n">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="X112" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y112" s="2" t="inlineStr"/>
@@ -17102,14 +17130,18 @@
         </is>
       </c>
       <c r="W113" s="2" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="X113" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y113" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>2A→3·1d ← 2C→2A·11d</t>
+        </is>
+      </c>
       <c r="Z113" s="2" t="inlineStr"/>
       <c r="AA113" s="2" t="inlineStr"/>
       <c r="AB113" s="2" t="inlineStr"/>
@@ -17239,20 +17271,20 @@
       </c>
       <c r="V114" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W114" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="X114" s="2" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>1B→4B·16d ← 1→1B·18d ← 4B→1·20d</t>
+          <t>1A→4·1d</t>
         </is>
       </c>
       <c r="Z114" s="2" t="inlineStr"/>
@@ -17386,23 +17418,27 @@
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W115" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>2B→1·3d ← 1→2B·13d ← 2B→1·15d</t>
-        </is>
-      </c>
-      <c r="Z115" s="2" t="inlineStr"/>
+          <t>1B→2A·4d</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
       <c r="AA115" s="2" t="inlineStr"/>
       <c r="AB115" s="2" t="inlineStr"/>
       <c r="AC115" s="2" t="n">
@@ -17551,11 +17587,11 @@
         </is>
       </c>
       <c r="W116" s="2" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X116" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y116" s="2" t="inlineStr"/>
@@ -17696,11 +17732,11 @@
         </is>
       </c>
       <c r="W117" s="2" t="n">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="X117" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y117" s="2" t="inlineStr"/>
@@ -17835,11 +17871,11 @@
         </is>
       </c>
       <c r="W118" s="2" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="X118" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y118" s="2" t="inlineStr"/>
@@ -17984,7 +18020,7 @@
         </is>
       </c>
       <c r="W119" s="2" t="n">
-        <v>52</v>
+        <v>272</v>
       </c>
       <c r="X119" s="2" t="inlineStr">
         <is>
@@ -17993,7 +18029,7 @@
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·5d ← 2B→2C·7d</t>
+          <t>2C→2B·3d</t>
         </is>
       </c>
       <c r="Z119" s="2" t="inlineStr"/>
@@ -18131,14 +18167,18 @@
         </is>
       </c>
       <c r="W120" s="2" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="X120" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y120" s="2" t="inlineStr"/>
+          <t>2C(顶背离)</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·3d ← 2C→2A·20d</t>
+        </is>
+      </c>
       <c r="Z120" s="2" t="inlineStr"/>
       <c r="AA120" s="2" t="inlineStr"/>
       <c r="AB120" s="2" t="inlineStr"/>
@@ -18264,20 +18304,20 @@
       </c>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W121" s="2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="X121" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>4A→4B·4d</t>
+          <t>1B→1A·12d</t>
         </is>
       </c>
       <c r="Z121" s="2" t="inlineStr"/>
@@ -18415,16 +18455,16 @@
         </is>
       </c>
       <c r="W122" s="2" t="n">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="X122" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 1→2B·18d</t>
+          <t>2A→2B·5d</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr"/>
@@ -18560,18 +18600,14 @@
         </is>
       </c>
       <c r="W123" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="X123" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y123" s="2" t="inlineStr">
-        <is>
-          <t>3A→2B·6d ← 2B→3A·10d</t>
-        </is>
-      </c>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
       <c r="Z123" s="2" t="inlineStr"/>
       <c r="AA123" s="2" t="inlineStr"/>
       <c r="AB123" s="2" t="inlineStr"/>
@@ -18703,11 +18739,11 @@
         </is>
       </c>
       <c r="W124" s="2" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y124" s="2" t="inlineStr"/>
@@ -18844,16 +18880,16 @@
         </is>
       </c>
       <c r="W125" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="X125" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y125" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·7d ← 1→2A·18d</t>
+          <t>3→2A·4d ← 4→3·20d</t>
         </is>
       </c>
       <c r="Z125" s="2" t="inlineStr"/>
@@ -19001,16 +19037,16 @@
         </is>
       </c>
       <c r="W126" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="X126" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y126" s="2" t="inlineStr">
         <is>
-          <t>1→4B·14d</t>
+          <t>1A→4·6d ← 1B→1A·15d</t>
         </is>
       </c>
       <c r="Z126" s="2" t="inlineStr"/>
@@ -19160,11 +19196,11 @@
         </is>
       </c>
       <c r="W127" s="2" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="X127" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸·减速)</t>
         </is>
       </c>
       <c r="Y127" s="2" t="inlineStr"/>
@@ -19291,20 +19327,20 @@
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W128" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="X128" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>2B→1·3d ← 2A→2B·8d ← 3A→2A·9d</t>
+          <t>1B→3·17d</t>
         </is>
       </c>
       <c r="Z128" s="2" t="inlineStr"/>
@@ -19442,14 +19478,18 @@
         </is>
       </c>
       <c r="W129" s="2" t="n">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="X129" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y129" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·15d</t>
+        </is>
+      </c>
       <c r="Z129" s="2" t="inlineStr"/>
       <c r="AA129" s="2" t="inlineStr"/>
       <c r="AB129" s="2" t="inlineStr"/>
@@ -19591,11 +19631,11 @@
         </is>
       </c>
       <c r="W130" s="2" t="n">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="X130" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸·减速)</t>
         </is>
       </c>
       <c r="Y130" s="2" t="inlineStr"/>
@@ -19734,7 +19774,7 @@
         </is>
       </c>
       <c r="W131" s="2" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="X131" s="2" t="inlineStr">
         <is>
@@ -19873,20 +19913,20 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W132" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X132" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y132" s="2" t="inlineStr">
         <is>
-          <t>2B→1·15d</t>
+          <t>3→1B·1d ← 2A→3·9d ← 2C→2A·20d</t>
         </is>
       </c>
       <c r="Z132" s="2" t="inlineStr"/>
@@ -20036,14 +20076,18 @@
         </is>
       </c>
       <c r="W133" s="2" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="X133" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y133" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·15d</t>
+        </is>
+      </c>
       <c r="Z133" s="2" t="inlineStr"/>
       <c r="AA133" s="2" t="inlineStr"/>
       <c r="AB133" s="2" t="n">
@@ -20177,7 +20221,7 @@
         </is>
       </c>
       <c r="W134" s="2" t="n">
-        <v>339</v>
+        <v>272</v>
       </c>
       <c r="X134" s="2" t="inlineStr">
         <is>
@@ -20186,7 +20230,7 @@
       </c>
       <c r="Y134" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·5d ← 2B→2C·20d</t>
+          <t>2C→2B·4d ← 2B→2C·20d</t>
         </is>
       </c>
       <c r="Z134" s="2" t="inlineStr"/>
@@ -20318,20 +20362,20 @@
       </c>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W135" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="X135" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y135" s="2" t="inlineStr">
         <is>
-          <t>3A→1B·6d ← 2B→3A·18d</t>
+          <t>2B→2C·16d ← 2A→2B·17d</t>
         </is>
       </c>
       <c r="Z135" s="2" t="inlineStr"/>
@@ -20481,11 +20525,11 @@
         </is>
       </c>
       <c r="W136" s="2" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="X136" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y136" s="2" t="inlineStr"/>
@@ -20632,14 +20676,18 @@
         </is>
       </c>
       <c r="W137" s="2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="X137" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y137" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·3d ← 3→2A·14d</t>
+        </is>
+      </c>
       <c r="Z137" s="2" t="inlineStr"/>
       <c r="AA137" s="2" t="inlineStr"/>
       <c r="AB137" s="2" t="n">
@@ -20767,20 +20815,20 @@
       </c>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W138" s="2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="X138" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y138" s="2" t="inlineStr">
         <is>
-          <t>3A→3B·6d ← 3B→3A·7d ← 1→3B·8d</t>
+          <t>2C→2A·2d ← 2B→2C·9d ← 2A→2B·12d</t>
         </is>
       </c>
       <c r="Z138" s="2" t="inlineStr"/>
@@ -20922,14 +20970,18 @@
         </is>
       </c>
       <c r="W139" s="2" t="n">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="X139" s="2" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·4d</t>
+        </is>
+      </c>
       <c r="Z139" s="2" t="inlineStr"/>
       <c r="AA139" s="2" t="inlineStr"/>
       <c r="AB139" s="2" t="inlineStr"/>
@@ -21071,16 +21123,16 @@
         </is>
       </c>
       <c r="W140" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="X140" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y140" s="2" t="inlineStr">
         <is>
-          <t>1→4B·18d ← 4B→1·20d</t>
+          <t>1A→4·6d</t>
         </is>
       </c>
       <c r="Z140" s="2" t="inlineStr"/>
@@ -21220,16 +21272,16 @@
         </is>
       </c>
       <c r="W141" s="2" t="n">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="X141" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y141" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d</t>
+          <t>2C→2B·10d ← 2A→2C·11d</t>
         </is>
       </c>
       <c r="Z141" s="2" t="inlineStr"/>
@@ -21381,11 +21433,11 @@
         </is>
       </c>
       <c r="W142" s="2" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y142" s="2" t="inlineStr"/>
@@ -21524,11 +21576,11 @@
         </is>
       </c>
       <c r="W143" s="2" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="X143" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y143" s="2" t="inlineStr"/>
@@ -21679,14 +21731,18 @@
         </is>
       </c>
       <c r="W144" s="2" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="X144" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="Y144" s="2" t="inlineStr"/>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>2C→2B·1d</t>
+        </is>
+      </c>
       <c r="Z144" s="2" t="inlineStr"/>
       <c r="AA144" s="2" t="inlineStr"/>
       <c r="AB144" s="2" t="inlineStr"/>
@@ -21824,20 +21880,20 @@
       </c>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W145" s="2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="X145" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y145" s="2" t="inlineStr">
         <is>
-          <t>3A→2A·1d ← 2B→3A·9d</t>
+          <t>2A→2C·14d</t>
         </is>
       </c>
       <c r="Z145" s="2" t="inlineStr"/>
@@ -21971,20 +22027,20 @@
       </c>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W146" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X146" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y146" s="2" t="inlineStr">
         <is>
-          <t>1C→3A·1d ← 3A→1C·6d ← 3B→3A·10d</t>
+          <t>1B→3·5d ← 2B→1B·15d ← 2A→2B·19d</t>
         </is>
       </c>
       <c r="Z146" s="2" t="inlineStr"/>
@@ -22118,16 +22174,16 @@
         </is>
       </c>
       <c r="W147" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="X147" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y147" s="2" t="inlineStr">
         <is>
-          <t>2B→2C·5d ← 2C→2B·14d ← 2B→2C·16d</t>
+          <t>2A→2C·10d</t>
         </is>
       </c>
       <c r="Z147" s="2" t="inlineStr"/>
@@ -22271,7 +22327,7 @@
         </is>
       </c>
       <c r="W148" s="2" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="X148" s="2" t="inlineStr">
         <is>
@@ -22280,7 +22336,7 @@
       </c>
       <c r="Y148" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·3d ← 3A→2A·5d ← 2B→3A·16d</t>
+          <t>2C→2B·7d</t>
         </is>
       </c>
       <c r="Z148" s="2" t="inlineStr"/>
@@ -22406,20 +22462,20 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W149" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X149" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y149" s="2" t="inlineStr">
         <is>
-          <t>1→3B·17d</t>
+          <t>1A→4·14d</t>
         </is>
       </c>
       <c r="Z149" s="2" t="inlineStr"/>
@@ -22569,18 +22625,14 @@
         </is>
       </c>
       <c r="W150" s="2" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="Y150" s="2" t="inlineStr">
-        <is>
-          <t>2B→2C·11d ← 2C→2B·12d</t>
-        </is>
-      </c>
+          <t>2C(延伸·减速)</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
       <c r="Z150" s="2" t="inlineStr"/>
       <c r="AA150" s="2" t="inlineStr"/>
       <c r="AB150" s="2" t="inlineStr"/>
@@ -22714,23 +22766,19 @@
         </is>
       </c>
       <c r="W151" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X151" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y151" s="2" t="inlineStr">
         <is>
-          <t>1→2B·10d ← 2B→1·11d ← 1→2B·12d</t>
-        </is>
-      </c>
-      <c r="Z151" s="2" t="inlineStr">
-        <is>
-          <t>10d</t>
-        </is>
-      </c>
+          <t>3→2A·9d</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr"/>
       <c r="AA151" s="2" t="inlineStr"/>
       <c r="AB151" s="2" t="inlineStr"/>
       <c r="AC151" s="2" t="inlineStr">
@@ -22863,20 +22911,20 @@
       </c>
       <c r="V152" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W152" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="X152" s="2" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y152" s="2" t="inlineStr">
         <is>
-          <t>2A→1B·9d ← 2B→2A·19d</t>
+          <t>2C→2A·5d ← 2A→2C·16d</t>
         </is>
       </c>
       <c r="Z152" s="2" t="inlineStr"/>
@@ -23008,20 +23056,20 @@
       </c>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W153" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="X153" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y153" s="2" t="inlineStr">
         <is>
-          <t>1→4B·1d ← 4B→1·4d ← 1→4B·6d</t>
+          <t>3→2A·7d</t>
         </is>
       </c>
       <c r="Z153" s="2" t="inlineStr"/>
@@ -23163,16 +23211,16 @@
         </is>
       </c>
       <c r="W154" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X154" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>1→3B·11d ← 2B→1·16d ← 1→2B·20d</t>
+          <t>2A→3·5d ← 2C→2A·11d ← 2B→2C·17d</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr"/>
@@ -23304,20 +23352,20 @@
       </c>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W155" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="X155" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y155" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·1d ← 2A→3B·20d</t>
+          <t>3→1B·11d ← 2A→3·15d</t>
         </is>
       </c>
       <c r="Z155" s="2" t="inlineStr"/>
@@ -23453,20 +23501,20 @@
       </c>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W156" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X156" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y156" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·4d ← 1→2A·11d ← 4B→1·20d</t>
+          <t>4→1B·15d</t>
         </is>
       </c>
       <c r="Z156" s="2" t="inlineStr"/>
@@ -23606,14 +23654,18 @@
         </is>
       </c>
       <c r="W157" s="2" t="n">
-        <v>318</v>
+        <v>228</v>
       </c>
       <c r="X157" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y157" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·13d ← 2C→2B·18d</t>
+        </is>
+      </c>
       <c r="Z157" s="2" t="inlineStr"/>
       <c r="AA157" s="2" t="inlineStr"/>
       <c r="AB157" s="2" t="n">
@@ -23739,20 +23791,20 @@
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W158" s="2" t="n">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y158" s="2" t="inlineStr">
         <is>
-          <t>2A→3A·15d ← 2B→2A·18d</t>
+          <t>2B→2C·17d</t>
         </is>
       </c>
       <c r="Z158" s="2" t="inlineStr"/>
@@ -23886,11 +23938,11 @@
         </is>
       </c>
       <c r="W159" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="X159" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y159" s="2" t="inlineStr"/>
@@ -24035,16 +24087,16 @@
         </is>
       </c>
       <c r="W160" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="X160" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y160" s="2" t="inlineStr">
         <is>
-          <t>2B→2C·7d ← 1B→2B·18d</t>
+          <t>2A→2C·19d</t>
         </is>
       </c>
       <c r="Z160" s="2" t="inlineStr"/>
@@ -24178,16 +24230,16 @@
         </is>
       </c>
       <c r="W161" s="2" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="X161" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y161" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·4d ← 2B→2C·9d ← 2C→2B·12d</t>
+          <t>2A→2C·1d ← 3→2A·12d ← 1B→3·17d</t>
         </is>
       </c>
       <c r="Z161" s="2" t="inlineStr"/>
@@ -24337,11 +24389,11 @@
         </is>
       </c>
       <c r="W162" s="2" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="X162" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y162" s="2" t="inlineStr"/>
@@ -24478,11 +24530,11 @@
         </is>
       </c>
       <c r="W163" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="X163" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y163" s="2" t="inlineStr"/>
@@ -24617,14 +24669,18 @@
         </is>
       </c>
       <c r="W164" s="2" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="X164" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="Y164" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>1A→4·6d</t>
+        </is>
+      </c>
       <c r="Z164" s="2" t="inlineStr"/>
       <c r="AA164" s="2" t="inlineStr"/>
       <c r="AB164" s="2" t="n">
@@ -24877,7 +24933,7 @@
         </is>
       </c>
       <c r="W166" s="2" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
@@ -25018,14 +25074,18 @@
         </is>
       </c>
       <c r="W167" s="2" t="n">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="X167" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y167" s="2" t="inlineStr"/>
+          <t>2C(减速)</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>2B→2C·17d</t>
+        </is>
+      </c>
       <c r="Z167" s="2" t="inlineStr"/>
       <c r="AA167" s="2" t="inlineStr"/>
       <c r="AB167" s="2" t="n">
@@ -25161,18 +25221,14 @@
         </is>
       </c>
       <c r="W168" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="Y168" s="2" t="inlineStr">
-        <is>
-          <t>4A→4B·20d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
       <c r="Z168" s="2" t="inlineStr"/>
       <c r="AA168" s="2" t="inlineStr"/>
       <c r="AB168" s="2" t="inlineStr"/>
@@ -25312,22 +25368,18 @@
       </c>
       <c r="V169" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W169" s="2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X169" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y169" s="2" t="inlineStr">
-        <is>
-          <t>4B→1·7d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
       <c r="Z169" s="2" t="inlineStr"/>
       <c r="AA169" s="2" t="inlineStr"/>
       <c r="AB169" s="2" t="n">
@@ -25463,16 +25515,16 @@
         </is>
       </c>
       <c r="W170" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y170" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·18d</t>
+          <t>2B→2C·1d ← 2C→2B·5d</t>
         </is>
       </c>
       <c r="Z170" s="2" t="inlineStr"/>
@@ -25614,16 +25666,16 @@
         </is>
       </c>
       <c r="W171" s="2" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="X171" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y171" s="2" t="inlineStr">
         <is>
-          <t>1→4B·2d ← 4B→1·4d ← 1→4B·6d</t>
+          <t>4→1B·2d</t>
         </is>
       </c>
       <c r="Z171" s="2" t="inlineStr"/>
@@ -25769,7 +25821,7 @@
         </is>
       </c>
       <c r="W172" s="2" t="n">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
@@ -25920,11 +25972,11 @@
         </is>
       </c>
       <c r="W173" s="2" t="n">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸)</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr"/>
@@ -26071,7 +26123,7 @@
         </is>
       </c>
       <c r="W174" s="2" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
@@ -26080,7 +26132,7 @@
       </c>
       <c r="Y174" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·7d</t>
+          <t>2C→2B·5d ← 2B→2C·6d ← 2C→2B·7d</t>
         </is>
       </c>
       <c r="Z174" s="2" t="inlineStr"/>
@@ -26214,11 +26266,11 @@
         </is>
       </c>
       <c r="W175" s="2" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速)</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr"/>
@@ -26351,20 +26403,20 @@
       </c>
       <c r="V176" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W176" s="2" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·15d</t>
+          <t>3→1A·1d</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr"/>
@@ -26508,11 +26560,11 @@
         </is>
       </c>
       <c r="W177" s="2" t="n">
-        <v>335</v>
+        <v>272</v>
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2C(延伸·减速)</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr"/>
@@ -26639,20 +26691,20 @@
       </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W178" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>1→3B·7d</t>
+          <t>1A→4·3d ← 1B→1A·15d</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr"/>
@@ -26786,16 +26838,16 @@
         </is>
       </c>
       <c r="W179" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>2B→3A·1d</t>
+          <t>2C→2A·3d</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr"/>
@@ -26927,22 +26979,18 @@
       </c>
       <c r="V180" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W180" s="2" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y180" s="2" t="inlineStr">
-        <is>
-          <t>4B→1·7d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
       <c r="Z180" s="2" t="inlineStr"/>
       <c r="AA180" s="2" t="inlineStr"/>
       <c r="AB180" s="2" t="n">
@@ -27078,16 +27126,16 @@
         </is>
       </c>
       <c r="W181" s="2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(减速·顶背离)</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·15d ← 2B→2C·16d ← 2C→2B·17d</t>
+          <t>2A→2C·14d</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr"/>
@@ -27221,20 +27269,20 @@
       </c>
       <c r="V182" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W182" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>1B→4B·2d ← 2A→1B·3d ← 4B→2A·4d</t>
+          <t>2C→1B·10d</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr"/>
@@ -27364,20 +27412,20 @@
       </c>
       <c r="V183" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W183" s="2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>1B→4A·1d ← 3A→1B·8d ← 2B→3A·15d</t>
+          <t>2C→2A·1d ← 2A→2C·12d</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr"/>
@@ -27521,19 +27569,23 @@
         </is>
       </c>
       <c r="W184" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>2B→2C·7d ← 2A→2B·11d ← 1→2A·17d</t>
-        </is>
-      </c>
-      <c r="Z184" s="2" t="inlineStr"/>
+          <t>1B→2A·7d</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
       <c r="AA184" s="2" t="inlineStr"/>
       <c r="AB184" s="2" t="n">
         <v>-1</v>
@@ -27626,7 +27678,7 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>3599</v>
+        <v>3610</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>10.44</v>
@@ -27668,11 +27720,11 @@
         </is>
       </c>
       <c r="W185" s="2" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr"/>
@@ -27683,23 +27735,23 @@
       <c r="AD185" s="2" t="inlineStr"/>
       <c r="AE185" s="2" t="inlineStr"/>
       <c r="AF185" s="2" t="n">
-        <v>-12.22</v>
+        <v>-12.16</v>
       </c>
       <c r="AG185" s="2" t="n">
-        <v>-23.67</v>
+        <v>-22.81</v>
       </c>
       <c r="AH185" s="2" t="n"/>
       <c r="AI185" s="2" t="n">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="AJ185" s="2" t="n">
-        <v>-0.75</v>
+        <v>0.11</v>
       </c>
       <c r="AK185" s="2" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="AL185" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM185" s="2" t="inlineStr"/>
       <c r="AN185" s="2" t="inlineStr"/>
@@ -27711,40 +27763,40 @@
         </is>
       </c>
       <c r="AR185" s="2" t="n">
-        <v>3679.2</v>
+        <v>3681.4</v>
       </c>
       <c r="AS185" s="2" t="n">
-        <v>3752</v>
+        <v>3753.1</v>
       </c>
       <c r="AT185" s="2" t="n">
-        <v>3785.924</v>
+        <v>3786.474</v>
       </c>
       <c r="AU185" s="2" t="n">
-        <v>3779.277</v>
+        <v>3779.644</v>
       </c>
       <c r="AV185" s="2" t="n">
-        <v>3880.494</v>
+        <v>3880.714</v>
       </c>
       <c r="AW185" s="2" t="n">
-        <v>3824.026</v>
+        <v>3824.136</v>
       </c>
       <c r="AX185" s="2" t="n">
-        <v>4180.703</v>
+        <v>4180.758</v>
       </c>
       <c r="AY185" s="2" t="n">
-        <v>-1.2258</v>
+        <v>-1.2109</v>
       </c>
       <c r="AZ185" s="2" t="n">
-        <v>-0.215</v>
+        <v>-0.2075</v>
       </c>
       <c r="BA185" s="2" t="n">
-        <v>-0.1742</v>
+        <v>-0.1713</v>
       </c>
       <c r="BB185" s="2" t="n">
-        <v>-0.2738</v>
+        <v>-0.2723</v>
       </c>
       <c r="BC185" s="2" t="n">
-        <v>-0.1222</v>
+        <v>-0.1216</v>
       </c>
     </row>
     <row r="186">
@@ -27801,11 +27853,11 @@
         </is>
       </c>
       <c r="W186" s="2" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(顶背离)</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr"/>
@@ -27934,20 +27986,20 @@
       </c>
       <c r="V187" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W187" s="2" t="n">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>2B→1·3d ← 2C→2B·15d ← 2B→2C·18d</t>
+          <t>2C→2B·13d ← 2A→2C·14d</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr"/>
@@ -28079,11 +28131,11 @@
         </is>
       </c>
       <c r="W188" s="2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr"/>
@@ -28220,18 +28272,14 @@
         </is>
       </c>
       <c r="W189" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="Y189" s="2" t="inlineStr">
-        <is>
-          <t>4B→1A·1d ← 1B→4B·3d ← 4B→1B·4d</t>
-        </is>
-      </c>
+          <t>1B(纠缠)</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
       <c r="Z189" s="2" t="inlineStr"/>
       <c r="AA189" s="2" t="inlineStr"/>
       <c r="AB189" s="2" t="inlineStr"/>
@@ -28359,22 +28407,18 @@
       </c>
       <c r="V190" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W190" s="2" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="Y190" s="2" t="inlineStr">
-        <is>
-          <t>1→1A·6d ← 1A→1·7d ← 1→1A·8d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
       <c r="Z190" s="2" t="inlineStr"/>
       <c r="AA190" s="2" t="inlineStr"/>
       <c r="AB190" s="2" t="inlineStr"/>
@@ -28504,16 +28548,16 @@
         </is>
       </c>
       <c r="W191" s="2" t="n">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>2C(顶背离)</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·13d ← 2B→2C·18d</t>
+          <t>2A→2C·17d</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr"/>
@@ -28643,20 +28687,20 @@
       </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W192" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>1→3A·8d ← 2B→1·11d</t>
+          <t>2A→2B·9d ← 3→2A·20d</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr"/>
@@ -28782,7 +28826,7 @@
       </c>
       <c r="V193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W193" s="2" t="n">
@@ -28790,12 +28834,12 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>1B(纠缠)</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·12d ← 1→2A·17d ← 4B→1·20d</t>
+          <t>4→1B·17d</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr"/>
@@ -28935,16 +28979,16 @@
         </is>
       </c>
       <c r="W194" s="2" t="n">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>2B→1·1d ← 2C→2B·14d ← 2B→2C·15d</t>
+          <t>2C→2B·3d ← 2B→2C·9d ← 2C→2B·10d</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr"/>
@@ -29072,28 +29116,24 @@
       </c>
       <c r="V195" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W195" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>4A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>3B→4A·9d</t>
+          <t>1B→3·15d</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr"/>
-      <c r="AA195" s="2" t="inlineStr">
-        <is>
-          <t>9d</t>
-        </is>
-      </c>
+      <c r="AA195" s="2" t="inlineStr"/>
       <c r="AB195" s="2" t="inlineStr"/>
       <c r="AC195" s="2" t="inlineStr"/>
       <c r="AD195" s="2" t="inlineStr"/>
@@ -29225,11 +29265,11 @@
         </is>
       </c>
       <c r="W196" s="2" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr"/>
@@ -29360,18 +29400,14 @@
         </is>
       </c>
       <c r="W197" s="2" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="Y197" s="2" t="inlineStr">
-        <is>
-          <t>1A→4B·6d ← 4A→1A·10d</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
       <c r="Z197" s="2" t="inlineStr"/>
       <c r="AA197" s="2" t="inlineStr"/>
       <c r="AB197" s="2" t="inlineStr"/>
@@ -29822,35 +29858,35 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stage (Weinstein 大阶段, MA150=30周线为锚, 内部11子档判定后归并为大阶段): 1=筑底 2=上行 3=做顶 4=下行; NA=历史不足(&lt;218日)</t>
+          <t xml:space="preserve">  Stage (Weinstein 大阶段 v2引擎 2026-10-15: EMA30W(150日EMA)锚+双确认斜率): 锚斜率=EMA30W变化年化(4周×13 与 13周×3.88 双确认)。2=双确认均&gt;+8% 4=均&lt;-6%(不对称,跌快于涨); 放平带(-6%~+8%)按52周位置+价格确认分1/3: 3=pos52w&gt;0.55且价≥0.95×EMA30W 1=pos&lt;0.45且价≤1.05×EMA30W, 0.45~0.55滞回维持原状态。NA=历史&lt;300交易日</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stage持续: 处于当前大阶段的天数 (距最近一次大阶段变化)</t>
+          <t xml:space="preserve">  Stage持续: 处于当前大阶段的天数 (3交易日防抖, 转换日期回填至真实穿越点)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1→2 / 3→4: 大阶段转换信号, 显示'Nd'=N个交易日前触发 (如'3d'=3天前刚完成1→2, 进场关注; 3→4=离场/回避)。触发后≤10个交易日持续显示(追溯保留, 同东吴B/S≤10天口径), 更早的转换不显示但Stage持续列可推</t>
+          <t xml:space="preserve">  1→2 / 3→4: 大阶段转换信号, 'Nd'=N个交易日前触发。触发后≤10个交易日持续显示(追溯保留); 转换后又跌回/回升的信号自动作废</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档: 当前11子档 (如 2A)。11子档: 1A卖压衰竭(均线下·走平·52周低位) 1筑底未定型 1B筑底后期(站上走平均线) 1C突破前夜(距60日收盘高点≤5%) 2A刚突破60日新高(均线未上弯·最佳买点) 2B趋势运行(均线上行·距均线≤30%) 2C趋势晚期(距均线&gt;30%忌追高) 3A做顶早期(均线上·走平·前期上行) 3B做顶后期(跌回均线下) 4A下行初段 4B下行确立</t>
+          <t xml:space="preserve">  子档(v2): 1A=价&lt;EMA10W且EMA10W≤EMA30W 1B=站上EMA10W或金叉 2A=修复态(2区回调未满配)或刚确立(进2区/金叉≤10日) 2B=满配多头排列(slope10&gt;0·EMA10W&gt;EMA30W·10日前也是) 2C=满配+延伸/减速/顶背离; 3/4不分档。括号内标记: 1B→纠缠(&lt;3%)·周线底背离; 2C→延伸(&gt;25%)·减速·顶背离</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档变化: 近20日内最近3次子档转换, 新→旧 (如 '1C→2A·5d ← 1→1C·6d')。贴着30周线拉锯的票会看到密集往返(如2B↔1逐日), 本身即是边界争夺信号</t>
+          <t xml:space="preserve">  子档变化: 近20日内最近3次子档转换, 新→旧 (如 '1A→1B·5d ← 2A→2B·12d')</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2722.5</v>
+        <v>2667.5</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>14.39</v>
@@ -889,20 +889,20 @@
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr"/>
       <c r="AG2" s="2" t="n">
-        <v>80.36</v>
+        <v>79.84</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.72</v>
+        <v>-1.29</v>
       </c>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="2" t="n">
-        <v>-21.97</v>
+        <v>-23.98</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>-12.39</v>
+        <v>-14.39</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AM2" s="2" t="n">
         <v>11</v>
@@ -923,40 +923,40 @@
         </is>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>3002</v>
+        <v>2991</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>3312.6</v>
+        <v>3307.1</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>3198.925</v>
+        <v>3196.175</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>3173.317</v>
+        <v>3171.483</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>3334.87</v>
+        <v>3333.77</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>3678.957</v>
+        <v>3678.407</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>2784.444</v>
+        <v>2784.169</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>-1.4571</v>
+        <v>-1.541</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>-0.0633</v>
+        <v>-0.108</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>-0.3266</v>
+        <v>-0.3437</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>-0.0128</v>
+        <v>-0.0205</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.8036</v>
+        <v>0.7984</v>
       </c>
     </row>
     <row r="3">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15465</v>
+        <v>15205</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>89.05</v>
@@ -994,20 +994,20 @@
         <v>-9</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>0110111100</t>
+          <t>0110011100</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -1045,23 +1045,23 @@
       </c>
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="n">
-        <v>97.34</v>
+        <v>96.84</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>18.79</v>
+        <v>16.83</v>
       </c>
       <c r="AI3" s="2" t="n"/>
       <c r="AJ3" s="2" t="n">
-        <v>-10.06</v>
+        <v>-12.02</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>6.3</v>
+        <v>4.34</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>56.5</v>
+        <v>55.9</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr"/>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>16161</v>
+        <v>16109</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>16953.5</v>
+        <v>16927.5</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>15668.612</v>
+        <v>15655.612</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>15595.575</v>
+        <v>15586.908</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>15799.745</v>
+        <v>15794.545</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>16256.572</v>
+        <v>16253.972</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>13604.666</v>
+        <v>13603.366</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>2.195</v>
+        <v>2.1119</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>0.898</v>
+        <v>0.8541</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>1.1007</v>
+        <v>1.0832</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>-0.0832</v>
+        <v>-0.0915</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9684</v>
       </c>
     </row>
     <row r="4">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9627</v>
+        <v>9607</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>107.99</v>
@@ -1191,20 +1191,20 @@
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="inlineStr"/>
       <c r="AG4" s="2" t="n">
-        <v>130.25</v>
+        <v>130.18</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>38.79</v>
+        <v>38.53</v>
       </c>
       <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="2" t="n">
-        <v>-26.11</v>
+        <v>-26.37</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>-17.21</v>
+        <v>-17.47</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="AM4" s="2" t="n">
         <v>12</v>
@@ -1223,40 +1223,40 @@
         </is>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>10294</v>
+        <v>10290</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>11231.5</v>
+        <v>11229.5</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>10917.029</v>
+        <v>10916.029</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>10686.014</v>
+        <v>10685.347</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>10341.916</v>
+        <v>10341.516</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>10262.627</v>
+        <v>10262.427</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>7453.667</v>
+        <v>7453.567</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>-2.3735</v>
+        <v>-2.3824</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>0.1752</v>
+        <v>0.1705</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>1.432</v>
+        <v>1.4299</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>1.3025</v>
+        <v>1.3018</v>
       </c>
     </row>
     <row r="5">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6046</v>
+        <v>6026</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>18.68</v>
@@ -1323,7 +1323,7 @@
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3→4·5d ← 1→3·8d</t>
+          <t>4+→4·2d ← 4→4+·3d ← 3→4·5d</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="n">
-        <v>27.81</v>
+        <v>27.73</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>-8.85</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="AI5" s="2" t="n"/>
       <c r="AJ5" s="2" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="AN5" s="2" t="inlineStr"/>
       <c r="AO5" s="2" t="n">
@@ -1373,40 +1373,40 @@
         </is>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>6068.2</v>
+        <v>6064.2</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>6126.5</v>
+        <v>6124.5</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>5978.545</v>
+        <v>5977.545</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>5911.45</v>
+        <v>5910.783</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>5992.289</v>
+        <v>5991.889</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>6527.814</v>
+        <v>6527.614</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>6261.537</v>
+        <v>6261.437</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>0.8254</v>
+        <v>0.8081</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7719</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.2052</v>
+        <v>0.2017</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>-0.3475</v>
+        <v>-0.349</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.2781</v>
+        <v>0.2773</v>
       </c>
     </row>
     <row r="6">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8356</v>
+        <v>8326</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>70.48999999999999</v>
@@ -1447,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0010000000</t>
+          <t>0010000010</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1485,20 +1485,20 @@
       </c>
       <c r="AF6" s="2" t="inlineStr"/>
       <c r="AG6" s="2" t="n">
-        <v>45.18</v>
+        <v>45.09</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>-7.16</v>
+        <v>-7.47</v>
       </c>
       <c r="AI6" s="2" t="n"/>
       <c r="AJ6" s="2" t="n">
-        <v>-6.07</v>
+        <v>-6.38</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AM6" s="2" t="n">
         <v>15</v>
@@ -1519,40 +1519,40 @@
         </is>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>8762</v>
+        <v>8756</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>8992.9</v>
+        <v>8989.9</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8640.85</v>
+        <v>8639.35</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>8505.433000000001</v>
+        <v>8504.433000000001</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>8704.959999999999</v>
+        <v>8704.360000000001</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>9564.022999999999</v>
+        <v>9563.723</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>8825.906999999999</v>
+        <v>8825.757</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>0.7812</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>0.9348</v>
+        <v>0.9257</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>-0.0911</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>-0.4201</v>
+        <v>-0.4217</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.4518</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="7">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6242</v>
+        <v>6279</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>75.40000000000001</v>
@@ -1592,7 +1592,7 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -1645,20 +1645,20 @@
       <c r="AE7" s="2" t="inlineStr"/>
       <c r="AF7" s="2" t="inlineStr"/>
       <c r="AG7" s="2" t="n">
-        <v>41.65</v>
+        <v>41.84</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>8.93</v>
+        <v>9.6</v>
       </c>
       <c r="AI7" s="2" t="n"/>
       <c r="AJ7" s="2" t="n">
-        <v>12.59</v>
+        <v>13.26</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>8.07</v>
+        <v>8.74</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>89</v>
@@ -1675,40 +1675,40 @@
         </is>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>6024</v>
+        <v>6031.4</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>5870.3</v>
+        <v>5874</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>5831.652</v>
+        <v>5833.502</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>5772.842</v>
+        <v>5774.076</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>5678.129</v>
+        <v>5678.869</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>5406.608</v>
+        <v>5406.978</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>5332.04</v>
+        <v>5332.225</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>1.0627</v>
+        <v>1.0962</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>0.9877</v>
+        <v>1.0045</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.3728</v>
+        <v>0.3796</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.4223</v>
+        <v>0.4258</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.4165</v>
+        <v>0.4184</v>
       </c>
     </row>
     <row r="8">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2402.5</v>
+        <v>2428</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>39.9</v>
@@ -1746,19 +1746,19 @@
         <v>1</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111101101</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1111101101</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1793,25 +1793,29 @@
       <c r="AE8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="AG8" s="2" t="n">
-        <v>16.76</v>
+        <v>17.05</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>-0.99</v>
+        <v>0.08</v>
       </c>
       <c r="AI8" s="2" t="n"/>
       <c r="AJ8" s="2" t="n">
-        <v>11.02</v>
+        <v>12.1</v>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>3.36</v>
+        <v>4.43</v>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>74.8</v>
+        <v>75.3</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AN8" s="2" t="inlineStr"/>
       <c r="AO8" s="2" t="inlineStr"/>
@@ -1825,40 +1829,40 @@
         </is>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>2313.9</v>
+        <v>2319</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>2279.65</v>
+        <v>2282.2</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>2296.516</v>
+        <v>2297.791</v>
       </c>
       <c r="AV8" s="2" t="n">
-        <v>2289.794</v>
+        <v>2290.644</v>
       </c>
       <c r="AW8" s="2" t="n">
-        <v>2290.679</v>
+        <v>2291.189</v>
       </c>
       <c r="AX8" s="2" t="n">
-        <v>2212.094</v>
+        <v>2212.349</v>
       </c>
       <c r="AY8" s="2" t="n">
-        <v>2260.002</v>
+        <v>2260.129</v>
       </c>
       <c r="AZ8" s="2" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0051</v>
       </c>
       <c r="BA8" s="2" t="n">
-        <v>0.5534</v>
+        <v>0.5825</v>
       </c>
       <c r="BB8" s="2" t="n">
-        <v>0.2428</v>
+        <v>0.2544</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>0.059</v>
+        <v>0.065</v>
       </c>
       <c r="BD8" s="2" t="n">
-        <v>0.1676</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="9">
@@ -1873,7 +1877,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6357</v>
+        <v>6404</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2.93</v>
@@ -1888,7 +1892,7 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -1921,13 +1925,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·日线纠缠</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·2d</t>
+          <t>4→4+·2d ← 4+→4·16d ← 4→4+·17d</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
@@ -1941,23 +1949,23 @@
       </c>
       <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="n">
-        <v>-32.77</v>
+        <v>-32.62</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>-28.08</v>
+        <v>-27.53</v>
       </c>
       <c r="AI9" s="2" t="n"/>
       <c r="AJ9" s="2" t="n">
-        <v>6.76</v>
+        <v>7.31</v>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.27</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN9" s="2" t="inlineStr">
         <is>
@@ -1975,40 +1983,40 @@
         </is>
       </c>
       <c r="AS9" s="2" t="n">
-        <v>6170.6</v>
+        <v>6180</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>6130.2</v>
+        <v>6134.9</v>
       </c>
       <c r="AU9" s="2" t="n">
-        <v>6290.1</v>
+        <v>6292.45</v>
       </c>
       <c r="AV9" s="2" t="n">
-        <v>6402.233</v>
+        <v>6403.8</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>6614.72</v>
+        <v>6615.66</v>
       </c>
       <c r="AX9" s="2" t="n">
-        <v>7016.541</v>
+        <v>7017.011</v>
       </c>
       <c r="AY9" s="2" t="n">
-        <v>7827.325</v>
+        <v>7827.56</v>
       </c>
       <c r="AZ9" s="2" t="n">
-        <v>-0.5215</v>
+        <v>-0.482</v>
       </c>
       <c r="BA9" s="2" t="n">
-        <v>-0.576</v>
+        <v>-0.5567</v>
       </c>
       <c r="BB9" s="2" t="n">
-        <v>-0.6315</v>
+        <v>-0.6242</v>
       </c>
       <c r="BC9" s="2" t="n">
-        <v>-0.6072</v>
+        <v>-0.6038</v>
       </c>
       <c r="BD9" s="2" t="n">
-        <v>-0.3277</v>
+        <v>-0.3262</v>
       </c>
     </row>
     <row r="10">
@@ -2023,7 +2031,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2731.5</v>
+        <v>2753</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>98.16</v>
@@ -2046,14 +2054,14 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>0100101100</t>
+          <t>0101101100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2093,23 +2101,23 @@
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="n">
-        <v>-30.75</v>
+        <v>-30.55</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>-19.3</v>
+        <v>-18.65</v>
       </c>
       <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="2" t="n">
-        <v>7.16</v>
+        <v>7.81</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>-0.23</v>
+        <v>0.42</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>57.6</v>
+        <v>58.3</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AN10" s="2" t="inlineStr"/>
       <c r="AO10" s="2" t="inlineStr"/>
@@ -2127,40 +2135,40 @@
         </is>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>2648.5</v>
+        <v>2652.8</v>
       </c>
       <c r="AT10" s="2" t="n">
-        <v>2677.55</v>
+        <v>2679.7</v>
       </c>
       <c r="AU10" s="2" t="n">
-        <v>2747.23</v>
+        <v>2748.305</v>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>2745.235</v>
+        <v>2745.952</v>
       </c>
       <c r="AW10" s="2" t="n">
-        <v>2732.009</v>
+        <v>2732.439</v>
       </c>
       <c r="AX10" s="2" t="n">
-        <v>2666.455</v>
+        <v>2666.67</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>2774.757</v>
+        <v>2774.864</v>
       </c>
       <c r="AZ10" s="2" t="n">
-        <v>-1.398</v>
+        <v>-1.3574</v>
       </c>
       <c r="BA10" s="2" t="n">
-        <v>-0.2842</v>
+        <v>-0.2639</v>
       </c>
       <c r="BB10" s="2" t="n">
-        <v>-0.2139</v>
+        <v>-0.2057</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>-0.3075</v>
+        <v>-0.3055</v>
       </c>
     </row>
     <row r="11">
@@ -2175,7 +2183,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12360</v>
+        <v>12435</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6.32</v>
@@ -2239,23 +2247,23 @@
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="n">
-        <v>33.28</v>
+        <v>33.46</v>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>7.51</v>
+        <v>8.19</v>
       </c>
       <c r="AI11" s="2" t="n"/>
       <c r="AJ11" s="2" t="n">
-        <v>10.98</v>
+        <v>11.66</v>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>6.78</v>
+        <v>7.46</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AN11" s="2" t="inlineStr"/>
       <c r="AO11" s="2" t="inlineStr"/>
@@ -2267,40 +2275,40 @@
         </is>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>11845</v>
+        <v>11860</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>11658</v>
+        <v>11665.5</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>11449.75</v>
+        <v>11453.5</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>11570.5</v>
+        <v>11573</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>11812.3</v>
+        <v>11813.8</v>
       </c>
       <c r="AX11" s="2" t="n">
-        <v>11374.778</v>
+        <v>11375.528</v>
       </c>
       <c r="AY11" s="2" t="n">
-        <v>10759.245</v>
+        <v>10759.62</v>
       </c>
       <c r="AZ11" s="2" t="n">
-        <v>1.1559</v>
+        <v>1.1901</v>
       </c>
       <c r="BA11" s="2" t="n">
-        <v>0.3855</v>
+        <v>0.4026</v>
       </c>
       <c r="BB11" s="2" t="n">
-        <v>0.2304</v>
+        <v>0.237</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>0.1426</v>
+        <v>0.146</v>
       </c>
       <c r="BD11" s="2" t="n">
-        <v>0.3328</v>
+        <v>0.3346</v>
       </c>
     </row>
     <row r="12">
@@ -2315,10 +2323,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>100.66</v>
+        <v>101.06</v>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
@@ -2379,23 +2387,23 @@
       <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="inlineStr"/>
       <c r="AG12" s="2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>-6.69</v>
+        <v>-6.61</v>
       </c>
       <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="2" t="n">
-        <v>6.34</v>
+        <v>6.42</v>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>6.74</v>
+        <v>6.82</v>
       </c>
       <c r="AL12" s="2" t="n">
         <v>31.3</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AN12" s="2" t="inlineStr"/>
       <c r="AO12" s="2" t="n">
@@ -2409,40 +2417,40 @@
         </is>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>3424.4</v>
+        <v>3424.8</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>3410.9</v>
+        <v>3411.1</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>3363.79</v>
+        <v>3363.89</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>3323.409</v>
+        <v>3323.476</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>3324.289</v>
+        <v>3324.329</v>
       </c>
       <c r="AX12" s="2" t="n">
-        <v>3394.927</v>
+        <v>3394.947</v>
       </c>
       <c r="AY12" s="2" t="n">
-        <v>3234.783</v>
+        <v>3234.793</v>
       </c>
       <c r="AZ12" s="2" t="n">
-        <v>0.5143</v>
+        <v>0.5174</v>
       </c>
       <c r="BA12" s="2" t="n">
-        <v>0.9356</v>
+        <v>0.9372</v>
       </c>
       <c r="BB12" s="2" t="n">
-        <v>-0.5326</v>
+        <v>-0.532</v>
       </c>
       <c r="BC12" s="2" t="n">
-        <v>0.2354</v>
+        <v>0.2358</v>
       </c>
       <c r="BD12" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="13">
@@ -2457,7 +2465,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3395</v>
+        <v>3387</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>91.12</v>
@@ -2529,20 +2537,20 @@
       <c r="AE13" s="2" t="inlineStr"/>
       <c r="AF13" s="2" t="inlineStr"/>
       <c r="AG13" s="2" t="n">
-        <v>108.24</v>
+        <v>108.18</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>8.68</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AI13" s="2" t="n"/>
       <c r="AJ13" s="2" t="n">
-        <v>-21.55</v>
+        <v>-21.78</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>-26.83</v>
+        <v>-27.06</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="AM13" s="2" t="n">
         <v>17</v>
@@ -2561,40 +2569,40 @@
         </is>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>3729.4</v>
+        <v>3727.8</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>4060.8</v>
+        <v>4060</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>3939.833</v>
+        <v>3939.433</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>3907.887</v>
+        <v>3907.621</v>
       </c>
       <c r="AW13" s="2" t="n">
-        <v>3909.212</v>
+        <v>3909.052</v>
       </c>
       <c r="AX13" s="2" t="n">
-        <v>4102.665</v>
+        <v>4102.585</v>
       </c>
       <c r="AY13" s="2" t="n">
-        <v>3429</v>
+        <v>3428.96</v>
       </c>
       <c r="AZ13" s="2" t="n">
-        <v>-0.7508</v>
+        <v>-0.7609</v>
       </c>
       <c r="BA13" s="2" t="n">
-        <v>-0.6136</v>
+        <v>-0.6188</v>
       </c>
       <c r="BB13" s="2" t="n">
-        <v>1.0062</v>
+        <v>1.0041</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>-0.9028</v>
+        <v>-0.9038</v>
       </c>
       <c r="BD13" s="2" t="n">
-        <v>1.0824</v>
+        <v>1.0818</v>
       </c>
     </row>
     <row r="14">
@@ -2609,7 +2617,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2169</v>
+        <v>2160.5</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>80.95</v>
@@ -2632,14 +2640,14 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>0100000100</t>
+          <t>0000000100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2663,7 +2671,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4→1·3d ← 1→4·11d</t>
+          <t>4→1·3d ← 4+→4·6d ← 1→4+·11d</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
@@ -2675,23 +2683,23 @@
       <c r="AE14" s="2" t="inlineStr"/>
       <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="n">
-        <v>36.61</v>
+        <v>36.52</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>-8.41</v>
+        <v>-8.75</v>
       </c>
       <c r="AI14" s="2" t="n"/>
       <c r="AJ14" s="2" t="n">
-        <v>-5.14</v>
+        <v>-5.48</v>
       </c>
       <c r="AK14" s="2" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN14" s="2" t="inlineStr"/>
       <c r="AO14" s="2" t="n">
@@ -2705,40 +2713,40 @@
         </is>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>2249.5</v>
+        <v>2247.8</v>
       </c>
       <c r="AT14" s="2" t="n">
-        <v>2358.1</v>
+        <v>2357.25</v>
       </c>
       <c r="AU14" s="2" t="n">
-        <v>2254.99</v>
+        <v>2254.565</v>
       </c>
       <c r="AV14" s="2" t="n">
-        <v>2205.84</v>
+        <v>2205.557</v>
       </c>
       <c r="AW14" s="2" t="n">
-        <v>2210.834</v>
+        <v>2210.664</v>
       </c>
       <c r="AX14" s="2" t="n">
-        <v>2484.218</v>
+        <v>2484.133</v>
       </c>
       <c r="AY14" s="2" t="n">
-        <v>2341.923</v>
+        <v>2341.881</v>
       </c>
       <c r="AZ14" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0123</v>
       </c>
       <c r="BA14" s="2" t="n">
-        <v>1.0358</v>
+        <v>1.0258</v>
       </c>
       <c r="BB14" s="2" t="n">
-        <v>0.2048</v>
+        <v>0.2008</v>
       </c>
       <c r="BC14" s="2" t="n">
-        <v>-0.4665</v>
+        <v>-0.4682</v>
       </c>
       <c r="BD14" s="2" t="n">
-        <v>0.3661</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="15">
@@ -2753,7 +2761,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>53600</v>
+        <v>53270</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>67.83</v>
@@ -2770,7 +2778,7 @@
         <v>-9</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -2807,7 +2815,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4+→4·11d ← 4→4+·13d</t>
+          <t>4+→4·7d ← 4→4+·14d</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
@@ -2819,23 +2827,23 @@
       <c r="AE15" s="2" t="inlineStr"/>
       <c r="AF15" s="2" t="inlineStr"/>
       <c r="AG15" s="2" t="n">
-        <v>19.57</v>
+        <v>19.43</v>
       </c>
       <c r="AH15" s="2" t="n">
-        <v>-22.75</v>
+        <v>-23.2</v>
       </c>
       <c r="AI15" s="2" t="n"/>
       <c r="AJ15" s="2" t="n">
-        <v>-6.14</v>
+        <v>-6.6</v>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN15" s="2" t="inlineStr"/>
       <c r="AO15" s="2" t="n">
@@ -2853,40 +2861,40 @@
         </is>
       </c>
       <c r="AS15" s="2" t="n">
-        <v>56984</v>
+        <v>56918</v>
       </c>
       <c r="AT15" s="2" t="n">
-        <v>59696</v>
+        <v>59663</v>
       </c>
       <c r="AU15" s="2" t="n">
-        <v>56886.264</v>
+        <v>56869.764</v>
       </c>
       <c r="AV15" s="2" t="n">
-        <v>55930.065</v>
+        <v>55919.065</v>
       </c>
       <c r="AW15" s="2" t="n">
-        <v>58122.58</v>
+        <v>58115.98</v>
       </c>
       <c r="AX15" s="2" t="n">
-        <v>64902.273</v>
+        <v>64898.973</v>
       </c>
       <c r="AY15" s="2" t="n">
-        <v>65382.936</v>
+        <v>65381.286</v>
       </c>
       <c r="AZ15" s="2" t="n">
-        <v>0.1811</v>
+        <v>0.1522</v>
       </c>
       <c r="BA15" s="2" t="n">
-        <v>0.9912</v>
+        <v>0.9758</v>
       </c>
       <c r="BB15" s="2" t="n">
-        <v>0.118</v>
+        <v>0.112</v>
       </c>
       <c r="BC15" s="2" t="n">
-        <v>-0.2478</v>
+        <v>-0.2504</v>
       </c>
       <c r="BD15" s="2" t="n">
-        <v>0.1957</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="16">
@@ -2901,7 +2909,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4231</v>
+        <v>4211</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>6.28</v>
@@ -2965,20 +2973,20 @@
       <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="inlineStr"/>
       <c r="AG16" s="2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>-21.95</v>
+        <v>-22.3</v>
       </c>
       <c r="AI16" s="2" t="n"/>
       <c r="AJ16" s="2" t="n">
-        <v>-4.53</v>
+        <v>-4.88</v>
       </c>
       <c r="AK16" s="2" t="n">
-        <v>-2.69</v>
+        <v>-3.04</v>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AM16" s="2" t="n">
         <v>12</v>
@@ -2999,40 +3007,40 @@
         </is>
       </c>
       <c r="AS16" s="2" t="n">
-        <v>4480</v>
+        <v>4476</v>
       </c>
       <c r="AT16" s="2" t="n">
-        <v>4638.3</v>
+        <v>4636.3</v>
       </c>
       <c r="AU16" s="2" t="n">
-        <v>4552.75</v>
+        <v>4551.75</v>
       </c>
       <c r="AV16" s="2" t="n">
-        <v>4500.067</v>
+        <v>4499.4</v>
       </c>
       <c r="AW16" s="2" t="n">
-        <v>4835.42</v>
+        <v>4835.02</v>
       </c>
       <c r="AX16" s="2" t="n">
-        <v>5315.53</v>
+        <v>5315.33</v>
       </c>
       <c r="AY16" s="2" t="n">
-        <v>5101.65</v>
+        <v>5101.55</v>
       </c>
       <c r="AZ16" s="2" t="n">
-        <v>-0.6979</v>
+        <v>-0.72</v>
       </c>
       <c r="BA16" s="2" t="n">
-        <v>0.465</v>
+        <v>0.4535</v>
       </c>
       <c r="BB16" s="2" t="n">
-        <v>-0.7992</v>
+        <v>-0.8035</v>
       </c>
       <c r="BC16" s="2" t="n">
-        <v>-0.3371</v>
+        <v>-0.3391</v>
       </c>
       <c r="BD16" s="2" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="17">
@@ -3047,10 +3055,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5010</v>
+        <v>5001</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5.75</v>
+        <v>5.21</v>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
@@ -3119,20 +3127,20 @@
       <c r="AE17" s="2" t="inlineStr"/>
       <c r="AF17" s="2" t="inlineStr"/>
       <c r="AG17" s="2" t="n">
-        <v>10.46</v>
+        <v>10.42</v>
       </c>
       <c r="AH17" s="2" t="n">
-        <v>-14.54</v>
+        <v>-14.67</v>
       </c>
       <c r="AI17" s="2" t="n"/>
       <c r="AJ17" s="2" t="n">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="AK17" s="2" t="n">
-        <v>-3.83</v>
+        <v>-3.97</v>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM17" s="2" t="n">
         <v>16</v>
@@ -3149,40 +3157,40 @@
         </is>
       </c>
       <c r="AS17" s="2" t="n">
-        <v>5085.8</v>
+        <v>5084</v>
       </c>
       <c r="AT17" s="2" t="n">
-        <v>5172.3</v>
+        <v>5171.4</v>
       </c>
       <c r="AU17" s="2" t="n">
-        <v>5171.912</v>
+        <v>5171.462</v>
       </c>
       <c r="AV17" s="2" t="n">
-        <v>5178.524</v>
+        <v>5178.224</v>
       </c>
       <c r="AW17" s="2" t="n">
-        <v>5399.645</v>
+        <v>5399.465</v>
       </c>
       <c r="AX17" s="2" t="n">
-        <v>5622.794</v>
+        <v>5622.704</v>
       </c>
       <c r="AY17" s="2" t="n">
-        <v>5517.682</v>
+        <v>5517.637</v>
       </c>
       <c r="AZ17" s="2" t="n">
-        <v>-0.607</v>
+        <v>-0.6159</v>
       </c>
       <c r="BA17" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.0446</v>
       </c>
       <c r="BB17" s="2" t="n">
-        <v>-0.345</v>
+        <v>-0.3468</v>
       </c>
       <c r="BC17" s="2" t="n">
-        <v>-0.458</v>
+        <v>-0.4589</v>
       </c>
       <c r="BD17" s="2" t="n">
-        <v>0.1046</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="18">
@@ -3197,7 +3205,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>14440</v>
+        <v>14160</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>86.78</v>
@@ -3212,20 +3220,20 @@
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>5</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>0111111000</t>
+          <t>0011111000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -3263,23 +3271,23 @@
       </c>
       <c r="AF18" s="2" t="inlineStr"/>
       <c r="AG18" s="2" t="n">
-        <v>34.57</v>
+        <v>34</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>4.15</v>
+        <v>2.17</v>
       </c>
       <c r="AI18" s="2" t="n"/>
       <c r="AJ18" s="2" t="n">
-        <v>3.69</v>
+        <v>1.7</v>
       </c>
       <c r="AK18" s="2" t="n">
-        <v>10.81</v>
+        <v>8.83</v>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>79.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AN18" s="2" t="inlineStr"/>
       <c r="AO18" s="2" t="inlineStr"/>
@@ -3291,40 +3299,40 @@
         </is>
       </c>
       <c r="AS18" s="2" t="n">
-        <v>14604</v>
+        <v>14548</v>
       </c>
       <c r="AT18" s="2" t="n">
-        <v>14812</v>
+        <v>14784</v>
       </c>
       <c r="AU18" s="2" t="n">
-        <v>14075.111</v>
+        <v>14061.111</v>
       </c>
       <c r="AV18" s="2" t="n">
-        <v>13684.232</v>
+        <v>13674.899</v>
       </c>
       <c r="AW18" s="2" t="n">
-        <v>13876.257</v>
+        <v>13870.657</v>
       </c>
       <c r="AX18" s="2" t="n">
-        <v>13870.281</v>
+        <v>13867.481</v>
       </c>
       <c r="AY18" s="2" t="n">
-        <v>12876.072</v>
+        <v>12874.672</v>
       </c>
       <c r="AZ18" s="2" t="n">
-        <v>1.3501</v>
+        <v>1.2492</v>
       </c>
       <c r="BA18" s="2" t="n">
-        <v>1.8151</v>
+        <v>1.7616</v>
       </c>
       <c r="BB18" s="2" t="n">
-        <v>0.6906</v>
+        <v>0.6693</v>
       </c>
       <c r="BC18" s="2" t="n">
-        <v>-0.0117</v>
+        <v>-0.0222</v>
       </c>
       <c r="BD18" s="2" t="n">
-        <v>0.3457</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="19">
@@ -3339,7 +3347,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4450</v>
+        <v>4397</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>13.4</v>
@@ -3365,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
@@ -3374,7 +3382,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0010000010</t>
+          <t>0000000010</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -3393,7 +3401,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4+→4·10d ← 1→4+·14d</t>
+          <t>4+→4·6d ← 1→4+·14d</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
@@ -3405,23 +3413,23 @@
       <c r="AE19" s="2" t="inlineStr"/>
       <c r="AF19" s="2" t="inlineStr"/>
       <c r="AG19" s="2" t="n">
-        <v>-2.97</v>
+        <v>-3.23</v>
       </c>
       <c r="AH19" s="2" t="n">
-        <v>-21.61</v>
+        <v>-22.52</v>
       </c>
       <c r="AI19" s="2" t="n"/>
       <c r="AJ19" s="2" t="n">
-        <v>-1.74</v>
+        <v>-2.65</v>
       </c>
       <c r="AK19" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AL19" s="2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AM19" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN19" s="2" t="inlineStr"/>
       <c r="AO19" s="2" t="n">
@@ -3435,40 +3443,40 @@
         </is>
       </c>
       <c r="AS19" s="2" t="n">
-        <v>4611.8</v>
+        <v>4601.2</v>
       </c>
       <c r="AT19" s="2" t="n">
-        <v>4746.7</v>
+        <v>4741.4</v>
       </c>
       <c r="AU19" s="2" t="n">
-        <v>4609.25</v>
+        <v>4606.6</v>
       </c>
       <c r="AV19" s="2" t="n">
-        <v>4569.4</v>
+        <v>4567.633</v>
       </c>
       <c r="AW19" s="2" t="n">
-        <v>4780.204</v>
+        <v>4779.144</v>
       </c>
       <c r="AX19" s="2" t="n">
-        <v>5593.966</v>
+        <v>5593.436</v>
       </c>
       <c r="AY19" s="2" t="n">
-        <v>5325.003</v>
+        <v>5324.738</v>
       </c>
       <c r="AZ19" s="2" t="n">
-        <v>0.2046</v>
+        <v>0.1463</v>
       </c>
       <c r="BA19" s="2" t="n">
-        <v>0.6095</v>
+        <v>0.5793</v>
       </c>
       <c r="BB19" s="2" t="n">
-        <v>-0.1771</v>
+        <v>-0.1886</v>
       </c>
       <c r="BC19" s="2" t="n">
-        <v>-0.8666</v>
+        <v>-0.8714</v>
       </c>
       <c r="BD19" s="2" t="n">
-        <v>-0.0297</v>
+        <v>-0.0323</v>
       </c>
     </row>
     <row r="20">
@@ -3483,10 +3491,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-6.96</v>
+        <v>-7.16</v>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
@@ -3547,20 +3555,20 @@
       <c r="AE20" s="2" t="inlineStr"/>
       <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="2" t="n">
-        <v>-6</v>
+        <v>-6.03</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>-33.76</v>
+        <v>-33.86</v>
       </c>
       <c r="AI20" s="2" t="n"/>
       <c r="AJ20" s="2" t="n">
-        <v>-8.23</v>
+        <v>-8.33</v>
       </c>
       <c r="AK20" s="2" t="n">
-        <v>-30.88</v>
+        <v>-30.98</v>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AM20" s="2" t="n">
         <v>22</v>
@@ -3579,40 +3587,40 @@
         </is>
       </c>
       <c r="AS20" s="2" t="n">
-        <v>1885.6</v>
+        <v>1885</v>
       </c>
       <c r="AT20" s="2" t="n">
-        <v>2019.5</v>
+        <v>2019.2</v>
       </c>
       <c r="AU20" s="2" t="n">
-        <v>2288.5</v>
+        <v>2288.35</v>
       </c>
       <c r="AV20" s="2" t="n">
-        <v>2403.667</v>
+        <v>2403.567</v>
       </c>
       <c r="AW20" s="2" t="n">
-        <v>2517.94</v>
+        <v>2517.88</v>
       </c>
       <c r="AX20" s="2" t="n">
-        <v>2594.15</v>
+        <v>2594.12</v>
       </c>
       <c r="AY20" s="2" t="n">
-        <v>2440.265</v>
+        <v>2440.25</v>
       </c>
       <c r="AZ20" s="2" t="n">
-        <v>-5.6403</v>
+        <v>-5.6472</v>
       </c>
       <c r="BA20" s="2" t="n">
-        <v>-4.1485</v>
+        <v>-4.1516</v>
       </c>
       <c r="BB20" s="2" t="n">
-        <v>-1.3404</v>
+        <v>-1.3416</v>
       </c>
       <c r="BC20" s="2" t="n">
-        <v>-0.701</v>
+        <v>-0.7016</v>
       </c>
       <c r="BD20" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.0603</v>
       </c>
     </row>
     <row r="21">
@@ -3627,7 +3635,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2967.5</v>
+        <v>2949</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>80.2</v>
@@ -3693,23 +3701,23 @@
       <c r="AE21" s="2" t="inlineStr"/>
       <c r="AF21" s="2" t="inlineStr"/>
       <c r="AG21" s="2" t="n">
-        <v>40.64</v>
+        <v>40.47</v>
       </c>
       <c r="AH21" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1.19</v>
       </c>
       <c r="AI21" s="2" t="n"/>
       <c r="AJ21" s="2" t="n">
-        <v>-7.25</v>
+        <v>-7.84</v>
       </c>
       <c r="AK21" s="2" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="AM21" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN21" s="2" t="inlineStr"/>
       <c r="AO21" s="2" t="n">
@@ -3727,40 +3735,40 @@
         </is>
       </c>
       <c r="AS21" s="2" t="n">
-        <v>3084.8</v>
+        <v>3081.1</v>
       </c>
       <c r="AT21" s="2" t="n">
-        <v>3258</v>
+        <v>3256.15</v>
       </c>
       <c r="AU21" s="2" t="n">
-        <v>3089.349</v>
+        <v>3088.424</v>
       </c>
       <c r="AV21" s="2" t="n">
-        <v>3011.297</v>
+        <v>3010.681</v>
       </c>
       <c r="AW21" s="2" t="n">
-        <v>3033.003</v>
+        <v>3032.633</v>
       </c>
       <c r="AX21" s="2" t="n">
-        <v>3272.108</v>
+        <v>3271.923</v>
       </c>
       <c r="AY21" s="2" t="n">
-        <v>2772.688</v>
+        <v>2772.596</v>
       </c>
       <c r="AZ21" s="2" t="n">
-        <v>0.6974</v>
+        <v>0.6675</v>
       </c>
       <c r="BA21" s="2" t="n">
-        <v>1.2551</v>
+        <v>1.2392</v>
       </c>
       <c r="BB21" s="2" t="n">
-        <v>0.3511</v>
+        <v>0.3448</v>
       </c>
       <c r="BC21" s="2" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="BD21" s="2" t="n">
-        <v>0.4064</v>
+        <v>0.4047</v>
       </c>
     </row>
     <row r="22">
@@ -3775,7 +3783,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>34870</v>
+        <v>34560</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>98.61</v>
@@ -3792,7 +3800,7 @@
         <v>-9</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -3843,20 +3851,20 @@
       </c>
       <c r="AF22" s="2" t="inlineStr"/>
       <c r="AG22" s="2" t="n">
-        <v>85.88</v>
+        <v>85.59</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>19.48</v>
+        <v>18.45</v>
       </c>
       <c r="AI22" s="2" t="n"/>
       <c r="AJ22" s="2" t="n">
-        <v>-15.17</v>
+        <v>-16.2</v>
       </c>
       <c r="AK22" s="2" t="n">
-        <v>4.7</v>
+        <v>3.67</v>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AM22" s="2" t="n">
         <v>12</v>
@@ -3877,40 +3885,40 @@
         </is>
       </c>
       <c r="AS22" s="2" t="n">
-        <v>38320</v>
+        <v>38258</v>
       </c>
       <c r="AT22" s="2" t="n">
-        <v>39460</v>
+        <v>39429</v>
       </c>
       <c r="AU22" s="2" t="n">
-        <v>36216</v>
+        <v>36200.5</v>
       </c>
       <c r="AV22" s="2" t="n">
-        <v>35115</v>
+        <v>35104.667</v>
       </c>
       <c r="AW22" s="2" t="n">
-        <v>34889.6</v>
+        <v>34883.4</v>
       </c>
       <c r="AX22" s="2" t="n">
-        <v>31888.7</v>
+        <v>31885.6</v>
       </c>
       <c r="AY22" s="2" t="n">
-        <v>28263.061</v>
+        <v>28261.511</v>
       </c>
       <c r="AZ22" s="2" t="n">
-        <v>2.4984</v>
+        <v>2.4556</v>
       </c>
       <c r="BA22" s="2" t="n">
-        <v>2.1096</v>
+        <v>2.0865</v>
       </c>
       <c r="BB22" s="2" t="n">
-        <v>1.6</v>
+        <v>1.5905</v>
       </c>
       <c r="BC22" s="2" t="n">
-        <v>1.0214</v>
+        <v>1.0162</v>
       </c>
       <c r="BD22" s="2" t="n">
-        <v>0.8588</v>
+        <v>0.8559</v>
       </c>
     </row>
     <row r="23">
@@ -3925,7 +3933,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>80950</v>
+        <v>80700</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>42.39</v>
@@ -3946,19 +3954,19 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>0111111001</t>
+          <t>0011111001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0011111001</t>
+          <t>0011111000</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3999,23 +4007,23 @@
         </is>
       </c>
       <c r="AG23" s="2" t="n">
-        <v>46.45</v>
+        <v>46.36</v>
       </c>
       <c r="AH23" s="2" t="n">
-        <v>8.27</v>
+        <v>7.96</v>
       </c>
       <c r="AI23" s="2" t="n"/>
       <c r="AJ23" s="2" t="n">
-        <v>6.68</v>
+        <v>6.38</v>
       </c>
       <c r="AK23" s="2" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="AM23" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AN23" s="2" t="inlineStr"/>
       <c r="AO23" s="2" t="inlineStr"/>
@@ -4027,40 +4035,40 @@
         </is>
       </c>
       <c r="AS23" s="2" t="n">
-        <v>80112</v>
+        <v>80062</v>
       </c>
       <c r="AT23" s="2" t="n">
-        <v>80556</v>
+        <v>80531</v>
       </c>
       <c r="AU23" s="2" t="n">
-        <v>79289.04300000001</v>
+        <v>79276.54300000001</v>
       </c>
       <c r="AV23" s="2" t="n">
-        <v>78645.262</v>
+        <v>78636.929</v>
       </c>
       <c r="AW23" s="2" t="n">
-        <v>80517.15700000001</v>
+        <v>80512.15700000001</v>
       </c>
       <c r="AX23" s="2" t="n">
-        <v>78416.622</v>
+        <v>78414.122</v>
       </c>
       <c r="AY23" s="2" t="n">
-        <v>69992.361</v>
+        <v>69991.111</v>
       </c>
       <c r="AZ23" s="2" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="BA23" s="2" t="n">
-        <v>0.6791</v>
+        <v>0.6708</v>
       </c>
       <c r="BB23" s="2" t="n">
-        <v>0.2481</v>
+        <v>0.2449</v>
       </c>
       <c r="BC23" s="2" t="n">
-        <v>0.1533</v>
+        <v>0.1517</v>
       </c>
       <c r="BD23" s="2" t="n">
-        <v>0.4645</v>
+        <v>0.4636</v>
       </c>
     </row>
     <row r="24">
@@ -4075,7 +4083,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>41310</v>
+        <v>41330</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>111</v>
@@ -4141,17 +4149,17 @@
       </c>
       <c r="AF24" s="2" t="inlineStr"/>
       <c r="AG24" s="2" t="n">
-        <v>47.96</v>
+        <v>47.98</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="AI24" s="2" t="n"/>
       <c r="AJ24" s="2" t="n">
-        <v>-8.16</v>
+        <v>-8.09</v>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>11.47</v>
+        <v>11.55</v>
       </c>
       <c r="AL24" s="2" t="n">
         <v>47.3</v>
@@ -4169,40 +4177,40 @@
         </is>
       </c>
       <c r="AS24" s="2" t="n">
-        <v>44110</v>
+        <v>44114</v>
       </c>
       <c r="AT24" s="2" t="n">
-        <v>45273</v>
+        <v>45275</v>
       </c>
       <c r="AU24" s="2" t="n">
-        <v>42382.5</v>
+        <v>42383.5</v>
       </c>
       <c r="AV24" s="2" t="n">
-        <v>39703.333</v>
+        <v>39704</v>
       </c>
       <c r="AW24" s="2" t="n">
-        <v>39005.4</v>
+        <v>39005.8</v>
       </c>
       <c r="AX24" s="2" t="n">
-        <v>41756.075</v>
+        <v>41756.275</v>
       </c>
       <c r="AY24" s="2" t="n">
-        <v>38647.544</v>
+        <v>38647.644</v>
       </c>
       <c r="AZ24" s="2" t="n">
-        <v>1.3916</v>
+        <v>1.394</v>
       </c>
       <c r="BA24" s="2" t="n">
-        <v>2.9147</v>
+        <v>2.916</v>
       </c>
       <c r="BB24" s="2" t="n">
-        <v>0.9141</v>
+        <v>0.9146</v>
       </c>
       <c r="BC24" s="2" t="n">
-        <v>0.4385</v>
+        <v>0.4387</v>
       </c>
       <c r="BD24" s="2" t="n">
-        <v>0.4796</v>
+        <v>0.4798</v>
       </c>
     </row>
     <row r="25">
@@ -4217,7 +4225,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10195</v>
+        <v>9962</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>76.94</v>
@@ -4238,14 +4246,14 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>0111110000</t>
+          <t>0011010000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -4285,23 +4293,23 @@
       </c>
       <c r="AF25" s="2" t="inlineStr"/>
       <c r="AG25" s="2" t="n">
-        <v>110.97</v>
+        <v>110.24</v>
       </c>
       <c r="AH25" s="2" t="n">
-        <v>29.17</v>
+        <v>26.26</v>
       </c>
       <c r="AI25" s="2" t="n"/>
       <c r="AJ25" s="2" t="n">
-        <v>-4.53</v>
+        <v>-7.43</v>
       </c>
       <c r="AK25" s="2" t="n">
-        <v>9.48</v>
+        <v>6.57</v>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AM25" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="AN25" s="2" t="inlineStr"/>
       <c r="AO25" s="2" t="n">
@@ -4315,40 +4323,40 @@
         </is>
       </c>
       <c r="AS25" s="2" t="n">
-        <v>10550.8</v>
+        <v>10504.2</v>
       </c>
       <c r="AT25" s="2" t="n">
-        <v>10688.9</v>
+        <v>10665.6</v>
       </c>
       <c r="AU25" s="2" t="n">
-        <v>9961.833000000001</v>
+        <v>9950.183000000001</v>
       </c>
       <c r="AV25" s="2" t="n">
-        <v>9679.179</v>
+        <v>9671.413</v>
       </c>
       <c r="AW25" s="2" t="n">
-        <v>9737.422</v>
+        <v>9732.762000000001</v>
       </c>
       <c r="AX25" s="2" t="n">
-        <v>12406.92</v>
+        <v>12404.59</v>
       </c>
       <c r="AY25" s="2" t="n">
-        <v>8477.306</v>
+        <v>8476.141</v>
       </c>
       <c r="AZ25" s="2" t="n">
-        <v>3.12</v>
+        <v>2.9999</v>
       </c>
       <c r="BA25" s="2" t="n">
-        <v>2.0719</v>
+        <v>2.0087</v>
       </c>
       <c r="BB25" s="2" t="n">
-        <v>0.347</v>
+        <v>0.3219</v>
       </c>
       <c r="BC25" s="2" t="n">
-        <v>0.6454</v>
+        <v>0.6355</v>
       </c>
       <c r="BD25" s="2" t="n">
-        <v>1.1097</v>
+        <v>1.1024</v>
       </c>
     </row>
     <row r="26">
@@ -4363,10 +4371,10 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3648</v>
+        <v>3655</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>101.74</v>
+        <v>102.64</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
@@ -4376,17 +4384,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="n">
         <v>-9</v>
@@ -4443,23 +4445,23 @@
       <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="inlineStr"/>
       <c r="AG26" s="2" t="n">
-        <v>-2.68</v>
+        <v>-2.62</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>-5.96</v>
+        <v>-5.75</v>
       </c>
       <c r="AI26" s="2" t="n"/>
       <c r="AJ26" s="2" t="n">
-        <v>8.33</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AK26" s="2" t="n">
-        <v>11.35</v>
+        <v>11.55</v>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="AM26" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AN26" s="2" t="inlineStr"/>
       <c r="AO26" s="2" t="inlineStr"/>
@@ -4477,40 +4479,40 @@
         </is>
       </c>
       <c r="AS26" s="2" t="n">
-        <v>3629.2</v>
+        <v>3630.6</v>
       </c>
       <c r="AT26" s="2" t="n">
-        <v>3589.1</v>
+        <v>3589.8</v>
       </c>
       <c r="AU26" s="2" t="n">
-        <v>3502.707</v>
+        <v>3503.057</v>
       </c>
       <c r="AV26" s="2" t="n">
-        <v>3435.649</v>
+        <v>3435.882</v>
       </c>
       <c r="AW26" s="2" t="n">
-        <v>3431.522</v>
+        <v>3431.662</v>
       </c>
       <c r="AX26" s="2" t="n">
-        <v>3291.916</v>
+        <v>3291.986</v>
       </c>
       <c r="AY26" s="2" t="n">
-        <v>3313.295</v>
+        <v>3313.33</v>
       </c>
       <c r="AZ26" s="2" t="n">
-        <v>1.0218</v>
+        <v>1.0321</v>
       </c>
       <c r="BA26" s="2" t="n">
-        <v>1.7693</v>
+        <v>1.7747</v>
       </c>
       <c r="BB26" s="2" t="n">
-        <v>0.3329</v>
+        <v>0.335</v>
       </c>
       <c r="BC26" s="2" t="n">
-        <v>0.5302</v>
+        <v>0.5313</v>
       </c>
       <c r="BD26" s="2" t="n">
-        <v>-0.0268</v>
+        <v>-0.0262</v>
       </c>
     </row>
     <row r="27">
@@ -4525,7 +4527,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>10.44</v>
@@ -4581,7 +4583,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4→4+·8d ← 4+→4·9d ← 4→4+·14d</t>
+          <t>4→4+·18d</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
@@ -4593,7 +4595,7 @@
       <c r="AE27" s="2" t="inlineStr"/>
       <c r="AF27" s="2" t="inlineStr"/>
       <c r="AG27" s="2" t="n">
-        <v>-9.66</v>
+        <v>-9.67</v>
       </c>
       <c r="AH27" s="2" t="n">
         <v>-21.01</v>
@@ -4621,40 +4623,40 @@
         </is>
       </c>
       <c r="AS27" s="2" t="n">
-        <v>3695.2</v>
+        <v>3695</v>
       </c>
       <c r="AT27" s="2" t="n">
-        <v>3743.8</v>
+        <v>3743.7</v>
       </c>
       <c r="AU27" s="2" t="n">
-        <v>3786.552</v>
+        <v>3786.502</v>
       </c>
       <c r="AV27" s="2" t="n">
-        <v>3775.444</v>
+        <v>3775.411</v>
       </c>
       <c r="AW27" s="2" t="n">
-        <v>3880.686</v>
+        <v>3880.666</v>
       </c>
       <c r="AX27" s="2" t="n">
-        <v>3822.189</v>
+        <v>3822.179</v>
       </c>
       <c r="AY27" s="2" t="n">
-        <v>4180.083</v>
+        <v>4180.078</v>
       </c>
       <c r="AZ27" s="2" t="n">
-        <v>-1.0252</v>
+        <v>-1.0266</v>
       </c>
       <c r="BA27" s="2" t="n">
-        <v>-0.1141</v>
+        <v>-0.1148</v>
       </c>
       <c r="BB27" s="2" t="n">
-        <v>-0.1048</v>
+        <v>-0.1051</v>
       </c>
       <c r="BC27" s="2" t="n">
-        <v>-0.2358</v>
+        <v>-0.2359</v>
       </c>
       <c r="BD27" s="2" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.09669999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -4669,7 +4671,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13790</v>
+        <v>13800</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>107.6</v>
@@ -4737,17 +4739,17 @@
       </c>
       <c r="AF28" s="2" t="inlineStr"/>
       <c r="AG28" s="2" t="n">
-        <v>92.86</v>
+        <v>92.88</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>15.6</v>
+        <v>15.71</v>
       </c>
       <c r="AI28" s="2" t="n"/>
       <c r="AJ28" s="2" t="n">
-        <v>-12.1</v>
+        <v>-11.99</v>
       </c>
       <c r="AK28" s="2" t="n">
-        <v>7.62</v>
+        <v>7.73</v>
       </c>
       <c r="AL28" s="2" t="n">
         <v>37.7</v>
@@ -4769,40 +4771,40 @@
         </is>
       </c>
       <c r="AS28" s="2" t="n">
-        <v>14914</v>
+        <v>14916</v>
       </c>
       <c r="AT28" s="2" t="n">
-        <v>15387.5</v>
+        <v>15388.5</v>
       </c>
       <c r="AU28" s="2" t="n">
-        <v>14453.958</v>
+        <v>14454.458</v>
       </c>
       <c r="AV28" s="2" t="n">
-        <v>13944.541</v>
+        <v>13944.874</v>
       </c>
       <c r="AW28" s="2" t="n">
-        <v>13728.978</v>
+        <v>13729.178</v>
       </c>
       <c r="AX28" s="2" t="n">
-        <v>14378.754</v>
+        <v>14378.854</v>
       </c>
       <c r="AY28" s="2" t="n">
-        <v>12042.454</v>
+        <v>12042.504</v>
       </c>
       <c r="AZ28" s="2" t="n">
-        <v>0.7992</v>
+        <v>0.8026</v>
       </c>
       <c r="BA28" s="2" t="n">
-        <v>2.0869</v>
+        <v>2.0887</v>
       </c>
       <c r="BB28" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6508</v>
       </c>
       <c r="BC28" s="2" t="n">
-        <v>0.7628</v>
+        <v>0.7632</v>
       </c>
       <c r="BD28" s="2" t="n">
-        <v>0.9286</v>
+        <v>0.9288</v>
       </c>
     </row>
     <row r="29">
@@ -4817,7 +4819,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>25335</v>
+        <v>25450</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>15.87</v>
@@ -4865,41 +4867,47 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均</t>
+        </is>
+      </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4+→4·11d ← 4→4+·14d</t>
+          <t>4→4+·1d ← 4+→4·2d ← 4→4+·14d</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="inlineStr"/>
-      <c r="AC29" s="2" t="n">
-        <v>-1</v>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
       </c>
       <c r="AD29" s="2" t="inlineStr"/>
       <c r="AE29" s="2" t="inlineStr"/>
       <c r="AF29" s="2" t="inlineStr"/>
       <c r="AG29" s="2" t="n">
-        <v>7.56</v>
+        <v>7.68</v>
       </c>
       <c r="AH29" s="2" t="n">
-        <v>-12.12</v>
+        <v>-11.7</v>
       </c>
       <c r="AI29" s="2" t="n"/>
       <c r="AJ29" s="2" t="n">
-        <v>5.72</v>
+        <v>6.13</v>
       </c>
       <c r="AK29" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AN29" s="2" t="inlineStr"/>
       <c r="AO29" s="2" t="n">
@@ -4913,40 +4921,40 @@
         </is>
       </c>
       <c r="AS29" s="2" t="n">
-        <v>25212</v>
+        <v>25235</v>
       </c>
       <c r="AT29" s="2" t="n">
-        <v>25020</v>
+        <v>25031.5</v>
       </c>
       <c r="AU29" s="2" t="n">
-        <v>24079.5</v>
+        <v>24085.25</v>
       </c>
       <c r="AV29" s="2" t="n">
-        <v>23947.833</v>
+        <v>23951.667</v>
       </c>
       <c r="AW29" s="2" t="n">
-        <v>24573.3</v>
+        <v>24575.6</v>
       </c>
       <c r="AX29" s="2" t="n">
-        <v>25199.55</v>
+        <v>25200.7</v>
       </c>
       <c r="AY29" s="2" t="n">
-        <v>26071.592</v>
+        <v>26072.167</v>
       </c>
       <c r="AZ29" s="2" t="n">
-        <v>1.6711</v>
+        <v>1.6957</v>
       </c>
       <c r="BA29" s="2" t="n">
-        <v>1.246</v>
+        <v>1.2588</v>
       </c>
       <c r="BB29" s="2" t="n">
-        <v>0.2283</v>
+        <v>0.2332</v>
       </c>
       <c r="BC29" s="2" t="n">
-        <v>-0.1983</v>
+        <v>-0.1959</v>
       </c>
       <c r="BD29" s="2" t="n">
-        <v>0.0756</v>
+        <v>0.07679999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4961,10 +4969,10 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2262.5</v>
+        <v>2248</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11.78</v>
+        <v>9.65</v>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
@@ -5020,29 +5028,25 @@
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr"/>
       <c r="AE30" s="2" t="inlineStr"/>
       <c r="AF30" s="2" t="inlineStr"/>
       <c r="AG30" s="2" t="n">
-        <v>-4.81</v>
+        <v>-4.96</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>-12.56</v>
+        <v>-13.1</v>
       </c>
       <c r="AI30" s="2" t="n"/>
       <c r="AJ30" s="2" t="n">
-        <v>1.11</v>
+        <v>0.57</v>
       </c>
       <c r="AK30" s="2" t="n">
-        <v>-3.29</v>
+        <v>-3.83</v>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="AM30" s="2" t="n">
         <v>16</v>
@@ -5057,40 +5061,40 @@
         </is>
       </c>
       <c r="AS30" s="2" t="n">
-        <v>2312.8</v>
+        <v>2309.9</v>
       </c>
       <c r="AT30" s="2" t="n">
-        <v>2366.85</v>
+        <v>2365.4</v>
       </c>
       <c r="AU30" s="2" t="n">
-        <v>2361.609</v>
+        <v>2360.884</v>
       </c>
       <c r="AV30" s="2" t="n">
-        <v>2394.367</v>
+        <v>2393.884</v>
       </c>
       <c r="AW30" s="2" t="n">
-        <v>2420.791</v>
+        <v>2420.501</v>
       </c>
       <c r="AX30" s="2" t="n">
-        <v>2381.9</v>
+        <v>2381.755</v>
       </c>
       <c r="AY30" s="2" t="n">
-        <v>2364.614</v>
+        <v>2364.542</v>
       </c>
       <c r="AZ30" s="2" t="n">
-        <v>-0.8165</v>
+        <v>-0.8478</v>
       </c>
       <c r="BA30" s="2" t="n">
-        <v>-0.6216</v>
+        <v>-0.6373</v>
       </c>
       <c r="BB30" s="2" t="n">
-        <v>0.2498</v>
+        <v>0.2435</v>
       </c>
       <c r="BC30" s="2" t="n">
-        <v>0.1312</v>
+        <v>0.128</v>
       </c>
       <c r="BD30" s="2" t="n">
-        <v>-0.0481</v>
+        <v>-0.0496</v>
       </c>
     </row>
     <row r="31">
@@ -5105,7 +5109,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2269</v>
+        <v>2293.5</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>44.64</v>
@@ -5129,7 +5133,7 @@
         <v>8</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
@@ -5138,7 +5142,7 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -5167,33 +5171,31 @@
       <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr"/>
-      <c r="AD31" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
+      <c r="AD31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AE31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AF31" s="2" t="inlineStr"/>
       <c r="AG31" s="2" t="n">
-        <v>22.05</v>
+        <v>22.37</v>
       </c>
       <c r="AH31" s="2" t="n">
-        <v>2.58</v>
+        <v>3.71</v>
       </c>
       <c r="AI31" s="2" t="n"/>
       <c r="AJ31" s="2" t="n">
-        <v>10.95</v>
+        <v>12.08</v>
       </c>
       <c r="AK31" s="2" t="n">
-        <v>-4.51</v>
+        <v>-3.38</v>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="AM31" s="2" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="AN31" s="2" t="inlineStr"/>
       <c r="AO31" s="2" t="inlineStr"/>
@@ -5207,40 +5209,40 @@
         </is>
       </c>
       <c r="AS31" s="2" t="n">
-        <v>2219.2</v>
+        <v>2224.1</v>
       </c>
       <c r="AT31" s="2" t="n">
-        <v>2195.2</v>
+        <v>2197.65</v>
       </c>
       <c r="AU31" s="2" t="n">
-        <v>2216.98</v>
+        <v>2218.205</v>
       </c>
       <c r="AV31" s="2" t="n">
-        <v>2219.897</v>
+        <v>2220.714</v>
       </c>
       <c r="AW31" s="2" t="n">
-        <v>2146.864</v>
+        <v>2147.354</v>
       </c>
       <c r="AX31" s="2" t="n">
-        <v>2013.003</v>
+        <v>2013.248</v>
       </c>
       <c r="AY31" s="2" t="n">
-        <v>2008.664</v>
+        <v>2008.787</v>
       </c>
       <c r="AZ31" s="2" t="n">
-        <v>0.3214</v>
+        <v>0.3798</v>
       </c>
       <c r="BA31" s="2" t="n">
-        <v>-0.3308</v>
+        <v>-0.3023</v>
       </c>
       <c r="BB31" s="2" t="n">
-        <v>0.5542</v>
+        <v>0.5662</v>
       </c>
       <c r="BC31" s="2" t="n">
-        <v>0.3321</v>
+        <v>0.3385</v>
       </c>
       <c r="BD31" s="2" t="n">
-        <v>0.2205</v>
+        <v>0.2237</v>
       </c>
     </row>
     <row r="32">
@@ -5255,7 +5257,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4860</v>
+        <v>4897</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>4.42</v>
@@ -5276,19 +5278,19 @@
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0001000000</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0001000100</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -5301,13 +5303,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·日线纠缠</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·9d</t>
+          <t>4→4+·9d</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
@@ -5321,23 +5327,23 @@
       </c>
       <c r="AF32" s="2" t="inlineStr"/>
       <c r="AG32" s="2" t="n">
-        <v>11.74</v>
+        <v>11.93</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>-11.43</v>
+        <v>-10.73</v>
       </c>
       <c r="AI32" s="2" t="n"/>
       <c r="AJ32" s="2" t="n">
-        <v>7.19</v>
+        <v>7.89</v>
       </c>
       <c r="AK32" s="2" t="n">
-        <v>-5.59</v>
+        <v>-4.9</v>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
       <c r="AM32" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AN32" s="2" t="inlineStr"/>
       <c r="AO32" s="2" t="inlineStr"/>
@@ -5349,40 +5355,40 @@
         </is>
       </c>
       <c r="AS32" s="2" t="n">
-        <v>4819.6</v>
+        <v>4827</v>
       </c>
       <c r="AT32" s="2" t="n">
-        <v>4794.3</v>
+        <v>4798</v>
       </c>
       <c r="AU32" s="2" t="n">
-        <v>4823.811</v>
+        <v>4825.661</v>
       </c>
       <c r="AV32" s="2" t="n">
-        <v>4896.201</v>
+        <v>4897.434</v>
       </c>
       <c r="AW32" s="2" t="n">
-        <v>4889.272</v>
+        <v>4890.012</v>
       </c>
       <c r="AX32" s="2" t="n">
-        <v>4917.459</v>
+        <v>4917.829</v>
       </c>
       <c r="AY32" s="2" t="n">
-        <v>5138.06</v>
+        <v>5138.245</v>
       </c>
       <c r="AZ32" s="2" t="n">
-        <v>0.0912</v>
+        <v>0.1314</v>
       </c>
       <c r="BA32" s="2" t="n">
-        <v>-0.5252</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="BB32" s="2" t="n">
-        <v>-0.4038</v>
+        <v>-0.396</v>
       </c>
       <c r="BC32" s="2" t="n">
-        <v>-0.3485</v>
+        <v>-0.3447</v>
       </c>
       <c r="BD32" s="2" t="n">
-        <v>0.1174</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="33">
@@ -5464,14 +5470,14 @@
         <v>34.23</v>
       </c>
       <c r="AH33" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="2" t="n"/>
       <c r="AJ33" s="2" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
       <c r="AK33" s="2" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="AL33" s="2" t="n">
         <v>50.3</v>
@@ -5537,7 +5543,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>7483</v>
+        <v>7512</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>35.91</v>
@@ -5611,23 +5617,23 @@
         <v>1</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>44.76</v>
+        <v>44.88</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>10.01</v>
+        <v>10.46</v>
       </c>
       <c r="AI34" s="2" t="n"/>
       <c r="AJ34" s="2" t="n">
-        <v>8.98</v>
+        <v>9.43</v>
       </c>
       <c r="AK34" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4.35</v>
       </c>
       <c r="AL34" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AM34" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AN34" s="2" t="inlineStr"/>
       <c r="AO34" s="2" t="inlineStr"/>
@@ -5641,40 +5647,40 @@
         </is>
       </c>
       <c r="AS34" s="2" t="n">
-        <v>7322.6</v>
+        <v>7328.4</v>
       </c>
       <c r="AT34" s="2" t="n">
-        <v>7335.3</v>
+        <v>7338.2</v>
       </c>
       <c r="AU34" s="2" t="n">
-        <v>7320.673</v>
+        <v>7322.123</v>
       </c>
       <c r="AV34" s="2" t="n">
-        <v>7381.786</v>
+        <v>7382.752</v>
       </c>
       <c r="AW34" s="2" t="n">
-        <v>7321.698</v>
+        <v>7322.278</v>
       </c>
       <c r="AX34" s="2" t="n">
-        <v>6806.633</v>
+        <v>6806.923</v>
       </c>
       <c r="AY34" s="2" t="n">
-        <v>6475.107</v>
+        <v>6475.252</v>
       </c>
       <c r="AZ34" s="2" t="n">
-        <v>0.2246</v>
+        <v>0.2453</v>
       </c>
       <c r="BA34" s="2" t="n">
-        <v>-0.1987</v>
+        <v>-0.1884</v>
       </c>
       <c r="BB34" s="2" t="n">
-        <v>0.5661</v>
+        <v>0.5703</v>
       </c>
       <c r="BC34" s="2" t="n">
-        <v>0.1399</v>
+        <v>0.1421</v>
       </c>
       <c r="BD34" s="2" t="n">
-        <v>0.4476</v>
+        <v>0.4488</v>
       </c>
     </row>
     <row r="35">
@@ -5689,7 +5695,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>4954</v>
+        <v>4988</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>21.7</v>
@@ -5757,23 +5763,23 @@
       </c>
       <c r="AF35" s="2" t="inlineStr"/>
       <c r="AG35" s="2" t="n">
-        <v>11.74</v>
+        <v>11.91</v>
       </c>
       <c r="AH35" s="2" t="n">
-        <v>-10.32</v>
+        <v>-9.69</v>
       </c>
       <c r="AI35" s="2" t="n"/>
       <c r="AJ35" s="2" t="n">
-        <v>7.91</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AK35" s="2" t="n">
-        <v>-4.96</v>
+        <v>-4.32</v>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AN35" s="2" t="inlineStr"/>
       <c r="AO35" s="2" t="inlineStr"/>
@@ -5785,40 +5791,40 @@
         </is>
       </c>
       <c r="AS35" s="2" t="n">
-        <v>4902.8</v>
+        <v>4909.6</v>
       </c>
       <c r="AT35" s="2" t="n">
-        <v>4897.4</v>
+        <v>4900.8</v>
       </c>
       <c r="AU35" s="2" t="n">
-        <v>4945.178</v>
+        <v>4946.878</v>
       </c>
       <c r="AV35" s="2" t="n">
-        <v>4981.433</v>
+        <v>4982.566</v>
       </c>
       <c r="AW35" s="2" t="n">
-        <v>4910.037</v>
+        <v>4910.717</v>
       </c>
       <c r="AX35" s="2" t="n">
-        <v>4844.593</v>
+        <v>4844.933</v>
       </c>
       <c r="AY35" s="2" t="n">
-        <v>5160.448</v>
+        <v>5160.618</v>
       </c>
       <c r="AZ35" s="2" t="n">
-        <v>-0.119</v>
+        <v>-0.083</v>
       </c>
       <c r="BA35" s="2" t="n">
-        <v>-0.3632</v>
+        <v>-0.3454</v>
       </c>
       <c r="BB35" s="2" t="n">
-        <v>0.0461</v>
+        <v>0.0533</v>
       </c>
       <c r="BC35" s="2" t="n">
-        <v>-0.4688</v>
+        <v>-0.4652</v>
       </c>
       <c r="BD35" s="2" t="n">
-        <v>0.1174</v>
+        <v>0.1191</v>
       </c>
     </row>
     <row r="36">
@@ -5833,7 +5839,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>10575</v>
+        <v>10585</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>96.47</v>
@@ -5899,17 +5905,17 @@
       <c r="AE36" s="2" t="inlineStr"/>
       <c r="AF36" s="2" t="inlineStr"/>
       <c r="AG36" s="2" t="n">
-        <v>69.23999999999999</v>
+        <v>69.27</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>5.89</v>
+        <v>6.01</v>
       </c>
       <c r="AI36" s="2" t="n"/>
       <c r="AJ36" s="2" t="n">
-        <v>-10.87</v>
+        <v>-10.74</v>
       </c>
       <c r="AK36" s="2" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
       <c r="AL36" s="2" t="n">
         <v>26</v>
@@ -5931,40 +5937,40 @@
         </is>
       </c>
       <c r="AS36" s="2" t="n">
-        <v>11236</v>
+        <v>11238</v>
       </c>
       <c r="AT36" s="2" t="n">
-        <v>11854</v>
+        <v>11855</v>
       </c>
       <c r="AU36" s="2" t="n">
-        <v>11326.579</v>
+        <v>11327.079</v>
       </c>
       <c r="AV36" s="2" t="n">
-        <v>10986.148</v>
+        <v>10986.481</v>
       </c>
       <c r="AW36" s="2" t="n">
-        <v>10949.175</v>
+        <v>10949.375</v>
       </c>
       <c r="AX36" s="2" t="n">
-        <v>11784.736</v>
+        <v>11784.836</v>
       </c>
       <c r="AY36" s="2" t="n">
-        <v>9904.757</v>
+        <v>9904.807000000001</v>
       </c>
       <c r="AZ36" s="2" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6534</v>
       </c>
       <c r="BA36" s="2" t="n">
-        <v>1.268</v>
+        <v>1.2704</v>
       </c>
       <c r="BB36" s="2" t="n">
-        <v>0.2647</v>
+        <v>0.2657</v>
       </c>
       <c r="BC36" s="2" t="n">
-        <v>0.4228</v>
+        <v>0.4233</v>
       </c>
       <c r="BD36" s="2" t="n">
-        <v>0.6924</v>
+        <v>0.6927</v>
       </c>
     </row>
     <row r="37">
@@ -5979,10 +5985,10 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1735.5</v>
+        <v>1751</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>80.55</v>
+        <v>29.83</v>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
@@ -6049,23 +6055,23 @@
       </c>
       <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="2" t="n">
-        <v>35.16</v>
+        <v>35.42</v>
       </c>
       <c r="AH37" s="2" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AI37" s="2" t="n"/>
       <c r="AJ37" s="2" t="n">
-        <v>7.04</v>
+        <v>7.99</v>
       </c>
       <c r="AK37" s="2" t="n">
-        <v>-7.68</v>
+        <v>-6.73</v>
       </c>
       <c r="AL37" s="2" t="n">
-        <v>71.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AN37" s="2" t="inlineStr"/>
       <c r="AO37" s="2" t="inlineStr"/>
@@ -6079,40 +6085,40 @@
         </is>
       </c>
       <c r="AS37" s="2" t="n">
-        <v>1729.7</v>
+        <v>1732.8</v>
       </c>
       <c r="AT37" s="2" t="n">
-        <v>1727.55</v>
+        <v>1729.1</v>
       </c>
       <c r="AU37" s="2" t="n">
-        <v>1747.105</v>
+        <v>1747.88</v>
       </c>
       <c r="AV37" s="2" t="n">
-        <v>1767.716</v>
+        <v>1768.233</v>
       </c>
       <c r="AW37" s="2" t="n">
-        <v>1751.465</v>
+        <v>1751.775</v>
       </c>
       <c r="AX37" s="2" t="n">
-        <v>1680.17</v>
+        <v>1680.325</v>
       </c>
       <c r="AY37" s="2" t="n">
-        <v>1593.624</v>
+        <v>1593.701</v>
       </c>
       <c r="AZ37" s="2" t="n">
-        <v>-0.4576</v>
+        <v>-0.4114</v>
       </c>
       <c r="BA37" s="2" t="n">
-        <v>-0.5484</v>
+        <v>-0.5256</v>
       </c>
       <c r="BB37" s="2" t="n">
-        <v>0.4037</v>
+        <v>0.413</v>
       </c>
       <c r="BC37" s="2" t="n">
-        <v>-0.0863</v>
+        <v>-0.0815</v>
       </c>
       <c r="BD37" s="2" t="n">
-        <v>0.3516</v>
+        <v>0.3542</v>
       </c>
     </row>
     <row r="38">
@@ -6127,7 +6133,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>4705</v>
+        <v>4737</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>12.95</v>
@@ -6152,14 +6158,14 @@
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0100000100</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -6199,23 +6205,23 @@
       </c>
       <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="2" t="n">
-        <v>29.81</v>
+        <v>29.99</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>-6.27</v>
+        <v>-5.61</v>
       </c>
       <c r="AI38" s="2" t="n"/>
       <c r="AJ38" s="2" t="n">
-        <v>7.03</v>
+        <v>7.69</v>
       </c>
       <c r="AK38" s="2" t="n">
-        <v>-7.1</v>
+        <v>-6.44</v>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>66.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AM38" s="2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN38" s="2" t="inlineStr"/>
       <c r="AO38" s="2" t="inlineStr"/>
@@ -6227,40 +6233,40 @@
         </is>
       </c>
       <c r="AS38" s="2" t="n">
-        <v>4687.6</v>
+        <v>4694</v>
       </c>
       <c r="AT38" s="2" t="n">
-        <v>4682</v>
+        <v>4685.2</v>
       </c>
       <c r="AU38" s="2" t="n">
-        <v>4738.751</v>
+        <v>4740.351</v>
       </c>
       <c r="AV38" s="2" t="n">
-        <v>4795.009</v>
+        <v>4796.076</v>
       </c>
       <c r="AW38" s="2" t="n">
-        <v>4758.794</v>
+        <v>4759.434</v>
       </c>
       <c r="AX38" s="2" t="n">
-        <v>4698.939</v>
+        <v>4699.259</v>
       </c>
       <c r="AY38" s="2" t="n">
-        <v>4708.841</v>
+        <v>4709.001</v>
       </c>
       <c r="AZ38" s="2" t="n">
-        <v>-0.2679</v>
+        <v>-0.2326</v>
       </c>
       <c r="BA38" s="2" t="n">
-        <v>-0.6443</v>
+        <v>-0.6269</v>
       </c>
       <c r="BB38" s="2" t="n">
-        <v>-0.0542</v>
+        <v>-0.0472</v>
       </c>
       <c r="BC38" s="2" t="n">
-        <v>-0.4302</v>
+        <v>-0.4267</v>
       </c>
       <c r="BD38" s="2" t="n">
-        <v>0.2981</v>
+        <v>0.2999</v>
       </c>
     </row>
     <row r="39">
@@ -6275,7 +6281,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>7307</v>
+        <v>7308</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>93.44</v>
@@ -6345,17 +6351,17 @@
       <c r="AE39" s="2" t="inlineStr"/>
       <c r="AF39" s="2" t="inlineStr"/>
       <c r="AG39" s="2" t="n">
-        <v>61.01</v>
+        <v>61.02</v>
       </c>
       <c r="AH39" s="2" t="n">
-        <v>17.43</v>
+        <v>17.47</v>
       </c>
       <c r="AI39" s="2" t="n"/>
       <c r="AJ39" s="2" t="n">
-        <v>7.12</v>
+        <v>7.17</v>
       </c>
       <c r="AK39" s="2" t="n">
-        <v>-1.63</v>
+        <v>-1.58</v>
       </c>
       <c r="AL39" s="2" t="n">
         <v>99.3</v>
@@ -6375,40 +6381,40 @@
         </is>
       </c>
       <c r="AS39" s="2" t="n">
-        <v>7409</v>
+        <v>7409.2</v>
       </c>
       <c r="AT39" s="2" t="n">
-        <v>7271.5</v>
+        <v>7271.6</v>
       </c>
       <c r="AU39" s="2" t="n">
-        <v>7244.167</v>
+        <v>7244.217</v>
       </c>
       <c r="AV39" s="2" t="n">
-        <v>7201.254</v>
+        <v>7201.288</v>
       </c>
       <c r="AW39" s="2" t="n">
-        <v>6899.59</v>
+        <v>6899.61</v>
       </c>
       <c r="AX39" s="2" t="n">
-        <v>6146.69</v>
+        <v>6146.7</v>
       </c>
       <c r="AY39" s="2" t="n">
-        <v>5733.35</v>
+        <v>5733.355</v>
       </c>
       <c r="AZ39" s="2" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8652</v>
       </c>
       <c r="BA39" s="2" t="n">
-        <v>0.4903</v>
+        <v>0.4906</v>
       </c>
       <c r="BB39" s="2" t="n">
-        <v>1.0923</v>
+        <v>1.0924</v>
       </c>
       <c r="BC39" s="2" t="n">
-        <v>0.8354</v>
+        <v>0.8355</v>
       </c>
       <c r="BD39" s="2" t="n">
-        <v>0.6101</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="40">
@@ -6423,7 +6429,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>7320</v>
+        <v>7340</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>91.93000000000001</v>
@@ -6497,23 +6503,23 @@
       <c r="AE40" s="2" t="inlineStr"/>
       <c r="AF40" s="2" t="inlineStr"/>
       <c r="AG40" s="2" t="n">
-        <v>68.45</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>18.76</v>
+        <v>19.12</v>
       </c>
       <c r="AI40" s="2" t="n"/>
       <c r="AJ40" s="2" t="n">
-        <v>8.77</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AK40" s="2" t="n">
-        <v>0.84</v>
+        <v>1.19</v>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AM40" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AN40" s="2" t="inlineStr"/>
       <c r="AO40" s="2" t="inlineStr"/>
@@ -6527,40 +6533,40 @@
         </is>
       </c>
       <c r="AS40" s="2" t="n">
-        <v>7426.6</v>
+        <v>7430.6</v>
       </c>
       <c r="AT40" s="2" t="n">
-        <v>7264.1</v>
+        <v>7266.1</v>
       </c>
       <c r="AU40" s="2" t="n">
-        <v>7158.114</v>
+        <v>7159.114</v>
       </c>
       <c r="AV40" s="2" t="n">
-        <v>7095.517</v>
+        <v>7096.183</v>
       </c>
       <c r="AW40" s="2" t="n">
-        <v>6872.561</v>
+        <v>6872.961</v>
       </c>
       <c r="AX40" s="2" t="n">
-        <v>6160.766</v>
+        <v>6160.966</v>
       </c>
       <c r="AY40" s="2" t="n">
-        <v>5830.213</v>
+        <v>5830.313</v>
       </c>
       <c r="AZ40" s="2" t="n">
-        <v>1.5198</v>
+        <v>1.5345</v>
       </c>
       <c r="BA40" s="2" t="n">
-        <v>0.8643</v>
+        <v>0.8717</v>
       </c>
       <c r="BB40" s="2" t="n">
-        <v>1.2384</v>
+        <v>1.2415</v>
       </c>
       <c r="BC40" s="2" t="n">
-        <v>0.7274</v>
+        <v>0.7291</v>
       </c>
       <c r="BD40" s="2" t="n">
-        <v>0.6845</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="41">
@@ -6575,7 +6581,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>3375</v>
+        <v>3393</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>86.33</v>
@@ -6592,7 +6598,7 @@
         <v>9</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -6644,28 +6650,28 @@
         </is>
       </c>
       <c r="AD41" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE41" s="2" t="inlineStr"/>
       <c r="AF41" s="2" t="inlineStr"/>
       <c r="AG41" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="AH41" s="2" t="n">
-        <v>20.55</v>
+        <v>21.22</v>
       </c>
       <c r="AI41" s="2" t="n"/>
       <c r="AJ41" s="2" t="n">
-        <v>9.029999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AK41" s="2" t="n">
-        <v>-4.18</v>
+        <v>-3.51</v>
       </c>
       <c r="AL41" s="2" t="n">
-        <v>88.5</v>
+        <v>88.7</v>
       </c>
       <c r="AM41" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AN41" s="2" t="inlineStr">
         <is>
@@ -6683,40 +6689,40 @@
         </is>
       </c>
       <c r="AS41" s="2" t="n">
-        <v>3419.8</v>
+        <v>3423.4</v>
       </c>
       <c r="AT41" s="2" t="n">
-        <v>3338.4</v>
+        <v>3340.2</v>
       </c>
       <c r="AU41" s="2" t="n">
-        <v>3349.478</v>
+        <v>3350.378</v>
       </c>
       <c r="AV41" s="2" t="n">
-        <v>3339.876</v>
+        <v>3340.476</v>
       </c>
       <c r="AW41" s="2" t="n">
-        <v>3220.359</v>
+        <v>3220.719</v>
       </c>
       <c r="AX41" s="2" t="n">
-        <v>2891.186</v>
+        <v>2891.366</v>
       </c>
       <c r="AY41" s="2" t="n">
-        <v>2635.013</v>
+        <v>2635.103</v>
       </c>
       <c r="AZ41" s="2" t="n">
-        <v>0.7726</v>
+        <v>0.8011</v>
       </c>
       <c r="BA41" s="2" t="n">
-        <v>0.3876</v>
+        <v>0.4017</v>
       </c>
       <c r="BB41" s="2" t="n">
-        <v>1.0267</v>
+        <v>1.0326</v>
       </c>
       <c r="BC41" s="2" t="n">
-        <v>0.8359</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="BD41" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6858</v>
       </c>
     </row>
     <row r="42">
@@ -6731,10 +6737,10 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>76450</v>
+        <v>77000</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.37</v>
+        <v>96.77</v>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
@@ -6791,23 +6797,23 @@
       <c r="AE42" s="2" t="inlineStr"/>
       <c r="AF42" s="2" t="inlineStr"/>
       <c r="AG42" s="2" t="n">
-        <v>35.07</v>
+        <v>35.27</v>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="AI42" s="2" t="n"/>
       <c r="AJ42" s="2" t="n">
-        <v>7.02</v>
+        <v>7.78</v>
       </c>
       <c r="AK42" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="AL42" s="2" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="AM42" s="2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AN42" s="2" t="inlineStr"/>
       <c r="AO42" s="2" t="n">
@@ -6821,40 +6827,40 @@
         </is>
       </c>
       <c r="AS42" s="2" t="n">
-        <v>74852</v>
+        <v>74962</v>
       </c>
       <c r="AT42" s="2" t="n">
-        <v>74589</v>
+        <v>74644</v>
       </c>
       <c r="AU42" s="2" t="n">
-        <v>71581.5</v>
+        <v>71609</v>
       </c>
       <c r="AV42" s="2" t="n">
-        <v>70506.333</v>
+        <v>70524.667</v>
       </c>
       <c r="AW42" s="2" t="n">
-        <v>72378.97900000001</v>
+        <v>72389.97900000001</v>
       </c>
       <c r="AX42" s="2" t="n">
-        <v>76222.49400000001</v>
+        <v>76227.99400000001</v>
       </c>
       <c r="AY42" s="2" t="n">
-        <v>70575.247</v>
+        <v>70577.997</v>
       </c>
       <c r="AZ42" s="2" t="n">
-        <v>1.8384</v>
+        <v>1.8781</v>
       </c>
       <c r="BA42" s="2" t="n">
-        <v>1.4417</v>
+        <v>1.4622</v>
       </c>
       <c r="BB42" s="2" t="n">
-        <v>-0.2464</v>
+        <v>-0.2385</v>
       </c>
       <c r="BC42" s="2" t="n">
-        <v>0.0919</v>
+        <v>0.0956</v>
       </c>
       <c r="BD42" s="2" t="n">
-        <v>0.3507</v>
+        <v>0.3527</v>
       </c>
     </row>
     <row r="43">
@@ -7219,13 +7225,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·周J超卖·底背离·日线纠缠</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·7d ← 1→4·14d</t>
+          <t>4→4+·7d ← 1→4·14d</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
@@ -7665,7 +7675,11 @@
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4+→4·12d ← 4→4+·16d ← 4+→4·17d</t>
+        </is>
+      </c>
       <c r="AA48" s="2" t="inlineStr"/>
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="n">
@@ -9165,7 +9179,7 @@
       <c r="Y58" s="2" t="inlineStr"/>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4+→4·4d ← 4→4+·5d</t>
+          <t>4+→4·4d ← 4→4+·5d ← 4+→4·6d</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr"/>
@@ -9315,7 +9329,7 @@
       <c r="Y59" s="2" t="inlineStr"/>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>4+→4·12d ← 4→4+·18d</t>
+          <t>4+→4·12d</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr"/>
@@ -9891,11 +9905,19 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y63" s="2" t="inlineStr"/>
-      <c r="Z63" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·日线纠缠</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4→4+·2d ← 4+→4·13d ← 4→4+·15d</t>
+        </is>
+      </c>
       <c r="AA63" s="2" t="inlineStr"/>
       <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr"/>
@@ -11509,7 +11531,7 @@
       <c r="Y74" s="2" t="inlineStr"/>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>4+→4·2d ← 4→4+·6d</t>
+          <t>4+→4·2d ← 4→4+·6d ← 4+→4·7d</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr"/>
@@ -11657,7 +11679,7 @@
       <c r="Y75" s="2" t="inlineStr"/>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>4+→4·8d ← 4→4+·9d ← 1→4·19d</t>
+          <t>4+→4·2d ← 4→4+·3d ← 4+→4·4d</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr"/>
@@ -12095,7 +12117,7 @@
       <c r="Y78" s="2" t="inlineStr"/>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>1+→1·15d ← 4→1+·18d</t>
+          <t>1+→1·15d ← 4+→1+·18d ← 4→4+·20d</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr"/>
@@ -12243,15 +12265,15 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y79" s="2" t="inlineStr"/>
-      <c r="Z79" s="2" t="inlineStr">
-        <is>
-          <t>4+→4·8d</t>
-        </is>
-      </c>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·底背离</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr"/>
       <c r="AA79" s="2" t="inlineStr"/>
       <c r="AB79" s="2" t="inlineStr"/>
       <c r="AC79" s="2" t="n">
@@ -12991,7 +13013,7 @@
       <c r="Y84" s="2" t="inlineStr"/>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>4+→4·3d ← 4→4+·5d</t>
+          <t>4+→4·3d ← 4→4+·5d ← 4+→4·7d</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr"/>
@@ -13133,13 +13155,17 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y85" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·周J超卖</t>
+        </is>
+      </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·15d</t>
+          <t>4→4+·15d</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr"/>
@@ -15840,12 +15866,12 @@
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>周J超卖·日线纠缠</t>
+          <t>站稳短均·周J超卖·日线纠缠</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
         <is>
-          <t>4→4+·1d ← 4+→4·9d ← 4→4+·17d</t>
+          <t>4→4+·1d ← 4+→4·9d ← 3→4+·20d</t>
         </is>
       </c>
       <c r="AA103" s="2" t="inlineStr"/>
@@ -16309,7 +16335,7 @@
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>4→4+·1d ← 4+→4·10d</t>
+          <t>4→4+·1d ← 4+→4·2d ← 4→4+·3d</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr"/>
@@ -17057,13 +17083,17 @@
       </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y111" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·周J超卖</t>
+        </is>
+      </c>
       <c r="Z111" s="2" t="inlineStr">
         <is>
-          <t>4+→4·2d ← 4→4+·5d</t>
+          <t>4→4+·7d</t>
         </is>
       </c>
       <c r="AA111" s="2" t="inlineStr"/>
@@ -17199,11 +17229,19 @@
       </c>
       <c r="X112" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y112" s="2" t="inlineStr"/>
-      <c r="Z112" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>4→4+·1d ← 4+→4·2d ← 4→4+·9d</t>
+        </is>
+      </c>
       <c r="AA112" s="2" t="inlineStr"/>
       <c r="AB112" s="2" t="inlineStr"/>
       <c r="AC112" s="2" t="inlineStr"/>
@@ -17806,7 +17844,7 @@
       </c>
       <c r="Y116" s="2" t="inlineStr">
         <is>
-          <t>周J超卖·日线纠缠</t>
+          <t>站稳短均·周J超卖·日线纠缠</t>
         </is>
       </c>
       <c r="Z116" s="2" t="inlineStr">
@@ -17947,13 +17985,17 @@
       </c>
       <c r="X117" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y117" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·日线纠缠</t>
+        </is>
+      </c>
       <c r="Z117" s="2" t="inlineStr">
         <is>
-          <t>3→4·3d</t>
+          <t>3→4+·3d</t>
         </is>
       </c>
       <c r="AA117" s="2" t="inlineStr"/>
@@ -18698,7 +18740,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>周J超卖·底背离·日线纠缠</t>
+          <t>站稳短均·周J超卖·底背离·日线纠缠</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr">
@@ -20213,7 +20255,7 @@
       <c r="Y132" s="2" t="inlineStr"/>
       <c r="Z132" s="2" t="inlineStr">
         <is>
-          <t>1+→1·16d ← 4→1+·18d</t>
+          <t>1+→1·16d ← 4+→1+·18d ← 4→4+·20d</t>
         </is>
       </c>
       <c r="AA132" s="2" t="inlineStr"/>
@@ -20826,7 +20868,7 @@
       </c>
       <c r="Y136" s="2" t="inlineStr">
         <is>
-          <t>周J超卖·底背离·日线纠缠</t>
+          <t>站稳短均·周J超卖·底背离·日线纠缠</t>
         </is>
       </c>
       <c r="Z136" s="2" t="inlineStr">
@@ -21436,7 +21478,7 @@
       </c>
       <c r="Y140" s="2" t="inlineStr">
         <is>
-          <t>周J超卖·日线纠缠</t>
+          <t>站稳短均·周J超卖·日线纠缠</t>
         </is>
       </c>
       <c r="Z140" s="2" t="inlineStr">
@@ -21747,7 +21789,7 @@
       <c r="Y142" s="2" t="inlineStr"/>
       <c r="Z142" s="2" t="inlineStr">
         <is>
-          <t>4+→4·5d ← 4→4+·7d</t>
+          <t>4+→4·5d ← 4→4+·8d ← 4+→4·17d</t>
         </is>
       </c>
       <c r="AA142" s="2" t="inlineStr"/>
@@ -21895,7 +21937,11 @@
         </is>
       </c>
       <c r="Y143" s="2" t="inlineStr"/>
-      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>4+→4·2d ← 4→4+·3d ← 4+→4·6d</t>
+        </is>
+      </c>
       <c r="AA143" s="2" t="inlineStr"/>
       <c r="AB143" s="2" t="inlineStr"/>
       <c r="AC143" s="2" t="n">
@@ -22791,7 +22837,7 @@
       <c r="Y149" s="2" t="inlineStr"/>
       <c r="Z149" s="2" t="inlineStr">
         <is>
-          <t>1→4·15d</t>
+          <t>4+→4·6d ← 4→4+·11d ← 1→4·15d</t>
         </is>
       </c>
       <c r="AA149" s="2" t="inlineStr"/>
@@ -23681,7 +23727,7 @@
       <c r="Y155" s="2" t="inlineStr"/>
       <c r="Z155" s="2" t="inlineStr">
         <is>
-          <t>4+→4·3d ← 4→4+·7d ← 4+→4·10d</t>
+          <t>4+→4·3d</t>
         </is>
       </c>
       <c r="AA155" s="2" t="inlineStr"/>
@@ -25877,13 +25923,17 @@
       </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y170" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均</t>
+        </is>
+      </c>
       <c r="Z170" s="2" t="inlineStr">
         <is>
-          <t>4+→4·7d ← 4→4+·18d</t>
+          <t>4→4+·19d</t>
         </is>
       </c>
       <c r="AA170" s="2" t="inlineStr"/>
@@ -26041,7 +26091,7 @@
       <c r="Y171" s="2" t="inlineStr"/>
       <c r="Z171" s="2" t="inlineStr">
         <is>
-          <t>4+→4·11d ← 4→4+·18d</t>
+          <t>4+→4·2d ← 4→4+·18d</t>
         </is>
       </c>
       <c r="AA171" s="2" t="inlineStr"/>
@@ -26341,7 +26391,7 @@
       <c r="Y173" s="2" t="inlineStr"/>
       <c r="Z173" s="2" t="inlineStr">
         <is>
-          <t>4→1·3d</t>
+          <t>4→1·3d ← 4+→4·4d ← 4→4+·5d</t>
         </is>
       </c>
       <c r="AA173" s="2" t="inlineStr"/>
@@ -27255,7 +27305,7 @@
       <c r="Y179" s="2" t="inlineStr"/>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>1→4·9d</t>
+          <t>4+→4·7d ← 1→4+·9d</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr"/>
@@ -27549,7 +27599,7 @@
       <c r="Y181" s="2" t="inlineStr"/>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>4+→4·9d ← 4→4+·20d</t>
+          <t>4+→4·2d ← 4→4+·3d ← 4+→4·4d</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr"/>
@@ -28231,7 +28281,7 @@
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>47.18</v>
@@ -28293,23 +28343,23 @@
       <c r="AE186" s="2" t="inlineStr"/>
       <c r="AF186" s="2" t="inlineStr"/>
       <c r="AG186" s="2" t="n">
-        <v>32.32</v>
+        <v>32.4</v>
       </c>
       <c r="AH186" s="2" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="AI186" s="2" t="n"/>
       <c r="AJ186" s="2" t="n">
-        <v>7.25</v>
+        <v>7.56</v>
       </c>
       <c r="AK186" s="2" t="n">
-        <v>-5.99</v>
+        <v>-5.68</v>
       </c>
       <c r="AL186" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AM186" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AN186" s="2" t="inlineStr"/>
       <c r="AO186" s="2" t="inlineStr"/>
@@ -28323,40 +28373,40 @@
         </is>
       </c>
       <c r="AS186" s="2" t="n">
-        <v>1386.8</v>
+        <v>1387.6</v>
       </c>
       <c r="AT186" s="2" t="n">
-        <v>1376.8</v>
+        <v>1377.2</v>
       </c>
       <c r="AU186" s="2" t="n">
-        <v>1390.517</v>
+        <v>1390.717</v>
       </c>
       <c r="AV186" s="2" t="n">
-        <v>1388.915</v>
+        <v>1389.048</v>
       </c>
       <c r="AW186" s="2" t="n">
-        <v>1349.996</v>
+        <v>1350.076</v>
       </c>
       <c r="AX186" s="2" t="n">
-        <v>1298.934</v>
+        <v>1298.974</v>
       </c>
       <c r="AY186" s="2" t="n">
-        <v>1300.685</v>
+        <v>1300.705</v>
       </c>
       <c r="AZ186" s="2" t="n">
-        <v>-0.011</v>
+        <v>0.0041</v>
       </c>
       <c r="BA186" s="2" t="n">
-        <v>-0.3414</v>
+        <v>-0.3339</v>
       </c>
       <c r="BB186" s="2" t="n">
-        <v>0.3495</v>
+        <v>0.3526</v>
       </c>
       <c r="BC186" s="2" t="n">
-        <v>0.116</v>
+        <v>0.1176</v>
       </c>
       <c r="BD186" s="2" t="n">
-        <v>0.3232</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="187">
@@ -28371,7 +28421,7 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>7016</v>
+        <v>6911</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>104.12</v>
@@ -28437,23 +28487,23 @@
       <c r="AE187" s="2" t="inlineStr"/>
       <c r="AF187" s="2" t="inlineStr"/>
       <c r="AG187" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="AH187" s="2" t="n">
-        <v>17.72</v>
+        <v>15.99</v>
       </c>
       <c r="AI187" s="2" t="n"/>
       <c r="AJ187" s="2" t="n">
-        <v>-15.44</v>
+        <v>-17.17</v>
       </c>
       <c r="AK187" s="2" t="n">
-        <v>-12.8</v>
+        <v>-14.53</v>
       </c>
       <c r="AL187" s="2" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AM187" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN187" s="2" t="inlineStr"/>
       <c r="AO187" s="2" t="n">
@@ -28471,40 +28521,40 @@
         </is>
       </c>
       <c r="AS187" s="2" t="n">
-        <v>7363.6</v>
+        <v>7342.6</v>
       </c>
       <c r="AT187" s="2" t="n">
-        <v>7980.9</v>
+        <v>7970.4</v>
       </c>
       <c r="AU187" s="2" t="n">
-        <v>7905.027</v>
+        <v>7899.777</v>
       </c>
       <c r="AV187" s="2" t="n">
-        <v>7663.406</v>
+        <v>7659.906</v>
       </c>
       <c r="AW187" s="2" t="n">
-        <v>7562.643</v>
+        <v>7560.543</v>
       </c>
       <c r="AX187" s="2" t="n">
-        <v>8479.188</v>
+        <v>8478.138000000001</v>
       </c>
       <c r="AY187" s="2" t="n">
-        <v>6205.301</v>
+        <v>6204.776</v>
       </c>
       <c r="AZ187" s="2" t="n">
-        <v>-2.2389</v>
+        <v>-2.3044</v>
       </c>
       <c r="BA187" s="2" t="n">
-        <v>0.2582</v>
+        <v>0.2235</v>
       </c>
       <c r="BB187" s="2" t="n">
-        <v>0.2285</v>
+        <v>0.214</v>
       </c>
       <c r="BC187" s="2" t="n">
-        <v>0.3434</v>
+        <v>0.3369</v>
       </c>
       <c r="BD187" s="2" t="n">
-        <v>0.8815</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="188">
@@ -29849,13 +29899,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y197" s="2" t="inlineStr"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr">
+        <is>
+          <t>站稳短均·周J超卖·日线纠缠</t>
+        </is>
+      </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·18d ← 4+→4·19d</t>
+          <t>4→4+·18d ← 4+→4·19d</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr"/>
@@ -30341,7 +30395,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stage (Weinstein 大阶段 v2.2引擎: EMA30W(150日EMA)锚, 判定优先级从高到低): ①均线排列覆盖: MA20&gt;MA50&gt;MA100&gt;MA150(简单均线)多头排列→强制Stage2; MA20&lt;MA50&lt;MA100&lt;MA150空头排列→强制Stage4(忽略斜率, 解决慢磨盲区) ②斜率双确认: EMA30W变化年化(4周×13与13周×3.88)均&gt;+8%→2; 均&lt;-6%→4(不对称) ③放平带: 52周位置+价格确认分1/3(3:pos&gt;0.55且价≥0.95×EMA30W; 1:pos&lt;0.45且价≤1.05×; 0.45~0.55滞回)。降级层(v2.2): 151-252根新股→①可用②仅≥215根③用上市以来位置, 标记列带'新'; ≤150根→NA</t>
+          <t xml:space="preserve">  Stage (Weinstein 大阶段 v2.3引擎: EMA30W(150日EMA)锚, 判定优先级从高到低): ①均线排列覆盖: MA20&gt;MA50&gt;MA100&gt;MA150(简单均线)多头排列→强制Stage2; MA20&lt;MA50&lt;MA100&lt;MA150空头排列→强制Stage4(忽略斜率, 解决慢磨盲区) ②斜率双确认: EMA30W变化年化(4周×13与13周×3.88)均&gt;+8%→2; 均&lt;-6%→4(不对称) ③放平带: 52周位置+价格确认分1/3(3:pos&gt;0.55且价≥0.95×EMA30W; 1:pos&lt;0.45且价≤1.05×; 0.45~0.55滞回)。降级层(v2.2): 151-252根新股→①可用②仅≥215根③用上市以来位置, 标记列带'新'; ≤150根→NA</t>
         </is>
       </c>
     </row>
@@ -30362,14 +30416,14 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档(v2.1): 4+=止跌(日线MA5/10/20纠缠+快线&gt;慢线+周J超卖或底背离, 价&lt;EMA10W) | 1=筑底(不区分价格vs EMA10W) | 1+=强筑底(站稳MA5/10/20全三条+全上行+周MACD DIF&gt;DEA) | 2A=修复态或刚确立(≤10日) | 2B=满配(slope10&gt;0·EMA10W&gt;EMA30W·10日前也是) | 2C=满配+延伸/减速/顶背离 | 3/4不分档</t>
+          <t xml:space="preserve">  子档(v2.3): 4+=双路径: A止跌(纠缠/快慢线+周J超卖或底背离, 价&lt;EMA10W) ∨ B短期修复(站稳MA5/10/20三条) | 1=筑底(不区分价格vs EMA10W) | 1+=强筑底(站稳MA5/10/20全三条+全上行+周MACD DIF&gt;DEA) | 2A=修复态或刚确立(≤10日) | 2B=满配(slope10&gt;0·EMA10W&gt;EMA30W·10日前也是) | 2C=满配+延伸/减速/顶背离 | 3/4不分档</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档标记: 状态描述列(与子档列分开)。4+→周J超卖·底背离·日线纠缠(止跌命中条件); 1+→预金叉(EMA10W/30W将≤20日内纠缠或金叉)·纠缠·底背离; 2C→延伸(价超EMA30W达25%)·减速·顶背离; 新=降级层(上市151-252根弱规则档)</t>
+          <t xml:space="preserve">  子档标记: 状态描述列(与子档列分开)。4+→站稳短均(路径B)·周J超卖·底背离·日线纠缠(路径A); 1+→预金叉(EMA10W/30W将≤20日内纠缠或金叉)·纠缠·底背离; 2C→延伸(价超EMA30W达25%)·减速·顶背离; 新=降级层(上市151-252根弱规则档)</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -899,14 +899,14 @@
         <v>80.18000000000001</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.37</v>
       </c>
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="n">
-        <v>-28.57</v>
+        <v>-22.32</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>-16.09</v>
+        <v>-12.74</v>
       </c>
       <c r="AM2" s="2" t="n">
         <v>2.4</v>
@@ -1056,14 +1056,14 @@
         <v>96.52</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>17.75</v>
+        <v>15.97</v>
       </c>
       <c r="AJ3" s="2" t="n"/>
       <c r="AK3" s="2" t="n">
-        <v>-14.31</v>
+        <v>-12.88</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>-1.24</v>
+        <v>3.47</v>
       </c>
       <c r="AM3" s="2" t="n">
         <v>55.6</v>
@@ -1205,14 +1205,14 @@
         <v>130.74</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>35.66</v>
+        <v>41.27</v>
       </c>
       <c r="AJ4" s="2" t="n"/>
       <c r="AK4" s="2" t="n">
-        <v>-34.03</v>
+        <v>-23.63</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>-23.18</v>
+        <v>-14.73</v>
       </c>
       <c r="AM4" s="2" t="n">
         <v>61.3</v>
@@ -1354,14 +1354,14 @@
         <v>27.53</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>-8.56</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="AJ5" s="2" t="n"/>
       <c r="AK5" s="2" t="n">
-        <v>3.73</v>
+        <v>3.07</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>3.99</v>
+        <v>2.07</v>
       </c>
       <c r="AM5" s="2" t="n">
         <v>13.8</v>
@@ -1497,14 +1497,14 @@
         <v>45.11</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>-8.06</v>
+        <v>-7.1</v>
       </c>
       <c r="AJ6" s="2" t="n"/>
       <c r="AK6" s="2" t="n">
-        <v>-4.98</v>
+        <v>-6.01</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>-0.92</v>
+        <v>1.05</v>
       </c>
       <c r="AM6" s="2" t="n">
         <v>22.5</v>
@@ -1658,14 +1658,14 @@
         <v>41.56</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>9.82</v>
+        <v>9</v>
       </c>
       <c r="AJ7" s="2" t="n"/>
       <c r="AK7" s="2" t="n">
-        <v>15.7</v>
+        <v>12.66</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>11.07</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AM7" s="2" t="n">
         <v>98.40000000000001</v>
@@ -1815,14 +1815,14 @@
         <v>16.94</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>-1.15</v>
+        <v>0.03</v>
       </c>
       <c r="AJ8" s="2" t="n"/>
       <c r="AK8" s="2" t="n">
-        <v>11.84</v>
+        <v>12.05</v>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>6.14</v>
+        <v>4.39</v>
       </c>
       <c r="AM8" s="2" t="n">
         <v>74.59999999999999</v>
@@ -1958,14 +1958,14 @@
         <v>-32.79</v>
       </c>
       <c r="AI9" s="2" t="n">
-        <v>-27.95</v>
+        <v>-27.86</v>
       </c>
       <c r="AJ9" s="2" t="n"/>
       <c r="AK9" s="2" t="n">
-        <v>7.98</v>
+        <v>6.98</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.6</v>
       </c>
       <c r="AM9" s="2" t="n">
         <v>8.5</v>
@@ -2111,14 +2111,14 @@
         <v>-30.66</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>-20.49</v>
+        <v>-18.74</v>
       </c>
       <c r="AJ10" s="2" t="n"/>
       <c r="AK10" s="2" t="n">
-        <v>5.86</v>
+        <v>7.72</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>1.52</v>
+        <v>0.33</v>
       </c>
       <c r="AM10" s="2" t="n">
         <v>57.9</v>
@@ -2262,14 +2262,14 @@
         <v>33.18</v>
       </c>
       <c r="AI11" s="2" t="n">
-        <v>6.38</v>
+        <v>7.56</v>
       </c>
       <c r="AJ11" s="2" t="n"/>
       <c r="AK11" s="2" t="n">
-        <v>12.9</v>
+        <v>11.03</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>5.86</v>
+        <v>6.83</v>
       </c>
       <c r="AM11" s="2" t="n">
         <v>48.7</v>
@@ -2356,14 +2356,14 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>8</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>0011111001</t>
+          <t>0011101001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2407,14 +2407,14 @@
         <v>1.92</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>-6.51</v>
+        <v>-6.75</v>
       </c>
       <c r="AJ12" s="2" t="n"/>
       <c r="AK12" s="2" t="n">
-        <v>7.59</v>
+        <v>6.28</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>6.68</v>
       </c>
       <c r="AM12" s="2" t="n">
         <v>31</v>
@@ -2558,14 +2558,14 @@
         <v>108.01</v>
       </c>
       <c r="AI13" s="2" t="n">
-        <v>10.28</v>
+        <v>8.15</v>
       </c>
       <c r="AJ13" s="2" t="n"/>
       <c r="AK13" s="2" t="n">
-        <v>-25.39</v>
+        <v>-22.07</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>-29.38</v>
+        <v>-27.36</v>
       </c>
       <c r="AM13" s="2" t="n">
         <v>43.9</v>
@@ -2705,14 +2705,14 @@
         <v>36.08</v>
       </c>
       <c r="AI14" s="2" t="n">
-        <v>-9.33</v>
+        <v>-10.1</v>
       </c>
       <c r="AJ14" s="2" t="n"/>
       <c r="AK14" s="2" t="n">
-        <v>-8.16</v>
+        <v>-6.83</v>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>-0.64</v>
+        <v>1.02</v>
       </c>
       <c r="AM14" s="2" t="n">
         <v>20</v>
@@ -2846,14 +2846,14 @@
         <v>19.67</v>
       </c>
       <c r="AI15" s="2" t="n">
-        <v>-22.05</v>
+        <v>-22.1</v>
       </c>
       <c r="AJ15" s="2" t="n"/>
       <c r="AK15" s="2" t="n">
-        <v>-4.54</v>
+        <v>-5.5</v>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" s="2" t="n">
         <v>15.6</v>
@@ -2993,14 +2993,14 @@
         <v>17.94</v>
       </c>
       <c r="AI16" s="2" t="n">
-        <v>-22.35</v>
+        <v>-22.24</v>
       </c>
       <c r="AJ16" s="2" t="n"/>
       <c r="AK16" s="2" t="n">
-        <v>-5.76</v>
+        <v>-4.81</v>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>-2.46</v>
+        <v>-2.97</v>
       </c>
       <c r="AM16" s="2" t="n">
         <v>7.9</v>
@@ -3144,14 +3144,14 @@
         <v>10.44</v>
       </c>
       <c r="AI17" s="2" t="n">
-        <v>-14.7</v>
+        <v>-14.31</v>
       </c>
       <c r="AJ17" s="2" t="n"/>
       <c r="AK17" s="2" t="n">
-        <v>1.06</v>
+        <v>3.99</v>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>-1.62</v>
+        <v>-3.6</v>
       </c>
       <c r="AM17" s="2" t="n">
         <v>8.800000000000001</v>
@@ -3289,14 +3289,14 @@
         <v>34.05</v>
       </c>
       <c r="AI18" s="2" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AJ18" s="2" t="n"/>
       <c r="AK18" s="2" t="n">
-        <v>-0.26</v>
+        <v>2.24</v>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>9.75</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AM18" s="2" t="n">
         <v>78.40000000000001</v>
@@ -3432,14 +3432,14 @@
         <v>-3.32</v>
       </c>
       <c r="AI19" s="2" t="n">
-        <v>-23.37</v>
+        <v>-22.58</v>
       </c>
       <c r="AJ19" s="2" t="n"/>
       <c r="AK19" s="2" t="n">
-        <v>-4.97</v>
+        <v>-2.72</v>
       </c>
       <c r="AL19" s="2" t="n">
-        <v>-1.07</v>
+        <v>-0.88</v>
       </c>
       <c r="AM19" s="2" t="n">
         <v>4.1</v>
@@ -3577,14 +3577,14 @@
         <v>-5.81</v>
       </c>
       <c r="AI20" s="2" t="n">
-        <v>-31.39</v>
+        <v>-32.85</v>
       </c>
       <c r="AJ20" s="2" t="n"/>
       <c r="AK20" s="2" t="n">
-        <v>-5.47</v>
+        <v>-7.32</v>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>-28.73</v>
+        <v>-29.97</v>
       </c>
       <c r="AM20" s="2" t="n">
         <v>7.5</v>
@@ -3677,14 +3677,14 @@
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>0010011000</t>
+          <t>0010001000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3724,14 +3724,14 @@
         <v>40.39</v>
       </c>
       <c r="AI21" s="2" t="n">
-        <v>-1.03</v>
+        <v>-1.14</v>
       </c>
       <c r="AJ21" s="2" t="n"/>
       <c r="AK21" s="2" t="n">
-        <v>-11.75</v>
+        <v>-7.79</v>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>3.13</v>
+        <v>1.97</v>
       </c>
       <c r="AM21" s="2" t="n">
         <v>29.8</v>
@@ -3877,14 +3877,14 @@
         <v>85.56</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>19.96</v>
+        <v>18.75</v>
       </c>
       <c r="AJ22" s="2" t="n"/>
       <c r="AK22" s="2" t="n">
-        <v>-14.26</v>
+        <v>-15.9</v>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>3.51</v>
+        <v>3.97</v>
       </c>
       <c r="AM22" s="2" t="n">
         <v>82.59999999999999</v>
@@ -4034,14 +4034,14 @@
         <v>46.38</v>
       </c>
       <c r="AI23" s="2" t="n">
-        <v>7.49</v>
+        <v>8.41</v>
       </c>
       <c r="AJ23" s="2" t="n"/>
       <c r="AK23" s="2" t="n">
-        <v>5.41</v>
+        <v>6.83</v>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>4.26</v>
+        <v>4.35</v>
       </c>
       <c r="AM23" s="2" t="n">
         <v>54.7</v>
@@ -4128,19 +4128,19 @@
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>0111110110</t>
+          <t>0111100110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0111110110</t>
+          <t>0111100110</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -4179,14 +4179,14 @@
         <v>47.89</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>0.03</v>
+        <v>3.51</v>
       </c>
       <c r="AJ24" s="2" t="n"/>
       <c r="AK24" s="2" t="n">
-        <v>-10.31</v>
+        <v>-8.06</v>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>8.5</v>
+        <v>11.58</v>
       </c>
       <c r="AM24" s="2" t="n">
         <v>47.2</v>
@@ -4324,14 +4324,14 @@
         <v>110.58</v>
       </c>
       <c r="AI25" s="2" t="n">
-        <v>27.53</v>
+        <v>28.06</v>
       </c>
       <c r="AJ25" s="2" t="n"/>
       <c r="AK25" s="2" t="n">
-        <v>-10.74</v>
+        <v>-5.63</v>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>1.77</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AM25" s="2" t="n">
         <v>3</v>
@@ -4471,14 +4471,14 @@
         <v>87.66</v>
       </c>
       <c r="AI26" s="2" t="n">
-        <v>15.48</v>
+        <v>16.21</v>
       </c>
       <c r="AJ26" s="2" t="n"/>
       <c r="AK26" s="2" t="n">
-        <v>-22.77</v>
+        <v>-16.95</v>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>-17.67</v>
+        <v>-14.31</v>
       </c>
       <c r="AM26" s="2" t="n">
         <v>21.6</v>
@@ -4626,14 +4626,14 @@
         <v>-2.71</v>
       </c>
       <c r="AI27" s="2" t="n">
-        <v>-5.55</v>
+        <v>-5.71</v>
       </c>
       <c r="AJ27" s="2" t="n"/>
       <c r="AK27" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AL27" s="2" t="n">
-        <v>13.27</v>
+        <v>11.59</v>
       </c>
       <c r="AM27" s="2" t="n">
         <v>93.7</v>
@@ -4781,14 +4781,14 @@
         <v>-9.43</v>
       </c>
       <c r="AI28" s="2" t="n">
-        <v>-23.08</v>
+        <v>-19.92</v>
       </c>
       <c r="AJ28" s="2" t="n"/>
       <c r="AK28" s="2" t="n">
-        <v>2.65</v>
+        <v>7.21</v>
       </c>
       <c r="AL28" s="2" t="n">
-        <v>-0.16</v>
+        <v>1.08</v>
       </c>
       <c r="AM28" s="2" t="n">
         <v>26.4</v>
@@ -4926,14 +4926,14 @@
         <v>92.92</v>
       </c>
       <c r="AI29" s="2" t="n">
-        <v>15.89</v>
+        <v>16.24</v>
       </c>
       <c r="AJ29" s="2" t="n"/>
       <c r="AK29" s="2" t="n">
-        <v>-10.26</v>
+        <v>-11.46</v>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>7.3</v>
+        <v>8.26</v>
       </c>
       <c r="AM29" s="2" t="n">
         <v>37.7</v>
@@ -5081,14 +5081,14 @@
         <v>7.88</v>
       </c>
       <c r="AI30" s="2" t="n">
-        <v>-11.96</v>
+        <v>-10.7</v>
       </c>
       <c r="AJ30" s="2" t="n"/>
       <c r="AK30" s="2" t="n">
-        <v>6.75</v>
+        <v>7.13</v>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>8.91</v>
+        <v>10.37</v>
       </c>
       <c r="AM30" s="2" t="n">
         <v>49.7</v>
@@ -5230,14 +5230,14 @@
         <v>-4.78</v>
       </c>
       <c r="AI31" s="2" t="n">
-        <v>-12.19</v>
+        <v>-12.16</v>
       </c>
       <c r="AJ31" s="2" t="n"/>
       <c r="AK31" s="2" t="n">
-        <v>-0.55</v>
+        <v>1.51</v>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>-3.15</v>
+        <v>-2.89</v>
       </c>
       <c r="AM31" s="2" t="n">
         <v>40.7</v>
@@ -5377,14 +5377,14 @@
         <v>22.24</v>
       </c>
       <c r="AI32" s="2" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="AJ32" s="2" t="n"/>
       <c r="AK32" s="2" t="n">
-        <v>10.92</v>
+        <v>12.01</v>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>-1.92</v>
+        <v>-3.45</v>
       </c>
       <c r="AM32" s="2" t="n">
         <v>79</v>
@@ -5518,14 +5518,14 @@
         <v>11.87</v>
       </c>
       <c r="AI33" s="2" t="n">
-        <v>-10.72</v>
+        <v>-10.66</v>
       </c>
       <c r="AJ33" s="2" t="n"/>
       <c r="AK33" s="2" t="n">
-        <v>7.78</v>
+        <v>7.96</v>
       </c>
       <c r="AL33" s="2" t="n">
-        <v>-3.36</v>
+        <v>-4.83</v>
       </c>
       <c r="AM33" s="2" t="n">
         <v>35.2</v>
@@ -5663,14 +5663,14 @@
         <v>34.32</v>
       </c>
       <c r="AI34" s="2" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AJ34" s="2" t="n"/>
       <c r="AK34" s="2" t="n">
-        <v>8.43</v>
+        <v>6.75</v>
       </c>
       <c r="AL34" s="2" t="n">
-        <v>6.28</v>
+        <v>5.36</v>
       </c>
       <c r="AM34" s="2" t="n">
         <v>50.5</v>
@@ -5816,14 +5816,14 @@
         <v>44.6</v>
       </c>
       <c r="AI35" s="2" t="n">
-        <v>9.73</v>
+        <v>9.82</v>
       </c>
       <c r="AJ35" s="2" t="n"/>
       <c r="AK35" s="2" t="n">
-        <v>7.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>-4.97</v>
+        <v>-4.98</v>
       </c>
       <c r="AM35" s="2" t="n">
         <v>85.90000000000001</v>
@@ -5967,14 +5967,14 @@
         <v>11.97</v>
       </c>
       <c r="AI36" s="2" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.16</v>
       </c>
       <c r="AJ36" s="2" t="n"/>
       <c r="AK36" s="2" t="n">
-        <v>7.4</v>
+        <v>9.08</v>
       </c>
       <c r="AL36" s="2" t="n">
-        <v>-1.61</v>
+        <v>-3.79</v>
       </c>
       <c r="AM36" s="2" t="n">
         <v>75</v>
@@ -6066,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0110011000</t>
+          <t>0110001000</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -6110,14 +6110,14 @@
         <v>69.38</v>
       </c>
       <c r="AI37" s="2" t="n">
-        <v>5.76</v>
+        <v>6.83</v>
       </c>
       <c r="AJ37" s="2" t="n"/>
       <c r="AK37" s="2" t="n">
-        <v>-12.46</v>
+        <v>-9.93</v>
       </c>
       <c r="AL37" s="2" t="n">
-        <v>-0.13</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" s="2" t="n">
         <v>26.1</v>
@@ -6263,14 +6263,14 @@
         <v>35.32</v>
       </c>
       <c r="AI38" s="2" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="AJ38" s="2" t="n"/>
       <c r="AK38" s="2" t="n">
-        <v>7.89</v>
+        <v>7.99</v>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>-7.07</v>
+        <v>-6.73</v>
       </c>
       <c r="AM38" s="2" t="n">
         <v>71.90000000000001</v>
@@ -6414,14 +6414,14 @@
         <v>29.93</v>
       </c>
       <c r="AI39" s="2" t="n">
-        <v>-5.26</v>
+        <v>-5.51</v>
       </c>
       <c r="AJ39" s="2" t="n"/>
       <c r="AK39" s="2" t="n">
-        <v>7.7</v>
+        <v>7.79</v>
       </c>
       <c r="AL39" s="2" t="n">
-        <v>-5.56</v>
+        <v>-6.33</v>
       </c>
       <c r="AM39" s="2" t="n">
         <v>67.2</v>
@@ -6561,14 +6561,14 @@
         <v>60.79</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>19.28</v>
+        <v>17.09</v>
       </c>
       <c r="AJ40" s="2" t="n"/>
       <c r="AK40" s="2" t="n">
-        <v>12.57</v>
+        <v>6.78</v>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>2.42</v>
+        <v>-1.96</v>
       </c>
       <c r="AM40" s="2" t="n">
         <v>99.09999999999999</v>
@@ -6714,14 +6714,14 @@
         <v>68.59</v>
       </c>
       <c r="AI41" s="2" t="n">
-        <v>20.57</v>
+        <v>19.71</v>
       </c>
       <c r="AJ41" s="2" t="n"/>
       <c r="AK41" s="2" t="n">
-        <v>13.03</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AL41" s="2" t="n">
-        <v>4.61</v>
+        <v>1.78</v>
       </c>
       <c r="AM41" s="2" t="n">
         <v>99.7</v>
@@ -6867,14 +6867,14 @@
         <v>68.56</v>
       </c>
       <c r="AI42" s="2" t="n">
-        <v>22.69</v>
+        <v>21.57</v>
       </c>
       <c r="AJ42" s="2" t="n"/>
       <c r="AK42" s="2" t="n">
-        <v>14.11</v>
+        <v>10.05</v>
       </c>
       <c r="AL42" s="2" t="n">
-        <v>0.09</v>
+        <v>-3.16</v>
       </c>
       <c r="AM42" s="2" t="n">
         <v>88.7</v>
@@ -7012,14 +7012,14 @@
         <v>34.74</v>
       </c>
       <c r="AI43" s="2" t="n">
-        <v>3.95</v>
+        <v>1.37</v>
       </c>
       <c r="AJ43" s="2" t="n"/>
       <c r="AK43" s="2" t="n">
-        <v>10.17</v>
+        <v>6.24</v>
       </c>
       <c r="AL43" s="2" t="n">
-        <v>12.83</v>
+        <v>9.1</v>
       </c>
       <c r="AM43" s="2" t="n">
         <v>28</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>15.42</v>
+        <v>15.44</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>29.76</v>
@@ -15691,14 +15691,14 @@
       <c r="P101" s="2" t="inlineStr"/>
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S101" s="2" t="n">
         <v>6</v>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>0111111001</t>
+          <t>0111111011</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -15739,22 +15739,22 @@
       <c r="AF101" s="2" t="inlineStr"/>
       <c r="AG101" s="2" t="inlineStr"/>
       <c r="AH101" s="2" t="n">
-        <v>45.83</v>
+        <v>45.87</v>
       </c>
       <c r="AI101" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="AJ101" s="2" t="n">
-        <v>12.74</v>
+        <v>12.89</v>
       </c>
       <c r="AK101" s="2" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="AL101" s="2" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="AM101" s="2" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="AN101" s="2" t="n">
         <v>54</v>
@@ -15769,19 +15769,19 @@
         </is>
       </c>
       <c r="AT101" s="2" t="n">
-        <v>15.34</v>
+        <v>15.344</v>
       </c>
       <c r="AU101" s="2" t="n">
-        <v>15.243</v>
+        <v>15.245</v>
       </c>
       <c r="AV101" s="2" t="n">
-        <v>14.943</v>
+        <v>14.944</v>
       </c>
       <c r="AW101" s="2" t="n">
         <v>15.288</v>
       </c>
       <c r="AX101" s="2" t="n">
-        <v>15.355</v>
+        <v>15.356</v>
       </c>
       <c r="AY101" s="2" t="n">
         <v>14.804</v>
@@ -15790,19 +15790,19 @@
         <v>14.254</v>
       </c>
       <c r="BA101" s="2" t="n">
-        <v>1.1935</v>
+        <v>1.2005</v>
       </c>
       <c r="BB101" s="2" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="BC101" s="2" t="n">
-        <v>0.2571</v>
+        <v>0.2585</v>
       </c>
       <c r="BD101" s="2" t="n">
-        <v>0.0547</v>
+        <v>0.0554</v>
       </c>
       <c r="BE101" s="2" t="n">
-        <v>0.4583</v>
+        <v>0.4587</v>
       </c>
     </row>
     <row r="102">
@@ -19008,7 +19008,7 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>709.325</v>
+        <v>709.33</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>101.54</v>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="AT123" s="2" t="n">
-        <v>737.809</v>
+        <v>737.8099999999999</v>
       </c>
       <c r="AU123" s="2" t="n">
-        <v>733.069</v>
+        <v>733.0700000000001</v>
       </c>
       <c r="AV123" s="2" t="n">
         <v>735.775</v>
@@ -19119,7 +19119,7 @@
         <v>708.13</v>
       </c>
       <c r="AX123" s="2" t="n">
-        <v>654.955</v>
+        <v>654.956</v>
       </c>
       <c r="AY123" s="2" t="n">
         <v>627.479</v>
@@ -19131,7 +19131,7 @@
         <v>0.3963</v>
       </c>
       <c r="BB123" s="2" t="n">
-        <v>1.2094</v>
+        <v>1.2095</v>
       </c>
       <c r="BC123" s="2" t="n">
         <v>1.2651</v>
@@ -19309,7 +19309,7 @@
         <v>18.82</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>-15.04</v>
+        <v>-15.01</v>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr">
@@ -20186,10 +20186,10 @@
         </is>
       </c>
       <c r="AT130" s="2" t="n">
-        <v>249.787</v>
+        <v>249.788</v>
       </c>
       <c r="AU130" s="2" t="n">
-        <v>264.157</v>
+        <v>264.158</v>
       </c>
       <c r="AV130" s="2" t="n">
         <v>263.114</v>
@@ -20204,13 +20204,13 @@
         <v>240.697</v>
       </c>
       <c r="AZ130" s="2" t="n">
-        <v>175.784</v>
+        <v>175.785</v>
       </c>
       <c r="BA130" s="2" t="n">
-        <v>-1.3522</v>
+        <v>-1.3521</v>
       </c>
       <c r="BB130" s="2" t="n">
-        <v>0.9452</v>
+        <v>0.9453</v>
       </c>
       <c r="BC130" s="2" t="n">
         <v>1.0014</v>
@@ -28232,7 +28232,7 @@
         <v>134.18</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
@@ -28552,19 +28552,19 @@
       <c r="P186" s="2" t="inlineStr"/>
       <c r="Q186" s="2" t="inlineStr"/>
       <c r="R186" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S186" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>0111111100</t>
+          <t>0111101100</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
         <is>
-          <t>0111111100</t>
+          <t>0111101100</t>
         </is>
       </c>
       <c r="V186" s="2" t="inlineStr">
@@ -28597,14 +28597,14 @@
         <v>32.28</v>
       </c>
       <c r="AI186" s="2" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="AJ186" s="2" t="n"/>
       <c r="AK186" s="2" t="n">
-        <v>8.4</v>
+        <v>7.48</v>
       </c>
       <c r="AL186" s="2" t="n">
-        <v>-4.56</v>
+        <v>-5.76</v>
       </c>
       <c r="AM186" s="2" t="n">
         <v>79.09999999999999</v>
@@ -30412,7 +30412,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-17 | 197 只</t>
+          <t>截至: 2026-10-18 | 197 只</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2703</v>
+        <v>2635</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>14.39</v>
@@ -854,9 +854,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
@@ -881,21 +879,25 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W2" s="2" t="n">
-        <v>216</v>
+        <v>3</v>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>3-</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>预死叉</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·2d</t>
+          <t>2C→3-·3d</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
@@ -912,27 +914,27 @@
       <c r="AH2" s="2" t="inlineStr"/>
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="n">
-        <v>80.18000000000001</v>
+        <v>73.13</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.37</v>
+        <v>-0.97</v>
       </c>
       <c r="AL2" s="2" t="n"/>
       <c r="AM2" s="2" t="n">
-        <v>-22.32</v>
+        <v>-21.83</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>-12.74</v>
+        <v>-15.26</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AP2" s="2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS2" s="2" t="inlineStr"/>
       <c r="AT2" s="2" t="inlineStr">
@@ -946,40 +948,40 @@
         </is>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>2998.1</v>
+        <v>2839.9</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>3310.65</v>
+        <v>3215.35</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>3197.95</v>
+        <v>3184.675</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>3172.667</v>
+        <v>3149.933</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>3334.48</v>
+        <v>3318.04</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>3678.762</v>
+        <v>3673.425</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>2784.347</v>
+        <v>2791.238</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>-1.4869</v>
+        <v>-3.3817</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>-0.0791</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>-0.3327</v>
+        <v>-0.4843</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>-0.0155</v>
+        <v>-0.1394</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.8018</v>
+        <v>0.7313</v>
       </c>
     </row>
     <row r="3">
@@ -994,7 +996,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15040</v>
+        <v>14860</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>89.05</v>
@@ -1013,9 +1015,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
@@ -1023,45 +1023,43 @@
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>0110011110</t>
+          <t>0110011000</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>0010011010</t>
+          <t>0010010000</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W3" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>3-</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2C→2B·2d ← 3-→2C·12d</t>
+          <t>2C→3-·3d ← 3-→2C·13d</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>1</v>
       </c>
@@ -1070,73 +1068,75 @@
         <v>-1</v>
       </c>
       <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AH3" s="2" t="inlineStr"/>
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="n">
-        <v>96.52</v>
+        <v>91.91</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>15.97</v>
+        <v>15.78</v>
       </c>
       <c r="AL3" s="2" t="n"/>
       <c r="AM3" s="2" t="n">
-        <v>-12.88</v>
+        <v>-13.76</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>3.47</v>
+        <v>1.32</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>55.6</v>
+        <v>54.2</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU3" s="2" t="inlineStr">
         <is>
           <t>无背离</t>
         </is>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>16076</v>
+        <v>15533</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>16911</v>
+        <v>16669</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>15647.362</v>
+        <v>15704.862</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>15581.408</v>
+        <v>15542.741</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>15791.245</v>
+        <v>15807.245</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>16252.322</v>
+        <v>16220.822</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>13602.541</v>
+        <v>13648.185</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>2.0591</v>
+        <v>0.3608</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.8263</v>
+        <v>0.6954</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>1.0721</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>-0.0968</v>
+        <v>-0.2093</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9191</v>
       </c>
     </row>
     <row r="4">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9764</v>
+        <v>9459</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>107.99</v>
@@ -1180,19 +1180,19 @@
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>0110111010</t>
+          <t>0110111000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0110111000</t>
+          <t>0010111000</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1226,23 +1226,23 @@
       <c r="AH4" s="2" t="inlineStr"/>
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="n">
-        <v>130.74</v>
+        <v>124.03</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>41.27</v>
+        <v>38.1</v>
       </c>
       <c r="AL4" s="2" t="n"/>
       <c r="AM4" s="2" t="n">
-        <v>-23.63</v>
+        <v>-21.99</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>-14.73</v>
+        <v>-17.02</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>61.3</v>
+        <v>58.6</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1258,40 +1258,40 @@
         </is>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>10321.4</v>
+        <v>9910.200000000001</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>11245.2</v>
+        <v>10981.1</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>10923.879</v>
+        <v>10919.597</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>10690.58</v>
+        <v>10663.924</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>10344.656</v>
+        <v>10378.695</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>10263.997</v>
+        <v>10262.467</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>7454.352</v>
+        <v>7487.747</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>-2.313</v>
+        <v>-3.4214</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.208</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>1.4461</v>
+        <v>1.2857</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.5942</v>
+        <v>0.3955</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>1.3074</v>
+        <v>1.2403</v>
       </c>
     </row>
     <row r="5">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5978</v>
+        <v>5971</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>18.68</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="W5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2A→4·5d</t>
+          <t>2A→4·6d</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
@@ -1366,77 +1366,81 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AH5" s="2" t="inlineStr"/>
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="n">
-        <v>27.53</v>
+        <v>26.28</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>-9.539999999999999</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="AL5" s="2" t="n"/>
       <c r="AM5" s="2" t="n">
-        <v>3.07</v>
+        <v>4.61</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>2.07</v>
+        <v>3.98</v>
       </c>
       <c r="AO5" s="2" t="n">
         <v>13.8</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU5" s="2" t="inlineStr">
         <is>
           <t>背离</t>
         </is>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>6054.6</v>
+        <v>6031.8</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>6119.7</v>
+        <v>6113.8</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>5975.145</v>
+        <v>5990.025</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>5909.183</v>
+        <v>5909.967</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>5990.929</v>
+        <v>5993.851</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>6527.134</v>
+        <v>6516.745</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>6261.197</v>
+        <v>6267.4</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.7668</v>
+        <v>0.5275</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.7507</v>
+        <v>0.7019</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.1933</v>
+        <v>0.2258</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>-0.3528</v>
+        <v>-0.3568</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.2753</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="6">
@@ -1451,7 +1455,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8331</v>
+        <v>8219</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>70.48999999999999</v>
@@ -1464,9 +1468,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
@@ -1477,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
@@ -1486,24 +1488,28 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0010000010</t>
+          <t>0010000000</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W6" s="2" t="n">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>2A→4·3d</t>
+        </is>
+      </c>
       <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -1515,32 +1521,30 @@
         <v>-1</v>
       </c>
       <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AH6" s="2" t="inlineStr"/>
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="n">
-        <v>45.11</v>
+        <v>43.05</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>-7.1</v>
+        <v>-7.23</v>
       </c>
       <c r="AL6" s="2" t="n"/>
       <c r="AM6" s="2" t="n">
-        <v>-6.01</v>
+        <v>-6</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>1.05</v>
+        <v>-0.31</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS6" s="2" t="inlineStr"/>
       <c r="AT6" s="2" t="inlineStr">
@@ -1554,40 +1558,40 @@
         </is>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>8757</v>
+        <v>8534</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>8990.4</v>
+        <v>8921.5</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>8639.6</v>
+        <v>8649.799999999999</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>8504.6</v>
+        <v>8494.066999999999</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>8704.459999999999</v>
+        <v>8691.4</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>9563.772999999999</v>
+        <v>9535.309999999999</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>8825.781999999999</v>
+        <v>8839.476000000001</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.7665</v>
+        <v>-0.2084</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.9272</v>
+        <v>0.6085</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>-0.0941</v>
+        <v>-0.0987</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>-0.4214</v>
+        <v>-0.5008</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.4511</v>
+        <v>0.4305</v>
       </c>
     </row>
     <row r="7">
@@ -1602,7 +1606,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6223</v>
+        <v>6218</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>75.40000000000001</v>
@@ -1629,25 +1633,27 @@
       <c r="N7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1111111111</t>
+          <t>0111111101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1111111111</t>
+          <t>0111111101</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1656,7 +1662,7 @@
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
@@ -1681,28 +1687,28 @@
       <c r="AH7" s="2" t="inlineStr"/>
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="n">
-        <v>41.56</v>
+        <v>43.28</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>9</v>
+        <v>10.27</v>
       </c>
       <c r="AL7" s="2" t="n"/>
       <c r="AM7" s="2" t="n">
-        <v>12.66</v>
+        <v>13.44</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
       <c r="AS7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT7" s="2" t="inlineStr"/>
       <c r="AU7" s="2" t="inlineStr">
@@ -1711,40 +1717,40 @@
         </is>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>6020.2</v>
+        <v>6095.2</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>5868.4</v>
+        <v>5925.9</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>5830.702</v>
+        <v>5854.28</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>5772.209</v>
+        <v>5787.994</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>5677.749</v>
+        <v>5695.81</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>5406.418</v>
+        <v>5418.387</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>5331.945</v>
+        <v>5341.373</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>1.0455</v>
+        <v>1.587</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.9791</v>
+        <v>1.1088</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.3693</v>
+        <v>0.5036</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.4204</v>
+        <v>0.4722</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.4156</v>
+        <v>0.4328</v>
       </c>
     </row>
     <row r="8">
@@ -1759,7 +1765,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2418.5</v>
+        <v>2419</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>39.9</v>
@@ -1774,7 +1780,7 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1782,19 +1788,19 @@
         <v>1</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111111111</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1111111101</t>
+          <t>1101111101</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1803,7 +1809,7 @@
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
@@ -1825,79 +1831,75 @@
       <c r="AG8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AH8" s="2" t="n">
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AI8" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
       <c r="AJ8" s="2" t="n">
-        <v>16.94</v>
+        <v>18.14</v>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>0.03</v>
+        <v>1.3</v>
       </c>
       <c r="AL8" s="2" t="n"/>
       <c r="AM8" s="2" t="n">
-        <v>12.05</v>
+        <v>13.31</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>4.39</v>
+        <v>4.69</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
       <c r="AS8" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT8" s="2" t="inlineStr"/>
       <c r="AU8" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>柱≥0</t>
         </is>
       </c>
       <c r="AV8" s="2" t="n">
-        <v>2317.1</v>
+        <v>2351.4</v>
       </c>
       <c r="AW8" s="2" t="n">
-        <v>2281.25</v>
+        <v>2298.65</v>
       </c>
       <c r="AX8" s="2" t="n">
-        <v>2297.316</v>
+        <v>2304.483</v>
       </c>
       <c r="AY8" s="2" t="n">
-        <v>2290.327</v>
+        <v>2291.845</v>
       </c>
       <c r="AZ8" s="2" t="n">
-        <v>2290.999</v>
+        <v>2296.598</v>
       </c>
       <c r="BA8" s="2" t="n">
-        <v>2212.254</v>
+        <v>2214.135</v>
       </c>
       <c r="BB8" s="2" t="n">
-        <v>2260.082</v>
+        <v>2261.927</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>-0.0267</v>
+        <v>0.625</v>
       </c>
       <c r="BD8" s="2" t="n">
-        <v>0.5717</v>
+        <v>0.729</v>
       </c>
       <c r="BE8" s="2" t="n">
-        <v>0.2501</v>
+        <v>0.3433</v>
       </c>
       <c r="BF8" s="2" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1159</v>
       </c>
       <c r="BG8" s="2" t="n">
-        <v>0.1694</v>
+        <v>0.1814</v>
       </c>
     </row>
     <row r="9">
@@ -1912,7 +1914,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6353</v>
+        <v>6271</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2.93</v>
@@ -1938,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
@@ -1947,7 +1949,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1956,7 +1958,7 @@
         </is>
       </c>
       <c r="W9" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
@@ -1971,41 +1973,39 @@
         <v>1</v>
       </c>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
       <c r="AF9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH9" s="2" t="inlineStr"/>
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="n">
-        <v>-32.79</v>
+        <v>-31.4</v>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>-27.86</v>
+        <v>-27.78</v>
       </c>
       <c r="AL9" s="2" t="n"/>
       <c r="AM9" s="2" t="n">
-        <v>6.98</v>
+        <v>7.89</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="AQ9" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" s="2" t="inlineStr"/>
       <c r="AT9" s="2" t="inlineStr"/>
@@ -2015,40 +2015,40 @@
         </is>
       </c>
       <c r="AV9" s="2" t="n">
-        <v>6169.8</v>
+        <v>6220.2</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>6129.8</v>
+        <v>6153.7</v>
       </c>
       <c r="AX9" s="2" t="n">
-        <v>6289.9</v>
+        <v>6278.45</v>
       </c>
       <c r="AY9" s="2" t="n">
-        <v>6402.1</v>
+        <v>6380</v>
       </c>
       <c r="AZ9" s="2" t="n">
-        <v>6614.64</v>
+        <v>6606.32</v>
       </c>
       <c r="BA9" s="2" t="n">
-        <v>7016.501</v>
+        <v>6999.029</v>
       </c>
       <c r="BB9" s="2" t="n">
-        <v>7827.305</v>
+        <v>7818.778</v>
       </c>
       <c r="BC9" s="2" t="n">
-        <v>-0.5248</v>
+        <v>0.1789</v>
       </c>
       <c r="BD9" s="2" t="n">
-        <v>-0.5776</v>
+        <v>-0.4634</v>
       </c>
       <c r="BE9" s="2" t="n">
-        <v>-0.6321</v>
+        <v>-0.5694</v>
       </c>
       <c r="BF9" s="2" t="n">
-        <v>-0.6075</v>
+        <v>-0.6017</v>
       </c>
       <c r="BG9" s="2" t="n">
-        <v>-0.3279</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="10">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2740.5</v>
+        <v>2736</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>98.16</v>
@@ -2086,14 +2086,14 @@
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>0101101100</t>
+          <t>0100101100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4+→4·4d ← 4→4+·5d ← 4+→4·14d</t>
+          <t>4+→4·5d ← 4→4+·6d ← 4+→4·15d</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
@@ -2127,83 +2127,75 @@
       <c r="AE10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AF10" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr"/>
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="n">
-        <v>-30.66</v>
+        <v>-29.47</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>-18.74</v>
+        <v>-17.61</v>
       </c>
       <c r="AL10" s="2" t="n"/>
       <c r="AM10" s="2" t="n">
-        <v>7.72</v>
+        <v>9.49</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.33</v>
+        <v>1.49</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>57.9</v>
+        <v>58.1</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
       <c r="AS10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT10" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="AT10" s="2" t="inlineStr"/>
       <c r="AU10" s="2" t="inlineStr">
         <is>
           <t>柱≥0</t>
         </is>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>2650.3</v>
+        <v>2672.9</v>
       </c>
       <c r="AW10" s="2" t="n">
-        <v>2678.45</v>
+        <v>2681.15</v>
       </c>
       <c r="AX10" s="2" t="n">
-        <v>2747.68</v>
+        <v>2745.16</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>2745.535</v>
+        <v>2743.397</v>
       </c>
       <c r="AZ10" s="2" t="n">
-        <v>2732.189</v>
+        <v>2736.417</v>
       </c>
       <c r="BA10" s="2" t="n">
-        <v>2666.545</v>
+        <v>2667.878</v>
       </c>
       <c r="BB10" s="2" t="n">
-        <v>2774.802</v>
+        <v>2772.29</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>-1.381</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>-0.2757</v>
+        <v>-0.2487</v>
       </c>
       <c r="BE10" s="2" t="n">
-        <v>-0.2105</v>
+        <v>-0.0737</v>
       </c>
       <c r="BF10" s="2" t="n">
-        <v>0.0747</v>
+        <v>0.0822</v>
       </c>
       <c r="BG10" s="2" t="n">
-        <v>-0.3066</v>
+        <v>-0.2947</v>
       </c>
     </row>
     <row r="11">
@@ -2218,7 +2210,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12320</v>
+        <v>12230</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6.32</v>
@@ -2239,19 +2231,19 @@
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>0111111001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0011111001</t>
+          <t>0111111001</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -2260,7 +2252,7 @@
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
@@ -2274,15 +2266,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2B→2C·13d ← 2C→2B·14d ← 2B→2C·15d</t>
+          <t>2B→2C·14d ← 2C→2B·15d ← 2B→2C·16d</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr"/>
-      <c r="AE11" s="2" t="n">
-        <v>1</v>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
       </c>
       <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="inlineStr">
@@ -2291,25 +2285,29 @@
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
+      </c>
       <c r="AJ11" s="2" t="n">
-        <v>33.18</v>
+        <v>34.64</v>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>7.56</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AL11" s="2" t="n"/>
       <c r="AM11" s="2" t="n">
-        <v>11.03</v>
+        <v>11.68</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>6.83</v>
+        <v>5.92</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>48.7</v>
+        <v>51.8</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2321,40 +2319,40 @@
         </is>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>11837</v>
+        <v>11950</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>11654</v>
+        <v>11745</v>
       </c>
       <c r="AX11" s="2" t="n">
-        <v>11447.75</v>
+        <v>11488</v>
       </c>
       <c r="AY11" s="2" t="n">
-        <v>11569.167</v>
+        <v>11563.833</v>
       </c>
       <c r="AZ11" s="2" t="n">
-        <v>11811.5</v>
+        <v>11826.1</v>
       </c>
       <c r="BA11" s="2" t="n">
-        <v>11374.378</v>
+        <v>11381.247</v>
       </c>
       <c r="BB11" s="2" t="n">
-        <v>10759.045</v>
+        <v>10774.718</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>1.1376</v>
+        <v>1.3165</v>
       </c>
       <c r="BD11" s="2" t="n">
-        <v>0.3763</v>
+        <v>0.5917</v>
       </c>
       <c r="BE11" s="2" t="n">
-        <v>0.2268</v>
+        <v>0.2612</v>
       </c>
       <c r="BF11" s="2" t="n">
-        <v>0.1407</v>
+        <v>0.1477</v>
       </c>
       <c r="BG11" s="2" t="n">
-        <v>0.3318</v>
+        <v>0.3464</v>
       </c>
     </row>
     <row r="12">
@@ -2369,7 +2367,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3432</v>
+        <v>3378</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>97.72</v>
@@ -2390,19 +2388,19 @@
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>0011101001</t>
+          <t>0011101000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>0111111000</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -2411,7 +2409,7 @@
         </is>
       </c>
       <c r="W12" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
@@ -2425,7 +2423,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3→2C·15d ← 4→3·18d</t>
+          <t>3→2C·16d ← 4→3·19d</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
@@ -2435,36 +2433,38 @@
       <c r="AE12" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>-6.75</v>
+        <v>-6.88</v>
       </c>
       <c r="AL12" s="2" t="n"/>
       <c r="AM12" s="2" t="n">
-        <v>6.28</v>
+        <v>5.69</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>6.68</v>
+        <v>7.15</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS12" s="2" t="inlineStr"/>
       <c r="AT12" s="2" t="inlineStr"/>
@@ -2474,76 +2474,68 @@
         </is>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>3421.4</v>
+        <v>3411.6</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>3409.4</v>
+        <v>3415.8</v>
       </c>
       <c r="AX12" s="2" t="n">
-        <v>3363.04</v>
+        <v>3372.246</v>
       </c>
       <c r="AY12" s="2" t="n">
-        <v>3322.909</v>
+        <v>3321.531</v>
       </c>
       <c r="AZ12" s="2" t="n">
-        <v>3323.989</v>
+        <v>3316.833</v>
       </c>
       <c r="BA12" s="2" t="n">
-        <v>3394.777</v>
+        <v>3397.103</v>
       </c>
       <c r="BB12" s="2" t="n">
-        <v>3234.708</v>
+        <v>3235.076</v>
       </c>
       <c r="BC12" s="2" t="n">
-        <v>0.4912</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="BD12" s="2" t="n">
-        <v>0.9238</v>
+        <v>0.8562</v>
       </c>
       <c r="BE12" s="2" t="n">
-        <v>-0.5372</v>
+        <v>-0.5373</v>
       </c>
       <c r="BF12" s="2" t="n">
-        <v>0.2331</v>
+        <v>0.2146</v>
       </c>
       <c r="BG12" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>5801 JP</t>
+          <t>5020 JP</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Furukawa Electric</t>
+          <t>ENEOS Holdings, Inc.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3366</v>
+        <v>1396</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>91.12</v>
+        <v>47.18</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>顶背离</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="n">
         <v>1</v>
       </c>
@@ -2551,19 +2543,19 @@
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>0110000100</t>
+          <t>0111111101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0010000000</t>
+          <t>0101111100</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -2572,7 +2564,7 @@
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
@@ -2583,113 +2575,117 @@
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr"/>
       <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="n">
-        <v>-1</v>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
       </c>
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr"/>
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="n">
-        <v>108.01</v>
+        <v>33</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>8.15</v>
+        <v>2.43</v>
       </c>
       <c r="AL13" s="2" t="n"/>
       <c r="AM13" s="2" t="n">
-        <v>-22.07</v>
+        <v>8.81</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>-27.36</v>
+        <v>-1.33</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>43.9</v>
+        <v>79.2</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT13" s="2" t="inlineStr"/>
       <c r="AU13" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>柱≥0</t>
         </is>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>3723.6</v>
+        <v>1392.7</v>
       </c>
       <c r="AW13" s="2" t="n">
-        <v>4057.9</v>
+        <v>1379.8</v>
       </c>
       <c r="AX13" s="2" t="n">
-        <v>3938.383</v>
+        <v>1390.852</v>
       </c>
       <c r="AY13" s="2" t="n">
-        <v>3906.921</v>
+        <v>1389.632</v>
       </c>
       <c r="AZ13" s="2" t="n">
-        <v>3908.632</v>
+        <v>1352.304</v>
       </c>
       <c r="BA13" s="2" t="n">
-        <v>4102.375</v>
+        <v>1300.028</v>
       </c>
       <c r="BB13" s="2" t="n">
-        <v>3428.855</v>
+        <v>1302.429</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>-0.7874</v>
+        <v>0.309</v>
       </c>
       <c r="BD13" s="2" t="n">
-        <v>-0.6325</v>
+        <v>-0.306</v>
       </c>
       <c r="BE13" s="2" t="n">
-        <v>0.9984</v>
+        <v>0.3946</v>
       </c>
       <c r="BF13" s="2" t="n">
-        <v>-0.9064</v>
+        <v>0.1619</v>
       </c>
       <c r="BG13" s="2" t="n">
-        <v>1.0801</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>5802 JP</t>
+          <t>5801 JP</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo Electric</t>
+          <t>Furukawa Electric</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2121</v>
+        <v>3303</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>80.95</v>
+        <v>91.12</v>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>顶背离</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
-        <v>-9</v>
+        <v>13</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -2698,40 +2694,36 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S14" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0110000000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0100000100</t>
+          <t>0010000000</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>2A→4·4d</t>
-        </is>
-      </c>
+      <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr"/>
@@ -2744,88 +2736,90 @@
       <c r="AH14" s="2" t="inlineStr"/>
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="n">
-        <v>36.08</v>
+        <v>101.8</v>
       </c>
       <c r="AK14" s="2" t="n">
-        <v>-10.1</v>
+        <v>7.19</v>
       </c>
       <c r="AL14" s="2" t="n"/>
       <c r="AM14" s="2" t="n">
-        <v>-6.83</v>
+        <v>-18.81</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>1.02</v>
+        <v>-23.45</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>20</v>
+        <v>42.2</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ14" s="2" t="inlineStr"/>
-      <c r="AR14" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="AR14" s="2" t="inlineStr"/>
       <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU14" s="2" t="inlineStr">
         <is>
-          <t>背离</t>
+          <t>无背离</t>
         </is>
       </c>
       <c r="AV14" s="2" t="n">
-        <v>2239.9</v>
+        <v>3565</v>
       </c>
       <c r="AW14" s="2" t="n">
-        <v>2353.3</v>
+        <v>3945.3</v>
       </c>
       <c r="AX14" s="2" t="n">
-        <v>2252.59</v>
+        <v>3918.123</v>
       </c>
       <c r="AY14" s="2" t="n">
-        <v>2204.24</v>
+        <v>3888.794</v>
       </c>
       <c r="AZ14" s="2" t="n">
-        <v>2209.874</v>
+        <v>3910.878</v>
       </c>
       <c r="BA14" s="2" t="n">
-        <v>2483.738</v>
+        <v>4081.911</v>
       </c>
       <c r="BB14" s="2" t="n">
-        <v>2341.683</v>
+        <v>3440.884</v>
       </c>
       <c r="BC14" s="2" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-2.5458</v>
       </c>
       <c r="BD14" s="2" t="n">
-        <v>0.9794</v>
+        <v>-1.1776</v>
       </c>
       <c r="BE14" s="2" t="n">
-        <v>0.1822</v>
+        <v>0.8007</v>
       </c>
       <c r="BF14" s="2" t="n">
-        <v>-0.4764</v>
+        <v>-0.998</v>
       </c>
       <c r="BG14" s="2" t="n">
-        <v>0.3608</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>6146 JP</t>
+          <t>5802 JP</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DISCO</t>
+          <t>Sumitomo Electric</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>53850</v>
+        <v>2068</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>67.83</v>
+        <v>80.95</v>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
@@ -2835,9 +2829,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="n">
         <v>0</v>
       </c>
@@ -2848,16 +2840,16 @@
         <v>2</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>0000000110</t>
+          <t>0100000100</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2866,7 +2858,7 @@
         </is>
       </c>
       <c r="W15" s="2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
@@ -2874,7 +2866,11 @@
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2A→4·5d</t>
+        </is>
+      </c>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr"/>
@@ -2887,27 +2883,27 @@
       <c r="AH15" s="2" t="inlineStr"/>
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="n">
-        <v>19.67</v>
+        <v>34.37</v>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>-22.1</v>
+        <v>-11.33</v>
       </c>
       <c r="AL15" s="2" t="n"/>
       <c r="AM15" s="2" t="n">
-        <v>-5.5</v>
+        <v>-6.44</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>2.25</v>
+        <v>0.42</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AS15" s="2" t="inlineStr"/>
       <c r="AT15" s="2" t="inlineStr">
@@ -2917,62 +2913,62 @@
       </c>
       <c r="AU15" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>背离</t>
         </is>
       </c>
       <c r="AV15" s="2" t="n">
-        <v>57034</v>
+        <v>2181.4</v>
       </c>
       <c r="AW15" s="2" t="n">
-        <v>59721</v>
+        <v>2314.9</v>
       </c>
       <c r="AX15" s="2" t="n">
-        <v>56898.764</v>
+        <v>2257.102</v>
       </c>
       <c r="AY15" s="2" t="n">
-        <v>55938.398</v>
+        <v>2200.176</v>
       </c>
       <c r="AZ15" s="2" t="n">
-        <v>58127.58</v>
+        <v>2210.34</v>
       </c>
       <c r="BA15" s="2" t="n">
-        <v>64904.773</v>
+        <v>2475.123</v>
       </c>
       <c r="BB15" s="2" t="n">
-        <v>65384.186</v>
+        <v>2344.572</v>
       </c>
       <c r="BC15" s="2" t="n">
-        <v>0.2029</v>
+        <v>-1.2849</v>
       </c>
       <c r="BD15" s="2" t="n">
-        <v>1.0029</v>
+        <v>0.719</v>
       </c>
       <c r="BE15" s="2" t="n">
-        <v>0.1224</v>
+        <v>0.1809</v>
       </c>
       <c r="BF15" s="2" t="n">
-        <v>-0.2458</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="BG15" s="2" t="n">
-        <v>0.1967</v>
+        <v>0.3437</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>6361 JP</t>
+          <t>6146 JP</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ebara</t>
+          <t>DISCO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4200</v>
+        <v>53020</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6.28</v>
+        <v>67.83</v>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
@@ -3011,7 +3007,7 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
@@ -3023,9 +3019,7 @@
       <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr"/>
-      <c r="AD16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD16" s="2" t="inlineStr"/>
       <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="n">
         <v>-1</v>
@@ -3034,28 +3028,26 @@
       <c r="AH16" s="2" t="inlineStr"/>
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="n">
-        <v>17.94</v>
+        <v>18.32</v>
       </c>
       <c r="AK16" s="2" t="n">
         <v>-22.24</v>
       </c>
       <c r="AL16" s="2" t="n"/>
       <c r="AM16" s="2" t="n">
-        <v>-4.81</v>
+        <v>-6.14</v>
       </c>
       <c r="AN16" s="2" t="n">
-        <v>-2.97</v>
+        <v>2.13</v>
       </c>
       <c r="AO16" s="2" t="n">
-        <v>7.9</v>
+        <v>14.4</v>
       </c>
       <c r="AP16" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AQ16" s="2" t="inlineStr"/>
-      <c r="AR16" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="AR16" s="2" t="inlineStr"/>
       <c r="AS16" s="2" t="inlineStr"/>
       <c r="AT16" s="2" t="inlineStr">
         <is>
@@ -3068,58 +3060,58 @@
         </is>
       </c>
       <c r="AV16" s="2" t="n">
-        <v>4473.8</v>
+        <v>55346</v>
       </c>
       <c r="AW16" s="2" t="n">
-        <v>4635.2</v>
+        <v>58994</v>
       </c>
       <c r="AX16" s="2" t="n">
-        <v>4551.2</v>
+        <v>56987.842</v>
       </c>
       <c r="AY16" s="2" t="n">
-        <v>4499.033</v>
+        <v>55825.328</v>
       </c>
       <c r="AZ16" s="2" t="n">
-        <v>4834.8</v>
+        <v>57981.385</v>
       </c>
       <c r="BA16" s="2" t="n">
-        <v>5315.22</v>
+        <v>64778.443</v>
       </c>
       <c r="BB16" s="2" t="n">
-        <v>5101.495</v>
+        <v>65430.325</v>
       </c>
       <c r="BC16" s="2" t="n">
-        <v>-0.7322</v>
+        <v>-1.067</v>
       </c>
       <c r="BD16" s="2" t="n">
-        <v>0.4471</v>
+        <v>0.7204</v>
       </c>
       <c r="BE16" s="2" t="n">
-        <v>-0.8058</v>
+        <v>0.0092</v>
       </c>
       <c r="BF16" s="2" t="n">
-        <v>-0.3401</v>
+        <v>-0.3209</v>
       </c>
       <c r="BG16" s="2" t="n">
-        <v>0.1794</v>
+        <v>0.1832</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>6503 JP</t>
+          <t>6361 JP</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Mitsubishi Electric Corp.</t>
+          <t>Ebara</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5005</v>
+        <v>4126</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5.45</v>
+        <v>6.28</v>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
@@ -3131,7 +3123,7 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -3158,7 +3150,7 @@
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
@@ -3166,15 +3158,13 @@
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>2A→4·16d</t>
-        </is>
-      </c>
+      <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr"/>
-      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AE17" s="2" t="inlineStr"/>
       <c r="AF17" s="2" t="n">
         <v>-1</v>
@@ -3183,88 +3173,90 @@
       <c r="AH17" s="2" t="inlineStr"/>
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="n">
-        <v>10.44</v>
+        <v>16.92</v>
       </c>
       <c r="AK17" s="2" t="n">
-        <v>-14.31</v>
+        <v>-22.59</v>
       </c>
       <c r="AL17" s="2" t="n"/>
       <c r="AM17" s="2" t="n">
-        <v>3.99</v>
+        <v>-6.34</v>
       </c>
       <c r="AN17" s="2" t="n">
         <v>-3.6</v>
       </c>
       <c r="AO17" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AP17" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AQ17" s="2" t="inlineStr"/>
-      <c r="AR17" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AR17" s="2" t="inlineStr"/>
       <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU17" s="2" t="inlineStr">
         <is>
           <t>无背离</t>
         </is>
       </c>
       <c r="AV17" s="2" t="n">
-        <v>5084.8</v>
+        <v>4342</v>
       </c>
       <c r="AW17" s="2" t="n">
-        <v>5171.8</v>
+        <v>4577.7</v>
       </c>
       <c r="AX17" s="2" t="n">
-        <v>5171.662</v>
+        <v>4544.6</v>
       </c>
       <c r="AY17" s="2" t="n">
-        <v>5178.358</v>
+        <v>4484.233</v>
       </c>
       <c r="AZ17" s="2" t="n">
-        <v>5399.545</v>
+        <v>4806.22</v>
       </c>
       <c r="BA17" s="2" t="n">
-        <v>5622.744</v>
+        <v>5302.248</v>
       </c>
       <c r="BB17" s="2" t="n">
-        <v>5517.657</v>
+        <v>5104.539</v>
       </c>
       <c r="BC17" s="2" t="n">
-        <v>-0.6119</v>
+        <v>-1.737</v>
       </c>
       <c r="BD17" s="2" t="n">
-        <v>0.0466</v>
+        <v>0.1469</v>
       </c>
       <c r="BE17" s="2" t="n">
-        <v>-0.346</v>
+        <v>-0.9304</v>
       </c>
       <c r="BF17" s="2" t="n">
-        <v>-0.4585</v>
+        <v>-0.3969</v>
       </c>
       <c r="BG17" s="2" t="n">
-        <v>0.1044</v>
+        <v>0.1692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>6504 JP</t>
+          <t>6503 JP</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fuji Electric Co., Ltd.</t>
+          <t>Mitsubishi Electric Corp.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>14185</v>
+        <v>4935</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>86.78</v>
+        <v>5.45</v>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
@@ -3282,42 +3274,38 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>0111111010</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0011111010</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>周MACD死叉</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2A→2C·8d ← 2C→2A·11d</t>
+          <t>2A→4·17d</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
@@ -3329,91 +3317,91 @@
         <v>-1</v>
       </c>
       <c r="AG18" s="2" t="inlineStr"/>
-      <c r="AH18" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AH18" s="2" t="inlineStr"/>
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="n">
-        <v>34.05</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AK18" s="2" t="n">
-        <v>2.7</v>
+        <v>-14.42</v>
       </c>
       <c r="AL18" s="2" t="n"/>
       <c r="AM18" s="2" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>-3.35</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AQ18" s="2" t="inlineStr"/>
-      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="AS18" s="2" t="inlineStr"/>
       <c r="AT18" s="2" t="inlineStr"/>
       <c r="AU18" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>背离</t>
         </is>
       </c>
       <c r="AV18" s="2" t="n">
-        <v>14553</v>
+        <v>5043.2</v>
       </c>
       <c r="AW18" s="2" t="n">
-        <v>14786.5</v>
+        <v>5138.9</v>
       </c>
       <c r="AX18" s="2" t="n">
-        <v>14062.361</v>
+        <v>5164.879</v>
       </c>
       <c r="AY18" s="2" t="n">
-        <v>13675.732</v>
+        <v>5159.884</v>
       </c>
       <c r="AZ18" s="2" t="n">
-        <v>13871.157</v>
+        <v>5388.162</v>
       </c>
       <c r="BA18" s="2" t="n">
-        <v>13867.731</v>
+        <v>5609.447</v>
       </c>
       <c r="BB18" s="2" t="n">
-        <v>12874.797</v>
+        <v>5519.924</v>
       </c>
       <c r="BC18" s="2" t="n">
-        <v>1.2582</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="BD18" s="2" t="n">
-        <v>1.7664</v>
+        <v>-0.075</v>
       </c>
       <c r="BE18" s="2" t="n">
-        <v>0.6712</v>
+        <v>-0.3611</v>
       </c>
       <c r="BF18" s="2" t="n">
-        <v>-0.0213</v>
+        <v>-0.4681</v>
       </c>
       <c r="BG18" s="2" t="n">
-        <v>0.3405</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>6506 JP</t>
+          <t>6504 JP</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Yaskawa</t>
+          <t>Fuji Electric Co., Ltd.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4378</v>
+        <v>14040</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>13.4</v>
+        <v>86.78</v>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
@@ -3423,9 +3411,7 @@
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
@@ -3433,42 +3419,48 @@
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>0000000010</t>
+          <t>0111111000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0011111000</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" s="2" t="n">
-        <v>30</v>
+        <v>295</v>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr"/>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>周MACD死叉</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2A→2C·9d ← 2C→2A·12d</t>
+        </is>
+      </c>
       <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr"/>
-      <c r="AD19" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD19" s="2" t="inlineStr"/>
       <c r="AE19" s="2" t="inlineStr"/>
       <c r="AF19" s="2" t="n">
         <v>-1</v>
@@ -3477,28 +3469,26 @@
       <c r="AH19" s="2" t="inlineStr"/>
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="n">
-        <v>-3.32</v>
+        <v>32.45</v>
       </c>
       <c r="AK19" s="2" t="n">
-        <v>-22.58</v>
+        <v>2.94</v>
       </c>
       <c r="AL19" s="2" t="n"/>
       <c r="AM19" s="2" t="n">
-        <v>-2.72</v>
+        <v>0.04</v>
       </c>
       <c r="AN19" s="2" t="n">
-        <v>-0.88</v>
+        <v>10.84</v>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>4.1</v>
+        <v>77.5</v>
       </c>
       <c r="AP19" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ19" s="2" t="inlineStr"/>
-      <c r="AR19" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="AR19" s="2" t="inlineStr"/>
       <c r="AS19" s="2" t="inlineStr"/>
       <c r="AT19" s="2" t="inlineStr"/>
       <c r="AU19" s="2" t="inlineStr">
@@ -3507,58 +3497,58 @@
         </is>
       </c>
       <c r="AV19" s="2" t="n">
-        <v>4597.4</v>
+        <v>14358</v>
       </c>
       <c r="AW19" s="2" t="n">
-        <v>4739.5</v>
+        <v>14725</v>
       </c>
       <c r="AX19" s="2" t="n">
-        <v>4605.65</v>
+        <v>14145.481</v>
       </c>
       <c r="AY19" s="2" t="n">
-        <v>4567</v>
+        <v>13691.623</v>
       </c>
       <c r="AZ19" s="2" t="n">
-        <v>4778.764</v>
+        <v>13871.563</v>
       </c>
       <c r="BA19" s="2" t="n">
-        <v>5593.246</v>
+        <v>13846.602</v>
       </c>
       <c r="BB19" s="2" t="n">
-        <v>5324.643</v>
+        <v>12890.21</v>
       </c>
       <c r="BC19" s="2" t="n">
-        <v>0.1254</v>
+        <v>0.4891</v>
       </c>
       <c r="BD19" s="2" t="n">
-        <v>0.5684</v>
+        <v>1.62</v>
       </c>
       <c r="BE19" s="2" t="n">
-        <v>-0.1927</v>
+        <v>0.5093</v>
       </c>
       <c r="BF19" s="2" t="n">
-        <v>-0.8732</v>
+        <v>-0.1004</v>
       </c>
       <c r="BG19" s="2" t="n">
-        <v>-0.0332</v>
+        <v>0.3245</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>6594 JP</t>
+          <t>6506 JP</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Nidec Corporation</t>
+          <t>Yaskawa</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1800</v>
+        <v>4276</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-5.77</v>
+        <v>13.4</v>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
@@ -3567,25 +3557,23 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>-13</v>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>0000001000</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3599,7 +3587,7 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
@@ -3607,113 +3595,101 @@
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>3-→4·5d ← 2C→3-·14d</t>
-        </is>
-      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AE20" s="2" t="inlineStr"/>
-      <c r="AF20" s="2" t="inlineStr"/>
-      <c r="AG20" s="2" t="n">
+      <c r="AF20" s="2" t="n">
         <v>-1</v>
       </c>
+      <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr"/>
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="n">
-        <v>-5.81</v>
+        <v>-3.29</v>
       </c>
       <c r="AK20" s="2" t="n">
-        <v>-32.85</v>
+        <v>-23.42</v>
       </c>
       <c r="AL20" s="2" t="n"/>
       <c r="AM20" s="2" t="n">
-        <v>-7.32</v>
+        <v>-3.46</v>
       </c>
       <c r="AN20" s="2" t="n">
-        <v>-29.97</v>
+        <v>-1.67</v>
       </c>
       <c r="AO20" s="2" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="AP20" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
       <c r="AS20" s="2" t="inlineStr"/>
-      <c r="AT20" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT20" s="2" t="inlineStr"/>
       <c r="AU20" s="2" t="inlineStr">
         <is>
           <t>无背离</t>
         </is>
       </c>
       <c r="AV20" s="2" t="n">
-        <v>1889.2</v>
+        <v>4496</v>
       </c>
       <c r="AW20" s="2" t="n">
-        <v>2021.3</v>
+        <v>4686.5</v>
       </c>
       <c r="AX20" s="2" t="n">
-        <v>2289.4</v>
+        <v>4604.65</v>
       </c>
       <c r="AY20" s="2" t="n">
-        <v>2404.267</v>
+        <v>4552.867</v>
       </c>
       <c r="AZ20" s="2" t="n">
-        <v>2518.3</v>
+        <v>4766.311</v>
       </c>
       <c r="BA20" s="2" t="n">
-        <v>2594.33</v>
+        <v>5566.006</v>
       </c>
       <c r="BB20" s="2" t="n">
-        <v>2440.355</v>
+        <v>5324.343</v>
       </c>
       <c r="BC20" s="2" t="n">
-        <v>-5.599</v>
+        <v>-0.7857</v>
       </c>
       <c r="BD20" s="2" t="n">
-        <v>-4.1296</v>
+        <v>0.3691</v>
       </c>
       <c r="BE20" s="2" t="n">
-        <v>-1.3331</v>
+        <v>-0.2337</v>
       </c>
       <c r="BF20" s="2" t="n">
-        <v>-0.6975</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="BG20" s="2" t="n">
-        <v>-0.0581</v>
+        <v>-0.0329</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>6762 JP</t>
+          <t>6594 JP</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TDK</t>
+          <t>Nidec Corporation</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2940.5</v>
+        <v>1774</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>80.2</v>
+        <v>-5.77</v>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
@@ -3722,87 +3698,89 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="L21" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>0010001000</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0010000000</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W21" s="2" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2C→2A·6d</t>
+          <t>3-→4·6d ← 2C→3-·15d</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="n">
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD21" s="2" t="inlineStr"/>
       <c r="AE21" s="2" t="inlineStr"/>
-      <c r="AF21" s="2" t="n">
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr"/>
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="n">
-        <v>40.39</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AK21" s="2" t="n">
-        <v>-1.14</v>
+        <v>-32.78</v>
       </c>
       <c r="AL21" s="2" t="n"/>
       <c r="AM21" s="2" t="n">
-        <v>-7.79</v>
+        <v>-2.93</v>
       </c>
       <c r="AN21" s="2" t="n">
-        <v>1.97</v>
+        <v>-29.74</v>
       </c>
       <c r="AO21" s="2" t="n">
-        <v>29.8</v>
+        <v>4.5</v>
       </c>
       <c r="AP21" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AQ21" s="2" t="inlineStr"/>
-      <c r="AR21" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="AR21" s="2" t="inlineStr"/>
       <c r="AS21" s="2" t="inlineStr"/>
       <c r="AT21" s="2" t="inlineStr">
         <is>
@@ -3815,58 +3793,58 @@
         </is>
       </c>
       <c r="AV21" s="2" t="n">
-        <v>3079.4</v>
+        <v>1842</v>
       </c>
       <c r="AW21" s="2" t="n">
-        <v>3255.3</v>
+        <v>1987</v>
       </c>
       <c r="AX21" s="2" t="n">
-        <v>3087.999</v>
+        <v>2246</v>
       </c>
       <c r="AY21" s="2" t="n">
-        <v>3010.397</v>
+        <v>2377.7</v>
       </c>
       <c r="AZ21" s="2" t="n">
-        <v>3032.463</v>
+        <v>2500.04</v>
       </c>
       <c r="BA21" s="2" t="n">
-        <v>3271.838</v>
+        <v>2584.92</v>
       </c>
       <c r="BB21" s="2" t="n">
-        <v>2772.553</v>
+        <v>2439.27</v>
       </c>
       <c r="BC21" s="2" t="n">
-        <v>0.6536999999999999</v>
+        <v>-4.6515</v>
       </c>
       <c r="BD21" s="2" t="n">
-        <v>1.2318</v>
+        <v>-4.3551</v>
       </c>
       <c r="BE21" s="2" t="n">
-        <v>0.3418</v>
+        <v>-1.4867</v>
       </c>
       <c r="BF21" s="2" t="n">
-        <v>0.073</v>
+        <v>-0.7739</v>
       </c>
       <c r="BG21" s="2" t="n">
-        <v>0.4039</v>
+        <v>-0.0828</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>6857 JP</t>
+          <t>6762 JP</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Advantest</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>34530</v>
+        <v>2873</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>98.61</v>
+        <v>80.2</v>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
@@ -3876,9 +3854,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
@@ -3886,19 +3862,19 @@
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>0110111011</t>
+          <t>0010001000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0110111010</t>
+          <t>0010000000</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3907,60 +3883,56 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t>周MACD将死叉</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr"/>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2C→2A·7d</t>
+        </is>
+      </c>
       <c r="AA22" s="2" t="inlineStr"/>
       <c r="AB22" s="2" t="inlineStr"/>
-      <c r="AC22" s="2" t="inlineStr"/>
-      <c r="AD22" s="2" t="n">
+      <c r="AC22" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AD22" s="2" t="inlineStr"/>
       <c r="AE22" s="2" t="inlineStr"/>
       <c r="AF22" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AG22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH22" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="n">
-        <v>85.56</v>
+        <v>37.11</v>
       </c>
       <c r="AK22" s="2" t="n">
-        <v>18.75</v>
+        <v>-2.16</v>
       </c>
       <c r="AL22" s="2" t="n"/>
       <c r="AM22" s="2" t="n">
-        <v>-15.9</v>
+        <v>-6.11</v>
       </c>
       <c r="AN22" s="2" t="n">
-        <v>3.97</v>
+        <v>0.35</v>
       </c>
       <c r="AO22" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>28.5</v>
       </c>
       <c r="AP22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AQ22" s="2" t="inlineStr"/>
-      <c r="AR22" s="2" t="inlineStr"/>
-      <c r="AS22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS22" s="2" t="inlineStr"/>
       <c r="AT22" s="2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3968,62 +3940,62 @@
       </c>
       <c r="AU22" s="2" t="inlineStr">
         <is>
-          <t>柱≥0</t>
+          <t>无背离</t>
         </is>
       </c>
       <c r="AV22" s="2" t="n">
-        <v>38252</v>
+        <v>3000.4</v>
       </c>
       <c r="AW22" s="2" t="n">
-        <v>39426</v>
+        <v>3222.8</v>
       </c>
       <c r="AX22" s="2" t="n">
-        <v>36199</v>
+        <v>3090.933</v>
       </c>
       <c r="AY22" s="2" t="n">
-        <v>35103.667</v>
+        <v>3004.225</v>
       </c>
       <c r="AZ22" s="2" t="n">
-        <v>34882.8</v>
+        <v>3028.501</v>
       </c>
       <c r="BA22" s="2" t="n">
-        <v>31885.3</v>
+        <v>3267.096</v>
       </c>
       <c r="BB22" s="2" t="n">
-        <v>28261.361</v>
+        <v>2776.005</v>
       </c>
       <c r="BC22" s="2" t="n">
-        <v>2.4515</v>
+        <v>-0.3701</v>
       </c>
       <c r="BD22" s="2" t="n">
-        <v>2.0842</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="BE22" s="2" t="n">
-        <v>1.5896</v>
+        <v>0.1777</v>
       </c>
       <c r="BF22" s="2" t="n">
-        <v>1.0157</v>
+        <v>-0.0494</v>
       </c>
       <c r="BG22" s="2" t="n">
-        <v>0.8556</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>6861 JP</t>
+          <t>6857 JP</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Keyence</t>
+          <t>Advantest</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>80760</v>
+        <v>33640</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>42.39</v>
+        <v>98.61</v>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
@@ -4041,19 +4013,19 @@
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>0011111001</t>
+          <t>0110111000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0011111000</t>
+          <t>0010111000</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -4062,7 +4034,7 @@
         </is>
       </c>
       <c r="W23" s="2" t="n">
-        <v>125</v>
+        <v>302</v>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
@@ -4071,90 +4043,94 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>顶背离·周MACD死叉</t>
+          <t>周MACD将死叉</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="inlineStr"/>
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr"/>
-      <c r="AD23" s="2" t="inlineStr"/>
-      <c r="AE23" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
-      <c r="AF23" s="2" t="inlineStr"/>
-      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="AH23" s="2" t="inlineStr"/>
-      <c r="AI23" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
+      <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="n">
-        <v>46.38</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AK23" s="2" t="n">
-        <v>8.41</v>
+        <v>16.97</v>
       </c>
       <c r="AL23" s="2" t="n"/>
       <c r="AM23" s="2" t="n">
-        <v>6.83</v>
+        <v>-19.6</v>
       </c>
       <c r="AN23" s="2" t="n">
-        <v>4.35</v>
+        <v>5.8</v>
       </c>
       <c r="AO23" s="2" t="n">
-        <v>54.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AP23" s="2" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
-      <c r="AS23" s="2" t="inlineStr"/>
-      <c r="AT23" s="2" t="inlineStr"/>
+      <c r="AS23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT23" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU23" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>柱≥0</t>
         </is>
       </c>
       <c r="AV23" s="2" t="n">
-        <v>80074</v>
+        <v>36658</v>
       </c>
       <c r="AW23" s="2" t="n">
-        <v>80537</v>
+        <v>38927</v>
       </c>
       <c r="AX23" s="2" t="n">
-        <v>79279.54300000001</v>
+        <v>36373</v>
       </c>
       <c r="AY23" s="2" t="n">
-        <v>78638.929</v>
+        <v>35112.333</v>
       </c>
       <c r="AZ23" s="2" t="n">
-        <v>80513.357</v>
+        <v>34927</v>
       </c>
       <c r="BA23" s="2" t="n">
-        <v>78414.72199999999</v>
+        <v>31953.25</v>
       </c>
       <c r="BB23" s="2" t="n">
-        <v>69991.41099999999</v>
+        <v>28335.664</v>
       </c>
       <c r="BC23" s="2" t="n">
-        <v>0.0718</v>
+        <v>0.6972</v>
       </c>
       <c r="BD23" s="2" t="n">
-        <v>0.6728</v>
+        <v>1.7412</v>
       </c>
       <c r="BE23" s="2" t="n">
-        <v>0.2456</v>
+        <v>1.2413</v>
       </c>
       <c r="BF23" s="2" t="n">
-        <v>0.1521</v>
+        <v>0.8709</v>
       </c>
       <c r="BG23" s="2" t="n">
-        <v>0.4638</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="24">
@@ -4169,7 +4145,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>41200</v>
+        <v>39310</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>111</v>
@@ -4184,25 +4160,25 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>0111100110</t>
+          <t>0011000000</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0111100110</t>
+          <t>0111000000</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -4211,7 +4187,7 @@
         </is>
       </c>
       <c r="W24" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
@@ -4221,7 +4197,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1→2A·17d</t>
+          <t>1→2A·18d</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
@@ -4235,75 +4211,77 @@
         <v>-1</v>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH24" s="2" t="n">
         <v>-1</v>
       </c>
+      <c r="AH24" s="2" t="inlineStr"/>
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="n">
-        <v>47.89</v>
+        <v>43.47</v>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>3.51</v>
+        <v>-0.09</v>
       </c>
       <c r="AL24" s="2" t="n"/>
       <c r="AM24" s="2" t="n">
-        <v>-8.06</v>
+        <v>-16.16</v>
       </c>
       <c r="AN24" s="2" t="n">
-        <v>11.58</v>
+        <v>5.14</v>
       </c>
       <c r="AO24" s="2" t="n">
-        <v>47.2</v>
+        <v>46.1</v>
       </c>
       <c r="AP24" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
       <c r="AS24" s="2" t="inlineStr"/>
-      <c r="AT24" s="2" t="inlineStr"/>
+      <c r="AT24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU24" s="2" t="inlineStr">
         <is>
           <t>柱≥0</t>
         </is>
       </c>
       <c r="AV24" s="2" t="n">
-        <v>44088</v>
+        <v>42238</v>
       </c>
       <c r="AW24" s="2" t="n">
-        <v>45262</v>
+        <v>44580</v>
       </c>
       <c r="AX24" s="2" t="n">
-        <v>42377</v>
+        <v>42563</v>
       </c>
       <c r="AY24" s="2" t="n">
-        <v>39699.667</v>
+        <v>39907.333</v>
       </c>
       <c r="AZ24" s="2" t="n">
-        <v>39003.2</v>
+        <v>38971.2</v>
       </c>
       <c r="BA24" s="2" t="n">
-        <v>41754.975</v>
+        <v>41768.277</v>
       </c>
       <c r="BB24" s="2" t="n">
-        <v>38646.994</v>
+        <v>38704.263</v>
       </c>
       <c r="BC24" s="2" t="n">
-        <v>1.3786</v>
+        <v>-0.3223</v>
       </c>
       <c r="BD24" s="2" t="n">
-        <v>2.9075</v>
+        <v>2.2264</v>
       </c>
       <c r="BE24" s="2" t="n">
-        <v>0.9111</v>
+        <v>0.7301</v>
       </c>
       <c r="BF24" s="2" t="n">
-        <v>0.4371</v>
+        <v>0.3236</v>
       </c>
       <c r="BG24" s="2" t="n">
-        <v>0.4789</v>
+        <v>0.4347</v>
       </c>
     </row>
     <row r="25">
@@ -4318,7 +4296,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10070</v>
+        <v>9375</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>76.94</v>
@@ -4339,19 +4317,19 @@
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>0011110000</t>
+          <t>0010010000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0111010000</t>
+          <t>0010010000</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -4370,7 +4348,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2C→2A·8d</t>
+          <t>2C→2A·9d</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
@@ -4378,34 +4356,36 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr"/>
       <c r="AE25" s="2" t="inlineStr"/>
-      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="n">
+        <v>-1</v>
+      </c>
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="AI25" s="2" t="inlineStr"/>
       <c r="AJ25" s="2" t="n">
-        <v>110.58</v>
+        <v>105.42</v>
       </c>
       <c r="AK25" s="2" t="n">
-        <v>28.06</v>
+        <v>20.45</v>
       </c>
       <c r="AL25" s="2" t="n"/>
       <c r="AM25" s="2" t="n">
-        <v>-5.63</v>
+        <v>-15.05</v>
       </c>
       <c r="AN25" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>-5.56</v>
       </c>
       <c r="AO25" s="2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AP25" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS25" s="2" t="inlineStr"/>
       <c r="AT25" s="2" t="inlineStr"/>
@@ -4415,40 +4395,40 @@
         </is>
       </c>
       <c r="AV25" s="2" t="n">
-        <v>10525.8</v>
+        <v>10173.8</v>
       </c>
       <c r="AW25" s="2" t="n">
-        <v>10676.4</v>
+        <v>10604.4</v>
       </c>
       <c r="AX25" s="2" t="n">
-        <v>9955.583000000001</v>
+        <v>9966.759</v>
       </c>
       <c r="AY25" s="2" t="n">
-        <v>9675.013000000001</v>
+        <v>9679.611000000001</v>
       </c>
       <c r="AZ25" s="2" t="n">
-        <v>9734.922</v>
+        <v>9725.103999999999</v>
       </c>
       <c r="BA25" s="2" t="n">
-        <v>12405.67</v>
+        <v>12408.851</v>
       </c>
       <c r="BB25" s="2" t="n">
-        <v>8476.681</v>
+        <v>8507.007</v>
       </c>
       <c r="BC25" s="2" t="n">
-        <v>3.0555</v>
+        <v>1.6102</v>
       </c>
       <c r="BD25" s="2" t="n">
-        <v>2.038</v>
+        <v>1.5028</v>
       </c>
       <c r="BE25" s="2" t="n">
-        <v>0.3336</v>
+        <v>0.3189</v>
       </c>
       <c r="BF25" s="2" t="n">
-        <v>0.6401</v>
+        <v>0.465</v>
       </c>
       <c r="BG25" s="2" t="n">
-        <v>1.1058</v>
+        <v>1.0542</v>
       </c>
     </row>
     <row r="26">
@@ -4463,7 +4443,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6900</v>
+        <v>6744</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>104.12</v>
@@ -4487,7 +4467,7 @@
         <v>3</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
@@ -4496,7 +4476,7 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0010011000</t>
+          <t>0010000000</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -4505,7 +4485,7 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
@@ -4530,27 +4510,27 @@
       <c r="AH26" s="2" t="inlineStr"/>
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="n">
-        <v>87.66</v>
+        <v>82.73</v>
       </c>
       <c r="AK26" s="2" t="n">
-        <v>16.21</v>
+        <v>14.8</v>
       </c>
       <c r="AL26" s="2" t="n"/>
       <c r="AM26" s="2" t="n">
-        <v>-16.95</v>
+        <v>-13.28</v>
       </c>
       <c r="AN26" s="2" t="n">
-        <v>-14.31</v>
+        <v>-19.59</v>
       </c>
       <c r="AO26" s="2" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
       <c r="AP26" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS26" s="2" t="inlineStr"/>
       <c r="AT26" s="2" t="inlineStr">
@@ -4564,40 +4544,40 @@
         </is>
       </c>
       <c r="AV26" s="2" t="n">
-        <v>7340.4</v>
+        <v>7095.2</v>
       </c>
       <c r="AW26" s="2" t="n">
-        <v>7969.3</v>
+        <v>7797</v>
       </c>
       <c r="AX26" s="2" t="n">
-        <v>7899.227</v>
+        <v>7868.095</v>
       </c>
       <c r="AY26" s="2" t="n">
-        <v>7659.539</v>
+        <v>7642.402</v>
       </c>
       <c r="AZ26" s="2" t="n">
-        <v>7560.323</v>
+        <v>7552.609</v>
       </c>
       <c r="BA26" s="2" t="n">
-        <v>8478.028</v>
+        <v>8474.48</v>
       </c>
       <c r="BB26" s="2" t="n">
-        <v>6204.721</v>
+        <v>6222.862</v>
       </c>
       <c r="BC26" s="2" t="n">
-        <v>-2.3113</v>
+        <v>-3.3757</v>
       </c>
       <c r="BD26" s="2" t="n">
-        <v>0.2199</v>
+        <v>-0.3072</v>
       </c>
       <c r="BE26" s="2" t="n">
-        <v>0.2125</v>
+        <v>0.1726</v>
       </c>
       <c r="BF26" s="2" t="n">
-        <v>0.3362</v>
+        <v>0.1999</v>
       </c>
       <c r="BG26" s="2" t="n">
-        <v>0.8766</v>
+        <v>0.8273</v>
       </c>
     </row>
     <row r="27">
@@ -4612,7 +4592,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3644</v>
+        <v>3635</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>101.22</v>
@@ -4644,7 +4624,7 @@
         <v>8</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
@@ -4653,7 +4633,7 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1111111001</t>
+          <t>0111111001</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -4662,7 +4642,7 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4652,7 @@
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2A→2B·4d ← 4+→2A·9d ← 4→4+·11d</t>
+          <t>2A→2B·5d ← 4+→2A·10d ← 4→4+·12d</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
@@ -4687,74 +4667,70 @@
       <c r="AH27" s="2" t="inlineStr"/>
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="n">
-        <v>-2.71</v>
+        <v>-2.26</v>
       </c>
       <c r="AK27" s="2" t="n">
-        <v>-5.71</v>
+        <v>-4.62</v>
       </c>
       <c r="AL27" s="2" t="n"/>
       <c r="AM27" s="2" t="n">
-        <v>8.58</v>
+        <v>7.36</v>
       </c>
       <c r="AN27" s="2" t="n">
-        <v>11.59</v>
+        <v>12.63</v>
       </c>
       <c r="AO27" s="2" t="n">
-        <v>93.7</v>
+        <v>94.5</v>
       </c>
       <c r="AP27" s="2" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
       <c r="AS27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT27" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AT27" s="2" t="inlineStr"/>
       <c r="AU27" s="2" t="inlineStr">
         <is>
           <t>柱≥0</t>
         </is>
       </c>
       <c r="AV27" s="2" t="n">
-        <v>3628.4</v>
+        <v>3632.4</v>
       </c>
       <c r="AW27" s="2" t="n">
-        <v>3588.7</v>
+        <v>3601.6</v>
       </c>
       <c r="AX27" s="2" t="n">
-        <v>3502.507</v>
+        <v>3524.293</v>
       </c>
       <c r="AY27" s="2" t="n">
-        <v>3435.516</v>
+        <v>3438.447</v>
       </c>
       <c r="AZ27" s="2" t="n">
-        <v>3431.442</v>
+        <v>3437.779</v>
       </c>
       <c r="BA27" s="2" t="n">
-        <v>3291.876</v>
+        <v>3297.64</v>
       </c>
       <c r="BB27" s="2" t="n">
-        <v>3313.275</v>
+        <v>3313.399</v>
       </c>
       <c r="BC27" s="2" t="n">
-        <v>1.0159</v>
+        <v>1.0562</v>
       </c>
       <c r="BD27" s="2" t="n">
-        <v>1.7662</v>
+        <v>1.7317</v>
       </c>
       <c r="BE27" s="2" t="n">
-        <v>0.3317</v>
+        <v>0.3682</v>
       </c>
       <c r="BF27" s="2" t="n">
-        <v>0.5296</v>
+        <v>0.5114</v>
       </c>
       <c r="BG27" s="2" t="n">
-        <v>-0.0271</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="28">
@@ -4769,7 +4745,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3796</v>
+        <v>3760</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>10.44</v>
@@ -4790,19 +4766,19 @@
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>0100000110</t>
+          <t>0000000100</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -4811,7 +4787,7 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
@@ -4820,12 +4796,12 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>站稳短均·周J超卖·日线纠缠</t>
+          <t>周J超卖·日线纠缠</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4→4+·1d ← 4+→4·5d ← 4→4+·17d</t>
+          <t>4→4+·2d ← 4+→4·6d ← 4→4+·18d</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
@@ -4835,32 +4811,30 @@
       <c r="AE28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AF28" s="2" t="inlineStr"/>
       <c r="AG28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AH28" s="2" t="inlineStr"/>
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="n">
-        <v>-9.43</v>
+        <v>-7.39</v>
       </c>
       <c r="AK28" s="2" t="n">
-        <v>-19.92</v>
+        <v>-19.57</v>
       </c>
       <c r="AL28" s="2" t="n"/>
       <c r="AM28" s="2" t="n">
-        <v>7.21</v>
+        <v>7.65</v>
       </c>
       <c r="AN28" s="2" t="n">
-        <v>1.08</v>
+        <v>2.56</v>
       </c>
       <c r="AO28" s="2" t="n">
-        <v>26.4</v>
+        <v>25.5</v>
       </c>
       <c r="AP28" s="2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -4868,44 +4842,44 @@
       <c r="AT28" s="2" t="inlineStr"/>
       <c r="AU28" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>柱≥0</t>
         </is>
       </c>
       <c r="AV28" s="2" t="n">
-        <v>3702.8</v>
+        <v>3721</v>
       </c>
       <c r="AW28" s="2" t="n">
-        <v>3747.6</v>
+        <v>3742.3</v>
       </c>
       <c r="AX28" s="2" t="n">
-        <v>3788.452</v>
+        <v>3792.068</v>
       </c>
       <c r="AY28" s="2" t="n">
-        <v>3776.711</v>
+        <v>3773.974</v>
       </c>
       <c r="AZ28" s="2" t="n">
-        <v>3881.446</v>
+        <v>3880.939</v>
       </c>
       <c r="BA28" s="2" t="n">
-        <v>3822.569</v>
+        <v>3820.622</v>
       </c>
       <c r="BB28" s="2" t="n">
-        <v>4180.273</v>
+        <v>4180.141</v>
       </c>
       <c r="BC28" s="2" t="n">
-        <v>-0.9735</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="BD28" s="2" t="n">
-        <v>-0.0881</v>
+        <v>-0.021</v>
       </c>
       <c r="BE28" s="2" t="n">
-        <v>-0.0946</v>
+        <v>-0.0458</v>
       </c>
       <c r="BF28" s="2" t="n">
-        <v>-0.2306</v>
+        <v>-0.2035</v>
       </c>
       <c r="BG28" s="2" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.07389999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -4920,7 +4894,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13815</v>
+        <v>13295</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>107.6</v>
@@ -4943,19 +4917,19 @@
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>0111111000</t>
+          <t>0110111000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0110111010</t>
+          <t>0010011000</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -4986,28 +4960,26 @@
         <v>-1</v>
       </c>
       <c r="AG29" s="2" t="inlineStr"/>
-      <c r="AH29" s="2" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AH29" s="2" t="inlineStr"/>
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="n">
-        <v>92.92</v>
+        <v>85.89</v>
       </c>
       <c r="AK29" s="2" t="n">
-        <v>16.24</v>
+        <v>13.17</v>
       </c>
       <c r="AL29" s="2" t="n"/>
       <c r="AM29" s="2" t="n">
-        <v>-11.46</v>
+        <v>-19.39</v>
       </c>
       <c r="AN29" s="2" t="n">
-        <v>8.26</v>
+        <v>5.01</v>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>37.7</v>
+        <v>35.5</v>
       </c>
       <c r="AP29" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -5023,40 +4995,40 @@
         </is>
       </c>
       <c r="AV29" s="2" t="n">
-        <v>14919</v>
+        <v>14269</v>
       </c>
       <c r="AW29" s="2" t="n">
-        <v>15390</v>
+        <v>15173</v>
       </c>
       <c r="AX29" s="2" t="n">
-        <v>14455.208</v>
+        <v>14515.567</v>
       </c>
       <c r="AY29" s="2" t="n">
-        <v>13945.374</v>
+        <v>13941.139</v>
       </c>
       <c r="AZ29" s="2" t="n">
-        <v>13729.478</v>
+        <v>13749.44</v>
       </c>
       <c r="BA29" s="2" t="n">
-        <v>14379.004</v>
+        <v>14404.766</v>
       </c>
       <c r="BB29" s="2" t="n">
-        <v>12042.579</v>
+        <v>12077.501</v>
       </c>
       <c r="BC29" s="2" t="n">
-        <v>0.8077</v>
+        <v>-0.9025</v>
       </c>
       <c r="BD29" s="2" t="n">
-        <v>2.0915</v>
+        <v>1.6739</v>
       </c>
       <c r="BE29" s="2" t="n">
-        <v>0.652</v>
+        <v>0.6727</v>
       </c>
       <c r="BF29" s="2" t="n">
-        <v>0.7637</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="BG29" s="2" t="n">
-        <v>0.9292</v>
+        <v>0.8589</v>
       </c>
     </row>
     <row r="30">
@@ -5071,7 +5043,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>25650</v>
+        <v>25200</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>15.87</v>
@@ -5084,29 +5056,27 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>0101000100</t>
+          <t>0001000100</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0101000100</t>
+          <t>0001000000</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -5115,21 +5085,17 @@
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>站稳短均</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4→4+·1d</t>
+          <t>4+→4·1d ← 4→4+·2d</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
@@ -5137,38 +5103,36 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr"/>
       <c r="AE30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="AF30" s="2" t="inlineStr"/>
-      <c r="AG30" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
       </c>
       <c r="AH30" s="2" t="inlineStr"/>
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="n">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="AK30" s="2" t="n">
-        <v>-10.7</v>
+        <v>-11.09</v>
       </c>
       <c r="AL30" s="2" t="n"/>
       <c r="AM30" s="2" t="n">
-        <v>7.13</v>
+        <v>6.57</v>
       </c>
       <c r="AN30" s="2" t="n">
-        <v>10.37</v>
+        <v>10.26</v>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>49.7</v>
+        <v>53</v>
       </c>
       <c r="AP30" s="2" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS30" s="2" t="inlineStr"/>
       <c r="AT30" s="2" t="inlineStr"/>
@@ -5178,40 +5142,40 @@
         </is>
       </c>
       <c r="AV30" s="2" t="n">
-        <v>25275</v>
+        <v>25304</v>
       </c>
       <c r="AW30" s="2" t="n">
-        <v>25051.5</v>
+        <v>25153.5</v>
       </c>
       <c r="AX30" s="2" t="n">
-        <v>24095.25</v>
+        <v>24238.75</v>
       </c>
       <c r="AY30" s="2" t="n">
-        <v>23958.333</v>
+        <v>23968.667</v>
       </c>
       <c r="AZ30" s="2" t="n">
-        <v>24579.6</v>
+        <v>24578.4</v>
       </c>
       <c r="BA30" s="2" t="n">
-        <v>25202.7</v>
+        <v>25192.45</v>
       </c>
       <c r="BB30" s="2" t="n">
-        <v>26073.167</v>
+        <v>26081.728</v>
       </c>
       <c r="BC30" s="2" t="n">
-        <v>1.7386</v>
+        <v>1.6102</v>
       </c>
       <c r="BD30" s="2" t="n">
-        <v>1.2809</v>
+        <v>1.4018</v>
       </c>
       <c r="BE30" s="2" t="n">
-        <v>0.2417</v>
+        <v>0.225</v>
       </c>
       <c r="BF30" s="2" t="n">
-        <v>-0.1918</v>
+        <v>-0.1524</v>
       </c>
       <c r="BG30" s="2" t="n">
-        <v>0.0788</v>
+        <v>0.0786</v>
       </c>
     </row>
     <row r="31">
@@ -5226,7 +5190,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2264.5</v>
+        <v>2228.5</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>12.07</v>
@@ -5266,32 +5230,28 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2A→1·6d ← 2C→2A·10d</t>
+          <t>1→4·3d ← 2A→1·7d ← 2C→2A·11d</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr"/>
-      <c r="AE31" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="AE31" s="2" t="inlineStr"/>
       <c r="AF31" s="2" t="n">
         <v>-1</v>
       </c>
@@ -5299,23 +5259,23 @@
       <c r="AH31" s="2" t="inlineStr"/>
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="n">
-        <v>-4.78</v>
+        <v>-4.77</v>
       </c>
       <c r="AK31" s="2" t="n">
-        <v>-12.16</v>
+        <v>-12.4</v>
       </c>
       <c r="AL31" s="2" t="n"/>
       <c r="AM31" s="2" t="n">
-        <v>1.51</v>
+        <v>0.96</v>
       </c>
       <c r="AN31" s="2" t="n">
-        <v>-2.89</v>
+        <v>-2.4</v>
       </c>
       <c r="AO31" s="2" t="n">
-        <v>40.7</v>
+        <v>37.6</v>
       </c>
       <c r="AP31" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -5327,40 +5287,40 @@
         </is>
       </c>
       <c r="AV31" s="2" t="n">
-        <v>2313.2</v>
+        <v>2285.5</v>
       </c>
       <c r="AW31" s="2" t="n">
-        <v>2367.05</v>
+        <v>2351.45</v>
       </c>
       <c r="AX31" s="2" t="n">
-        <v>2361.709</v>
+        <v>2358.77</v>
       </c>
       <c r="AY31" s="2" t="n">
-        <v>2394.434</v>
+        <v>2387.337</v>
       </c>
       <c r="AZ31" s="2" t="n">
-        <v>2420.831</v>
+        <v>2420.95</v>
       </c>
       <c r="BA31" s="2" t="n">
-        <v>2381.92</v>
+        <v>2382.405</v>
       </c>
       <c r="BB31" s="2" t="n">
-        <v>2364.624</v>
+        <v>2364.222</v>
       </c>
       <c r="BC31" s="2" t="n">
-        <v>-0.8121</v>
+        <v>-1.0169</v>
       </c>
       <c r="BD31" s="2" t="n">
-        <v>-0.6194</v>
+        <v>-0.5618</v>
       </c>
       <c r="BE31" s="2" t="n">
-        <v>0.2507</v>
+        <v>0.2321</v>
       </c>
       <c r="BF31" s="2" t="n">
-        <v>0.1316</v>
+        <v>0.1085</v>
       </c>
       <c r="BG31" s="2" t="n">
-        <v>-0.0478</v>
+        <v>-0.0477</v>
       </c>
     </row>
     <row r="32">
@@ -5375,7 +5335,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2284</v>
+        <v>2305.5</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>44.64</v>
@@ -5390,7 +5350,7 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -5417,7 +5377,7 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
@@ -5431,7 +5391,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2A→2C·14d</t>
+          <t>2A→2C·15d</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
@@ -5443,33 +5403,31 @@
         <v>1</v>
       </c>
       <c r="AG32" s="2" t="inlineStr"/>
-      <c r="AH32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH32" s="2" t="inlineStr"/>
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="n">
-        <v>22.24</v>
+        <v>24.86</v>
       </c>
       <c r="AK32" s="2" t="n">
-        <v>3.63</v>
+        <v>5.95</v>
       </c>
       <c r="AL32" s="2" t="n"/>
       <c r="AM32" s="2" t="n">
-        <v>12.01</v>
+        <v>13.54</v>
       </c>
       <c r="AN32" s="2" t="n">
-        <v>-3.45</v>
+        <v>-0.3</v>
       </c>
       <c r="AO32" s="2" t="n">
-        <v>79</v>
+        <v>80.7</v>
       </c>
       <c r="AP32" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
       <c r="AS32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT32" s="2" t="inlineStr"/>
       <c r="AU32" s="2" t="inlineStr">
@@ -5478,40 +5436,40 @@
         </is>
       </c>
       <c r="AV32" s="2" t="n">
-        <v>2222.2</v>
+        <v>2252.3</v>
       </c>
       <c r="AW32" s="2" t="n">
-        <v>2196.7</v>
+        <v>2209.7</v>
       </c>
       <c r="AX32" s="2" t="n">
-        <v>2217.73</v>
+        <v>2218.101</v>
       </c>
       <c r="AY32" s="2" t="n">
-        <v>2220.397</v>
+        <v>2226.338</v>
       </c>
       <c r="AZ32" s="2" t="n">
-        <v>2147.164</v>
+        <v>2153.758</v>
       </c>
       <c r="BA32" s="2" t="n">
-        <v>2013.153</v>
+        <v>2016.906</v>
       </c>
       <c r="BB32" s="2" t="n">
-        <v>2008.739</v>
+        <v>2011.154</v>
       </c>
       <c r="BC32" s="2" t="n">
-        <v>0.3572</v>
+        <v>0.7496</v>
       </c>
       <c r="BD32" s="2" t="n">
-        <v>-0.3134</v>
+        <v>-0.1892</v>
       </c>
       <c r="BE32" s="2" t="n">
-        <v>0.5615</v>
+        <v>0.6288</v>
       </c>
       <c r="BF32" s="2" t="n">
-        <v>0.336</v>
+        <v>0.4031</v>
       </c>
       <c r="BG32" s="2" t="n">
-        <v>0.2224</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="33">
@@ -5526,7 +5484,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4884</v>
+        <v>4876</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>4.42</v>
@@ -5541,7 +5499,7 @@
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
@@ -5550,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
@@ -5559,7 +5517,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0001000100</t>
+          <t>0101000100</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -5568,7 +5526,7 @@
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
@@ -5582,32 +5540,30 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr"/>
       <c r="AE33" s="2" t="inlineStr"/>
-      <c r="AF33" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF33" s="2" t="inlineStr"/>
       <c r="AG33" s="2" t="inlineStr"/>
       <c r="AH33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="n">
-        <v>11.87</v>
+        <v>13.71</v>
       </c>
       <c r="AK33" s="2" t="n">
-        <v>-10.66</v>
+        <v>-9.65</v>
       </c>
       <c r="AL33" s="2" t="n"/>
       <c r="AM33" s="2" t="n">
-        <v>7.96</v>
+        <v>9.06</v>
       </c>
       <c r="AN33" s="2" t="n">
-        <v>-4.83</v>
+        <v>-1.27</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="AP33" s="2" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -5619,40 +5575,40 @@
         </is>
       </c>
       <c r="AV33" s="2" t="n">
-        <v>4824.4</v>
+        <v>4859.2</v>
       </c>
       <c r="AW33" s="2" t="n">
-        <v>4796.7</v>
+        <v>4811.8</v>
       </c>
       <c r="AX33" s="2" t="n">
-        <v>4825.011</v>
+        <v>4824.154</v>
       </c>
       <c r="AY33" s="2" t="n">
-        <v>4897.001</v>
+        <v>4890.83</v>
       </c>
       <c r="AZ33" s="2" t="n">
-        <v>4889.752</v>
+        <v>4885.852</v>
       </c>
       <c r="BA33" s="2" t="n">
-        <v>4917.699</v>
+        <v>4914.375</v>
       </c>
       <c r="BB33" s="2" t="n">
-        <v>5138.18</v>
+        <v>5141.821</v>
       </c>
       <c r="BC33" s="2" t="n">
-        <v>0.1173</v>
+        <v>0.4518</v>
       </c>
       <c r="BD33" s="2" t="n">
-        <v>-0.5124</v>
+        <v>-0.3532</v>
       </c>
       <c r="BE33" s="2" t="n">
-        <v>-0.3987</v>
+        <v>-0.2965</v>
       </c>
       <c r="BF33" s="2" t="n">
-        <v>-0.346</v>
+        <v>-0.2676</v>
       </c>
       <c r="BG33" s="2" t="n">
-        <v>0.1187</v>
+        <v>0.1371</v>
       </c>
     </row>
     <row r="34">
@@ -5667,7 +5623,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1216</v>
+        <v>1207</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>25.31</v>
@@ -5691,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
@@ -5700,7 +5656,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0011111011</t>
+          <t>0011111000</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -5709,7 +5665,7 @@
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
@@ -5723,7 +5679,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2A→2C·1d ← 2C→2A·4d</t>
+          <t>2A→2C·2d ← 2C→2A·5d</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
@@ -5733,32 +5689,32 @@
       <c r="AE34" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AF34" s="2" t="inlineStr"/>
-      <c r="AG34" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>预-1</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr"/>
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="n">
-        <v>34.32</v>
+        <v>33.74</v>
       </c>
       <c r="AK34" s="2" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="AL34" s="2" t="n"/>
       <c r="AM34" s="2" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="AN34" s="2" t="n">
-        <v>5.36</v>
+        <v>6.08</v>
       </c>
       <c r="AO34" s="2" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="AP34" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -5770,40 +5726,40 @@
         </is>
       </c>
       <c r="AV34" s="2" t="n">
-        <v>1215.1</v>
+        <v>1214.4</v>
       </c>
       <c r="AW34" s="2" t="n">
-        <v>1200.15</v>
+        <v>1205.7</v>
       </c>
       <c r="AX34" s="2" t="n">
-        <v>1177.465</v>
+        <v>1181.915</v>
       </c>
       <c r="AY34" s="2" t="n">
-        <v>1162.276</v>
+        <v>1163.413</v>
       </c>
       <c r="AZ34" s="2" t="n">
-        <v>1176.332</v>
+        <v>1177.499</v>
       </c>
       <c r="BA34" s="2" t="n">
-        <v>1162.714</v>
+        <v>1163.505</v>
       </c>
       <c r="BB34" s="2" t="n">
-        <v>1128.809</v>
+        <v>1130.235</v>
       </c>
       <c r="BC34" s="2" t="n">
-        <v>1.1632</v>
+        <v>1.2318</v>
       </c>
       <c r="BD34" s="2" t="n">
-        <v>1.0696</v>
+        <v>1.0167</v>
       </c>
       <c r="BE34" s="2" t="n">
-        <v>0.364</v>
+        <v>0.3946</v>
       </c>
       <c r="BF34" s="2" t="n">
-        <v>0.2174</v>
+        <v>0.2239</v>
       </c>
       <c r="BG34" s="2" t="n">
-        <v>0.3432</v>
+        <v>0.3374</v>
       </c>
     </row>
     <row r="35">
@@ -5818,7 +5774,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>7443</v>
+        <v>7427</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>35.91</v>
@@ -5844,7 +5800,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
@@ -5853,7 +5809,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0111111011</t>
+          <t>0111111001</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -5879,42 +5835,40 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr"/>
-      <c r="AE35" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE35" s="2" t="inlineStr"/>
       <c r="AF35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AG35" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="AH35" s="2" t="inlineStr"/>
-      <c r="AI35" s="2" t="n">
+      <c r="AH35" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="n">
-        <v>44.6</v>
+        <v>45.54</v>
       </c>
       <c r="AK35" s="2" t="n">
-        <v>9.82</v>
+        <v>10.88</v>
       </c>
       <c r="AL35" s="2" t="n"/>
       <c r="AM35" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>11.12</v>
       </c>
       <c r="AN35" s="2" t="n">
-        <v>-4.98</v>
+        <v>-1.12</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="AP35" s="2" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
       <c r="AS35" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT35" s="2" t="inlineStr"/>
       <c r="AU35" s="2" t="inlineStr">
@@ -5923,40 +5877,40 @@
         </is>
       </c>
       <c r="AV35" s="2" t="n">
-        <v>7314.6</v>
+        <v>7375.8</v>
       </c>
       <c r="AW35" s="2" t="n">
-        <v>7331.3</v>
+        <v>7347.6</v>
       </c>
       <c r="AX35" s="2" t="n">
-        <v>7318.673</v>
+        <v>7326.648</v>
       </c>
       <c r="AY35" s="2" t="n">
-        <v>7380.452</v>
+        <v>7373.274</v>
       </c>
       <c r="AZ35" s="2" t="n">
-        <v>7320.898</v>
+        <v>7337.177</v>
       </c>
       <c r="BA35" s="2" t="n">
-        <v>6806.233</v>
+        <v>6811.348</v>
       </c>
       <c r="BB35" s="2" t="n">
-        <v>6474.907</v>
+        <v>6486.931</v>
       </c>
       <c r="BC35" s="2" t="n">
-        <v>0.1961</v>
+        <v>0.5031</v>
       </c>
       <c r="BD35" s="2" t="n">
-        <v>-0.2128</v>
+        <v>-0.051</v>
       </c>
       <c r="BE35" s="2" t="n">
-        <v>0.5603</v>
+        <v>0.5875</v>
       </c>
       <c r="BF35" s="2" t="n">
-        <v>0.1368</v>
+        <v>0.1917</v>
       </c>
       <c r="BG35" s="2" t="n">
-        <v>0.446</v>
+        <v>0.4554</v>
       </c>
     </row>
     <row r="36">
@@ -5971,7 +5925,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5000</v>
+        <v>4962</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>21.7</v>
@@ -6013,7 +5967,7 @@
         </is>
       </c>
       <c r="W36" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
@@ -6036,29 +5990,25 @@
       <c r="AH36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
-      </c>
+      <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="n">
-        <v>11.97</v>
+        <v>13.26</v>
       </c>
       <c r="AK36" s="2" t="n">
-        <v>-9.16</v>
+        <v>-8.69</v>
       </c>
       <c r="AL36" s="2" t="n"/>
       <c r="AM36" s="2" t="n">
-        <v>9.08</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AN36" s="2" t="n">
-        <v>-3.79</v>
+        <v>-1.61</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="AP36" s="2" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -6066,44 +6016,44 @@
       <c r="AT36" s="2" t="inlineStr"/>
       <c r="AU36" s="2" t="inlineStr">
         <is>
-          <t>无背离</t>
+          <t>柱≥0</t>
         </is>
       </c>
       <c r="AV36" s="2" t="n">
-        <v>4912</v>
+        <v>4949.4</v>
       </c>
       <c r="AW36" s="2" t="n">
-        <v>4902</v>
+        <v>4908</v>
       </c>
       <c r="AX36" s="2" t="n">
-        <v>4947.478</v>
+        <v>4945.661</v>
       </c>
       <c r="AY36" s="2" t="n">
-        <v>4982.966</v>
+        <v>4977.515</v>
       </c>
       <c r="AZ36" s="2" t="n">
-        <v>4910.957</v>
+        <v>4914.076</v>
       </c>
       <c r="BA36" s="2" t="n">
-        <v>4845.053</v>
+        <v>4839.651</v>
       </c>
       <c r="BB36" s="2" t="n">
-        <v>5160.678</v>
+        <v>5163.647</v>
       </c>
       <c r="BC36" s="2" t="n">
-        <v>-0.0702</v>
+        <v>0.2331</v>
       </c>
       <c r="BD36" s="2" t="n">
-        <v>-0.3391</v>
+        <v>-0.2297</v>
       </c>
       <c r="BE36" s="2" t="n">
-        <v>0.0559</v>
+        <v>0.1167</v>
       </c>
       <c r="BF36" s="2" t="n">
-        <v>-0.4639</v>
+        <v>-0.3898</v>
       </c>
       <c r="BG36" s="2" t="n">
-        <v>0.1197</v>
+        <v>0.1326</v>
       </c>
     </row>
     <row r="37">
@@ -6118,7 +6068,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>10630</v>
+        <v>10400</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>96.47</v>
@@ -6131,9 +6081,7 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="n">
-        <v>-9</v>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="n">
         <v>0</v>
       </c>
@@ -6141,19 +6089,19 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>0010011000</t>
+          <t>0010001000</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0110001000</t>
+          <t>0010000000</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -6162,17 +6110,21 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr"/>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>周MACD死叉</t>
+        </is>
+      </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2C→2A·1d</t>
+          <t>2A→2C·1d ← 2C→2A·2d</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
@@ -6187,23 +6139,23 @@
       <c r="AH37" s="2" t="inlineStr"/>
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="n">
-        <v>69.38</v>
+        <v>64.91</v>
       </c>
       <c r="AK37" s="2" t="n">
-        <v>6.83</v>
+        <v>5.73</v>
       </c>
       <c r="AL37" s="2" t="n"/>
       <c r="AM37" s="2" t="n">
-        <v>-9.93</v>
+        <v>-13.29</v>
       </c>
       <c r="AN37" s="2" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>26.1</v>
+        <v>24.2</v>
       </c>
       <c r="AP37" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -6219,40 +6171,40 @@
         </is>
       </c>
       <c r="AV37" s="2" t="n">
-        <v>11247</v>
+        <v>10838</v>
       </c>
       <c r="AW37" s="2" t="n">
-        <v>11859.5</v>
+        <v>11689.5</v>
       </c>
       <c r="AX37" s="2" t="n">
-        <v>11329.329</v>
+        <v>11360.096</v>
       </c>
       <c r="AY37" s="2" t="n">
-        <v>10987.981</v>
+        <v>10980.61</v>
       </c>
       <c r="AZ37" s="2" t="n">
-        <v>10950.275</v>
+        <v>10945.813</v>
       </c>
       <c r="BA37" s="2" t="n">
-        <v>11785.286</v>
+        <v>11793.024</v>
       </c>
       <c r="BB37" s="2" t="n">
-        <v>9905.031999999999</v>
+        <v>9928.026</v>
       </c>
       <c r="BC37" s="2" t="n">
-        <v>-0.6339</v>
+        <v>-2.0058</v>
       </c>
       <c r="BD37" s="2" t="n">
-        <v>1.281</v>
+        <v>0.9437</v>
       </c>
       <c r="BE37" s="2" t="n">
-        <v>0.27</v>
+        <v>0.2187</v>
       </c>
       <c r="BF37" s="2" t="n">
-        <v>0.4253</v>
+        <v>0.3375</v>
       </c>
       <c r="BG37" s="2" t="n">
-        <v>0.6938</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="38">
@@ -6267,7 +6219,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1745</v>
+        <v>1731.5</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>80.55</v>
@@ -6338,29 +6290,27 @@
       </c>
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="n">
-        <v>35.32</v>
+        <v>35.56</v>
       </c>
       <c r="AK38" s="2" t="n">
-        <v>4.4</v>
+        <v>4.84</v>
       </c>
       <c r="AL38" s="2" t="n"/>
       <c r="AM38" s="2" t="n">
-        <v>7.99</v>
+        <v>7.97</v>
       </c>
       <c r="AN38" s="2" t="n">
-        <v>-6.73</v>
+        <v>-3.76</v>
       </c>
       <c r="AO38" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="AP38" s="2" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
-      <c r="AS38" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="AS38" s="2" t="inlineStr"/>
       <c r="AT38" s="2" t="inlineStr"/>
       <c r="AU38" s="2" t="inlineStr">
         <is>
@@ -6368,40 +6318,40 @@
         </is>
       </c>
       <c r="AV38" s="2" t="n">
-        <v>1731.6</v>
+        <v>1736.3</v>
       </c>
       <c r="AW38" s="2" t="n">
-        <v>1728.5</v>
+        <v>1728.85</v>
       </c>
       <c r="AX38" s="2" t="n">
-        <v>1747.58</v>
+        <v>1746.645</v>
       </c>
       <c r="AY38" s="2" t="n">
-        <v>1768.033</v>
+        <v>1764.789</v>
       </c>
       <c r="AZ38" s="2" t="n">
-        <v>1751.655</v>
+        <v>1753.446</v>
       </c>
       <c r="BA38" s="2" t="n">
-        <v>1680.265</v>
+        <v>1679.952</v>
       </c>
       <c r="BB38" s="2" t="n">
-        <v>1593.671</v>
+        <v>1595.852</v>
       </c>
       <c r="BC38" s="2" t="n">
-        <v>-0.4293</v>
+        <v>-0.2112</v>
       </c>
       <c r="BD38" s="2" t="n">
-        <v>-0.5344</v>
+        <v>-0.4014</v>
       </c>
       <c r="BE38" s="2" t="n">
-        <v>0.4094</v>
+        <v>0.394</v>
       </c>
       <c r="BF38" s="2" t="n">
-        <v>-0.0833</v>
+        <v>-0.0472</v>
       </c>
       <c r="BG38" s="2" t="n">
-        <v>0.3532</v>
+        <v>0.3556</v>
       </c>
     </row>
     <row r="39">
@@ -6416,7 +6366,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>4726</v>
+        <v>4732</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>12.95</v>
@@ -6444,7 +6394,7 @@
         <v>2</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
@@ -6453,7 +6403,7 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0000000100</t>
+          <t>0100000100</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -6462,7 +6412,7 @@
         </is>
       </c>
       <c r="W39" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
@@ -6472,7 +6422,7 @@
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4→3·3d ← 2A→4·6d</t>
+          <t>4→3·4d ← 2A→4·7d</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr"/>
@@ -6480,10 +6430,8 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr"/>
       <c r="AE39" s="2" t="inlineStr"/>
-      <c r="AF39" s="2" t="inlineStr">
-        <is>
-          <t>预1</t>
-        </is>
+      <c r="AF39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="n">
@@ -6491,23 +6439,23 @@
       </c>
       <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="n">
-        <v>29.93</v>
+        <v>31.16</v>
       </c>
       <c r="AK39" s="2" t="n">
-        <v>-5.51</v>
+        <v>-4.17</v>
       </c>
       <c r="AL39" s="2" t="n"/>
       <c r="AM39" s="2" t="n">
-        <v>7.79</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AN39" s="2" t="n">
-        <v>-6.33</v>
+        <v>-3.39</v>
       </c>
       <c r="AO39" s="2" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AP39" s="2" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -6519,40 +6467,40 @@
         </is>
       </c>
       <c r="AV39" s="2" t="n">
-        <v>4691.8</v>
+        <v>4719</v>
       </c>
       <c r="AW39" s="2" t="n">
-        <v>4684.1</v>
+        <v>4687.9</v>
       </c>
       <c r="AX39" s="2" t="n">
-        <v>4739.801</v>
+        <v>4734.06</v>
       </c>
       <c r="AY39" s="2" t="n">
-        <v>4795.709</v>
+        <v>4790.368</v>
       </c>
       <c r="AZ39" s="2" t="n">
-        <v>4759.214</v>
+        <v>4759.346</v>
       </c>
       <c r="BA39" s="2" t="n">
-        <v>4699.149</v>
+        <v>4692.848</v>
       </c>
       <c r="BB39" s="2" t="n">
-        <v>4708.946</v>
+        <v>4714.87</v>
       </c>
       <c r="BC39" s="2" t="n">
-        <v>-0.2447</v>
+        <v>0.0189</v>
       </c>
       <c r="BD39" s="2" t="n">
-        <v>-0.6329</v>
+        <v>-0.5516</v>
       </c>
       <c r="BE39" s="2" t="n">
-        <v>-0.0496</v>
+        <v>-0.007</v>
       </c>
       <c r="BF39" s="2" t="n">
-        <v>-0.4279</v>
+        <v>-0.3688</v>
       </c>
       <c r="BG39" s="2" t="n">
-        <v>0.2993</v>
+        <v>0.3116</v>
       </c>
     </row>
     <row r="40">
@@ -6567,7 +6515,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>7259</v>
+        <v>7354</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>93.44</v>
@@ -6609,7 +6557,7 @@
         </is>
       </c>
       <c r="W40" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
@@ -6636,28 +6584,28 @@
       <c r="AH40" s="2" t="inlineStr"/>
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="n">
-        <v>60.79</v>
+        <v>60.45</v>
       </c>
       <c r="AK40" s="2" t="n">
-        <v>17.09</v>
+        <v>20.1</v>
       </c>
       <c r="AL40" s="2" t="n"/>
       <c r="AM40" s="2" t="n">
-        <v>6.78</v>
+        <v>7.74</v>
       </c>
       <c r="AN40" s="2" t="n">
-        <v>-1.96</v>
+        <v>2.65</v>
       </c>
       <c r="AO40" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AP40" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
       <c r="AS40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT40" s="2" t="inlineStr"/>
       <c r="AU40" s="2" t="inlineStr">
@@ -6666,40 +6614,40 @@
         </is>
       </c>
       <c r="AV40" s="2" t="n">
-        <v>7399.4</v>
+        <v>7398.6</v>
       </c>
       <c r="AW40" s="2" t="n">
-        <v>7266.7</v>
+        <v>7288</v>
       </c>
       <c r="AX40" s="2" t="n">
-        <v>7241.767</v>
+        <v>7253.71</v>
       </c>
       <c r="AY40" s="2" t="n">
-        <v>7199.654</v>
+        <v>7212.272</v>
       </c>
       <c r="AZ40" s="2" t="n">
-        <v>6898.63</v>
+        <v>6926.856</v>
       </c>
       <c r="BA40" s="2" t="n">
-        <v>6146.21</v>
+        <v>6166.726</v>
       </c>
       <c r="BB40" s="2" t="n">
-        <v>5733.11</v>
+        <v>5746.127</v>
       </c>
       <c r="BC40" s="2" t="n">
-        <v>0.8295</v>
+        <v>0.9001</v>
       </c>
       <c r="BD40" s="2" t="n">
-        <v>0.4729</v>
+        <v>0.4908</v>
       </c>
       <c r="BE40" s="2" t="n">
-        <v>1.0849</v>
+        <v>1.085</v>
       </c>
       <c r="BF40" s="2" t="n">
-        <v>0.8313</v>
+        <v>0.8373</v>
       </c>
       <c r="BG40" s="2" t="n">
-        <v>0.6079</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="41">
@@ -6714,7 +6662,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>7351</v>
+        <v>7524</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>91.93000000000001</v>
@@ -6735,7 +6683,7 @@
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -6744,7 +6692,7 @@
         <v>8</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
@@ -6753,7 +6701,7 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1111111111</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -6762,7 +6710,7 @@
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
@@ -6781,36 +6729,38 @@
         <v>1</v>
       </c>
       <c r="AD41" s="2" t="inlineStr"/>
-      <c r="AE41" s="2" t="n">
-        <v>-1</v>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>预1</t>
+        </is>
       </c>
       <c r="AF41" s="2" t="inlineStr"/>
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr"/>
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="n">
-        <v>68.59</v>
+        <v>69.3</v>
       </c>
       <c r="AK41" s="2" t="n">
-        <v>19.71</v>
+        <v>23.96</v>
       </c>
       <c r="AL41" s="2" t="n"/>
       <c r="AM41" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>11.17</v>
       </c>
       <c r="AN41" s="2" t="n">
-        <v>1.78</v>
+        <v>7.42</v>
       </c>
       <c r="AO41" s="2" t="n">
-        <v>99.7</v>
+        <v>100.1</v>
       </c>
       <c r="AP41" s="2" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
       <c r="AS41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT41" s="2" t="inlineStr"/>
       <c r="AU41" s="2" t="inlineStr">
@@ -6819,40 +6769,40 @@
         </is>
       </c>
       <c r="AV41" s="2" t="n">
-        <v>7432.8</v>
+        <v>7477.4</v>
       </c>
       <c r="AW41" s="2" t="n">
-        <v>7267.2</v>
+        <v>7305.9</v>
       </c>
       <c r="AX41" s="2" t="n">
-        <v>7159.664</v>
+        <v>7189.547</v>
       </c>
       <c r="AY41" s="2" t="n">
-        <v>7096.55</v>
+        <v>7115.749</v>
       </c>
       <c r="AZ41" s="2" t="n">
-        <v>6873.181</v>
+        <v>6909.27</v>
       </c>
       <c r="BA41" s="2" t="n">
-        <v>6161.076</v>
+        <v>6180.609</v>
       </c>
       <c r="BB41" s="2" t="n">
-        <v>5830.368</v>
+        <v>5846.056</v>
       </c>
       <c r="BC41" s="2" t="n">
-        <v>1.5426</v>
+        <v>1.6039</v>
       </c>
       <c r="BD41" s="2" t="n">
-        <v>0.8757</v>
+        <v>0.9885</v>
       </c>
       <c r="BE41" s="2" t="n">
-        <v>1.2432</v>
+        <v>1.289</v>
       </c>
       <c r="BF41" s="2" t="n">
-        <v>0.73</v>
+        <v>0.7652</v>
       </c>
       <c r="BG41" s="2" t="n">
-        <v>0.6859</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -6867,7 +6817,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3391</v>
+        <v>3448</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>86.33</v>
@@ -6893,7 +6843,7 @@
         <v>8</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
@@ -6902,7 +6852,7 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0111111101</t>
+          <t>1111111101</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -6911,7 +6861,7 @@
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
@@ -6928,44 +6878,34 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr"/>
-      <c r="AE42" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
-      </c>
-      <c r="AF42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
       <c r="AG42" s="2" t="inlineStr"/>
       <c r="AH42" s="2" t="inlineStr"/>
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="n">
-        <v>68.56</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="AK42" s="2" t="n">
-        <v>21.57</v>
+        <v>25.08</v>
       </c>
       <c r="AL42" s="2" t="n"/>
       <c r="AM42" s="2" t="n">
-        <v>10.05</v>
+        <v>10.51</v>
       </c>
       <c r="AN42" s="2" t="n">
-        <v>-3.16</v>
+        <v>1.94</v>
       </c>
       <c r="AO42" s="2" t="n">
-        <v>88.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AP42" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ42" s="2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr"/>
       <c r="AR42" s="2" t="inlineStr"/>
       <c r="AS42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT42" s="2" t="inlineStr"/>
       <c r="AU42" s="2" t="inlineStr">
@@ -6974,40 +6914,40 @@
         </is>
       </c>
       <c r="AV42" s="2" t="n">
-        <v>3423</v>
+        <v>3438.8</v>
       </c>
       <c r="AW42" s="2" t="n">
-        <v>3340</v>
+        <v>3358.4</v>
       </c>
       <c r="AX42" s="2" t="n">
-        <v>3350.278</v>
+        <v>3356.409</v>
       </c>
       <c r="AY42" s="2" t="n">
-        <v>3340.409</v>
+        <v>3344.562</v>
       </c>
       <c r="AZ42" s="2" t="n">
-        <v>3220.679</v>
+        <v>3233.289</v>
       </c>
       <c r="BA42" s="2" t="n">
-        <v>2891.346</v>
+        <v>2901.158</v>
       </c>
       <c r="BB42" s="2" t="n">
-        <v>2635.093</v>
+        <v>2642.028</v>
       </c>
       <c r="BC42" s="2" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.1231</v>
       </c>
       <c r="BD42" s="2" t="n">
-        <v>0.4001</v>
+        <v>0.4941</v>
       </c>
       <c r="BE42" s="2" t="n">
-        <v>1.032</v>
+        <v>1.0484</v>
       </c>
       <c r="BF42" s="2" t="n">
-        <v>0.8388</v>
+        <v>0.8527</v>
       </c>
       <c r="BG42" s="2" t="n">
-        <v>0.6856</v>
+        <v>0.6882</v>
       </c>
     </row>
     <row r="43">
@@ -7022,7 +6962,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>75580</v>
+        <v>74730</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>14.37</v>
@@ -7043,19 +6983,19 @@
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>0011110010</t>
+          <t>0011110000</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0011110010</t>
+          <t>0011010000</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -7064,7 +7004,7 @@
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
@@ -7074,7 +7014,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2C→2A·10d ← 3-→2C·18d</t>
+          <t>2C→2A·11d ← 3-→2C·19d</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr"/>
@@ -7083,37 +7023,35 @@
       <c r="AD43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AE43" s="2" t="inlineStr">
-        <is>
-          <t>预-1</t>
-        </is>
+      <c r="AE43" s="2" t="n">
+        <v>-1</v>
       </c>
       <c r="AF43" s="2" t="inlineStr"/>
       <c r="AG43" s="2" t="inlineStr"/>
       <c r="AH43" s="2" t="inlineStr"/>
       <c r="AI43" s="2" t="inlineStr"/>
       <c r="AJ43" s="2" t="n">
-        <v>34.74</v>
+        <v>35.49</v>
       </c>
       <c r="AK43" s="2" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL43" s="2" t="n"/>
       <c r="AM43" s="2" t="n">
-        <v>6.24</v>
+        <v>10.16</v>
       </c>
       <c r="AN43" s="2" t="n">
-        <v>9.1</v>
+        <v>9.34</v>
       </c>
       <c r="AO43" s="2" t="n">
-        <v>28</v>
+        <v>29.8</v>
       </c>
       <c r="AP43" s="2" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="AQ43" s="2" t="inlineStr"/>
       <c r="AR43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="2" t="inlineStr"/>
       <c r="AT43" s="2" t="inlineStr"/>
@@ -7123,40 +7061,40 @@
         </is>
       </c>
       <c r="AV43" s="2" t="n">
-        <v>74678</v>
+        <v>75268</v>
       </c>
       <c r="AW43" s="2" t="n">
-        <v>74502</v>
+        <v>74798</v>
       </c>
       <c r="AX43" s="2" t="n">
-        <v>71538</v>
+        <v>71943.5</v>
       </c>
       <c r="AY43" s="2" t="n">
-        <v>70477.333</v>
+        <v>70593</v>
       </c>
       <c r="AZ43" s="2" t="n">
-        <v>72361.579</v>
+        <v>72275.973</v>
       </c>
       <c r="BA43" s="2" t="n">
-        <v>76213.79399999999</v>
+        <v>76211.588</v>
       </c>
       <c r="BB43" s="2" t="n">
-        <v>70570.897</v>
+        <v>70666.00900000001</v>
       </c>
       <c r="BC43" s="2" t="n">
-        <v>1.7756</v>
+        <v>1.7535</v>
       </c>
       <c r="BD43" s="2" t="n">
-        <v>1.4092</v>
+        <v>1.5946</v>
       </c>
       <c r="BE43" s="2" t="n">
-        <v>-0.2588</v>
+        <v>-0.2486</v>
       </c>
       <c r="BF43" s="2" t="n">
-        <v>0.0859</v>
+        <v>0.0798</v>
       </c>
       <c r="BG43" s="2" t="n">
-        <v>0.3474</v>
+        <v>0.3549</v>
       </c>
     </row>
     <row r="44">
@@ -7280,7 +7218,7 @@
         <v>41.928</v>
       </c>
       <c r="AX44" s="2" t="n">
-        <v>42.421</v>
+        <v>42.42</v>
       </c>
       <c r="AY44" s="2" t="n">
         <v>44.285</v>
@@ -7666,7 +7604,7 @@
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
@@ -8280,7 +8218,7 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9527,7 @@
         <v>132.066</v>
       </c>
       <c r="AX59" s="2" t="n">
-        <v>140.903</v>
+        <v>140.904</v>
       </c>
       <c r="AY59" s="2" t="n">
         <v>144.542</v>
@@ -10583,7 +10521,7 @@
         </is>
       </c>
       <c r="W66" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11590,7 @@
         </is>
       </c>
       <c r="W73" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12110,7 @@
         <v>116.351</v>
       </c>
       <c r="AX76" s="2" t="n">
-        <v>116.854</v>
+        <v>116.855</v>
       </c>
       <c r="AY76" s="2" t="n">
         <v>122.378</v>
@@ -13959,7 +13897,7 @@
         </is>
       </c>
       <c r="W88" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
@@ -16170,7 +16108,7 @@
         <v>150.824</v>
       </c>
       <c r="AX102" s="2" t="n">
-        <v>154.047</v>
+        <v>154.048</v>
       </c>
       <c r="AY102" s="2" t="n">
         <v>154.282</v>
@@ -16468,7 +16406,7 @@
         <v>889.288</v>
       </c>
       <c r="AX104" s="2" t="n">
-        <v>906.448</v>
+        <v>906.449</v>
       </c>
       <c r="AY104" s="2" t="n">
         <v>935.947</v>
@@ -16619,7 +16557,7 @@
         <v>47.28</v>
       </c>
       <c r="AX105" s="2" t="n">
-        <v>48.232</v>
+        <v>48.231</v>
       </c>
       <c r="AY105" s="2" t="n">
         <v>48.652</v>
@@ -16941,7 +16879,7 @@
         <v>67.14</v>
       </c>
       <c r="AX107" s="2" t="n">
-        <v>65.245</v>
+        <v>65.244</v>
       </c>
       <c r="AY107" s="2" t="n">
         <v>62.592</v>
@@ -17168,7 +17106,7 @@
         </is>
       </c>
       <c r="W109" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
@@ -18088,7 +18026,7 @@
         </is>
       </c>
       <c r="W115" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X115" s="2" t="inlineStr">
         <is>
@@ -18406,7 +18344,7 @@
         </is>
       </c>
       <c r="W117" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X117" s="2" t="inlineStr">
         <is>
@@ -18730,7 +18668,7 @@
         </is>
       </c>
       <c r="W119" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X119" s="2" t="inlineStr">
         <is>
@@ -18950,7 +18888,7 @@
         <v>1190.471</v>
       </c>
       <c r="AX120" s="2" t="n">
-        <v>1178.764</v>
+        <v>1178.763</v>
       </c>
       <c r="AY120" s="2" t="n">
         <v>1164.301</v>
@@ -19809,7 +19747,7 @@
         </is>
       </c>
       <c r="W126" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X126" s="2" t="inlineStr">
         <is>
@@ -20482,10 +20420,10 @@
         </is>
       </c>
       <c r="AV130" s="2" t="n">
-        <v>249.788</v>
+        <v>249.787</v>
       </c>
       <c r="AW130" s="2" t="n">
-        <v>264.158</v>
+        <v>264.157</v>
       </c>
       <c r="AX130" s="2" t="n">
         <v>263.114</v>
@@ -20500,13 +20438,13 @@
         <v>240.697</v>
       </c>
       <c r="BB130" s="2" t="n">
-        <v>175.785</v>
+        <v>175.784</v>
       </c>
       <c r="BC130" s="2" t="n">
-        <v>-1.3521</v>
+        <v>-1.3522</v>
       </c>
       <c r="BD130" s="2" t="n">
-        <v>0.9453</v>
+        <v>0.9452</v>
       </c>
       <c r="BE130" s="2" t="n">
         <v>1.0014</v>
@@ -20890,7 +20828,7 @@
         </is>
       </c>
       <c r="W133" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X133" s="2" t="inlineStr">
         <is>
@@ -23515,7 +23453,7 @@
         </is>
       </c>
       <c r="W150" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
@@ -23664,7 +23602,7 @@
         </is>
       </c>
       <c r="W151" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X151" s="2" t="inlineStr">
         <is>
@@ -24172,7 +24110,7 @@
         <v>93.196</v>
       </c>
       <c r="AX154" s="2" t="n">
-        <v>94.03</v>
+        <v>94.029</v>
       </c>
       <c r="AY154" s="2" t="n">
         <v>95.896</v>
@@ -24717,7 +24655,7 @@
         </is>
       </c>
       <c r="W158" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
@@ -25835,7 +25773,7 @@
         <v>341.52</v>
       </c>
       <c r="AX165" s="2" t="n">
-        <v>338.847</v>
+        <v>338.848</v>
       </c>
       <c r="AY165" s="2" t="n">
         <v>336.566</v>
@@ -27115,7 +27053,7 @@
         </is>
       </c>
       <c r="W174" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
@@ -27449,7 +27387,7 @@
         </is>
       </c>
       <c r="W176" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
@@ -27749,7 +27687,7 @@
         </is>
       </c>
       <c r="W178" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
@@ -28922,19 +28860,19 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>5020 JP</t>
+          <t>6861 JP</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>ENEOS Holdings, Inc.</t>
+          <t>Keyence</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>1387</v>
+        <v>79830</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>47.18</v>
+        <v>42.39</v>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
@@ -28952,19 +28890,19 @@
       <c r="P186" s="2" t="inlineStr"/>
       <c r="Q186" s="2" t="inlineStr"/>
       <c r="R186" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S186" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>0111101100</t>
+          <t>0010111000</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
         <is>
-          <t>0111101100</t>
+          <t>0011111000</t>
         </is>
       </c>
       <c r="V186" s="2" t="inlineStr">
@@ -28973,14 +28911,18 @@
         </is>
       </c>
       <c r="W186" s="2" t="n">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="Y186" s="2" t="inlineStr"/>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>顶背离·周MACD死叉</t>
+        </is>
+      </c>
       <c r="Z186" s="2" t="inlineStr"/>
       <c r="AA186" s="2" t="inlineStr"/>
       <c r="AB186" s="2" t="inlineStr"/>
@@ -28992,70 +28934,68 @@
       <c r="AH186" s="2" t="inlineStr"/>
       <c r="AI186" s="2" t="inlineStr"/>
       <c r="AJ186" s="2" t="n">
-        <v>32.28</v>
+        <v>45.52</v>
       </c>
       <c r="AK186" s="2" t="n">
-        <v>0.52</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AL186" s="2" t="n"/>
       <c r="AM186" s="2" t="n">
-        <v>7.48</v>
+        <v>6.23</v>
       </c>
       <c r="AN186" s="2" t="n">
-        <v>-5.76</v>
+        <v>4.81</v>
       </c>
       <c r="AO186" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="AP186" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AQ186" s="2" t="inlineStr"/>
       <c r="AR186" s="2" t="inlineStr"/>
-      <c r="AS186" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="AS186" s="2" t="inlineStr"/>
       <c r="AT186" s="2" t="inlineStr"/>
       <c r="AU186" s="2" t="inlineStr">
         <is>
-          <t>柱≥0</t>
+          <t>无背离</t>
         </is>
       </c>
       <c r="AV186" s="2" t="n">
-        <v>1386.4</v>
+        <v>79932</v>
       </c>
       <c r="AW186" s="2" t="n">
-        <v>1376.6</v>
+        <v>80493</v>
       </c>
       <c r="AX186" s="2" t="n">
-        <v>1390.417</v>
+        <v>79501.75</v>
       </c>
       <c r="AY186" s="2" t="n">
-        <v>1388.848</v>
+        <v>78567.19899999999</v>
       </c>
       <c r="AZ186" s="2" t="n">
-        <v>1349.956</v>
+        <v>80503.599</v>
       </c>
       <c r="BA186" s="2" t="n">
-        <v>1298.914</v>
+        <v>78422.198</v>
       </c>
       <c r="BB186" s="2" t="n">
-        <v>1300.675</v>
+        <v>70112.716</v>
       </c>
       <c r="BC186" s="2" t="n">
-        <v>-0.0185</v>
+        <v>-0.0174</v>
       </c>
       <c r="BD186" s="2" t="n">
-        <v>-0.3451</v>
+        <v>0.6838</v>
       </c>
       <c r="BE186" s="2" t="n">
-        <v>0.3479</v>
+        <v>0.1529</v>
       </c>
       <c r="BF186" s="2" t="n">
-        <v>0.1152</v>
+        <v>0.1328</v>
       </c>
       <c r="BG186" s="2" t="n">
-        <v>0.3228</v>
+        <v>0.4552</v>
       </c>
     </row>
     <row r="187">
@@ -30190,7 +30130,7 @@
         <v>236.374</v>
       </c>
       <c r="AX194" s="2" t="n">
-        <v>236.803</v>
+        <v>236.802</v>
       </c>
       <c r="AY194" s="2" t="n">
         <v>242.072</v>
@@ -30834,7 +30774,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-18 | 197 只</t>
+          <t>截至: 2026-10-19 | 197 只</t>
         </is>
       </c>
     </row>
@@ -31070,7 +31010,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stage (Weinstein 大阶段 v2.5引擎: 10W/30W全线SMA(50/150日), 锚=SMA30W): 优先级: ②′交叉通道(2A条件:金叉状态+M1+M2)→2 | ①均线排列覆盖: 四线全多头→强制2, 全空头→强制4 | ②斜率双确认(SMA30W 4周×13与13周×3.88年化)均&gt;+8%→2, 均&lt;-6%→4 | ③放平带: 低位(pos&lt;0.45且价≤1.05×锚)须慢门+4-先行情境→1否则4; 高位(pos&gt;0.55且价≥0.95×锚)须慢门镜像+2-先行情境→3否则2; 0.45~0.55滞回。慢门(10日年化斜率, delta=斜率10日变化): S1 SMA30W delta&gt;0, S2 SMA10W delta&gt;0, S3 10W改善&gt;30W, S4 sl10&gt;-6%(&gt;+8%临毕业保留); 镜像S1′-S4′全部取反(S4′: sl10&lt;+8%)。情境: has4=自上次退出Stage2以来出现过Stage4(起点种子:回撤≥25%); has2=自上次退出Stage1以来出现过Stage2(种子:涨幅≥30%)。降级层(v2.2): 151-252根新股弱规则标'新'; ≤150根→NA</t>
+          <t xml:space="preserve">  Stage (Weinstein 大阶段 3.0引擎: 10W/30W全线SMA(50/150日), 锚=SMA30W): 优先级: ②′交叉通道(2A条件:金叉状态+M1+M2)→2 | ①均线排列覆盖: 四线全多头→强制2, 全空头→强制4 | ②斜率双确认(SMA30W 4周×13与13周×3.88年化)均&gt;+8%→2, 均&lt;-6%→4 | ③放平带: 低位(pos&lt;0.45且价≤1.05×锚)须慢门+4-先行情境→1否则4; 高位(pos&gt;0.55且价≥0.95×锚)须慢门镜像+2-先行情境→3否则2; 0.45~0.55滞回。慢门(10日年化斜率, delta=斜率10日变化): S1 SMA30W delta&gt;0, S2 SMA10W delta&gt;0, S3 10W改善&gt;30W, S4 sl10&gt;-6%(&gt;+8%临毕业保留); 镜像S1′-S4′全部取反(S4′: sl10&lt;+8%)。情境: has4=自上次退出Stage2以来出现过Stage4(起点种子:回撤≥25%); has2=自上次退出Stage1以来出现过Stage2(种子:涨幅≥30%)。降级层(v2.2): 151-252根新股弱规则标'新'; ≤150根→NA</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31038,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档(v2.5): 4+ = A止跌((纠缠∨MA5&gt;MA20)+(周J超卖∨底背离)+价&lt;SMA10W) ∨ B站稳短均(MA5/10/20三条) ; 均须周MACD柱为正或≤1周将金叉 | 1 = 筑底(过准入, 不满足1+) | 1+ = α(站稳三均线+全上行+周MACD金叉+RS&gt;0) ∨ β(SOS直通) | 2A = 金叉状态(已金叉≤20日∨纠缠&lt;3%∨外推≤20日金叉)+M1(sl10&gt;+8%且delta&gt;0)+M2(d30&gt;+5pp) | 2B = 大致多头(SMA10W&gt;SMA30W且10日前也是)+斜率好(30W双确认&gt;+8%∨完整四线多头) | 2C = 2B基础+衰竭信号(本轮闩锁): ATR延伸99%分位∨50D斜率delta首次转负∨周线顶背离∨周MACD死叉或将死叉 | 3 = 筑顶过渡 | 3- = 跌破三均线+全下行+周MACD死叉+RS&lt;0 | 4 = 默认。生命周期 4→4+→1→1+→2A→2B→2C→3→3-→4, SOS/SOW可跳级</t>
+          <t xml:space="preserve">  子档(3.0): 4+ = A止跌((纠缠∨MA5&gt;MA20)+(周J超卖∨底背离)+价&lt;SMA10W) ∨ B站稳短均(MA5/10/20三条) ; 均须周MACD柱为正或≤1周将金叉 | 1 = 筑底(过准入, 不满足1+) | 1+ = α(站稳三均线+全上行+周MACD金叉+RS&gt;0) ∨ β(SOS直通) | 2A = 金叉状态(已金叉≤20日∨纠缠&lt;3%∨外推≤20日金叉)+M1(sl10&gt;+8%且delta&gt;0)+M2(d30&gt;+5pp) | 2B = 大致多头(SMA10W&gt;SMA30W且10日前也是)+斜率好(30W双确认&gt;+8%∨完整四线多头) | 2C = 2B基础+衰竭信号(本轮闩锁): ATR延伸99%分位∨50D斜率delta首次转负∨周线顶背离∨周MACD死叉或将死叉 | 3 = 筑顶过渡 | 3- = 跌破三均线+全下行+周MACD死叉+RS&lt;0 | 4 = 默认。生命周期 4→4+→1→1+→2A→2B→2C→3→3-→4, SOS/SOW可跳级</t>
         </is>
       </c>
     </row>

--- a/OVERSEAS_Swing_Pattern.xlsx
+++ b/OVERSEAS_Swing_Pattern.xlsx
@@ -4239,7 +4239,7 @@
         <v>78584.819</v>
       </c>
       <c r="BB23" s="2" t="n">
-        <v>70593.933</v>
+        <v>70593.93399999999</v>
       </c>
       <c r="BC23" s="2" t="n">
         <v>-0.1989</v>
@@ -7624,7 +7624,7 @@
         <v>173.94</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
@@ -15440,10 +15440,10 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>14.3</v>
+        <v>14.31</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>6.33</v>
+        <v>7.58</v>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
@@ -15511,22 +15511,22 @@
       <c r="AH97" s="2" t="inlineStr"/>
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="n">
-        <v>34.23</v>
+        <v>34.25</v>
       </c>
       <c r="AK97" s="2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AL97" s="2" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AM97" s="2" t="n">
-        <v>-8.23</v>
+        <v>-8.16</v>
       </c>
       <c r="AN97" s="2" t="n">
-        <v>-5.04</v>
+        <v>-4.97</v>
       </c>
       <c r="AO97" s="2" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AP97" s="2" t="n">
         <v>15</v>
@@ -15541,10 +15541,10 @@
         </is>
       </c>
       <c r="AV97" s="2" t="n">
-        <v>14.616</v>
+        <v>14.618</v>
       </c>
       <c r="AW97" s="2" t="n">
-        <v>14.98</v>
+        <v>14.981</v>
       </c>
       <c r="AX97" s="2" t="n">
         <v>14.941</v>
@@ -15562,19 +15562,19 @@
         <v>14.348</v>
       </c>
       <c r="BC97" s="2" t="n">
-        <v>-0.9039</v>
+        <v>-0.9005</v>
       </c>
       <c r="BD97" s="2" t="n">
-        <v>-0.0104</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="BE97" s="2" t="n">
-        <v>-0.0968</v>
+        <v>-0.0961</v>
       </c>
       <c r="BF97" s="2" t="n">
-        <v>-0.1338</v>
+        <v>-0.1334</v>
       </c>
       <c r="BG97" s="2" t="n">
-        <v>0.3423</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="98">
@@ -15592,7 +15592,7 @@
         <v>123.69</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="AV99" s="2" t="n">
-        <v>332.729</v>
+        <v>332.73</v>
       </c>
       <c r="AW99" s="2" t="n">
         <v>340.76</v>
@@ -15864,7 +15864,7 @@
         <v>340.985</v>
       </c>
       <c r="BC99" s="2" t="n">
-        <v>-1.2067</v>
+        <v>-1.2066</v>
       </c>
       <c r="BD99" s="2" t="n">
         <v>-0.4998</v>
@@ -17122,7 +17122,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
@@ -30922,7 +30922,7 @@
         <v>59.05</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
@@ -31082,7 +31082,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>截至: 2026-10-24 | 197 只</t>
+          <t>截至: 2026-10-25 | 197 只</t>
         </is>
       </c>
     </row>
